--- a/Carta Gantt.xlsx
+++ b/Carta Gantt.xlsx
@@ -8,12 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Carlos\Documents\GitHub\duoc_fullstack\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F63837CF-297A-4EED-8081-DB582661CF90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F046080F-D13B-499E-8BD3-3E35C6874D8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6CCCA798-E65F-4DDC-AD8C-08062A140C3B}"/>
   </bookViews>
   <sheets>
-    <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
+    <sheet name="Original" sheetId="1" r:id="rId1"/>
+    <sheet name="P01" sheetId="2" r:id="rId2"/>
+    <sheet name="P02" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,10 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="27">
-  <si>
-    <t>CARTA GANTT - FULLSTACK 3 - 2026</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="27">
   <si>
     <t>Semanas</t>
   </si>
@@ -60,9 +59,6 @@
   </si>
   <si>
     <t>Junio</t>
-  </si>
-  <si>
-    <t>Explicación Semestre</t>
   </si>
   <si>
     <t>Scrum</t>
@@ -121,6 +117,12 @@
   <si>
     <t>Actividades</t>
   </si>
+  <si>
+    <t>CARTA GANTT</t>
+  </si>
+  <si>
+    <t>FULLSTACK 3</t>
+  </si>
 </sst>
 </file>
 
@@ -129,7 +131,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="00"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -149,6 +151,35 @@
       <color rgb="FFFF0000"/>
       <name val="Georgia"/>
       <family val="1"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Georgia"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Georgia"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Georgia"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="Georgia"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Georgia"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="5">
@@ -177,7 +208,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="19">
     <border>
       <left/>
       <right/>
@@ -287,30 +318,124 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thick">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -326,10 +451,64 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="13" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -664,898 +843,4943 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{477A3499-DDAC-41C4-A409-E01E2AE8668D}">
-  <dimension ref="A1:DK38"/>
+  <dimension ref="A1:DF40"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="20.88671875" bestFit="1" customWidth="1"/>
-    <col min="2" max="21" width="2.77734375" customWidth="1"/>
-    <col min="22" max="22" width="3.21875" bestFit="1" customWidth="1"/>
-    <col min="23" max="49" width="2.77734375" customWidth="1"/>
-    <col min="50" max="50" width="3.21875" bestFit="1" customWidth="1"/>
-    <col min="51" max="112" width="2.77734375" customWidth="1"/>
-    <col min="113" max="114" width="3.21875" bestFit="1" customWidth="1"/>
-    <col min="115" max="115" width="2.77734375" customWidth="1"/>
+    <col min="1" max="1" width="21.88671875" style="17" bestFit="1" customWidth="1"/>
+    <col min="2" max="7" width="2.77734375" style="17" customWidth="1"/>
+    <col min="8" max="8" width="3.44140625" style="17" bestFit="1" customWidth="1"/>
+    <col min="9" max="14" width="2.77734375" style="17" customWidth="1"/>
+    <col min="15" max="15" width="3.21875" style="17" bestFit="1" customWidth="1"/>
+    <col min="16" max="42" width="2.77734375" style="17" customWidth="1"/>
+    <col min="43" max="43" width="3.21875" style="17" bestFit="1" customWidth="1"/>
+    <col min="44" max="56" width="2.77734375" style="17" customWidth="1"/>
+    <col min="57" max="57" width="3.44140625" style="17" bestFit="1" customWidth="1"/>
+    <col min="58" max="70" width="2.77734375" style="17" customWidth="1"/>
+    <col min="71" max="71" width="3.44140625" style="17" bestFit="1" customWidth="1"/>
+    <col min="72" max="105" width="2.77734375" style="17" customWidth="1"/>
+    <col min="106" max="107" width="3.21875" style="17" bestFit="1" customWidth="1"/>
+    <col min="108" max="108" width="2.77734375" style="17" customWidth="1"/>
+    <col min="109" max="110" width="11.5546875" style="17"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:115" x14ac:dyDescent="0.2">
-      <c r="A1" s="4" t="s">
+    <row r="1" spans="1:110" ht="20.25" x14ac:dyDescent="0.3">
+      <c r="A1" s="31" t="s">
+        <v>25</v>
+      </c>
+      <c r="B1" s="32"/>
+      <c r="C1" s="32"/>
+      <c r="D1" s="32"/>
+      <c r="E1" s="32"/>
+      <c r="F1" s="32"/>
+      <c r="G1" s="32"/>
+      <c r="H1" s="32"/>
+      <c r="I1" s="32"/>
+      <c r="J1" s="32"/>
+      <c r="K1" s="32"/>
+      <c r="L1" s="32"/>
+      <c r="M1" s="32"/>
+      <c r="N1" s="32"/>
+      <c r="O1" s="32"/>
+      <c r="P1" s="32"/>
+      <c r="Q1" s="32"/>
+    </row>
+    <row r="2" spans="1:110" ht="20.25" x14ac:dyDescent="0.3">
+      <c r="A2" s="31" t="s">
+        <v>26</v>
+      </c>
+      <c r="B2" s="32"/>
+      <c r="C2" s="32"/>
+      <c r="D2" s="32"/>
+      <c r="E2" s="32"/>
+      <c r="F2" s="32"/>
+      <c r="G2" s="32"/>
+      <c r="H2" s="32"/>
+      <c r="I2" s="32"/>
+      <c r="J2" s="32"/>
+      <c r="K2" s="32"/>
+      <c r="L2" s="32"/>
+      <c r="M2" s="32"/>
+      <c r="N2" s="32"/>
+      <c r="O2" s="32"/>
+      <c r="P2" s="32"/>
+      <c r="Q2" s="32"/>
+    </row>
+    <row r="3" spans="1:110" ht="20.25" x14ac:dyDescent="0.3">
+      <c r="A3" s="31">
+        <v>2026</v>
+      </c>
+      <c r="B3" s="32"/>
+      <c r="C3" s="32"/>
+      <c r="D3" s="32"/>
+      <c r="E3" s="32"/>
+      <c r="F3" s="32"/>
+      <c r="G3" s="32"/>
+      <c r="H3" s="32"/>
+      <c r="I3" s="32"/>
+      <c r="J3" s="32"/>
+      <c r="K3" s="32"/>
+      <c r="L3" s="32"/>
+      <c r="M3" s="32"/>
+      <c r="N3" s="32"/>
+      <c r="O3" s="32"/>
+      <c r="P3" s="32"/>
+      <c r="Q3" s="32"/>
+    </row>
+    <row r="4" spans="1:110" s="47" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A4" s="45"/>
+      <c r="B4" s="45"/>
+      <c r="C4" s="45"/>
+      <c r="D4" s="45"/>
+      <c r="E4" s="45"/>
+      <c r="F4" s="45"/>
+      <c r="G4" s="45"/>
+      <c r="H4" s="45"/>
+      <c r="I4" s="45"/>
+      <c r="J4" s="45"/>
+      <c r="K4" s="45"/>
+      <c r="L4" s="45"/>
+      <c r="M4" s="45"/>
+      <c r="N4" s="45"/>
+      <c r="O4" s="45"/>
+      <c r="P4" s="45"/>
+      <c r="Q4" s="45"/>
+      <c r="R4" s="46"/>
+      <c r="S4" s="46"/>
+      <c r="T4" s="46"/>
+      <c r="U4" s="46"/>
+      <c r="V4" s="46"/>
+      <c r="W4" s="46"/>
+      <c r="X4" s="46"/>
+      <c r="Y4" s="46"/>
+      <c r="Z4" s="46"/>
+      <c r="AA4" s="46"/>
+      <c r="AB4" s="46"/>
+      <c r="AC4" s="46"/>
+      <c r="AD4" s="46"/>
+      <c r="AE4" s="46"/>
+      <c r="AF4" s="46"/>
+      <c r="AG4" s="46"/>
+      <c r="AH4" s="46"/>
+      <c r="AI4" s="46"/>
+      <c r="AJ4" s="46"/>
+      <c r="AK4" s="46"/>
+      <c r="AL4" s="46"/>
+      <c r="AM4" s="46"/>
+      <c r="AN4" s="46"/>
+      <c r="AO4" s="46"/>
+      <c r="AP4" s="46"/>
+      <c r="AQ4" s="46"/>
+      <c r="AR4" s="46"/>
+      <c r="AS4" s="46"/>
+      <c r="AT4" s="46"/>
+      <c r="AU4" s="46"/>
+      <c r="AV4" s="46"/>
+      <c r="AW4" s="46"/>
+      <c r="AX4" s="46"/>
+      <c r="AY4" s="46"/>
+      <c r="AZ4" s="46"/>
+      <c r="BA4" s="46"/>
+      <c r="BB4" s="46"/>
+      <c r="BC4" s="46"/>
+      <c r="BD4" s="46"/>
+      <c r="BE4" s="46"/>
+      <c r="BF4" s="46"/>
+      <c r="BG4" s="46"/>
+      <c r="BH4" s="46"/>
+      <c r="BI4" s="46"/>
+      <c r="BJ4" s="46"/>
+      <c r="BK4" s="46"/>
+      <c r="BL4" s="46"/>
+      <c r="BM4" s="46"/>
+      <c r="BN4" s="46"/>
+      <c r="BO4" s="46"/>
+      <c r="BP4" s="46"/>
+      <c r="BQ4" s="46"/>
+      <c r="BR4" s="46"/>
+      <c r="BS4" s="46"/>
+      <c r="BT4" s="46"/>
+      <c r="BU4" s="46"/>
+      <c r="BV4" s="46"/>
+      <c r="BW4" s="46"/>
+      <c r="BX4" s="46"/>
+      <c r="BY4" s="46"/>
+      <c r="BZ4" s="46"/>
+      <c r="CA4" s="46"/>
+      <c r="CB4" s="46"/>
+      <c r="CC4" s="46"/>
+      <c r="CD4" s="46"/>
+      <c r="CE4" s="46"/>
+      <c r="CF4" s="46"/>
+      <c r="CG4" s="46"/>
+      <c r="CH4" s="46"/>
+      <c r="CI4" s="46"/>
+      <c r="CJ4" s="46"/>
+      <c r="CK4" s="46"/>
+      <c r="CL4" s="46"/>
+      <c r="CM4" s="46"/>
+      <c r="CN4" s="46"/>
+      <c r="CO4" s="46"/>
+      <c r="CP4" s="46"/>
+      <c r="CQ4" s="46"/>
+      <c r="CR4" s="46"/>
+      <c r="CS4" s="46"/>
+      <c r="CT4" s="46"/>
+      <c r="CU4" s="46"/>
+      <c r="CV4" s="46"/>
+      <c r="CW4" s="46"/>
+      <c r="CX4" s="46"/>
+      <c r="CY4" s="46"/>
+      <c r="CZ4" s="46"/>
+      <c r="DA4" s="46"/>
+      <c r="DB4" s="46"/>
+      <c r="DC4" s="46"/>
+      <c r="DD4" s="46"/>
+      <c r="DE4" s="46"/>
+      <c r="DF4" s="46"/>
+    </row>
+    <row r="5" spans="1:110" ht="18" x14ac:dyDescent="0.25">
+      <c r="A5" s="34" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" spans="1:110" ht="18" x14ac:dyDescent="0.25">
+      <c r="A6" s="34" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="7" spans="1:110" s="47" customFormat="1" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="46"/>
+      <c r="B7" s="46"/>
+      <c r="C7" s="46"/>
+      <c r="D7" s="46"/>
+      <c r="E7" s="46"/>
+      <c r="F7" s="46"/>
+      <c r="G7" s="46"/>
+      <c r="H7" s="46"/>
+      <c r="I7" s="46"/>
+      <c r="J7" s="46"/>
+      <c r="K7" s="46"/>
+      <c r="L7" s="46"/>
+      <c r="M7" s="46"/>
+      <c r="N7" s="46"/>
+      <c r="O7" s="46"/>
+      <c r="P7" s="46"/>
+      <c r="Q7" s="46"/>
+      <c r="R7" s="46"/>
+      <c r="S7" s="46"/>
+      <c r="T7" s="46"/>
+      <c r="U7" s="46"/>
+      <c r="V7" s="46"/>
+      <c r="W7" s="46"/>
+      <c r="X7" s="46"/>
+      <c r="Y7" s="46"/>
+      <c r="Z7" s="46"/>
+      <c r="AA7" s="46"/>
+      <c r="AB7" s="46"/>
+      <c r="AC7" s="46"/>
+      <c r="AD7" s="46"/>
+      <c r="AE7" s="46"/>
+      <c r="AF7" s="46"/>
+      <c r="AG7" s="46"/>
+      <c r="AH7" s="46"/>
+      <c r="AI7" s="46"/>
+      <c r="AJ7" s="46"/>
+      <c r="AK7" s="46"/>
+      <c r="AL7" s="46"/>
+      <c r="AM7" s="46"/>
+      <c r="AN7" s="46"/>
+      <c r="AO7" s="46"/>
+      <c r="AP7" s="46"/>
+      <c r="AQ7" s="46"/>
+      <c r="AR7" s="46"/>
+      <c r="AS7" s="46"/>
+      <c r="AT7" s="46"/>
+      <c r="AU7" s="46"/>
+      <c r="AV7" s="46"/>
+      <c r="AW7" s="46"/>
+      <c r="AX7" s="46"/>
+      <c r="AY7" s="46"/>
+      <c r="AZ7" s="46"/>
+      <c r="BA7" s="46"/>
+      <c r="BB7" s="46"/>
+      <c r="BC7" s="46"/>
+      <c r="BD7" s="46"/>
+      <c r="BE7" s="46"/>
+      <c r="BF7" s="46"/>
+      <c r="BG7" s="46"/>
+      <c r="BH7" s="46"/>
+      <c r="BI7" s="46"/>
+      <c r="BJ7" s="46"/>
+      <c r="BK7" s="46"/>
+      <c r="BL7" s="46"/>
+      <c r="BM7" s="46"/>
+      <c r="BN7" s="46"/>
+      <c r="BO7" s="46"/>
+      <c r="BP7" s="46"/>
+      <c r="BQ7" s="46"/>
+      <c r="BR7" s="46"/>
+      <c r="BS7" s="46"/>
+      <c r="BT7" s="46"/>
+      <c r="BU7" s="46"/>
+      <c r="BV7" s="46"/>
+      <c r="BW7" s="46"/>
+      <c r="BX7" s="46"/>
+      <c r="BY7" s="46"/>
+      <c r="BZ7" s="46"/>
+      <c r="CA7" s="46"/>
+      <c r="CB7" s="46"/>
+      <c r="CC7" s="46"/>
+      <c r="CD7" s="46"/>
+      <c r="CE7" s="46"/>
+      <c r="CF7" s="46"/>
+      <c r="CG7" s="46"/>
+      <c r="CH7" s="46"/>
+      <c r="CI7" s="46"/>
+      <c r="CJ7" s="46"/>
+      <c r="CK7" s="46"/>
+      <c r="CL7" s="46"/>
+      <c r="CM7" s="46"/>
+      <c r="CN7" s="46"/>
+      <c r="CO7" s="46"/>
+      <c r="CP7" s="46"/>
+      <c r="CQ7" s="46"/>
+      <c r="CR7" s="46"/>
+      <c r="CS7" s="46"/>
+      <c r="CT7" s="46"/>
+      <c r="CU7" s="46"/>
+      <c r="CV7" s="46"/>
+      <c r="CW7" s="46"/>
+      <c r="CX7" s="46"/>
+      <c r="CY7" s="46"/>
+      <c r="CZ7" s="46"/>
+      <c r="DA7" s="46"/>
+      <c r="DB7" s="46"/>
+      <c r="DC7" s="46"/>
+      <c r="DD7" s="46"/>
+      <c r="DE7" s="46"/>
+      <c r="DF7" s="46"/>
+    </row>
+    <row r="8" spans="1:110" x14ac:dyDescent="0.2">
+      <c r="A8" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
-      <c r="G1" s="4"/>
-      <c r="H1" s="4"/>
-      <c r="I1" s="4"/>
-      <c r="J1" s="4"/>
-      <c r="K1" s="4"/>
-      <c r="L1" s="4"/>
-      <c r="M1" s="4"/>
-      <c r="N1" s="4"/>
-      <c r="O1" s="4"/>
-      <c r="P1" s="4"/>
-      <c r="Q1" s="4"/>
-      <c r="R1" s="4"/>
-      <c r="S1" s="4"/>
-      <c r="T1" s="4"/>
-      <c r="U1" s="4"/>
-      <c r="V1" s="4"/>
-      <c r="W1" s="4"/>
-      <c r="X1" s="4"/>
-    </row>
-    <row r="2" spans="1:115" x14ac:dyDescent="0.2">
-      <c r="A2" s="3" t="s">
+      <c r="B8" s="30" t="s">
+        <v>2</v>
+      </c>
+      <c r="C8" s="28"/>
+      <c r="D8" s="28"/>
+      <c r="E8" s="28"/>
+      <c r="F8" s="28"/>
+      <c r="G8" s="28"/>
+      <c r="H8" s="28"/>
+      <c r="I8" s="28"/>
+      <c r="J8" s="28"/>
+      <c r="K8" s="28"/>
+      <c r="L8" s="28"/>
+      <c r="M8" s="28"/>
+      <c r="N8" s="28"/>
+      <c r="O8" s="28"/>
+      <c r="P8" s="28"/>
+      <c r="Q8" s="29"/>
+      <c r="R8" s="30" t="s">
+        <v>3</v>
+      </c>
+      <c r="S8" s="28"/>
+      <c r="T8" s="28"/>
+      <c r="U8" s="28"/>
+      <c r="V8" s="28"/>
+      <c r="W8" s="28"/>
+      <c r="X8" s="28"/>
+      <c r="Y8" s="28"/>
+      <c r="Z8" s="28"/>
+      <c r="AA8" s="28"/>
+      <c r="AB8" s="28"/>
+      <c r="AC8" s="28"/>
+      <c r="AD8" s="28"/>
+      <c r="AE8" s="28"/>
+      <c r="AF8" s="28"/>
+      <c r="AG8" s="28"/>
+      <c r="AH8" s="28"/>
+      <c r="AI8" s="28"/>
+      <c r="AJ8" s="28"/>
+      <c r="AK8" s="28"/>
+      <c r="AL8" s="28"/>
+      <c r="AM8" s="28"/>
+      <c r="AN8" s="28"/>
+      <c r="AO8" s="28"/>
+      <c r="AP8" s="28"/>
+      <c r="AQ8" s="28"/>
+      <c r="AR8" s="28"/>
+      <c r="AS8" s="28"/>
+      <c r="AT8" s="28"/>
+      <c r="AU8" s="29"/>
+      <c r="AV8" s="30" t="s">
+        <v>4</v>
+      </c>
+      <c r="AW8" s="28"/>
+      <c r="AX8" s="28"/>
+      <c r="AY8" s="28"/>
+      <c r="AZ8" s="28"/>
+      <c r="BA8" s="28"/>
+      <c r="BB8" s="28"/>
+      <c r="BC8" s="28"/>
+      <c r="BD8" s="28"/>
+      <c r="BE8" s="28"/>
+      <c r="BF8" s="28"/>
+      <c r="BG8" s="28"/>
+      <c r="BH8" s="28"/>
+      <c r="BI8" s="28"/>
+      <c r="BJ8" s="28"/>
+      <c r="BK8" s="28"/>
+      <c r="BL8" s="28"/>
+      <c r="BM8" s="28"/>
+      <c r="BN8" s="28"/>
+      <c r="BO8" s="28"/>
+      <c r="BP8" s="28"/>
+      <c r="BQ8" s="28"/>
+      <c r="BR8" s="28"/>
+      <c r="BS8" s="28"/>
+      <c r="BT8" s="28"/>
+      <c r="BU8" s="28"/>
+      <c r="BV8" s="28"/>
+      <c r="BW8" s="28"/>
+      <c r="BX8" s="28"/>
+      <c r="BY8" s="28"/>
+      <c r="BZ8" s="29"/>
+      <c r="CA8" s="30" t="s">
+        <v>5</v>
+      </c>
+      <c r="CB8" s="28"/>
+      <c r="CC8" s="28"/>
+      <c r="CD8" s="28"/>
+      <c r="CE8" s="28"/>
+      <c r="CF8" s="28"/>
+      <c r="CG8" s="28"/>
+      <c r="CH8" s="28"/>
+      <c r="CI8" s="28"/>
+      <c r="CJ8" s="28"/>
+      <c r="CK8" s="28"/>
+      <c r="CL8" s="28"/>
+      <c r="CM8" s="28"/>
+      <c r="CN8" s="28"/>
+      <c r="CO8" s="28"/>
+      <c r="CP8" s="28"/>
+      <c r="CQ8" s="28"/>
+      <c r="CR8" s="28"/>
+      <c r="CS8" s="28"/>
+      <c r="CT8" s="28"/>
+      <c r="CU8" s="28"/>
+      <c r="CV8" s="28"/>
+      <c r="CW8" s="28"/>
+      <c r="CX8" s="28"/>
+      <c r="CY8" s="28"/>
+      <c r="CZ8" s="28"/>
+      <c r="DA8" s="28"/>
+      <c r="DB8" s="28"/>
+      <c r="DC8" s="28"/>
+      <c r="DD8" s="29"/>
+    </row>
+    <row r="9" spans="1:110" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="36" t="s">
         <v>24</v>
       </c>
-      <c r="B2" s="24"/>
-      <c r="C2" s="24"/>
-      <c r="D2" s="24"/>
-      <c r="E2" s="24"/>
-      <c r="F2" s="24"/>
-    </row>
-    <row r="3" spans="1:115" x14ac:dyDescent="0.2">
-      <c r="A3" s="3" t="s">
+      <c r="B9" s="9">
+        <v>16</v>
+      </c>
+      <c r="C9" s="5">
+        <v>17</v>
+      </c>
+      <c r="D9" s="5">
+        <v>18</v>
+      </c>
+      <c r="E9" s="5">
+        <v>19</v>
+      </c>
+      <c r="F9" s="5">
+        <v>20</v>
+      </c>
+      <c r="G9" s="5">
+        <v>21</v>
+      </c>
+      <c r="H9" s="6">
+        <v>22</v>
+      </c>
+      <c r="I9" s="7">
+        <v>23</v>
+      </c>
+      <c r="J9" s="2">
+        <v>24</v>
+      </c>
+      <c r="K9" s="2">
         <v>25</v>
       </c>
-      <c r="B3" s="24"/>
-      <c r="C3" s="24"/>
-      <c r="D3" s="24"/>
-      <c r="E3" s="24"/>
-      <c r="F3" s="24"/>
-    </row>
-    <row r="4" spans="1:115" ht="15" thickBot="1" x14ac:dyDescent="0.25"/>
-    <row r="5" spans="1:115" x14ac:dyDescent="0.2">
-      <c r="A5" s="25" t="s">
+      <c r="L9" s="2">
+        <v>26</v>
+      </c>
+      <c r="M9" s="2">
+        <v>27</v>
+      </c>
+      <c r="N9" s="2">
+        <v>28</v>
+      </c>
+      <c r="O9" s="3">
+        <v>29</v>
+      </c>
+      <c r="P9" s="4">
+        <v>30</v>
+      </c>
+      <c r="Q9" s="8">
+        <v>31</v>
+      </c>
+      <c r="R9" s="9">
         <v>1</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="S9" s="5">
+        <v>2</v>
+      </c>
+      <c r="T9" s="10">
         <v>3</v>
       </c>
-      <c r="C5" s="7"/>
-      <c r="D5" s="7"/>
-      <c r="E5" s="7"/>
-      <c r="F5" s="7"/>
-      <c r="G5" s="7"/>
-      <c r="H5" s="7"/>
-      <c r="I5" s="7"/>
-      <c r="J5" s="7"/>
-      <c r="K5" s="7"/>
-      <c r="L5" s="7"/>
-      <c r="M5" s="7"/>
-      <c r="N5" s="7"/>
-      <c r="O5" s="7"/>
-      <c r="P5" s="7"/>
-      <c r="Q5" s="7"/>
-      <c r="R5" s="7"/>
-      <c r="S5" s="7"/>
-      <c r="T5" s="7"/>
-      <c r="U5" s="7"/>
-      <c r="V5" s="7"/>
-      <c r="W5" s="7"/>
-      <c r="X5" s="8"/>
-      <c r="Y5" s="6" t="s">
+      <c r="U9" s="10">
         <v>4</v>
       </c>
-      <c r="Z5" s="7"/>
-      <c r="AA5" s="7"/>
-      <c r="AB5" s="7"/>
-      <c r="AC5" s="7"/>
-      <c r="AD5" s="7"/>
-      <c r="AE5" s="7"/>
-      <c r="AF5" s="7"/>
-      <c r="AG5" s="7"/>
-      <c r="AH5" s="7"/>
-      <c r="AI5" s="7"/>
-      <c r="AJ5" s="7"/>
-      <c r="AK5" s="7"/>
-      <c r="AL5" s="7"/>
-      <c r="AM5" s="7"/>
-      <c r="AN5" s="7"/>
-      <c r="AO5" s="7"/>
-      <c r="AP5" s="7"/>
-      <c r="AQ5" s="7"/>
-      <c r="AR5" s="7"/>
-      <c r="AS5" s="7"/>
-      <c r="AT5" s="7"/>
-      <c r="AU5" s="7"/>
-      <c r="AV5" s="7"/>
-      <c r="AW5" s="7"/>
-      <c r="AX5" s="7"/>
-      <c r="AY5" s="7"/>
-      <c r="AZ5" s="7"/>
-      <c r="BA5" s="7"/>
-      <c r="BB5" s="8"/>
-      <c r="BC5" s="6" t="s">
+      <c r="V9" s="6">
         <v>5</v>
       </c>
-      <c r="BD5" s="7"/>
-      <c r="BE5" s="7"/>
-      <c r="BF5" s="7"/>
-      <c r="BG5" s="7"/>
-      <c r="BH5" s="7"/>
-      <c r="BI5" s="7"/>
-      <c r="BJ5" s="7"/>
-      <c r="BK5" s="7"/>
-      <c r="BL5" s="7"/>
-      <c r="BM5" s="7"/>
-      <c r="BN5" s="7"/>
-      <c r="BO5" s="7"/>
-      <c r="BP5" s="7"/>
-      <c r="BQ5" s="7"/>
-      <c r="BR5" s="7"/>
-      <c r="BS5" s="7"/>
-      <c r="BT5" s="7"/>
-      <c r="BU5" s="7"/>
-      <c r="BV5" s="7"/>
-      <c r="BW5" s="7"/>
-      <c r="BX5" s="7"/>
-      <c r="BY5" s="7"/>
-      <c r="BZ5" s="7"/>
-      <c r="CA5" s="7"/>
-      <c r="CB5" s="7"/>
-      <c r="CC5" s="7"/>
-      <c r="CD5" s="7"/>
-      <c r="CE5" s="7"/>
-      <c r="CF5" s="7"/>
-      <c r="CG5" s="8"/>
-      <c r="CH5" s="6" t="s">
+      <c r="W9" s="7">
         <v>6</v>
       </c>
-      <c r="CI5" s="7"/>
-      <c r="CJ5" s="7"/>
-      <c r="CK5" s="7"/>
-      <c r="CL5" s="7"/>
-      <c r="CM5" s="7"/>
-      <c r="CN5" s="7"/>
-      <c r="CO5" s="7"/>
-      <c r="CP5" s="7"/>
-      <c r="CQ5" s="7"/>
-      <c r="CR5" s="7"/>
-      <c r="CS5" s="7"/>
-      <c r="CT5" s="7"/>
-      <c r="CU5" s="7"/>
-      <c r="CV5" s="7"/>
-      <c r="CW5" s="7"/>
-      <c r="CX5" s="7"/>
-      <c r="CY5" s="7"/>
-      <c r="CZ5" s="7"/>
-      <c r="DA5" s="7"/>
-      <c r="DB5" s="7"/>
-      <c r="DC5" s="7"/>
-      <c r="DD5" s="7"/>
-      <c r="DE5" s="7"/>
-      <c r="DF5" s="7"/>
-      <c r="DG5" s="7"/>
-      <c r="DH5" s="7"/>
-      <c r="DI5" s="7"/>
-      <c r="DJ5" s="7"/>
-      <c r="DK5" s="8"/>
-    </row>
-    <row r="6" spans="1:115" ht="15" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
+      <c r="X9" s="2">
+        <v>7</v>
+      </c>
+      <c r="Y9" s="2">
+        <v>8</v>
+      </c>
+      <c r="Z9" s="2">
+        <v>9</v>
+      </c>
+      <c r="AA9" s="2">
+        <v>10</v>
+      </c>
+      <c r="AB9" s="2">
+        <v>11</v>
+      </c>
+      <c r="AC9" s="3">
+        <v>12</v>
+      </c>
+      <c r="AD9" s="4">
+        <v>13</v>
+      </c>
+      <c r="AE9" s="5">
+        <v>14</v>
+      </c>
+      <c r="AF9" s="5">
+        <v>15</v>
+      </c>
+      <c r="AG9" s="5">
+        <v>16</v>
+      </c>
+      <c r="AH9" s="5">
+        <v>17</v>
+      </c>
+      <c r="AI9" s="5">
+        <v>18</v>
+      </c>
+      <c r="AJ9" s="6">
+        <v>19</v>
+      </c>
+      <c r="AK9" s="7">
+        <v>20</v>
+      </c>
+      <c r="AL9" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM9" s="2">
+        <v>22</v>
+      </c>
+      <c r="AN9" s="2">
+        <v>23</v>
+      </c>
+      <c r="AO9" s="2">
+        <v>24</v>
+      </c>
+      <c r="AP9" s="2">
+        <v>25</v>
+      </c>
+      <c r="AQ9" s="3">
         <v>26</v>
       </c>
-      <c r="B6" s="9">
+      <c r="AR9" s="4">
+        <v>27</v>
+      </c>
+      <c r="AS9" s="5">
+        <v>28</v>
+      </c>
+      <c r="AT9" s="5">
+        <v>29</v>
+      </c>
+      <c r="AU9" s="8">
+        <v>30</v>
+      </c>
+      <c r="AV9" s="11">
+        <v>1</v>
+      </c>
+      <c r="AW9" s="5">
+        <v>2</v>
+      </c>
+      <c r="AX9" s="6">
+        <v>3</v>
+      </c>
+      <c r="AY9" s="7">
+        <v>4</v>
+      </c>
+      <c r="AZ9" s="2">
+        <v>5</v>
+      </c>
+      <c r="BA9" s="2">
+        <v>6</v>
+      </c>
+      <c r="BB9" s="2">
+        <v>7</v>
+      </c>
+      <c r="BC9" s="2">
+        <v>8</v>
+      </c>
+      <c r="BD9" s="2">
         <v>9</v>
       </c>
-      <c r="C6" s="10">
+      <c r="BE9" s="3">
         <v>10</v>
       </c>
-      <c r="D6" s="10">
+      <c r="BF9" s="4">
         <v>11</v>
       </c>
-      <c r="E6" s="10">
+      <c r="BG9" s="5">
         <v>12</v>
       </c>
-      <c r="F6" s="10">
+      <c r="BH9" s="5">
         <v>13</v>
       </c>
-      <c r="G6" s="10">
+      <c r="BI9" s="5">
         <v>14</v>
       </c>
-      <c r="H6" s="11">
+      <c r="BJ9" s="5">
         <v>15</v>
       </c>
-      <c r="I6" s="12">
+      <c r="BK9" s="5">
         <v>16</v>
       </c>
-      <c r="J6" s="13">
+      <c r="BL9" s="6">
         <v>17</v>
       </c>
-      <c r="K6" s="13">
+      <c r="BM9" s="7">
         <v>18</v>
       </c>
-      <c r="L6" s="13">
+      <c r="BN9" s="2">
         <v>19</v>
       </c>
-      <c r="M6" s="13">
+      <c r="BO9" s="2">
         <v>20</v>
       </c>
-      <c r="N6" s="13">
+      <c r="BP9" s="12">
         <v>21</v>
       </c>
-      <c r="O6" s="14">
+      <c r="BQ9" s="2">
         <v>22</v>
       </c>
-      <c r="P6" s="15">
+      <c r="BR9" s="2">
         <v>23</v>
       </c>
-      <c r="Q6" s="10">
+      <c r="BS9" s="3">
         <v>24</v>
       </c>
-      <c r="R6" s="10">
+      <c r="BT9" s="4">
         <v>25</v>
       </c>
-      <c r="S6" s="10">
+      <c r="BU9" s="5">
         <v>26</v>
       </c>
-      <c r="T6" s="10">
+      <c r="BV9" s="5">
         <v>27</v>
       </c>
-      <c r="U6" s="10">
+      <c r="BW9" s="5">
         <v>28</v>
       </c>
-      <c r="V6" s="11">
+      <c r="BX9" s="5">
         <v>29</v>
       </c>
-      <c r="W6" s="12">
+      <c r="BY9" s="5">
         <v>30</v>
       </c>
-      <c r="X6" s="16">
+      <c r="BZ9" s="13">
         <v>31</v>
       </c>
-      <c r="Y6" s="17">
+      <c r="CA9" s="1">
         <v>1</v>
       </c>
-      <c r="Z6" s="13">
+      <c r="CB9" s="2">
         <v>2</v>
       </c>
-      <c r="AA6" s="18">
+      <c r="CC9" s="2">
         <v>3</v>
       </c>
-      <c r="AB6" s="18">
+      <c r="CD9" s="2">
         <v>4</v>
       </c>
-      <c r="AC6" s="14">
+      <c r="CE9" s="2">
         <v>5</v>
       </c>
-      <c r="AD6" s="15">
+      <c r="CF9" s="2">
         <v>6</v>
       </c>
-      <c r="AE6" s="10">
+      <c r="CG9" s="3">
         <v>7</v>
       </c>
-      <c r="AF6" s="10">
+      <c r="CH9" s="4">
         <v>8</v>
       </c>
-      <c r="AG6" s="10">
+      <c r="CI9" s="5">
         <v>9</v>
       </c>
-      <c r="AH6" s="10">
+      <c r="CJ9" s="5">
         <v>10</v>
       </c>
-      <c r="AI6" s="10">
+      <c r="CK9" s="5">
         <v>11</v>
       </c>
-      <c r="AJ6" s="11">
+      <c r="CL9" s="5">
         <v>12</v>
       </c>
-      <c r="AK6" s="12">
+      <c r="CM9" s="5">
         <v>13</v>
       </c>
-      <c r="AL6" s="13">
+      <c r="CN9" s="6">
         <v>14</v>
       </c>
-      <c r="AM6" s="13">
+      <c r="CO9" s="7">
         <v>15</v>
       </c>
-      <c r="AN6" s="13">
+      <c r="CP9" s="2">
         <v>16</v>
       </c>
-      <c r="AO6" s="13">
+      <c r="CQ9" s="2">
         <v>17</v>
       </c>
-      <c r="AP6" s="13">
+      <c r="CR9" s="2">
         <v>18</v>
       </c>
-      <c r="AQ6" s="14">
+      <c r="CS9" s="2">
         <v>19</v>
       </c>
-      <c r="AR6" s="15">
+      <c r="CT9" s="2">
         <v>20</v>
       </c>
-      <c r="AS6" s="10">
+      <c r="CU9" s="3">
         <v>21</v>
       </c>
-      <c r="AT6" s="10">
+      <c r="CV9" s="4">
         <v>22</v>
       </c>
-      <c r="AU6" s="10">
+      <c r="CW9" s="5">
         <v>23</v>
       </c>
-      <c r="AV6" s="10">
+      <c r="CX9" s="5">
         <v>24</v>
       </c>
-      <c r="AW6" s="10">
+      <c r="CY9" s="5">
         <v>25</v>
       </c>
-      <c r="AX6" s="11">
+      <c r="CZ9" s="5">
         <v>26</v>
       </c>
-      <c r="AY6" s="12">
+      <c r="DA9" s="5">
         <v>27</v>
       </c>
-      <c r="AZ6" s="13">
+      <c r="DB9" s="6">
         <v>28</v>
       </c>
-      <c r="BA6" s="13">
+      <c r="DC9" s="14">
         <v>29</v>
       </c>
-      <c r="BB6" s="16">
+      <c r="DD9" s="15">
         <v>30</v>
       </c>
-      <c r="BC6" s="19">
+    </row>
+    <row r="10" spans="1:110" x14ac:dyDescent="0.2">
+      <c r="B10" s="16"/>
+      <c r="H10" s="18"/>
+      <c r="I10" s="16"/>
+      <c r="O10" s="18"/>
+      <c r="P10" s="16"/>
+      <c r="V10" s="18"/>
+      <c r="W10" s="16"/>
+      <c r="AC10" s="18"/>
+      <c r="AD10" s="16"/>
+      <c r="AJ10" s="18"/>
+      <c r="AK10" s="16"/>
+      <c r="AQ10" s="18"/>
+      <c r="AR10" s="16"/>
+      <c r="AX10" s="18"/>
+      <c r="AY10" s="16"/>
+      <c r="BE10" s="18"/>
+      <c r="BF10" s="16"/>
+      <c r="BL10" s="18"/>
+      <c r="BM10" s="16"/>
+      <c r="BS10" s="18"/>
+      <c r="BT10" s="16"/>
+      <c r="BZ10" s="18"/>
+      <c r="CA10" s="16"/>
+      <c r="CG10" s="18"/>
+      <c r="CH10" s="16"/>
+      <c r="CN10" s="18"/>
+      <c r="CO10" s="16"/>
+      <c r="CU10" s="18"/>
+      <c r="CV10" s="16"/>
+      <c r="DB10" s="18"/>
+      <c r="DC10" s="16"/>
+      <c r="DD10" s="18"/>
+    </row>
+    <row r="11" spans="1:110" ht="15" x14ac:dyDescent="0.2">
+      <c r="A11" s="43" t="s">
         <v>1</v>
       </c>
-      <c r="BD6" s="13">
+      <c r="B11" s="22"/>
+      <c r="C11" s="23"/>
+      <c r="D11" s="23"/>
+      <c r="E11" s="23"/>
+      <c r="F11" s="23"/>
+      <c r="G11" s="23"/>
+      <c r="H11" s="24"/>
+      <c r="I11" s="16"/>
+      <c r="O11" s="18"/>
+      <c r="P11" s="16"/>
+      <c r="V11" s="18"/>
+      <c r="W11" s="16"/>
+      <c r="AC11" s="18"/>
+      <c r="AD11" s="16"/>
+      <c r="AJ11" s="18"/>
+      <c r="AK11" s="16"/>
+      <c r="AQ11" s="18"/>
+      <c r="AR11" s="16"/>
+      <c r="AX11" s="18"/>
+      <c r="AY11" s="16"/>
+      <c r="BE11" s="18"/>
+      <c r="BF11" s="16"/>
+      <c r="BL11" s="18"/>
+      <c r="BM11" s="16"/>
+      <c r="BS11" s="18"/>
+      <c r="BT11" s="16"/>
+      <c r="BZ11" s="18"/>
+      <c r="CA11" s="16"/>
+      <c r="CG11" s="18"/>
+      <c r="CH11" s="16"/>
+      <c r="CN11" s="18"/>
+      <c r="CO11" s="16"/>
+      <c r="CU11" s="18"/>
+      <c r="CV11" s="16"/>
+      <c r="DB11" s="18"/>
+      <c r="DC11" s="16"/>
+      <c r="DD11" s="18"/>
+    </row>
+    <row r="12" spans="1:110" ht="15" x14ac:dyDescent="0.2">
+      <c r="A12" s="43" t="s">
+        <v>6</v>
+      </c>
+      <c r="B12" s="16"/>
+      <c r="H12" s="18"/>
+      <c r="I12" s="22"/>
+      <c r="J12" s="23"/>
+      <c r="K12" s="23"/>
+      <c r="L12" s="23"/>
+      <c r="M12" s="23"/>
+      <c r="N12" s="23"/>
+      <c r="O12" s="24"/>
+      <c r="P12" s="16"/>
+      <c r="V12" s="18"/>
+      <c r="W12" s="16"/>
+      <c r="AC12" s="18"/>
+      <c r="AD12" s="16"/>
+      <c r="AJ12" s="18"/>
+      <c r="AK12" s="16"/>
+      <c r="AQ12" s="18"/>
+      <c r="AR12" s="16"/>
+      <c r="AX12" s="18"/>
+      <c r="AY12" s="16"/>
+      <c r="BE12" s="18"/>
+      <c r="BF12" s="16"/>
+      <c r="BL12" s="18"/>
+      <c r="BM12" s="16"/>
+      <c r="BS12" s="18"/>
+      <c r="BT12" s="16"/>
+      <c r="BZ12" s="18"/>
+      <c r="CA12" s="16"/>
+      <c r="CG12" s="18"/>
+      <c r="CH12" s="16"/>
+      <c r="CN12" s="18"/>
+      <c r="CO12" s="16"/>
+      <c r="CU12" s="18"/>
+      <c r="CV12" s="16"/>
+      <c r="DB12" s="18"/>
+      <c r="DC12" s="16"/>
+      <c r="DD12" s="18"/>
+    </row>
+    <row r="13" spans="1:110" ht="15" x14ac:dyDescent="0.2">
+      <c r="A13" s="43" t="s">
+        <v>11</v>
+      </c>
+      <c r="B13" s="16"/>
+      <c r="H13" s="18"/>
+      <c r="I13" s="16"/>
+      <c r="O13" s="18"/>
+      <c r="P13" s="22"/>
+      <c r="Q13" s="23"/>
+      <c r="R13" s="23"/>
+      <c r="S13" s="23"/>
+      <c r="T13" s="23"/>
+      <c r="U13" s="23"/>
+      <c r="V13" s="24"/>
+      <c r="W13" s="16"/>
+      <c r="AC13" s="18"/>
+      <c r="AD13" s="16"/>
+      <c r="AJ13" s="18"/>
+      <c r="AK13" s="16"/>
+      <c r="AQ13" s="18"/>
+      <c r="AR13" s="16"/>
+      <c r="AX13" s="18"/>
+      <c r="AY13" s="16"/>
+      <c r="BE13" s="18"/>
+      <c r="BF13" s="16"/>
+      <c r="BL13" s="18"/>
+      <c r="BM13" s="16"/>
+      <c r="BS13" s="18"/>
+      <c r="BT13" s="16"/>
+      <c r="BZ13" s="18"/>
+      <c r="CA13" s="16"/>
+      <c r="CG13" s="18"/>
+      <c r="CH13" s="16"/>
+      <c r="CN13" s="18"/>
+      <c r="CO13" s="16"/>
+      <c r="CU13" s="18"/>
+      <c r="CV13" s="16"/>
+      <c r="DB13" s="18"/>
+      <c r="DC13" s="16"/>
+      <c r="DD13" s="18"/>
+    </row>
+    <row r="14" spans="1:110" ht="15" x14ac:dyDescent="0.2">
+      <c r="A14" s="43" t="s">
+        <v>7</v>
+      </c>
+      <c r="B14" s="16"/>
+      <c r="H14" s="18"/>
+      <c r="I14" s="16"/>
+      <c r="O14" s="18"/>
+      <c r="P14" s="22"/>
+      <c r="Q14" s="23"/>
+      <c r="R14" s="23"/>
+      <c r="S14" s="23"/>
+      <c r="T14" s="23"/>
+      <c r="U14" s="23"/>
+      <c r="V14" s="24"/>
+      <c r="W14" s="16"/>
+      <c r="AC14" s="18"/>
+      <c r="AD14" s="16"/>
+      <c r="AJ14" s="18"/>
+      <c r="AK14" s="16"/>
+      <c r="AQ14" s="18"/>
+      <c r="AR14" s="16"/>
+      <c r="AX14" s="18"/>
+      <c r="AY14" s="16"/>
+      <c r="BE14" s="18"/>
+      <c r="BF14" s="16"/>
+      <c r="BL14" s="18"/>
+      <c r="BM14" s="16"/>
+      <c r="BS14" s="18"/>
+      <c r="BT14" s="16"/>
+      <c r="BZ14" s="18"/>
+      <c r="CA14" s="16"/>
+      <c r="CG14" s="18"/>
+      <c r="CH14" s="16"/>
+      <c r="CN14" s="18"/>
+      <c r="CO14" s="16"/>
+      <c r="CU14" s="18"/>
+      <c r="CV14" s="16"/>
+      <c r="DB14" s="18"/>
+      <c r="DC14" s="16"/>
+      <c r="DD14" s="18"/>
+    </row>
+    <row r="15" spans="1:110" ht="15" x14ac:dyDescent="0.2">
+      <c r="A15" s="43" t="s">
+        <v>8</v>
+      </c>
+      <c r="B15" s="16"/>
+      <c r="H15" s="18"/>
+      <c r="I15" s="16"/>
+      <c r="O15" s="18"/>
+      <c r="P15" s="16"/>
+      <c r="V15" s="18"/>
+      <c r="W15" s="22"/>
+      <c r="X15" s="23"/>
+      <c r="Y15" s="23"/>
+      <c r="Z15" s="23"/>
+      <c r="AA15" s="23"/>
+      <c r="AB15" s="23"/>
+      <c r="AC15" s="24"/>
+      <c r="AD15" s="16"/>
+      <c r="AJ15" s="18"/>
+      <c r="AK15" s="16"/>
+      <c r="AQ15" s="18"/>
+      <c r="AR15" s="16"/>
+      <c r="AX15" s="18"/>
+      <c r="AY15" s="16"/>
+      <c r="BE15" s="18"/>
+      <c r="BF15" s="16"/>
+      <c r="BL15" s="18"/>
+      <c r="BM15" s="16"/>
+      <c r="BS15" s="18"/>
+      <c r="BT15" s="16"/>
+      <c r="BZ15" s="18"/>
+      <c r="CA15" s="16"/>
+      <c r="CG15" s="18"/>
+      <c r="CH15" s="16"/>
+      <c r="CN15" s="18"/>
+      <c r="CO15" s="16"/>
+      <c r="CU15" s="18"/>
+      <c r="CV15" s="16"/>
+      <c r="DB15" s="18"/>
+      <c r="DC15" s="16"/>
+      <c r="DD15" s="18"/>
+    </row>
+    <row r="16" spans="1:110" ht="15" x14ac:dyDescent="0.2">
+      <c r="A16" s="43" t="s">
+        <v>10</v>
+      </c>
+      <c r="B16" s="16"/>
+      <c r="H16" s="18"/>
+      <c r="I16" s="16"/>
+      <c r="O16" s="18"/>
+      <c r="P16" s="16"/>
+      <c r="V16" s="18"/>
+      <c r="W16" s="16"/>
+      <c r="AC16" s="18"/>
+      <c r="AD16" s="22"/>
+      <c r="AE16" s="23"/>
+      <c r="AF16" s="23"/>
+      <c r="AG16" s="23"/>
+      <c r="AH16" s="23"/>
+      <c r="AI16" s="23"/>
+      <c r="AJ16" s="24"/>
+      <c r="AK16" s="16"/>
+      <c r="AQ16" s="18"/>
+      <c r="AR16" s="16"/>
+      <c r="AX16" s="18"/>
+      <c r="AY16" s="16"/>
+      <c r="BE16" s="18"/>
+      <c r="BF16" s="16"/>
+      <c r="BL16" s="18"/>
+      <c r="BM16" s="16"/>
+      <c r="BS16" s="18"/>
+      <c r="BT16" s="16"/>
+      <c r="BZ16" s="18"/>
+      <c r="CA16" s="16"/>
+      <c r="CG16" s="18"/>
+      <c r="CH16" s="16"/>
+      <c r="CN16" s="18"/>
+      <c r="CO16" s="16"/>
+      <c r="CU16" s="18"/>
+      <c r="CV16" s="16"/>
+      <c r="DB16" s="18"/>
+      <c r="DC16" s="16"/>
+      <c r="DD16" s="18"/>
+    </row>
+    <row r="17" spans="1:108" ht="15" x14ac:dyDescent="0.2">
+      <c r="A17" s="43" t="s">
+        <v>9</v>
+      </c>
+      <c r="B17" s="16"/>
+      <c r="H17" s="18"/>
+      <c r="I17" s="16"/>
+      <c r="O17" s="18"/>
+      <c r="P17" s="16"/>
+      <c r="V17" s="18"/>
+      <c r="W17" s="16"/>
+      <c r="AC17" s="18"/>
+      <c r="AD17" s="16"/>
+      <c r="AJ17" s="18"/>
+      <c r="AK17" s="22"/>
+      <c r="AL17" s="23"/>
+      <c r="AM17" s="23"/>
+      <c r="AN17" s="23"/>
+      <c r="AO17" s="23"/>
+      <c r="AP17" s="23"/>
+      <c r="AQ17" s="24"/>
+      <c r="AR17" s="16"/>
+      <c r="AX17" s="18"/>
+      <c r="AY17" s="16"/>
+      <c r="BE17" s="18"/>
+      <c r="BF17" s="16"/>
+      <c r="BL17" s="18"/>
+      <c r="BM17" s="16"/>
+      <c r="BS17" s="18"/>
+      <c r="BT17" s="16"/>
+      <c r="BZ17" s="18"/>
+      <c r="CA17" s="16"/>
+      <c r="CG17" s="18"/>
+      <c r="CH17" s="16"/>
+      <c r="CN17" s="18"/>
+      <c r="CO17" s="16"/>
+      <c r="CU17" s="18"/>
+      <c r="CV17" s="16"/>
+      <c r="DB17" s="18"/>
+      <c r="DC17" s="16"/>
+      <c r="DD17" s="18"/>
+    </row>
+    <row r="18" spans="1:108" ht="15" x14ac:dyDescent="0.2">
+      <c r="A18" s="43" t="s">
+        <v>12</v>
+      </c>
+      <c r="B18" s="16"/>
+      <c r="H18" s="18"/>
+      <c r="I18" s="16"/>
+      <c r="O18" s="18"/>
+      <c r="P18" s="16"/>
+      <c r="V18" s="18"/>
+      <c r="W18" s="16"/>
+      <c r="AC18" s="18"/>
+      <c r="AD18" s="16"/>
+      <c r="AJ18" s="18"/>
+      <c r="AK18" s="22"/>
+      <c r="AL18" s="23"/>
+      <c r="AM18" s="23"/>
+      <c r="AN18" s="23"/>
+      <c r="AO18" s="23"/>
+      <c r="AP18" s="23"/>
+      <c r="AQ18" s="24"/>
+      <c r="AR18" s="22"/>
+      <c r="AS18" s="23"/>
+      <c r="AT18" s="23"/>
+      <c r="AU18" s="23"/>
+      <c r="AV18" s="23"/>
+      <c r="AW18" s="23"/>
+      <c r="AX18" s="24"/>
+      <c r="AY18" s="22"/>
+      <c r="AZ18" s="23"/>
+      <c r="BA18" s="23"/>
+      <c r="BB18" s="23"/>
+      <c r="BC18" s="23"/>
+      <c r="BD18" s="23"/>
+      <c r="BE18" s="24"/>
+      <c r="BF18" s="16"/>
+      <c r="BL18" s="18"/>
+      <c r="BM18" s="16"/>
+      <c r="BS18" s="18"/>
+      <c r="BT18" s="16"/>
+      <c r="BZ18" s="18"/>
+      <c r="CA18" s="16"/>
+      <c r="CG18" s="18"/>
+      <c r="CH18" s="16"/>
+      <c r="CN18" s="18"/>
+      <c r="CO18" s="16"/>
+      <c r="CU18" s="18"/>
+      <c r="CV18" s="16"/>
+      <c r="DB18" s="18"/>
+      <c r="DC18" s="16"/>
+      <c r="DD18" s="18"/>
+    </row>
+    <row r="19" spans="1:108" ht="15" x14ac:dyDescent="0.2">
+      <c r="A19" s="43" t="s">
+        <v>13</v>
+      </c>
+      <c r="B19" s="16"/>
+      <c r="H19" s="18"/>
+      <c r="I19" s="16"/>
+      <c r="O19" s="18"/>
+      <c r="P19" s="16"/>
+      <c r="V19" s="18"/>
+      <c r="W19" s="16"/>
+      <c r="AC19" s="18"/>
+      <c r="AD19" s="16"/>
+      <c r="AJ19" s="18"/>
+      <c r="AK19" s="22"/>
+      <c r="AL19" s="23"/>
+      <c r="AM19" s="23"/>
+      <c r="AN19" s="23"/>
+      <c r="AO19" s="23"/>
+      <c r="AP19" s="23"/>
+      <c r="AQ19" s="24"/>
+      <c r="AR19" s="22"/>
+      <c r="AS19" s="23"/>
+      <c r="AT19" s="23"/>
+      <c r="AU19" s="23"/>
+      <c r="AV19" s="23"/>
+      <c r="AW19" s="23"/>
+      <c r="AX19" s="24"/>
+      <c r="AY19" s="22"/>
+      <c r="AZ19" s="23"/>
+      <c r="BA19" s="23"/>
+      <c r="BB19" s="23"/>
+      <c r="BC19" s="23"/>
+      <c r="BD19" s="23"/>
+      <c r="BE19" s="24"/>
+      <c r="BF19" s="16"/>
+      <c r="BL19" s="18"/>
+      <c r="BM19" s="16"/>
+      <c r="BS19" s="18"/>
+      <c r="BT19" s="16"/>
+      <c r="BZ19" s="18"/>
+      <c r="CA19" s="16"/>
+      <c r="CG19" s="18"/>
+      <c r="CH19" s="16"/>
+      <c r="CN19" s="18"/>
+      <c r="CO19" s="16"/>
+      <c r="CU19" s="18"/>
+      <c r="CV19" s="16"/>
+      <c r="DB19" s="18"/>
+      <c r="DC19" s="16"/>
+      <c r="DD19" s="18"/>
+    </row>
+    <row r="20" spans="1:108" ht="15" x14ac:dyDescent="0.2">
+      <c r="A20" s="43" t="s">
+        <v>14</v>
+      </c>
+      <c r="B20" s="16"/>
+      <c r="H20" s="18"/>
+      <c r="I20" s="16"/>
+      <c r="O20" s="18"/>
+      <c r="P20" s="16"/>
+      <c r="V20" s="18"/>
+      <c r="W20" s="16"/>
+      <c r="AC20" s="18"/>
+      <c r="AD20" s="16"/>
+      <c r="AJ20" s="18"/>
+      <c r="AK20" s="16"/>
+      <c r="AQ20" s="18"/>
+      <c r="AR20" s="22"/>
+      <c r="AS20" s="23"/>
+      <c r="AT20" s="23"/>
+      <c r="AU20" s="23"/>
+      <c r="AV20" s="23"/>
+      <c r="AW20" s="23"/>
+      <c r="AX20" s="24"/>
+      <c r="AY20" s="16"/>
+      <c r="BE20" s="18"/>
+      <c r="BF20" s="16"/>
+      <c r="BL20" s="18"/>
+      <c r="BM20" s="16"/>
+      <c r="BS20" s="18"/>
+      <c r="BT20" s="16"/>
+      <c r="BZ20" s="18"/>
+      <c r="CA20" s="16"/>
+      <c r="CG20" s="18"/>
+      <c r="CH20" s="16"/>
+      <c r="CN20" s="18"/>
+      <c r="CO20" s="16"/>
+      <c r="CU20" s="18"/>
+      <c r="CV20" s="16"/>
+      <c r="DB20" s="18"/>
+      <c r="DC20" s="16"/>
+      <c r="DD20" s="18"/>
+    </row>
+    <row r="21" spans="1:108" ht="15" x14ac:dyDescent="0.2">
+      <c r="A21" s="43" t="s">
+        <v>15</v>
+      </c>
+      <c r="B21" s="16"/>
+      <c r="H21" s="18"/>
+      <c r="I21" s="16"/>
+      <c r="O21" s="18"/>
+      <c r="P21" s="16"/>
+      <c r="V21" s="18"/>
+      <c r="W21" s="16"/>
+      <c r="AC21" s="18"/>
+      <c r="AD21" s="16"/>
+      <c r="AJ21" s="18"/>
+      <c r="AK21" s="16"/>
+      <c r="AQ21" s="18"/>
+      <c r="AR21" s="16"/>
+      <c r="AX21" s="18"/>
+      <c r="AY21" s="16"/>
+      <c r="BE21" s="18"/>
+      <c r="BF21" s="22"/>
+      <c r="BG21" s="23"/>
+      <c r="BH21" s="23"/>
+      <c r="BI21" s="23"/>
+      <c r="BJ21" s="23"/>
+      <c r="BK21" s="23"/>
+      <c r="BL21" s="24"/>
+      <c r="BM21" s="16"/>
+      <c r="BS21" s="18"/>
+      <c r="BT21" s="16"/>
+      <c r="BZ21" s="18"/>
+      <c r="CA21" s="16"/>
+      <c r="CG21" s="18"/>
+      <c r="CH21" s="16"/>
+      <c r="CN21" s="18"/>
+      <c r="CO21" s="16"/>
+      <c r="CU21" s="18"/>
+      <c r="CV21" s="16"/>
+      <c r="DB21" s="18"/>
+      <c r="DC21" s="16"/>
+      <c r="DD21" s="18"/>
+    </row>
+    <row r="22" spans="1:108" ht="15" x14ac:dyDescent="0.2">
+      <c r="A22" s="43" t="s">
+        <v>16</v>
+      </c>
+      <c r="B22" s="16"/>
+      <c r="H22" s="18"/>
+      <c r="I22" s="16"/>
+      <c r="O22" s="18"/>
+      <c r="P22" s="16"/>
+      <c r="V22" s="18"/>
+      <c r="W22" s="16"/>
+      <c r="AC22" s="18"/>
+      <c r="AD22" s="16"/>
+      <c r="AJ22" s="18"/>
+      <c r="AK22" s="16"/>
+      <c r="AQ22" s="18"/>
+      <c r="AR22" s="16"/>
+      <c r="AX22" s="18"/>
+      <c r="AY22" s="16"/>
+      <c r="BE22" s="18"/>
+      <c r="BF22" s="22"/>
+      <c r="BG22" s="23"/>
+      <c r="BH22" s="23"/>
+      <c r="BI22" s="23"/>
+      <c r="BJ22" s="23"/>
+      <c r="BK22" s="23"/>
+      <c r="BL22" s="24"/>
+      <c r="BM22" s="16"/>
+      <c r="BS22" s="18"/>
+      <c r="BT22" s="16"/>
+      <c r="BZ22" s="18"/>
+      <c r="CA22" s="16"/>
+      <c r="CG22" s="18"/>
+      <c r="CH22" s="16"/>
+      <c r="CN22" s="18"/>
+      <c r="CO22" s="16"/>
+      <c r="CU22" s="18"/>
+      <c r="CV22" s="16"/>
+      <c r="DB22" s="18"/>
+      <c r="DC22" s="16"/>
+      <c r="DD22" s="18"/>
+    </row>
+    <row r="23" spans="1:108" ht="15" x14ac:dyDescent="0.2">
+      <c r="A23" s="43" t="s">
+        <v>12</v>
+      </c>
+      <c r="B23" s="16"/>
+      <c r="H23" s="18"/>
+      <c r="I23" s="16"/>
+      <c r="O23" s="18"/>
+      <c r="P23" s="16"/>
+      <c r="V23" s="18"/>
+      <c r="W23" s="16"/>
+      <c r="AC23" s="18"/>
+      <c r="AD23" s="16"/>
+      <c r="AJ23" s="18"/>
+      <c r="AK23" s="16"/>
+      <c r="AQ23" s="18"/>
+      <c r="AR23" s="16"/>
+      <c r="AX23" s="18"/>
+      <c r="AY23" s="16"/>
+      <c r="BE23" s="18"/>
+      <c r="BF23" s="16"/>
+      <c r="BL23" s="18"/>
+      <c r="BM23" s="22"/>
+      <c r="BN23" s="23"/>
+      <c r="BO23" s="23"/>
+      <c r="BP23" s="23"/>
+      <c r="BQ23" s="23"/>
+      <c r="BR23" s="23"/>
+      <c r="BS23" s="24"/>
+      <c r="BT23" s="22"/>
+      <c r="BU23" s="23"/>
+      <c r="BV23" s="23"/>
+      <c r="BW23" s="23"/>
+      <c r="BX23" s="23"/>
+      <c r="BY23" s="23"/>
+      <c r="BZ23" s="24"/>
+      <c r="CA23" s="22"/>
+      <c r="CB23" s="23"/>
+      <c r="CC23" s="23"/>
+      <c r="CD23" s="23"/>
+      <c r="CE23" s="23"/>
+      <c r="CF23" s="23"/>
+      <c r="CG23" s="24"/>
+      <c r="CH23" s="22"/>
+      <c r="CI23" s="23"/>
+      <c r="CJ23" s="23"/>
+      <c r="CK23" s="23"/>
+      <c r="CL23" s="23"/>
+      <c r="CM23" s="23"/>
+      <c r="CN23" s="24"/>
+      <c r="CO23" s="16"/>
+      <c r="CU23" s="18"/>
+      <c r="CV23" s="16"/>
+      <c r="DB23" s="18"/>
+      <c r="DC23" s="16"/>
+      <c r="DD23" s="18"/>
+    </row>
+    <row r="24" spans="1:108" ht="15" x14ac:dyDescent="0.2">
+      <c r="A24" s="43" t="s">
+        <v>13</v>
+      </c>
+      <c r="B24" s="16"/>
+      <c r="H24" s="18"/>
+      <c r="I24" s="16"/>
+      <c r="O24" s="18"/>
+      <c r="P24" s="16"/>
+      <c r="V24" s="18"/>
+      <c r="W24" s="16"/>
+      <c r="AC24" s="18"/>
+      <c r="AD24" s="16"/>
+      <c r="AJ24" s="18"/>
+      <c r="AK24" s="16"/>
+      <c r="AQ24" s="18"/>
+      <c r="AR24" s="16"/>
+      <c r="AX24" s="18"/>
+      <c r="AY24" s="16"/>
+      <c r="BE24" s="18"/>
+      <c r="BF24" s="16"/>
+      <c r="BL24" s="18"/>
+      <c r="BM24" s="22"/>
+      <c r="BN24" s="23"/>
+      <c r="BO24" s="23"/>
+      <c r="BP24" s="23"/>
+      <c r="BQ24" s="23"/>
+      <c r="BR24" s="23"/>
+      <c r="BS24" s="24"/>
+      <c r="BT24" s="22"/>
+      <c r="BU24" s="23"/>
+      <c r="BV24" s="23"/>
+      <c r="BW24" s="23"/>
+      <c r="BX24" s="23"/>
+      <c r="BY24" s="23"/>
+      <c r="BZ24" s="24"/>
+      <c r="CA24" s="22"/>
+      <c r="CB24" s="23"/>
+      <c r="CC24" s="23"/>
+      <c r="CD24" s="23"/>
+      <c r="CE24" s="23"/>
+      <c r="CF24" s="23"/>
+      <c r="CG24" s="24"/>
+      <c r="CH24" s="22"/>
+      <c r="CI24" s="23"/>
+      <c r="CJ24" s="23"/>
+      <c r="CK24" s="23"/>
+      <c r="CL24" s="23"/>
+      <c r="CM24" s="23"/>
+      <c r="CN24" s="24"/>
+      <c r="CO24" s="16"/>
+      <c r="CU24" s="18"/>
+      <c r="CV24" s="16"/>
+      <c r="DB24" s="18"/>
+      <c r="DC24" s="16"/>
+      <c r="DD24" s="18"/>
+    </row>
+    <row r="25" spans="1:108" ht="15" x14ac:dyDescent="0.2">
+      <c r="A25" s="43" t="s">
+        <v>17</v>
+      </c>
+      <c r="B25" s="16"/>
+      <c r="H25" s="18"/>
+      <c r="I25" s="16"/>
+      <c r="O25" s="18"/>
+      <c r="P25" s="16"/>
+      <c r="V25" s="18"/>
+      <c r="W25" s="16"/>
+      <c r="AC25" s="18"/>
+      <c r="AD25" s="16"/>
+      <c r="AJ25" s="18"/>
+      <c r="AK25" s="16"/>
+      <c r="AQ25" s="18"/>
+      <c r="AR25" s="16"/>
+      <c r="AX25" s="18"/>
+      <c r="AY25" s="16"/>
+      <c r="BE25" s="18"/>
+      <c r="BF25" s="16"/>
+      <c r="BL25" s="18"/>
+      <c r="BM25" s="16"/>
+      <c r="BS25" s="18"/>
+      <c r="BT25" s="16"/>
+      <c r="BZ25" s="18"/>
+      <c r="CA25" s="16"/>
+      <c r="CG25" s="18"/>
+      <c r="CH25" s="16"/>
+      <c r="CN25" s="18"/>
+      <c r="CO25" s="22"/>
+      <c r="CP25" s="23"/>
+      <c r="CQ25" s="23"/>
+      <c r="CR25" s="23"/>
+      <c r="CS25" s="23"/>
+      <c r="CT25" s="23"/>
+      <c r="CU25" s="24"/>
+      <c r="CV25" s="16"/>
+      <c r="DB25" s="18"/>
+      <c r="DC25" s="16"/>
+      <c r="DD25" s="18"/>
+    </row>
+    <row r="26" spans="1:108" ht="15" x14ac:dyDescent="0.2">
+      <c r="A26" s="43" t="s">
+        <v>18</v>
+      </c>
+      <c r="B26" s="16"/>
+      <c r="H26" s="18"/>
+      <c r="I26" s="16"/>
+      <c r="O26" s="18"/>
+      <c r="P26" s="16"/>
+      <c r="V26" s="18"/>
+      <c r="W26" s="16"/>
+      <c r="AC26" s="18"/>
+      <c r="AD26" s="16"/>
+      <c r="AJ26" s="18"/>
+      <c r="AK26" s="16"/>
+      <c r="AQ26" s="18"/>
+      <c r="AR26" s="16"/>
+      <c r="AX26" s="18"/>
+      <c r="AY26" s="16"/>
+      <c r="BE26" s="18"/>
+      <c r="BF26" s="16"/>
+      <c r="BL26" s="18"/>
+      <c r="BM26" s="16"/>
+      <c r="BS26" s="18"/>
+      <c r="BT26" s="16"/>
+      <c r="BZ26" s="18"/>
+      <c r="CA26" s="16"/>
+      <c r="CG26" s="18"/>
+      <c r="CH26" s="16"/>
+      <c r="CN26" s="18"/>
+      <c r="CO26" s="22"/>
+      <c r="CP26" s="23"/>
+      <c r="CQ26" s="23"/>
+      <c r="CR26" s="23"/>
+      <c r="CS26" s="23"/>
+      <c r="CT26" s="23"/>
+      <c r="CU26" s="24"/>
+      <c r="CV26" s="16"/>
+      <c r="DB26" s="18"/>
+      <c r="DC26" s="16"/>
+      <c r="DD26" s="18"/>
+    </row>
+    <row r="27" spans="1:108" ht="15" x14ac:dyDescent="0.2">
+      <c r="A27" s="43" t="s">
+        <v>19</v>
+      </c>
+      <c r="B27" s="16"/>
+      <c r="H27" s="18"/>
+      <c r="I27" s="16"/>
+      <c r="O27" s="18"/>
+      <c r="P27" s="16"/>
+      <c r="V27" s="18"/>
+      <c r="W27" s="16"/>
+      <c r="AC27" s="18"/>
+      <c r="AD27" s="16"/>
+      <c r="AJ27" s="18"/>
+      <c r="AK27" s="16"/>
+      <c r="AQ27" s="18"/>
+      <c r="AR27" s="16"/>
+      <c r="AX27" s="18"/>
+      <c r="AY27" s="16"/>
+      <c r="BE27" s="18"/>
+      <c r="BF27" s="16"/>
+      <c r="BL27" s="18"/>
+      <c r="BM27" s="16"/>
+      <c r="BS27" s="18"/>
+      <c r="BT27" s="16"/>
+      <c r="BZ27" s="18"/>
+      <c r="CA27" s="16"/>
+      <c r="CG27" s="18"/>
+      <c r="CH27" s="16"/>
+      <c r="CN27" s="18"/>
+      <c r="CO27" s="16"/>
+      <c r="CU27" s="18"/>
+      <c r="CV27" s="22"/>
+      <c r="CW27" s="23"/>
+      <c r="CX27" s="23"/>
+      <c r="CY27" s="23"/>
+      <c r="CZ27" s="23"/>
+      <c r="DA27" s="23"/>
+      <c r="DB27" s="24"/>
+      <c r="DC27" s="22"/>
+      <c r="DD27" s="24"/>
+    </row>
+    <row r="28" spans="1:108" ht="15" x14ac:dyDescent="0.2">
+      <c r="A28" s="43" t="s">
+        <v>20</v>
+      </c>
+      <c r="B28" s="16"/>
+      <c r="H28" s="18"/>
+      <c r="I28" s="16"/>
+      <c r="O28" s="18"/>
+      <c r="P28" s="16"/>
+      <c r="V28" s="18"/>
+      <c r="W28" s="16"/>
+      <c r="AC28" s="18"/>
+      <c r="AD28" s="16"/>
+      <c r="AJ28" s="18"/>
+      <c r="AK28" s="16"/>
+      <c r="AQ28" s="18"/>
+      <c r="AR28" s="16"/>
+      <c r="AX28" s="18"/>
+      <c r="AY28" s="16"/>
+      <c r="BE28" s="18"/>
+      <c r="BF28" s="16"/>
+      <c r="BL28" s="18"/>
+      <c r="BM28" s="16"/>
+      <c r="BS28" s="18"/>
+      <c r="BT28" s="16"/>
+      <c r="BZ28" s="18"/>
+      <c r="CA28" s="16"/>
+      <c r="CG28" s="18"/>
+      <c r="CH28" s="16"/>
+      <c r="CN28" s="18"/>
+      <c r="CO28" s="16"/>
+      <c r="CU28" s="18"/>
+      <c r="CV28" s="22"/>
+      <c r="CW28" s="23"/>
+      <c r="CX28" s="23"/>
+      <c r="CY28" s="23"/>
+      <c r="CZ28" s="23"/>
+      <c r="DA28" s="23"/>
+      <c r="DB28" s="24"/>
+      <c r="DC28" s="22"/>
+      <c r="DD28" s="24"/>
+    </row>
+    <row r="29" spans="1:108" ht="15" x14ac:dyDescent="0.2">
+      <c r="A29" s="44" t="s">
+        <v>21</v>
+      </c>
+      <c r="B29" s="19"/>
+      <c r="C29" s="20"/>
+      <c r="D29" s="20"/>
+      <c r="E29" s="20"/>
+      <c r="F29" s="20"/>
+      <c r="G29" s="20"/>
+      <c r="H29" s="21"/>
+      <c r="I29" s="19"/>
+      <c r="J29" s="20"/>
+      <c r="K29" s="20"/>
+      <c r="L29" s="20"/>
+      <c r="M29" s="20"/>
+      <c r="N29" s="20"/>
+      <c r="O29" s="21"/>
+      <c r="P29" s="19"/>
+      <c r="Q29" s="20"/>
+      <c r="R29" s="20"/>
+      <c r="S29" s="20"/>
+      <c r="T29" s="20"/>
+      <c r="U29" s="20"/>
+      <c r="V29" s="21"/>
+      <c r="W29" s="19"/>
+      <c r="X29" s="20"/>
+      <c r="Y29" s="20"/>
+      <c r="Z29" s="20"/>
+      <c r="AA29" s="20"/>
+      <c r="AB29" s="20"/>
+      <c r="AC29" s="21"/>
+      <c r="AD29" s="19"/>
+      <c r="AE29" s="20"/>
+      <c r="AF29" s="20"/>
+      <c r="AG29" s="20"/>
+      <c r="AH29" s="20"/>
+      <c r="AI29" s="20"/>
+      <c r="AJ29" s="21"/>
+      <c r="AK29" s="19"/>
+      <c r="AL29" s="20"/>
+      <c r="AM29" s="20"/>
+      <c r="AN29" s="20"/>
+      <c r="AO29" s="20"/>
+      <c r="AP29" s="20"/>
+      <c r="AQ29" s="21"/>
+      <c r="AR29" s="19"/>
+      <c r="AS29" s="20"/>
+      <c r="AT29" s="20"/>
+      <c r="AU29" s="20"/>
+      <c r="AV29" s="20"/>
+      <c r="AW29" s="20"/>
+      <c r="AX29" s="21"/>
+      <c r="AY29" s="19"/>
+      <c r="AZ29" s="20"/>
+      <c r="BA29" s="20"/>
+      <c r="BB29" s="20"/>
+      <c r="BC29" s="20"/>
+      <c r="BD29" s="20"/>
+      <c r="BE29" s="21"/>
+      <c r="BF29" s="19"/>
+      <c r="BG29" s="20"/>
+      <c r="BH29" s="20"/>
+      <c r="BI29" s="20"/>
+      <c r="BJ29" s="20"/>
+      <c r="BK29" s="20"/>
+      <c r="BL29" s="21"/>
+      <c r="BM29" s="19"/>
+      <c r="BN29" s="20"/>
+      <c r="BO29" s="20"/>
+      <c r="BP29" s="20"/>
+      <c r="BQ29" s="20"/>
+      <c r="BR29" s="20"/>
+      <c r="BS29" s="21"/>
+      <c r="BT29" s="19"/>
+      <c r="BU29" s="20"/>
+      <c r="BV29" s="20"/>
+      <c r="BW29" s="20"/>
+      <c r="BX29" s="20"/>
+      <c r="BY29" s="20"/>
+      <c r="BZ29" s="21"/>
+      <c r="CA29" s="19"/>
+      <c r="CB29" s="20"/>
+      <c r="CC29" s="20"/>
+      <c r="CD29" s="20"/>
+      <c r="CE29" s="20"/>
+      <c r="CF29" s="20"/>
+      <c r="CG29" s="21"/>
+      <c r="CH29" s="19"/>
+      <c r="CI29" s="20"/>
+      <c r="CJ29" s="20"/>
+      <c r="CK29" s="20"/>
+      <c r="CL29" s="20"/>
+      <c r="CM29" s="20"/>
+      <c r="CN29" s="21"/>
+      <c r="CO29" s="19"/>
+      <c r="CP29" s="20"/>
+      <c r="CQ29" s="20"/>
+      <c r="CR29" s="20"/>
+      <c r="CS29" s="20"/>
+      <c r="CT29" s="20"/>
+      <c r="CU29" s="21"/>
+      <c r="CV29" s="25"/>
+      <c r="CW29" s="26"/>
+      <c r="CX29" s="26"/>
+      <c r="CY29" s="26"/>
+      <c r="CZ29" s="26"/>
+      <c r="DA29" s="26"/>
+      <c r="DB29" s="27"/>
+      <c r="DC29" s="25"/>
+      <c r="DD29" s="27"/>
+    </row>
+    <row r="30" spans="1:108" x14ac:dyDescent="0.2">
+      <c r="A30" s="37"/>
+    </row>
+    <row r="31" spans="1:108" x14ac:dyDescent="0.2">
+      <c r="A31" s="37"/>
+    </row>
+    <row r="32" spans="1:108" x14ac:dyDescent="0.2">
+      <c r="A32" s="37"/>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A33" s="37"/>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A34" s="37"/>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A35" s="37"/>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A36" s="37"/>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A37" s="37"/>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A38" s="37"/>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A39" s="37"/>
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A40" s="37"/>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="CA8:DD8"/>
+    <mergeCell ref="B8:Q8"/>
+    <mergeCell ref="R8:AU8"/>
+    <mergeCell ref="AV8:BZ8"/>
+  </mergeCells>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A2DD1884-97C5-4E94-84EE-735838CDBC98}">
+  <dimension ref="A1:DF40"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="20.88671875" style="17" bestFit="1" customWidth="1"/>
+    <col min="2" max="14" width="2.77734375" style="17" customWidth="1"/>
+    <col min="15" max="15" width="3.21875" style="17" bestFit="1" customWidth="1"/>
+    <col min="16" max="42" width="2.77734375" style="17" customWidth="1"/>
+    <col min="43" max="43" width="3.21875" style="17" bestFit="1" customWidth="1"/>
+    <col min="44" max="105" width="2.77734375" style="17" customWidth="1"/>
+    <col min="106" max="107" width="3.21875" style="17" bestFit="1" customWidth="1"/>
+    <col min="108" max="108" width="2.77734375" style="17" customWidth="1"/>
+    <col min="109" max="110" width="11.5546875" style="17"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:108" ht="20.25" x14ac:dyDescent="0.3">
+      <c r="A1" s="31" t="s">
+        <v>25</v>
+      </c>
+      <c r="B1" s="32"/>
+      <c r="C1" s="32"/>
+      <c r="D1" s="32"/>
+      <c r="E1" s="32"/>
+      <c r="F1" s="32"/>
+      <c r="G1" s="32"/>
+      <c r="H1" s="32"/>
+      <c r="I1" s="32"/>
+      <c r="J1" s="32"/>
+      <c r="K1" s="32"/>
+      <c r="L1" s="32"/>
+      <c r="M1" s="32"/>
+      <c r="N1" s="32"/>
+      <c r="O1" s="32"/>
+      <c r="P1" s="32"/>
+      <c r="Q1" s="32"/>
+    </row>
+    <row r="2" spans="1:108" ht="20.25" x14ac:dyDescent="0.3">
+      <c r="A2" s="31" t="s">
+        <v>26</v>
+      </c>
+      <c r="B2" s="32"/>
+      <c r="C2" s="32"/>
+      <c r="D2" s="32"/>
+      <c r="E2" s="32"/>
+      <c r="F2" s="32"/>
+      <c r="G2" s="32"/>
+      <c r="H2" s="32"/>
+      <c r="I2" s="32"/>
+      <c r="J2" s="32"/>
+      <c r="K2" s="32"/>
+      <c r="L2" s="32"/>
+      <c r="M2" s="32"/>
+      <c r="N2" s="32"/>
+      <c r="O2" s="32"/>
+      <c r="P2" s="32"/>
+      <c r="Q2" s="32"/>
+    </row>
+    <row r="3" spans="1:108" ht="20.25" x14ac:dyDescent="0.3">
+      <c r="A3" s="31">
+        <v>2026</v>
+      </c>
+      <c r="B3" s="32"/>
+      <c r="C3" s="32"/>
+      <c r="D3" s="32"/>
+      <c r="E3" s="32"/>
+      <c r="F3" s="32"/>
+      <c r="G3" s="32"/>
+      <c r="H3" s="32"/>
+      <c r="I3" s="32"/>
+      <c r="J3" s="32"/>
+      <c r="K3" s="32"/>
+      <c r="L3" s="32"/>
+      <c r="M3" s="32"/>
+      <c r="N3" s="32"/>
+      <c r="O3" s="32"/>
+      <c r="P3" s="32"/>
+      <c r="Q3" s="32"/>
+    </row>
+    <row r="4" spans="1:108" x14ac:dyDescent="0.2">
+      <c r="A4" s="33"/>
+      <c r="B4" s="33"/>
+      <c r="C4" s="33"/>
+      <c r="D4" s="33"/>
+      <c r="E4" s="33"/>
+      <c r="F4" s="33"/>
+      <c r="G4" s="33"/>
+      <c r="H4" s="33"/>
+      <c r="I4" s="33"/>
+      <c r="J4" s="33"/>
+      <c r="K4" s="33"/>
+      <c r="L4" s="33"/>
+      <c r="M4" s="33"/>
+      <c r="N4" s="33"/>
+      <c r="O4" s="33"/>
+      <c r="P4" s="33"/>
+      <c r="Q4" s="33"/>
+    </row>
+    <row r="5" spans="1:108" ht="18" x14ac:dyDescent="0.25">
+      <c r="A5" s="34" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" spans="1:108" ht="18" x14ac:dyDescent="0.25">
+      <c r="A6" s="34" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="7" spans="1:108" ht="15" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="8" spans="1:108" x14ac:dyDescent="0.2">
+      <c r="A8" s="35" t="s">
+        <v>0</v>
+      </c>
+      <c r="B8" s="30" t="s">
         <v>2</v>
       </c>
-      <c r="BE6" s="14">
+      <c r="C8" s="28"/>
+      <c r="D8" s="28"/>
+      <c r="E8" s="28"/>
+      <c r="F8" s="28"/>
+      <c r="G8" s="28"/>
+      <c r="H8" s="28"/>
+      <c r="I8" s="28"/>
+      <c r="J8" s="28"/>
+      <c r="K8" s="28"/>
+      <c r="L8" s="28"/>
+      <c r="M8" s="28"/>
+      <c r="N8" s="28"/>
+      <c r="O8" s="28"/>
+      <c r="P8" s="28"/>
+      <c r="Q8" s="29"/>
+      <c r="R8" s="30" t="s">
         <v>3</v>
       </c>
-      <c r="BF6" s="15">
+      <c r="S8" s="28"/>
+      <c r="T8" s="28"/>
+      <c r="U8" s="28"/>
+      <c r="V8" s="28"/>
+      <c r="W8" s="28"/>
+      <c r="X8" s="28"/>
+      <c r="Y8" s="28"/>
+      <c r="Z8" s="28"/>
+      <c r="AA8" s="28"/>
+      <c r="AB8" s="28"/>
+      <c r="AC8" s="28"/>
+      <c r="AD8" s="28"/>
+      <c r="AE8" s="28"/>
+      <c r="AF8" s="28"/>
+      <c r="AG8" s="28"/>
+      <c r="AH8" s="28"/>
+      <c r="AI8" s="28"/>
+      <c r="AJ8" s="28"/>
+      <c r="AK8" s="28"/>
+      <c r="AL8" s="28"/>
+      <c r="AM8" s="28"/>
+      <c r="AN8" s="28"/>
+      <c r="AO8" s="28"/>
+      <c r="AP8" s="28"/>
+      <c r="AQ8" s="28"/>
+      <c r="AR8" s="28"/>
+      <c r="AS8" s="28"/>
+      <c r="AT8" s="28"/>
+      <c r="AU8" s="29"/>
+      <c r="AV8" s="30" t="s">
         <v>4</v>
       </c>
-      <c r="BG6" s="10">
+      <c r="AW8" s="28"/>
+      <c r="AX8" s="28"/>
+      <c r="AY8" s="28"/>
+      <c r="AZ8" s="28"/>
+      <c r="BA8" s="28"/>
+      <c r="BB8" s="28"/>
+      <c r="BC8" s="28"/>
+      <c r="BD8" s="28"/>
+      <c r="BE8" s="28"/>
+      <c r="BF8" s="28"/>
+      <c r="BG8" s="28"/>
+      <c r="BH8" s="28"/>
+      <c r="BI8" s="28"/>
+      <c r="BJ8" s="28"/>
+      <c r="BK8" s="28"/>
+      <c r="BL8" s="28"/>
+      <c r="BM8" s="28"/>
+      <c r="BN8" s="28"/>
+      <c r="BO8" s="28"/>
+      <c r="BP8" s="28"/>
+      <c r="BQ8" s="28"/>
+      <c r="BR8" s="28"/>
+      <c r="BS8" s="28"/>
+      <c r="BT8" s="28"/>
+      <c r="BU8" s="28"/>
+      <c r="BV8" s="28"/>
+      <c r="BW8" s="28"/>
+      <c r="BX8" s="28"/>
+      <c r="BY8" s="28"/>
+      <c r="BZ8" s="29"/>
+      <c r="CA8" s="30" t="s">
         <v>5</v>
       </c>
-      <c r="BH6" s="10">
+      <c r="CB8" s="28"/>
+      <c r="CC8" s="28"/>
+      <c r="CD8" s="28"/>
+      <c r="CE8" s="28"/>
+      <c r="CF8" s="28"/>
+      <c r="CG8" s="28"/>
+      <c r="CH8" s="28"/>
+      <c r="CI8" s="28"/>
+      <c r="CJ8" s="28"/>
+      <c r="CK8" s="28"/>
+      <c r="CL8" s="28"/>
+      <c r="CM8" s="28"/>
+      <c r="CN8" s="28"/>
+      <c r="CO8" s="28"/>
+      <c r="CP8" s="28"/>
+      <c r="CQ8" s="28"/>
+      <c r="CR8" s="28"/>
+      <c r="CS8" s="28"/>
+      <c r="CT8" s="28"/>
+      <c r="CU8" s="28"/>
+      <c r="CV8" s="28"/>
+      <c r="CW8" s="28"/>
+      <c r="CX8" s="28"/>
+      <c r="CY8" s="28"/>
+      <c r="CZ8" s="28"/>
+      <c r="DA8" s="28"/>
+      <c r="DB8" s="28"/>
+      <c r="DC8" s="28"/>
+      <c r="DD8" s="29"/>
+    </row>
+    <row r="9" spans="1:108" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="36" t="s">
+        <v>24</v>
+      </c>
+      <c r="B9" s="9">
+        <v>16</v>
+      </c>
+      <c r="C9" s="5">
+        <v>17</v>
+      </c>
+      <c r="D9" s="5">
+        <v>18</v>
+      </c>
+      <c r="E9" s="5">
+        <v>19</v>
+      </c>
+      <c r="F9" s="5">
+        <v>20</v>
+      </c>
+      <c r="G9" s="5">
+        <v>21</v>
+      </c>
+      <c r="H9" s="6">
+        <v>22</v>
+      </c>
+      <c r="I9" s="7">
+        <v>23</v>
+      </c>
+      <c r="J9" s="2">
+        <v>24</v>
+      </c>
+      <c r="K9" s="2">
+        <v>25</v>
+      </c>
+      <c r="L9" s="2">
+        <v>26</v>
+      </c>
+      <c r="M9" s="2">
+        <v>27</v>
+      </c>
+      <c r="N9" s="2">
+        <v>28</v>
+      </c>
+      <c r="O9" s="3">
+        <v>29</v>
+      </c>
+      <c r="P9" s="4">
+        <v>30</v>
+      </c>
+      <c r="Q9" s="8">
+        <v>31</v>
+      </c>
+      <c r="R9" s="9">
+        <v>1</v>
+      </c>
+      <c r="S9" s="5">
+        <v>2</v>
+      </c>
+      <c r="T9" s="10">
+        <v>3</v>
+      </c>
+      <c r="U9" s="10">
+        <v>4</v>
+      </c>
+      <c r="V9" s="6">
+        <v>5</v>
+      </c>
+      <c r="W9" s="7">
         <v>6</v>
       </c>
-      <c r="BI6" s="10">
+      <c r="X9" s="2">
         <v>7</v>
       </c>
-      <c r="BJ6" s="10">
+      <c r="Y9" s="2">
         <v>8</v>
       </c>
-      <c r="BK6" s="10">
+      <c r="Z9" s="2">
         <v>9</v>
       </c>
-      <c r="BL6" s="11">
+      <c r="AA9" s="2">
         <v>10</v>
       </c>
-      <c r="BM6" s="12">
+      <c r="AB9" s="2">
         <v>11</v>
       </c>
-      <c r="BN6" s="13">
+      <c r="AC9" s="3">
         <v>12</v>
       </c>
-      <c r="BO6" s="13">
+      <c r="AD9" s="4">
         <v>13</v>
       </c>
-      <c r="BP6" s="13">
+      <c r="AE9" s="5">
         <v>14</v>
       </c>
-      <c r="BQ6" s="13">
+      <c r="AF9" s="5">
         <v>15</v>
       </c>
-      <c r="BR6" s="13">
+      <c r="AG9" s="5">
         <v>16</v>
       </c>
-      <c r="BS6" s="14">
+      <c r="AH9" s="5">
         <v>17</v>
       </c>
-      <c r="BT6" s="15">
+      <c r="AI9" s="5">
         <v>18</v>
       </c>
-      <c r="BU6" s="10">
+      <c r="AJ9" s="6">
         <v>19</v>
       </c>
-      <c r="BV6" s="10">
+      <c r="AK9" s="7">
         <v>20</v>
       </c>
-      <c r="BW6" s="20">
+      <c r="AL9" s="2">
         <v>21</v>
       </c>
-      <c r="BX6" s="10">
+      <c r="AM9" s="2">
         <v>22</v>
       </c>
-      <c r="BY6" s="10">
+      <c r="AN9" s="2">
         <v>23</v>
       </c>
-      <c r="BZ6" s="11">
+      <c r="AO9" s="2">
         <v>24</v>
       </c>
-      <c r="CA6" s="12">
+      <c r="AP9" s="2">
         <v>25</v>
       </c>
-      <c r="CB6" s="13">
+      <c r="AQ9" s="3">
         <v>26</v>
       </c>
-      <c r="CC6" s="13">
+      <c r="AR9" s="4">
         <v>27</v>
       </c>
-      <c r="CD6" s="13">
+      <c r="AS9" s="5">
         <v>28</v>
       </c>
-      <c r="CE6" s="13">
+      <c r="AT9" s="5">
         <v>29</v>
       </c>
-      <c r="CF6" s="13">
+      <c r="AU9" s="8">
         <v>30</v>
       </c>
-      <c r="CG6" s="21">
+      <c r="AV9" s="11">
+        <v>1</v>
+      </c>
+      <c r="AW9" s="5">
+        <v>2</v>
+      </c>
+      <c r="AX9" s="6">
+        <v>3</v>
+      </c>
+      <c r="AY9" s="7">
+        <v>4</v>
+      </c>
+      <c r="AZ9" s="2">
+        <v>5</v>
+      </c>
+      <c r="BA9" s="2">
+        <v>6</v>
+      </c>
+      <c r="BB9" s="2">
+        <v>7</v>
+      </c>
+      <c r="BC9" s="2">
+        <v>8</v>
+      </c>
+      <c r="BD9" s="2">
+        <v>9</v>
+      </c>
+      <c r="BE9" s="3">
+        <v>10</v>
+      </c>
+      <c r="BF9" s="4">
+        <v>11</v>
+      </c>
+      <c r="BG9" s="5">
+        <v>12</v>
+      </c>
+      <c r="BH9" s="5">
+        <v>13</v>
+      </c>
+      <c r="BI9" s="5">
+        <v>14</v>
+      </c>
+      <c r="BJ9" s="5">
+        <v>15</v>
+      </c>
+      <c r="BK9" s="5">
+        <v>16</v>
+      </c>
+      <c r="BL9" s="6">
+        <v>17</v>
+      </c>
+      <c r="BM9" s="7">
+        <v>18</v>
+      </c>
+      <c r="BN9" s="2">
+        <v>19</v>
+      </c>
+      <c r="BO9" s="2">
+        <v>20</v>
+      </c>
+      <c r="BP9" s="12">
+        <v>21</v>
+      </c>
+      <c r="BQ9" s="2">
+        <v>22</v>
+      </c>
+      <c r="BR9" s="2">
+        <v>23</v>
+      </c>
+      <c r="BS9" s="3">
+        <v>24</v>
+      </c>
+      <c r="BT9" s="4">
+        <v>25</v>
+      </c>
+      <c r="BU9" s="5">
+        <v>26</v>
+      </c>
+      <c r="BV9" s="5">
+        <v>27</v>
+      </c>
+      <c r="BW9" s="5">
+        <v>28</v>
+      </c>
+      <c r="BX9" s="5">
+        <v>29</v>
+      </c>
+      <c r="BY9" s="5">
+        <v>30</v>
+      </c>
+      <c r="BZ9" s="13">
         <v>31</v>
       </c>
-      <c r="CH6" s="9">
+      <c r="CA9" s="1">
         <v>1</v>
       </c>
-      <c r="CI6" s="10">
+      <c r="CB9" s="2">
         <v>2</v>
       </c>
-      <c r="CJ6" s="10">
+      <c r="CC9" s="2">
         <v>3</v>
       </c>
-      <c r="CK6" s="10">
+      <c r="CD9" s="2">
         <v>4</v>
       </c>
-      <c r="CL6" s="10">
+      <c r="CE9" s="2">
         <v>5</v>
       </c>
-      <c r="CM6" s="10">
+      <c r="CF9" s="2">
         <v>6</v>
       </c>
-      <c r="CN6" s="11">
+      <c r="CG9" s="3">
         <v>7</v>
       </c>
-      <c r="CO6" s="12">
+      <c r="CH9" s="4">
         <v>8</v>
       </c>
-      <c r="CP6" s="13">
+      <c r="CI9" s="5">
         <v>9</v>
       </c>
-      <c r="CQ6" s="13">
+      <c r="CJ9" s="5">
         <v>10</v>
       </c>
-      <c r="CR6" s="13">
+      <c r="CK9" s="5">
         <v>11</v>
       </c>
-      <c r="CS6" s="13">
+      <c r="CL9" s="5">
         <v>12</v>
       </c>
-      <c r="CT6" s="13">
+      <c r="CM9" s="5">
         <v>13</v>
       </c>
-      <c r="CU6" s="14">
+      <c r="CN9" s="6">
         <v>14</v>
       </c>
-      <c r="CV6" s="15">
+      <c r="CO9" s="7">
         <v>15</v>
       </c>
-      <c r="CW6" s="10">
+      <c r="CP9" s="2">
         <v>16</v>
       </c>
-      <c r="CX6" s="10">
+      <c r="CQ9" s="2">
         <v>17</v>
       </c>
-      <c r="CY6" s="10">
+      <c r="CR9" s="2">
         <v>18</v>
       </c>
-      <c r="CZ6" s="10">
+      <c r="CS9" s="2">
         <v>19</v>
       </c>
-      <c r="DA6" s="10">
+      <c r="CT9" s="2">
         <v>20</v>
       </c>
-      <c r="DB6" s="11">
+      <c r="CU9" s="3">
         <v>21</v>
       </c>
-      <c r="DC6" s="12">
+      <c r="CV9" s="4">
         <v>22</v>
       </c>
-      <c r="DD6" s="13">
+      <c r="CW9" s="5">
         <v>23</v>
       </c>
-      <c r="DE6" s="13">
+      <c r="CX9" s="5">
         <v>24</v>
       </c>
-      <c r="DF6" s="13">
+      <c r="CY9" s="5">
         <v>25</v>
       </c>
-      <c r="DG6" s="13">
+      <c r="CZ9" s="5">
         <v>26</v>
       </c>
-      <c r="DH6" s="13">
+      <c r="DA9" s="5">
         <v>27</v>
       </c>
-      <c r="DI6" s="14">
+      <c r="DB9" s="6">
         <v>28</v>
       </c>
-      <c r="DJ6" s="22">
+      <c r="DC9" s="14">
         <v>29</v>
       </c>
-      <c r="DK6" s="23">
+      <c r="DD9" s="15">
         <v>30</v>
       </c>
     </row>
-    <row r="8" spans="1:115" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
+    <row r="10" spans="1:108" x14ac:dyDescent="0.2">
+      <c r="B10" s="16"/>
+      <c r="H10" s="18"/>
+      <c r="I10" s="16"/>
+      <c r="O10" s="18"/>
+      <c r="P10" s="16"/>
+      <c r="V10" s="18"/>
+      <c r="W10" s="16"/>
+      <c r="AC10" s="18"/>
+      <c r="AD10" s="16"/>
+      <c r="AJ10" s="18"/>
+      <c r="AK10" s="16"/>
+      <c r="AQ10" s="18"/>
+      <c r="AR10" s="16"/>
+      <c r="AX10" s="18"/>
+      <c r="AY10" s="16"/>
+      <c r="BE10" s="18"/>
+      <c r="BF10" s="16"/>
+      <c r="BL10" s="18"/>
+      <c r="BM10" s="16"/>
+      <c r="BS10" s="18"/>
+      <c r="BT10" s="16"/>
+      <c r="BZ10" s="18"/>
+      <c r="CA10" s="16"/>
+      <c r="CG10" s="18"/>
+      <c r="CH10" s="16"/>
+      <c r="CN10" s="18"/>
+      <c r="CO10" s="16"/>
+      <c r="CU10" s="18"/>
+      <c r="CV10" s="16"/>
+      <c r="DB10" s="18"/>
+      <c r="DC10" s="16"/>
+      <c r="DD10" s="18"/>
+    </row>
+    <row r="11" spans="1:108" x14ac:dyDescent="0.2">
+      <c r="A11" s="17" t="s">
+        <v>1</v>
+      </c>
+      <c r="B11" s="22"/>
+      <c r="C11" s="23"/>
+      <c r="D11" s="23"/>
+      <c r="E11" s="23"/>
+      <c r="F11" s="23"/>
+      <c r="G11" s="23"/>
+      <c r="H11" s="24"/>
+      <c r="I11" s="16"/>
+      <c r="O11" s="18"/>
+      <c r="P11" s="16"/>
+      <c r="V11" s="18"/>
+      <c r="W11" s="16"/>
+      <c r="AC11" s="18"/>
+      <c r="AD11" s="16"/>
+      <c r="AJ11" s="18"/>
+      <c r="AK11" s="16"/>
+      <c r="AQ11" s="18"/>
+      <c r="AR11" s="16"/>
+      <c r="AX11" s="18"/>
+      <c r="AY11" s="16"/>
+      <c r="BE11" s="18"/>
+      <c r="BF11" s="16"/>
+      <c r="BL11" s="18"/>
+      <c r="BM11" s="16"/>
+      <c r="BS11" s="18"/>
+      <c r="BT11" s="16"/>
+      <c r="BZ11" s="18"/>
+      <c r="CA11" s="16"/>
+      <c r="CG11" s="18"/>
+      <c r="CH11" s="16"/>
+      <c r="CN11" s="18"/>
+      <c r="CO11" s="16"/>
+      <c r="CU11" s="18"/>
+      <c r="CV11" s="16"/>
+      <c r="DB11" s="18"/>
+      <c r="DC11" s="16"/>
+      <c r="DD11" s="18"/>
+    </row>
+    <row r="12" spans="1:108" x14ac:dyDescent="0.2">
+      <c r="A12" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="B12" s="16"/>
+      <c r="H12" s="18"/>
+      <c r="I12" s="22"/>
+      <c r="J12" s="23"/>
+      <c r="K12" s="23"/>
+      <c r="L12" s="23"/>
+      <c r="M12" s="23"/>
+      <c r="N12" s="23"/>
+      <c r="O12" s="24"/>
+      <c r="P12" s="16"/>
+      <c r="V12" s="18"/>
+      <c r="W12" s="16"/>
+      <c r="AC12" s="18"/>
+      <c r="AD12" s="16"/>
+      <c r="AJ12" s="18"/>
+      <c r="AK12" s="16"/>
+      <c r="AQ12" s="18"/>
+      <c r="AR12" s="16"/>
+      <c r="AX12" s="18"/>
+      <c r="AY12" s="16"/>
+      <c r="BE12" s="18"/>
+      <c r="BF12" s="16"/>
+      <c r="BL12" s="18"/>
+      <c r="BM12" s="16"/>
+      <c r="BS12" s="18"/>
+      <c r="BT12" s="16"/>
+      <c r="BZ12" s="18"/>
+      <c r="CA12" s="16"/>
+      <c r="CG12" s="18"/>
+      <c r="CH12" s="16"/>
+      <c r="CN12" s="18"/>
+      <c r="CO12" s="16"/>
+      <c r="CU12" s="18"/>
+      <c r="CV12" s="16"/>
+      <c r="DB12" s="18"/>
+      <c r="DC12" s="16"/>
+      <c r="DD12" s="18"/>
+    </row>
+    <row r="13" spans="1:108" x14ac:dyDescent="0.2">
+      <c r="A13" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="B13" s="16"/>
+      <c r="H13" s="18"/>
+      <c r="I13" s="16"/>
+      <c r="O13" s="18"/>
+      <c r="P13" s="22"/>
+      <c r="Q13" s="23"/>
+      <c r="R13" s="23"/>
+      <c r="S13" s="23"/>
+      <c r="T13" s="23"/>
+      <c r="U13" s="23"/>
+      <c r="V13" s="24"/>
+      <c r="W13" s="16"/>
+      <c r="AC13" s="18"/>
+      <c r="AD13" s="16"/>
+      <c r="AJ13" s="18"/>
+      <c r="AK13" s="16"/>
+      <c r="AQ13" s="18"/>
+      <c r="AR13" s="16"/>
+      <c r="AX13" s="18"/>
+      <c r="AY13" s="16"/>
+      <c r="BE13" s="18"/>
+      <c r="BF13" s="16"/>
+      <c r="BL13" s="18"/>
+      <c r="BM13" s="16"/>
+      <c r="BS13" s="18"/>
+      <c r="BT13" s="16"/>
+      <c r="BZ13" s="18"/>
+      <c r="CA13" s="16"/>
+      <c r="CG13" s="18"/>
+      <c r="CH13" s="16"/>
+      <c r="CN13" s="18"/>
+      <c r="CO13" s="16"/>
+      <c r="CU13" s="18"/>
+      <c r="CV13" s="16"/>
+      <c r="DB13" s="18"/>
+      <c r="DC13" s="16"/>
+      <c r="DD13" s="18"/>
+    </row>
+    <row r="14" spans="1:108" x14ac:dyDescent="0.2">
+      <c r="A14" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="5"/>
-      <c r="C8" s="5"/>
-      <c r="D8" s="5"/>
-      <c r="E8" s="5"/>
-      <c r="F8" s="5"/>
-      <c r="G8" s="5"/>
-      <c r="H8" s="5"/>
-    </row>
-    <row r="9" spans="1:115" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
+      <c r="B14" s="16"/>
+      <c r="H14" s="18"/>
+      <c r="I14" s="16"/>
+      <c r="O14" s="18"/>
+      <c r="P14" s="22"/>
+      <c r="Q14" s="23"/>
+      <c r="R14" s="23"/>
+      <c r="S14" s="23"/>
+      <c r="T14" s="23"/>
+      <c r="U14" s="23"/>
+      <c r="V14" s="24"/>
+      <c r="W14" s="16"/>
+      <c r="AC14" s="18"/>
+      <c r="AD14" s="16"/>
+      <c r="AJ14" s="18"/>
+      <c r="AK14" s="16"/>
+      <c r="AQ14" s="18"/>
+      <c r="AR14" s="16"/>
+      <c r="AX14" s="18"/>
+      <c r="AY14" s="16"/>
+      <c r="BE14" s="18"/>
+      <c r="BF14" s="16"/>
+      <c r="BL14" s="18"/>
+      <c r="BM14" s="16"/>
+      <c r="BS14" s="18"/>
+      <c r="BT14" s="16"/>
+      <c r="BZ14" s="18"/>
+      <c r="CA14" s="16"/>
+      <c r="CG14" s="18"/>
+      <c r="CH14" s="16"/>
+      <c r="CN14" s="18"/>
+      <c r="CO14" s="16"/>
+      <c r="CU14" s="18"/>
+      <c r="CV14" s="16"/>
+      <c r="DB14" s="18"/>
+      <c r="DC14" s="16"/>
+      <c r="DD14" s="18"/>
+    </row>
+    <row r="15" spans="1:108" x14ac:dyDescent="0.2">
+      <c r="A15" s="17" t="s">
+        <v>8</v>
+      </c>
+      <c r="B15" s="16"/>
+      <c r="H15" s="18"/>
+      <c r="I15" s="16"/>
+      <c r="O15" s="18"/>
+      <c r="P15" s="16"/>
+      <c r="V15" s="18"/>
+      <c r="W15" s="22"/>
+      <c r="X15" s="23"/>
+      <c r="Y15" s="23"/>
+      <c r="Z15" s="23"/>
+      <c r="AA15" s="23"/>
+      <c r="AB15" s="23"/>
+      <c r="AC15" s="24"/>
+      <c r="AD15" s="16"/>
+      <c r="AJ15" s="18"/>
+      <c r="AK15" s="16"/>
+      <c r="AQ15" s="18"/>
+      <c r="AR15" s="16"/>
+      <c r="AX15" s="18"/>
+      <c r="AY15" s="16"/>
+      <c r="BE15" s="18"/>
+      <c r="BF15" s="16"/>
+      <c r="BL15" s="18"/>
+      <c r="BM15" s="16"/>
+      <c r="BS15" s="18"/>
+      <c r="BT15" s="16"/>
+      <c r="BZ15" s="18"/>
+      <c r="CA15" s="16"/>
+      <c r="CG15" s="18"/>
+      <c r="CH15" s="16"/>
+      <c r="CN15" s="18"/>
+      <c r="CO15" s="16"/>
+      <c r="CU15" s="18"/>
+      <c r="CV15" s="16"/>
+      <c r="DB15" s="18"/>
+      <c r="DC15" s="16"/>
+      <c r="DD15" s="18"/>
+    </row>
+    <row r="16" spans="1:108" x14ac:dyDescent="0.2">
+      <c r="A16" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="B16" s="16"/>
+      <c r="H16" s="18"/>
+      <c r="I16" s="16"/>
+      <c r="O16" s="18"/>
+      <c r="P16" s="16"/>
+      <c r="V16" s="18"/>
+      <c r="W16" s="16"/>
+      <c r="AC16" s="18"/>
+      <c r="AD16" s="22"/>
+      <c r="AE16" s="23"/>
+      <c r="AF16" s="23"/>
+      <c r="AG16" s="23"/>
+      <c r="AH16" s="23"/>
+      <c r="AI16" s="23"/>
+      <c r="AJ16" s="24"/>
+      <c r="AK16" s="16"/>
+      <c r="AQ16" s="18"/>
+      <c r="AR16" s="16"/>
+      <c r="AX16" s="18"/>
+      <c r="AY16" s="16"/>
+      <c r="BE16" s="18"/>
+      <c r="BF16" s="16"/>
+      <c r="BL16" s="18"/>
+      <c r="BM16" s="16"/>
+      <c r="BS16" s="18"/>
+      <c r="BT16" s="16"/>
+      <c r="BZ16" s="18"/>
+      <c r="CA16" s="16"/>
+      <c r="CG16" s="18"/>
+      <c r="CH16" s="16"/>
+      <c r="CN16" s="18"/>
+      <c r="CO16" s="16"/>
+      <c r="CU16" s="18"/>
+      <c r="CV16" s="16"/>
+      <c r="DB16" s="18"/>
+      <c r="DC16" s="16"/>
+      <c r="DD16" s="18"/>
+    </row>
+    <row r="17" spans="1:108" x14ac:dyDescent="0.2">
+      <c r="A17" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="B17" s="16"/>
+      <c r="H17" s="18"/>
+      <c r="I17" s="16"/>
+      <c r="O17" s="18"/>
+      <c r="P17" s="16"/>
+      <c r="V17" s="18"/>
+      <c r="W17" s="16"/>
+      <c r="AC17" s="18"/>
+      <c r="AD17" s="16"/>
+      <c r="AJ17" s="18"/>
+      <c r="AK17" s="22"/>
+      <c r="AL17" s="23"/>
+      <c r="AM17" s="23"/>
+      <c r="AN17" s="23"/>
+      <c r="AO17" s="23"/>
+      <c r="AP17" s="23"/>
+      <c r="AQ17" s="24"/>
+      <c r="AR17" s="16"/>
+      <c r="AX17" s="18"/>
+      <c r="AY17" s="16"/>
+      <c r="BE17" s="18"/>
+      <c r="BF17" s="16"/>
+      <c r="BL17" s="18"/>
+      <c r="BM17" s="16"/>
+      <c r="BS17" s="18"/>
+      <c r="BT17" s="16"/>
+      <c r="BZ17" s="18"/>
+      <c r="CA17" s="16"/>
+      <c r="CG17" s="18"/>
+      <c r="CH17" s="16"/>
+      <c r="CN17" s="18"/>
+      <c r="CO17" s="16"/>
+      <c r="CU17" s="18"/>
+      <c r="CV17" s="16"/>
+      <c r="DB17" s="18"/>
+      <c r="DC17" s="16"/>
+      <c r="DD17" s="18"/>
+    </row>
+    <row r="18" spans="1:108" x14ac:dyDescent="0.2">
+      <c r="A18" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="B18" s="16"/>
+      <c r="H18" s="18"/>
+      <c r="I18" s="16"/>
+      <c r="O18" s="18"/>
+      <c r="P18" s="16"/>
+      <c r="V18" s="18"/>
+      <c r="W18" s="16"/>
+      <c r="AC18" s="18"/>
+      <c r="AD18" s="16"/>
+      <c r="AJ18" s="18"/>
+      <c r="AK18" s="22"/>
+      <c r="AL18" s="23"/>
+      <c r="AM18" s="23"/>
+      <c r="AN18" s="23"/>
+      <c r="AO18" s="23"/>
+      <c r="AP18" s="23"/>
+      <c r="AQ18" s="24"/>
+      <c r="AR18" s="22"/>
+      <c r="AS18" s="23"/>
+      <c r="AT18" s="23"/>
+      <c r="AU18" s="23"/>
+      <c r="AV18" s="23"/>
+      <c r="AW18" s="23"/>
+      <c r="AX18" s="24"/>
+      <c r="AY18" s="22"/>
+      <c r="AZ18" s="23"/>
+      <c r="BA18" s="23"/>
+      <c r="BB18" s="23"/>
+      <c r="BC18" s="23"/>
+      <c r="BD18" s="23"/>
+      <c r="BE18" s="24"/>
+      <c r="BF18" s="16"/>
+      <c r="BL18" s="18"/>
+      <c r="BM18" s="16"/>
+      <c r="BS18" s="18"/>
+      <c r="BT18" s="16"/>
+      <c r="BZ18" s="18"/>
+      <c r="CA18" s="16"/>
+      <c r="CG18" s="18"/>
+      <c r="CH18" s="16"/>
+      <c r="CN18" s="18"/>
+      <c r="CO18" s="16"/>
+      <c r="CU18" s="18"/>
+      <c r="CV18" s="16"/>
+      <c r="DB18" s="18"/>
+      <c r="DC18" s="16"/>
+      <c r="DD18" s="18"/>
+    </row>
+    <row r="19" spans="1:108" x14ac:dyDescent="0.2">
+      <c r="A19" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="B19" s="16"/>
+      <c r="H19" s="18"/>
+      <c r="I19" s="16"/>
+      <c r="O19" s="18"/>
+      <c r="P19" s="16"/>
+      <c r="V19" s="18"/>
+      <c r="W19" s="16"/>
+      <c r="AC19" s="18"/>
+      <c r="AD19" s="16"/>
+      <c r="AJ19" s="18"/>
+      <c r="AK19" s="22"/>
+      <c r="AL19" s="23"/>
+      <c r="AM19" s="23"/>
+      <c r="AN19" s="23"/>
+      <c r="AO19" s="23"/>
+      <c r="AP19" s="23"/>
+      <c r="AQ19" s="24"/>
+      <c r="AR19" s="22"/>
+      <c r="AS19" s="23"/>
+      <c r="AT19" s="23"/>
+      <c r="AU19" s="23"/>
+      <c r="AV19" s="23"/>
+      <c r="AW19" s="23"/>
+      <c r="AX19" s="24"/>
+      <c r="AY19" s="22"/>
+      <c r="AZ19" s="23"/>
+      <c r="BA19" s="23"/>
+      <c r="BB19" s="23"/>
+      <c r="BC19" s="23"/>
+      <c r="BD19" s="23"/>
+      <c r="BE19" s="24"/>
+      <c r="BF19" s="16"/>
+      <c r="BL19" s="18"/>
+      <c r="BM19" s="16"/>
+      <c r="BS19" s="18"/>
+      <c r="BT19" s="16"/>
+      <c r="BZ19" s="18"/>
+      <c r="CA19" s="16"/>
+      <c r="CG19" s="18"/>
+      <c r="CH19" s="16"/>
+      <c r="CN19" s="18"/>
+      <c r="CO19" s="16"/>
+      <c r="CU19" s="18"/>
+      <c r="CV19" s="16"/>
+      <c r="DB19" s="18"/>
+      <c r="DC19" s="16"/>
+      <c r="DD19" s="18"/>
+    </row>
+    <row r="20" spans="1:108" x14ac:dyDescent="0.2">
+      <c r="A20" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="B20" s="16"/>
+      <c r="H20" s="18"/>
+      <c r="I20" s="16"/>
+      <c r="O20" s="18"/>
+      <c r="P20" s="16"/>
+      <c r="V20" s="18"/>
+      <c r="W20" s="16"/>
+      <c r="AC20" s="18"/>
+      <c r="AD20" s="16"/>
+      <c r="AJ20" s="18"/>
+      <c r="AK20" s="16"/>
+      <c r="AQ20" s="18"/>
+      <c r="AR20" s="22"/>
+      <c r="AS20" s="23"/>
+      <c r="AT20" s="23"/>
+      <c r="AU20" s="23"/>
+      <c r="AV20" s="23"/>
+      <c r="AW20" s="23"/>
+      <c r="AX20" s="24"/>
+      <c r="AY20" s="16"/>
+      <c r="BE20" s="18"/>
+      <c r="BF20" s="16"/>
+      <c r="BL20" s="18"/>
+      <c r="BM20" s="16"/>
+      <c r="BS20" s="18"/>
+      <c r="BT20" s="16"/>
+      <c r="BZ20" s="18"/>
+      <c r="CA20" s="16"/>
+      <c r="CG20" s="18"/>
+      <c r="CH20" s="16"/>
+      <c r="CN20" s="18"/>
+      <c r="CO20" s="16"/>
+      <c r="CU20" s="18"/>
+      <c r="CV20" s="16"/>
+      <c r="DB20" s="18"/>
+      <c r="DC20" s="16"/>
+      <c r="DD20" s="18"/>
+    </row>
+    <row r="21" spans="1:108" x14ac:dyDescent="0.2">
+      <c r="A21" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="B21" s="16"/>
+      <c r="H21" s="18"/>
+      <c r="I21" s="16"/>
+      <c r="O21" s="18"/>
+      <c r="P21" s="16"/>
+      <c r="V21" s="18"/>
+      <c r="W21" s="16"/>
+      <c r="AC21" s="18"/>
+      <c r="AD21" s="16"/>
+      <c r="AJ21" s="18"/>
+      <c r="AK21" s="16"/>
+      <c r="AQ21" s="18"/>
+      <c r="AR21" s="16"/>
+      <c r="AX21" s="18"/>
+      <c r="AY21" s="16"/>
+      <c r="BE21" s="18"/>
+      <c r="BF21" s="22"/>
+      <c r="BG21" s="23"/>
+      <c r="BH21" s="23"/>
+      <c r="BI21" s="23"/>
+      <c r="BJ21" s="23"/>
+      <c r="BK21" s="23"/>
+      <c r="BL21" s="24"/>
+      <c r="BM21" s="16"/>
+      <c r="BS21" s="18"/>
+      <c r="BT21" s="16"/>
+      <c r="BZ21" s="18"/>
+      <c r="CA21" s="16"/>
+      <c r="CG21" s="18"/>
+      <c r="CH21" s="16"/>
+      <c r="CN21" s="18"/>
+      <c r="CO21" s="16"/>
+      <c r="CU21" s="18"/>
+      <c r="CV21" s="16"/>
+      <c r="DB21" s="18"/>
+      <c r="DC21" s="16"/>
+      <c r="DD21" s="18"/>
+    </row>
+    <row r="22" spans="1:108" x14ac:dyDescent="0.2">
+      <c r="A22" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="B22" s="16"/>
+      <c r="H22" s="18"/>
+      <c r="I22" s="16"/>
+      <c r="O22" s="18"/>
+      <c r="P22" s="16"/>
+      <c r="V22" s="18"/>
+      <c r="W22" s="16"/>
+      <c r="AC22" s="18"/>
+      <c r="AD22" s="16"/>
+      <c r="AJ22" s="18"/>
+      <c r="AK22" s="16"/>
+      <c r="AQ22" s="18"/>
+      <c r="AR22" s="16"/>
+      <c r="AX22" s="18"/>
+      <c r="AY22" s="16"/>
+      <c r="BE22" s="18"/>
+      <c r="BF22" s="22"/>
+      <c r="BG22" s="23"/>
+      <c r="BH22" s="23"/>
+      <c r="BI22" s="23"/>
+      <c r="BJ22" s="23"/>
+      <c r="BK22" s="23"/>
+      <c r="BL22" s="24"/>
+      <c r="BM22" s="16"/>
+      <c r="BS22" s="18"/>
+      <c r="BT22" s="16"/>
+      <c r="BZ22" s="18"/>
+      <c r="CA22" s="16"/>
+      <c r="CG22" s="18"/>
+      <c r="CH22" s="16"/>
+      <c r="CN22" s="18"/>
+      <c r="CO22" s="16"/>
+      <c r="CU22" s="18"/>
+      <c r="CV22" s="16"/>
+      <c r="DB22" s="18"/>
+      <c r="DC22" s="16"/>
+      <c r="DD22" s="18"/>
+    </row>
+    <row r="23" spans="1:108" x14ac:dyDescent="0.2">
+      <c r="A23" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="B23" s="16"/>
+      <c r="H23" s="18"/>
+      <c r="I23" s="16"/>
+      <c r="O23" s="18"/>
+      <c r="P23" s="16"/>
+      <c r="V23" s="18"/>
+      <c r="W23" s="16"/>
+      <c r="AC23" s="18"/>
+      <c r="AD23" s="16"/>
+      <c r="AJ23" s="18"/>
+      <c r="AK23" s="16"/>
+      <c r="AQ23" s="18"/>
+      <c r="AR23" s="16"/>
+      <c r="AX23" s="18"/>
+      <c r="AY23" s="16"/>
+      <c r="BE23" s="18"/>
+      <c r="BF23" s="16"/>
+      <c r="BL23" s="18"/>
+      <c r="BM23" s="22"/>
+      <c r="BN23" s="23"/>
+      <c r="BO23" s="23"/>
+      <c r="BP23" s="23"/>
+      <c r="BQ23" s="23"/>
+      <c r="BR23" s="23"/>
+      <c r="BS23" s="24"/>
+      <c r="BT23" s="22"/>
+      <c r="BU23" s="23"/>
+      <c r="BV23" s="23"/>
+      <c r="BW23" s="23"/>
+      <c r="BX23" s="23"/>
+      <c r="BY23" s="23"/>
+      <c r="BZ23" s="24"/>
+      <c r="CA23" s="22"/>
+      <c r="CB23" s="23"/>
+      <c r="CC23" s="23"/>
+      <c r="CD23" s="23"/>
+      <c r="CE23" s="23"/>
+      <c r="CF23" s="23"/>
+      <c r="CG23" s="24"/>
+      <c r="CH23" s="22"/>
+      <c r="CI23" s="23"/>
+      <c r="CJ23" s="23"/>
+      <c r="CK23" s="23"/>
+      <c r="CL23" s="23"/>
+      <c r="CM23" s="23"/>
+      <c r="CN23" s="24"/>
+      <c r="CO23" s="16"/>
+      <c r="CU23" s="18"/>
+      <c r="CV23" s="16"/>
+      <c r="DB23" s="18"/>
+      <c r="DC23" s="16"/>
+      <c r="DD23" s="18"/>
+    </row>
+    <row r="24" spans="1:108" x14ac:dyDescent="0.2">
+      <c r="A24" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="B24" s="16"/>
+      <c r="H24" s="18"/>
+      <c r="I24" s="16"/>
+      <c r="O24" s="18"/>
+      <c r="P24" s="16"/>
+      <c r="V24" s="18"/>
+      <c r="W24" s="16"/>
+      <c r="AC24" s="18"/>
+      <c r="AD24" s="16"/>
+      <c r="AJ24" s="18"/>
+      <c r="AK24" s="16"/>
+      <c r="AQ24" s="18"/>
+      <c r="AR24" s="16"/>
+      <c r="AX24" s="18"/>
+      <c r="AY24" s="16"/>
+      <c r="BE24" s="18"/>
+      <c r="BF24" s="16"/>
+      <c r="BL24" s="18"/>
+      <c r="BM24" s="22"/>
+      <c r="BN24" s="23"/>
+      <c r="BO24" s="23"/>
+      <c r="BP24" s="23"/>
+      <c r="BQ24" s="23"/>
+      <c r="BR24" s="23"/>
+      <c r="BS24" s="24"/>
+      <c r="BT24" s="22"/>
+      <c r="BU24" s="23"/>
+      <c r="BV24" s="23"/>
+      <c r="BW24" s="23"/>
+      <c r="BX24" s="23"/>
+      <c r="BY24" s="23"/>
+      <c r="BZ24" s="24"/>
+      <c r="CA24" s="22"/>
+      <c r="CB24" s="23"/>
+      <c r="CC24" s="23"/>
+      <c r="CD24" s="23"/>
+      <c r="CE24" s="23"/>
+      <c r="CF24" s="23"/>
+      <c r="CG24" s="24"/>
+      <c r="CH24" s="22"/>
+      <c r="CI24" s="23"/>
+      <c r="CJ24" s="23"/>
+      <c r="CK24" s="23"/>
+      <c r="CL24" s="23"/>
+      <c r="CM24" s="23"/>
+      <c r="CN24" s="24"/>
+      <c r="CO24" s="16"/>
+      <c r="CU24" s="18"/>
+      <c r="CV24" s="16"/>
+      <c r="DB24" s="18"/>
+      <c r="DC24" s="16"/>
+      <c r="DD24" s="18"/>
+    </row>
+    <row r="25" spans="1:108" x14ac:dyDescent="0.2">
+      <c r="A25" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="B25" s="16"/>
+      <c r="H25" s="18"/>
+      <c r="I25" s="16"/>
+      <c r="O25" s="18"/>
+      <c r="P25" s="16"/>
+      <c r="V25" s="18"/>
+      <c r="W25" s="16"/>
+      <c r="AC25" s="18"/>
+      <c r="AD25" s="16"/>
+      <c r="AJ25" s="18"/>
+      <c r="AK25" s="16"/>
+      <c r="AQ25" s="18"/>
+      <c r="AR25" s="16"/>
+      <c r="AX25" s="18"/>
+      <c r="AY25" s="16"/>
+      <c r="BE25" s="18"/>
+      <c r="BF25" s="16"/>
+      <c r="BL25" s="18"/>
+      <c r="BM25" s="16"/>
+      <c r="BS25" s="18"/>
+      <c r="BT25" s="16"/>
+      <c r="BZ25" s="18"/>
+      <c r="CA25" s="16"/>
+      <c r="CG25" s="18"/>
+      <c r="CH25" s="16"/>
+      <c r="CN25" s="18"/>
+      <c r="CO25" s="22"/>
+      <c r="CP25" s="23"/>
+      <c r="CQ25" s="23"/>
+      <c r="CR25" s="23"/>
+      <c r="CS25" s="23"/>
+      <c r="CT25" s="23"/>
+      <c r="CU25" s="24"/>
+      <c r="CV25" s="16"/>
+      <c r="DB25" s="18"/>
+      <c r="DC25" s="16"/>
+      <c r="DD25" s="18"/>
+    </row>
+    <row r="26" spans="1:108" x14ac:dyDescent="0.2">
+      <c r="A26" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="B26" s="16"/>
+      <c r="H26" s="18"/>
+      <c r="I26" s="16"/>
+      <c r="O26" s="18"/>
+      <c r="P26" s="16"/>
+      <c r="V26" s="18"/>
+      <c r="W26" s="16"/>
+      <c r="AC26" s="18"/>
+      <c r="AD26" s="16"/>
+      <c r="AJ26" s="18"/>
+      <c r="AK26" s="16"/>
+      <c r="AQ26" s="18"/>
+      <c r="AR26" s="16"/>
+      <c r="AX26" s="18"/>
+      <c r="AY26" s="16"/>
+      <c r="BE26" s="18"/>
+      <c r="BF26" s="16"/>
+      <c r="BL26" s="18"/>
+      <c r="BM26" s="16"/>
+      <c r="BS26" s="18"/>
+      <c r="BT26" s="16"/>
+      <c r="BZ26" s="18"/>
+      <c r="CA26" s="16"/>
+      <c r="CG26" s="18"/>
+      <c r="CH26" s="16"/>
+      <c r="CN26" s="18"/>
+      <c r="CO26" s="22"/>
+      <c r="CP26" s="23"/>
+      <c r="CQ26" s="23"/>
+      <c r="CR26" s="23"/>
+      <c r="CS26" s="23"/>
+      <c r="CT26" s="23"/>
+      <c r="CU26" s="24"/>
+      <c r="CV26" s="16"/>
+      <c r="DB26" s="18"/>
+      <c r="DC26" s="16"/>
+      <c r="DD26" s="18"/>
+    </row>
+    <row r="27" spans="1:108" x14ac:dyDescent="0.2">
+      <c r="A27" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="B27" s="16"/>
+      <c r="H27" s="18"/>
+      <c r="I27" s="16"/>
+      <c r="O27" s="18"/>
+      <c r="P27" s="16"/>
+      <c r="V27" s="18"/>
+      <c r="W27" s="16"/>
+      <c r="AC27" s="18"/>
+      <c r="AD27" s="16"/>
+      <c r="AJ27" s="18"/>
+      <c r="AK27" s="16"/>
+      <c r="AQ27" s="18"/>
+      <c r="AR27" s="16"/>
+      <c r="AX27" s="18"/>
+      <c r="AY27" s="16"/>
+      <c r="BE27" s="18"/>
+      <c r="BF27" s="16"/>
+      <c r="BL27" s="18"/>
+      <c r="BM27" s="16"/>
+      <c r="BS27" s="18"/>
+      <c r="BT27" s="16"/>
+      <c r="BZ27" s="18"/>
+      <c r="CA27" s="16"/>
+      <c r="CG27" s="18"/>
+      <c r="CH27" s="16"/>
+      <c r="CN27" s="18"/>
+      <c r="CO27" s="16"/>
+      <c r="CU27" s="18"/>
+      <c r="CV27" s="22"/>
+      <c r="CW27" s="23"/>
+      <c r="CX27" s="23"/>
+      <c r="CY27" s="23"/>
+      <c r="CZ27" s="23"/>
+      <c r="DA27" s="23"/>
+      <c r="DB27" s="24"/>
+      <c r="DC27" s="22"/>
+      <c r="DD27" s="24"/>
+    </row>
+    <row r="28" spans="1:108" x14ac:dyDescent="0.2">
+      <c r="A28" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="B28" s="16"/>
+      <c r="H28" s="18"/>
+      <c r="I28" s="16"/>
+      <c r="O28" s="18"/>
+      <c r="P28" s="16"/>
+      <c r="V28" s="18"/>
+      <c r="W28" s="16"/>
+      <c r="AC28" s="18"/>
+      <c r="AD28" s="16"/>
+      <c r="AJ28" s="18"/>
+      <c r="AK28" s="16"/>
+      <c r="AQ28" s="18"/>
+      <c r="AR28" s="16"/>
+      <c r="AX28" s="18"/>
+      <c r="AY28" s="16"/>
+      <c r="BE28" s="18"/>
+      <c r="BF28" s="16"/>
+      <c r="BL28" s="18"/>
+      <c r="BM28" s="16"/>
+      <c r="BS28" s="18"/>
+      <c r="BT28" s="16"/>
+      <c r="BZ28" s="18"/>
+      <c r="CA28" s="16"/>
+      <c r="CG28" s="18"/>
+      <c r="CH28" s="16"/>
+      <c r="CN28" s="18"/>
+      <c r="CO28" s="16"/>
+      <c r="CU28" s="18"/>
+      <c r="CV28" s="22"/>
+      <c r="CW28" s="23"/>
+      <c r="CX28" s="23"/>
+      <c r="CY28" s="23"/>
+      <c r="CZ28" s="23"/>
+      <c r="DA28" s="23"/>
+      <c r="DB28" s="24"/>
+      <c r="DC28" s="22"/>
+      <c r="DD28" s="24"/>
+    </row>
+    <row r="29" spans="1:108" x14ac:dyDescent="0.2">
+      <c r="A29" s="37" t="s">
+        <v>21</v>
+      </c>
+      <c r="B29" s="19"/>
+      <c r="C29" s="20"/>
+      <c r="D29" s="20"/>
+      <c r="E29" s="20"/>
+      <c r="F29" s="20"/>
+      <c r="G29" s="20"/>
+      <c r="H29" s="21"/>
+      <c r="I29" s="19"/>
+      <c r="J29" s="20"/>
+      <c r="K29" s="20"/>
+      <c r="L29" s="20"/>
+      <c r="M29" s="20"/>
+      <c r="N29" s="20"/>
+      <c r="O29" s="21"/>
+      <c r="P29" s="19"/>
+      <c r="Q29" s="20"/>
+      <c r="R29" s="20"/>
+      <c r="S29" s="20"/>
+      <c r="T29" s="20"/>
+      <c r="U29" s="20"/>
+      <c r="V29" s="21"/>
+      <c r="W29" s="19"/>
+      <c r="X29" s="20"/>
+      <c r="Y29" s="20"/>
+      <c r="Z29" s="20"/>
+      <c r="AA29" s="20"/>
+      <c r="AB29" s="20"/>
+      <c r="AC29" s="21"/>
+      <c r="AD29" s="19"/>
+      <c r="AE29" s="20"/>
+      <c r="AF29" s="20"/>
+      <c r="AG29" s="20"/>
+      <c r="AH29" s="20"/>
+      <c r="AI29" s="20"/>
+      <c r="AJ29" s="21"/>
+      <c r="AK29" s="19"/>
+      <c r="AL29" s="20"/>
+      <c r="AM29" s="20"/>
+      <c r="AN29" s="20"/>
+      <c r="AO29" s="20"/>
+      <c r="AP29" s="20"/>
+      <c r="AQ29" s="21"/>
+      <c r="AR29" s="19"/>
+      <c r="AS29" s="20"/>
+      <c r="AT29" s="20"/>
+      <c r="AU29" s="20"/>
+      <c r="AV29" s="20"/>
+      <c r="AW29" s="20"/>
+      <c r="AX29" s="21"/>
+      <c r="AY29" s="19"/>
+      <c r="AZ29" s="20"/>
+      <c r="BA29" s="20"/>
+      <c r="BB29" s="20"/>
+      <c r="BC29" s="20"/>
+      <c r="BD29" s="20"/>
+      <c r="BE29" s="21"/>
+      <c r="BF29" s="19"/>
+      <c r="BG29" s="20"/>
+      <c r="BH29" s="20"/>
+      <c r="BI29" s="20"/>
+      <c r="BJ29" s="20"/>
+      <c r="BK29" s="20"/>
+      <c r="BL29" s="21"/>
+      <c r="BM29" s="19"/>
+      <c r="BN29" s="20"/>
+      <c r="BO29" s="20"/>
+      <c r="BP29" s="20"/>
+      <c r="BQ29" s="20"/>
+      <c r="BR29" s="20"/>
+      <c r="BS29" s="21"/>
+      <c r="BT29" s="19"/>
+      <c r="BU29" s="20"/>
+      <c r="BV29" s="20"/>
+      <c r="BW29" s="20"/>
+      <c r="BX29" s="20"/>
+      <c r="BY29" s="20"/>
+      <c r="BZ29" s="21"/>
+      <c r="CA29" s="19"/>
+      <c r="CB29" s="20"/>
+      <c r="CC29" s="20"/>
+      <c r="CD29" s="20"/>
+      <c r="CE29" s="20"/>
+      <c r="CF29" s="20"/>
+      <c r="CG29" s="21"/>
+      <c r="CH29" s="19"/>
+      <c r="CI29" s="20"/>
+      <c r="CJ29" s="20"/>
+      <c r="CK29" s="20"/>
+      <c r="CL29" s="20"/>
+      <c r="CM29" s="20"/>
+      <c r="CN29" s="21"/>
+      <c r="CO29" s="19"/>
+      <c r="CP29" s="20"/>
+      <c r="CQ29" s="20"/>
+      <c r="CR29" s="20"/>
+      <c r="CS29" s="20"/>
+      <c r="CT29" s="20"/>
+      <c r="CU29" s="21"/>
+      <c r="CV29" s="25"/>
+      <c r="CW29" s="26"/>
+      <c r="CX29" s="26"/>
+      <c r="CY29" s="26"/>
+      <c r="CZ29" s="26"/>
+      <c r="DA29" s="26"/>
+      <c r="DB29" s="27"/>
+      <c r="DC29" s="25"/>
+      <c r="DD29" s="27"/>
+    </row>
+    <row r="30" spans="1:108" x14ac:dyDescent="0.2">
+      <c r="A30" s="37"/>
+    </row>
+    <row r="31" spans="1:108" x14ac:dyDescent="0.2">
+      <c r="A31" s="37"/>
+    </row>
+    <row r="32" spans="1:108" x14ac:dyDescent="0.2">
+      <c r="A32" s="37"/>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A33" s="37"/>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A34" s="37"/>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A35" s="37"/>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A36" s="37"/>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A37" s="37"/>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A38" s="37"/>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A39" s="37"/>
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A40" s="37"/>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="B8:Q8"/>
+    <mergeCell ref="R8:AU8"/>
+    <mergeCell ref="AV8:BZ8"/>
+    <mergeCell ref="CA8:DD8"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D7CCD592-E217-46A0-898D-B6277524B4F3}">
+  <dimension ref="A1:BF52"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="20.88671875" style="17" bestFit="1" customWidth="1"/>
+    <col min="2" max="14" width="2.77734375" style="17" customWidth="1"/>
+    <col min="15" max="15" width="3.21875" style="17" bestFit="1" customWidth="1"/>
+    <col min="16" max="42" width="2.77734375" style="17" customWidth="1"/>
+    <col min="43" max="43" width="3.21875" style="17" bestFit="1" customWidth="1"/>
+    <col min="44" max="49" width="2.77734375" style="17" customWidth="1"/>
+    <col min="50" max="51" width="3.21875" style="17" bestFit="1" customWidth="1"/>
+    <col min="52" max="57" width="2.77734375" style="17" customWidth="1"/>
+    <col min="58" max="58" width="11.5546875" style="17"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:57" ht="20.25" x14ac:dyDescent="0.3">
+      <c r="A1" s="31" t="s">
+        <v>25</v>
+      </c>
+      <c r="B1" s="32"/>
+      <c r="C1" s="32"/>
+      <c r="D1" s="32"/>
+      <c r="E1" s="32"/>
+      <c r="F1" s="32"/>
+      <c r="G1" s="32"/>
+      <c r="H1" s="32"/>
+      <c r="I1" s="32"/>
+      <c r="J1" s="32"/>
+      <c r="K1" s="32"/>
+      <c r="L1" s="32"/>
+      <c r="M1" s="32"/>
+      <c r="N1" s="32"/>
+      <c r="O1" s="32"/>
+      <c r="P1" s="32"/>
+      <c r="Q1" s="32"/>
+    </row>
+    <row r="2" spans="1:57" ht="20.25" x14ac:dyDescent="0.3">
+      <c r="A2" s="31" t="s">
+        <v>26</v>
+      </c>
+      <c r="B2" s="32"/>
+      <c r="C2" s="32"/>
+      <c r="D2" s="32"/>
+      <c r="E2" s="32"/>
+      <c r="F2" s="32"/>
+      <c r="G2" s="32"/>
+      <c r="H2" s="32"/>
+      <c r="I2" s="32"/>
+      <c r="J2" s="32"/>
+      <c r="K2" s="32"/>
+      <c r="L2" s="32"/>
+      <c r="M2" s="32"/>
+      <c r="N2" s="32"/>
+      <c r="O2" s="32"/>
+      <c r="P2" s="32"/>
+      <c r="Q2" s="32"/>
+    </row>
+    <row r="3" spans="1:57" ht="20.25" x14ac:dyDescent="0.3">
+      <c r="A3" s="31">
+        <v>2026</v>
+      </c>
+      <c r="B3" s="32"/>
+      <c r="C3" s="32"/>
+      <c r="D3" s="32"/>
+      <c r="E3" s="32"/>
+      <c r="F3" s="32"/>
+      <c r="G3" s="32"/>
+      <c r="H3" s="32"/>
+      <c r="I3" s="32"/>
+      <c r="J3" s="32"/>
+      <c r="K3" s="32"/>
+      <c r="L3" s="32"/>
+      <c r="M3" s="32"/>
+      <c r="N3" s="32"/>
+      <c r="O3" s="32"/>
+      <c r="P3" s="32"/>
+      <c r="Q3" s="32"/>
+    </row>
+    <row r="4" spans="1:57" x14ac:dyDescent="0.2">
+      <c r="A4" s="33"/>
+      <c r="B4" s="33"/>
+      <c r="C4" s="33"/>
+      <c r="D4" s="33"/>
+      <c r="E4" s="33"/>
+      <c r="F4" s="33"/>
+      <c r="G4" s="33"/>
+      <c r="H4" s="33"/>
+      <c r="I4" s="33"/>
+      <c r="J4" s="33"/>
+      <c r="K4" s="33"/>
+      <c r="L4" s="33"/>
+      <c r="M4" s="33"/>
+      <c r="N4" s="33"/>
+      <c r="O4" s="33"/>
+      <c r="P4" s="33"/>
+      <c r="Q4" s="33"/>
+    </row>
+    <row r="5" spans="1:57" ht="18" x14ac:dyDescent="0.25">
+      <c r="A5" s="34" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" spans="1:57" ht="18" x14ac:dyDescent="0.25">
+      <c r="A6" s="34" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="7" spans="1:57" ht="15" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="8" spans="1:57" x14ac:dyDescent="0.2">
+      <c r="A8" s="35" t="s">
+        <v>0</v>
+      </c>
+      <c r="B8" s="30" t="s">
         <v>2</v>
       </c>
-      <c r="I9" s="5"/>
-      <c r="J9" s="5"/>
-      <c r="K9" s="5"/>
-      <c r="L9" s="5"/>
-      <c r="M9" s="5"/>
-      <c r="N9" s="5"/>
-      <c r="O9" s="5"/>
-    </row>
-    <row r="10" spans="1:115" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
+      <c r="C8" s="28"/>
+      <c r="D8" s="28"/>
+      <c r="E8" s="28"/>
+      <c r="F8" s="28"/>
+      <c r="G8" s="28"/>
+      <c r="H8" s="28"/>
+      <c r="I8" s="28"/>
+      <c r="J8" s="28"/>
+      <c r="K8" s="28"/>
+      <c r="L8" s="28"/>
+      <c r="M8" s="28"/>
+      <c r="N8" s="28"/>
+      <c r="O8" s="28"/>
+      <c r="P8" s="28"/>
+      <c r="Q8" s="29"/>
+      <c r="R8" s="30" t="s">
+        <v>3</v>
+      </c>
+      <c r="S8" s="28"/>
+      <c r="T8" s="28"/>
+      <c r="U8" s="28"/>
+      <c r="V8" s="28"/>
+      <c r="W8" s="28"/>
+      <c r="X8" s="28"/>
+      <c r="Y8" s="28"/>
+      <c r="Z8" s="28"/>
+      <c r="AA8" s="28"/>
+      <c r="AB8" s="28"/>
+      <c r="AC8" s="28"/>
+      <c r="AD8" s="28"/>
+      <c r="AE8" s="28"/>
+      <c r="AF8" s="28"/>
+      <c r="AG8" s="28"/>
+      <c r="AH8" s="28"/>
+      <c r="AI8" s="28"/>
+      <c r="AJ8" s="28"/>
+      <c r="AK8" s="28"/>
+      <c r="AL8" s="28"/>
+      <c r="AM8" s="28"/>
+      <c r="AN8" s="28"/>
+      <c r="AO8" s="28"/>
+      <c r="AP8" s="28"/>
+      <c r="AQ8" s="28"/>
+      <c r="AR8" s="28"/>
+      <c r="AS8" s="28"/>
+      <c r="AT8" s="28"/>
+      <c r="AU8" s="29"/>
+      <c r="AV8" s="42" t="s">
+        <v>4</v>
+      </c>
+      <c r="AW8" s="39"/>
+      <c r="AX8" s="39"/>
+      <c r="AY8" s="39"/>
+      <c r="AZ8" s="39"/>
+      <c r="BA8" s="39"/>
+      <c r="BB8" s="39"/>
+      <c r="BC8" s="39"/>
+      <c r="BD8" s="39"/>
+      <c r="BE8" s="41"/>
+    </row>
+    <row r="9" spans="1:57" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="36" t="s">
+        <v>24</v>
+      </c>
+      <c r="B9" s="9">
+        <v>16</v>
+      </c>
+      <c r="C9" s="5">
+        <v>17</v>
+      </c>
+      <c r="D9" s="5">
+        <v>18</v>
+      </c>
+      <c r="E9" s="5">
+        <v>19</v>
+      </c>
+      <c r="F9" s="5">
+        <v>20</v>
+      </c>
+      <c r="G9" s="5">
+        <v>21</v>
+      </c>
+      <c r="H9" s="6">
+        <v>22</v>
+      </c>
+      <c r="I9" s="7">
+        <v>23</v>
+      </c>
+      <c r="J9" s="2">
+        <v>24</v>
+      </c>
+      <c r="K9" s="2">
+        <v>25</v>
+      </c>
+      <c r="L9" s="2">
+        <v>26</v>
+      </c>
+      <c r="M9" s="2">
+        <v>27</v>
+      </c>
+      <c r="N9" s="2">
+        <v>28</v>
+      </c>
+      <c r="O9" s="3">
+        <v>29</v>
+      </c>
+      <c r="P9" s="4">
+        <v>30</v>
+      </c>
+      <c r="Q9" s="8">
+        <v>31</v>
+      </c>
+      <c r="R9" s="9">
+        <v>1</v>
+      </c>
+      <c r="S9" s="5">
+        <v>2</v>
+      </c>
+      <c r="T9" s="10">
+        <v>3</v>
+      </c>
+      <c r="U9" s="10">
+        <v>4</v>
+      </c>
+      <c r="V9" s="6">
+        <v>5</v>
+      </c>
+      <c r="W9" s="7">
+        <v>6</v>
+      </c>
+      <c r="X9" s="2">
+        <v>7</v>
+      </c>
+      <c r="Y9" s="2">
         <v>8</v>
       </c>
-      <c r="P10" s="5"/>
-      <c r="Q10" s="5"/>
-      <c r="R10" s="5"/>
-      <c r="S10" s="5"/>
-      <c r="T10" s="5"/>
-      <c r="U10" s="5"/>
-      <c r="V10" s="5"/>
-    </row>
-    <row r="11" spans="1:115" x14ac:dyDescent="0.2">
-      <c r="A11" t="s">
+      <c r="Z9" s="2">
+        <v>9</v>
+      </c>
+      <c r="AA9" s="2">
+        <v>10</v>
+      </c>
+      <c r="AB9" s="2">
+        <v>11</v>
+      </c>
+      <c r="AC9" s="3">
+        <v>12</v>
+      </c>
+      <c r="AD9" s="4">
         <v>13</v>
       </c>
-      <c r="W11" s="5"/>
-      <c r="X11" s="5"/>
-      <c r="Y11" s="5"/>
-      <c r="Z11" s="5"/>
-      <c r="AA11" s="5"/>
-      <c r="AB11" s="5"/>
-      <c r="AC11" s="5"/>
-    </row>
-    <row r="12" spans="1:115" x14ac:dyDescent="0.2">
-      <c r="A12" t="s">
+      <c r="AE9" s="5">
+        <v>14</v>
+      </c>
+      <c r="AF9" s="5">
+        <v>15</v>
+      </c>
+      <c r="AG9" s="5">
+        <v>16</v>
+      </c>
+      <c r="AH9" s="5">
+        <v>17</v>
+      </c>
+      <c r="AI9" s="5">
+        <v>18</v>
+      </c>
+      <c r="AJ9" s="6">
+        <v>19</v>
+      </c>
+      <c r="AK9" s="7">
+        <v>20</v>
+      </c>
+      <c r="AL9" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM9" s="2">
+        <v>22</v>
+      </c>
+      <c r="AN9" s="2">
+        <v>23</v>
+      </c>
+      <c r="AO9" s="2">
+        <v>24</v>
+      </c>
+      <c r="AP9" s="2">
+        <v>25</v>
+      </c>
+      <c r="AQ9" s="3">
+        <v>26</v>
+      </c>
+      <c r="AR9" s="4">
+        <v>27</v>
+      </c>
+      <c r="AS9" s="5">
+        <v>28</v>
+      </c>
+      <c r="AT9" s="5">
+        <v>29</v>
+      </c>
+      <c r="AU9" s="8">
+        <v>30</v>
+      </c>
+      <c r="AV9" s="11">
+        <v>1</v>
+      </c>
+      <c r="AW9" s="5">
+        <v>2</v>
+      </c>
+      <c r="AX9" s="6">
+        <v>3</v>
+      </c>
+      <c r="AY9" s="7">
+        <v>4</v>
+      </c>
+      <c r="AZ9" s="2">
+        <v>5</v>
+      </c>
+      <c r="BA9" s="2">
+        <v>6</v>
+      </c>
+      <c r="BB9" s="2">
+        <v>7</v>
+      </c>
+      <c r="BC9" s="2">
+        <v>8</v>
+      </c>
+      <c r="BD9" s="2">
         <v>9</v>
       </c>
-      <c r="W12" s="5"/>
-      <c r="X12" s="5"/>
-      <c r="Y12" s="5"/>
-      <c r="Z12" s="5"/>
-      <c r="AA12" s="5"/>
-      <c r="AB12" s="5"/>
-      <c r="AC12" s="5"/>
-    </row>
-    <row r="13" spans="1:115" x14ac:dyDescent="0.2">
-      <c r="A13" t="s">
+      <c r="BE9" s="3">
         <v>10</v>
       </c>
-      <c r="AD13" s="5"/>
-      <c r="AE13" s="5"/>
-      <c r="AF13" s="5"/>
-      <c r="AG13" s="5"/>
-      <c r="AH13" s="5"/>
-      <c r="AI13" s="5"/>
-      <c r="AJ13" s="5"/>
-    </row>
-    <row r="14" spans="1:115" x14ac:dyDescent="0.2">
-      <c r="A14" t="s">
+    </row>
+    <row r="10" spans="1:57" x14ac:dyDescent="0.2">
+      <c r="B10" s="16"/>
+      <c r="H10" s="18"/>
+      <c r="I10" s="16"/>
+      <c r="O10" s="18"/>
+      <c r="P10" s="16"/>
+      <c r="V10" s="18"/>
+      <c r="W10" s="16"/>
+      <c r="AC10" s="18"/>
+      <c r="AD10" s="16"/>
+      <c r="AJ10" s="18"/>
+      <c r="AK10" s="16"/>
+      <c r="AQ10" s="18"/>
+      <c r="AR10" s="16"/>
+      <c r="AX10" s="18"/>
+      <c r="AY10" s="16"/>
+      <c r="BE10" s="18"/>
+    </row>
+    <row r="11" spans="1:57" x14ac:dyDescent="0.2">
+      <c r="A11" s="17" t="s">
+        <v>1</v>
+      </c>
+      <c r="B11" s="22"/>
+      <c r="C11" s="23"/>
+      <c r="D11" s="23"/>
+      <c r="E11" s="23"/>
+      <c r="F11" s="23"/>
+      <c r="G11" s="23"/>
+      <c r="H11" s="24"/>
+      <c r="I11" s="16"/>
+      <c r="O11" s="18"/>
+      <c r="P11" s="16"/>
+      <c r="V11" s="18"/>
+      <c r="W11" s="16"/>
+      <c r="AC11" s="18"/>
+      <c r="AD11" s="16"/>
+      <c r="AJ11" s="18"/>
+      <c r="AK11" s="16"/>
+      <c r="AQ11" s="18"/>
+      <c r="AR11" s="16"/>
+      <c r="AX11" s="18"/>
+      <c r="AY11" s="16"/>
+      <c r="BE11" s="18"/>
+    </row>
+    <row r="12" spans="1:57" x14ac:dyDescent="0.2">
+      <c r="A12" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="B12" s="16"/>
+      <c r="H12" s="18"/>
+      <c r="I12" s="22"/>
+      <c r="J12" s="23"/>
+      <c r="K12" s="23"/>
+      <c r="L12" s="23"/>
+      <c r="M12" s="23"/>
+      <c r="N12" s="23"/>
+      <c r="O12" s="24"/>
+      <c r="P12" s="16"/>
+      <c r="V12" s="18"/>
+      <c r="W12" s="16"/>
+      <c r="AC12" s="18"/>
+      <c r="AD12" s="16"/>
+      <c r="AJ12" s="18"/>
+      <c r="AK12" s="16"/>
+      <c r="AQ12" s="18"/>
+      <c r="AR12" s="16"/>
+      <c r="AX12" s="18"/>
+      <c r="AY12" s="16"/>
+      <c r="BE12" s="18"/>
+    </row>
+    <row r="13" spans="1:57" x14ac:dyDescent="0.2">
+      <c r="A13" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="B13" s="16"/>
+      <c r="H13" s="18"/>
+      <c r="I13" s="16"/>
+      <c r="O13" s="18"/>
+      <c r="P13" s="22"/>
+      <c r="Q13" s="23"/>
+      <c r="R13" s="23"/>
+      <c r="S13" s="23"/>
+      <c r="T13" s="23"/>
+      <c r="U13" s="23"/>
+      <c r="V13" s="24"/>
+      <c r="W13" s="16"/>
+      <c r="AC13" s="18"/>
+      <c r="AD13" s="16"/>
+      <c r="AJ13" s="18"/>
+      <c r="AK13" s="16"/>
+      <c r="AQ13" s="18"/>
+      <c r="AR13" s="16"/>
+      <c r="AX13" s="18"/>
+      <c r="AY13" s="16"/>
+      <c r="BE13" s="18"/>
+    </row>
+    <row r="14" spans="1:57" x14ac:dyDescent="0.2">
+      <c r="A14" s="17" t="s">
+        <v>7</v>
+      </c>
+      <c r="B14" s="16"/>
+      <c r="H14" s="18"/>
+      <c r="I14" s="16"/>
+      <c r="O14" s="18"/>
+      <c r="P14" s="22"/>
+      <c r="Q14" s="23"/>
+      <c r="R14" s="23"/>
+      <c r="S14" s="23"/>
+      <c r="T14" s="23"/>
+      <c r="U14" s="23"/>
+      <c r="V14" s="24"/>
+      <c r="W14" s="16"/>
+      <c r="AC14" s="18"/>
+      <c r="AD14" s="16"/>
+      <c r="AJ14" s="18"/>
+      <c r="AK14" s="16"/>
+      <c r="AQ14" s="18"/>
+      <c r="AR14" s="16"/>
+      <c r="AX14" s="18"/>
+      <c r="AY14" s="16"/>
+      <c r="BE14" s="18"/>
+    </row>
+    <row r="15" spans="1:57" x14ac:dyDescent="0.2">
+      <c r="A15" s="17" t="s">
+        <v>8</v>
+      </c>
+      <c r="B15" s="16"/>
+      <c r="H15" s="18"/>
+      <c r="I15" s="16"/>
+      <c r="O15" s="18"/>
+      <c r="P15" s="16"/>
+      <c r="V15" s="18"/>
+      <c r="W15" s="22"/>
+      <c r="X15" s="23"/>
+      <c r="Y15" s="23"/>
+      <c r="Z15" s="23"/>
+      <c r="AA15" s="23"/>
+      <c r="AB15" s="23"/>
+      <c r="AC15" s="24"/>
+      <c r="AD15" s="16"/>
+      <c r="AJ15" s="18"/>
+      <c r="AK15" s="16"/>
+      <c r="AQ15" s="18"/>
+      <c r="AR15" s="16"/>
+      <c r="AX15" s="18"/>
+      <c r="AY15" s="16"/>
+      <c r="BE15" s="18"/>
+    </row>
+    <row r="16" spans="1:57" x14ac:dyDescent="0.2">
+      <c r="A16" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="B16" s="16"/>
+      <c r="H16" s="18"/>
+      <c r="I16" s="16"/>
+      <c r="O16" s="18"/>
+      <c r="P16" s="16"/>
+      <c r="V16" s="18"/>
+      <c r="W16" s="16"/>
+      <c r="AC16" s="18"/>
+      <c r="AD16" s="22"/>
+      <c r="AE16" s="23"/>
+      <c r="AF16" s="23"/>
+      <c r="AG16" s="23"/>
+      <c r="AH16" s="23"/>
+      <c r="AI16" s="23"/>
+      <c r="AJ16" s="24"/>
+      <c r="AK16" s="16"/>
+      <c r="AQ16" s="18"/>
+      <c r="AR16" s="16"/>
+      <c r="AX16" s="18"/>
+      <c r="AY16" s="16"/>
+      <c r="BE16" s="18"/>
+    </row>
+    <row r="17" spans="1:57" x14ac:dyDescent="0.2">
+      <c r="A17" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="B17" s="16"/>
+      <c r="H17" s="18"/>
+      <c r="I17" s="16"/>
+      <c r="O17" s="18"/>
+      <c r="P17" s="16"/>
+      <c r="V17" s="18"/>
+      <c r="W17" s="16"/>
+      <c r="AC17" s="18"/>
+      <c r="AD17" s="16"/>
+      <c r="AJ17" s="18"/>
+      <c r="AK17" s="22"/>
+      <c r="AL17" s="23"/>
+      <c r="AM17" s="23"/>
+      <c r="AN17" s="23"/>
+      <c r="AO17" s="23"/>
+      <c r="AP17" s="23"/>
+      <c r="AQ17" s="24"/>
+      <c r="AR17" s="16"/>
+      <c r="AX17" s="18"/>
+      <c r="AY17" s="16"/>
+      <c r="BE17" s="18"/>
+    </row>
+    <row r="18" spans="1:57" x14ac:dyDescent="0.2">
+      <c r="A18" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="AK14" s="5"/>
-      <c r="AL14" s="5"/>
-      <c r="AM14" s="5"/>
-      <c r="AN14" s="5"/>
-      <c r="AO14" s="5"/>
-      <c r="AP14" s="5"/>
-      <c r="AQ14" s="5"/>
-    </row>
-    <row r="15" spans="1:115" x14ac:dyDescent="0.2">
-      <c r="A15" t="s">
+      <c r="B18" s="16"/>
+      <c r="H18" s="18"/>
+      <c r="I18" s="16"/>
+      <c r="O18" s="18"/>
+      <c r="P18" s="16"/>
+      <c r="V18" s="18"/>
+      <c r="W18" s="16"/>
+      <c r="AC18" s="18"/>
+      <c r="AD18" s="16"/>
+      <c r="AJ18" s="18"/>
+      <c r="AK18" s="22"/>
+      <c r="AL18" s="23"/>
+      <c r="AM18" s="23"/>
+      <c r="AN18" s="23"/>
+      <c r="AO18" s="23"/>
+      <c r="AP18" s="23"/>
+      <c r="AQ18" s="24"/>
+      <c r="AR18" s="22"/>
+      <c r="AS18" s="23"/>
+      <c r="AT18" s="23"/>
+      <c r="AU18" s="23"/>
+      <c r="AV18" s="23"/>
+      <c r="AW18" s="23"/>
+      <c r="AX18" s="24"/>
+      <c r="AY18" s="22"/>
+      <c r="AZ18" s="23"/>
+      <c r="BA18" s="23"/>
+      <c r="BB18" s="23"/>
+      <c r="BC18" s="23"/>
+      <c r="BD18" s="23"/>
+      <c r="BE18" s="24"/>
+    </row>
+    <row r="19" spans="1:57" x14ac:dyDescent="0.2">
+      <c r="A19" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="B19" s="16"/>
+      <c r="H19" s="18"/>
+      <c r="I19" s="16"/>
+      <c r="O19" s="18"/>
+      <c r="P19" s="16"/>
+      <c r="V19" s="18"/>
+      <c r="W19" s="16"/>
+      <c r="AC19" s="18"/>
+      <c r="AD19" s="16"/>
+      <c r="AJ19" s="18"/>
+      <c r="AK19" s="22"/>
+      <c r="AL19" s="23"/>
+      <c r="AM19" s="23"/>
+      <c r="AN19" s="23"/>
+      <c r="AO19" s="23"/>
+      <c r="AP19" s="23"/>
+      <c r="AQ19" s="24"/>
+      <c r="AR19" s="22"/>
+      <c r="AS19" s="23"/>
+      <c r="AT19" s="23"/>
+      <c r="AU19" s="23"/>
+      <c r="AV19" s="23"/>
+      <c r="AW19" s="23"/>
+      <c r="AX19" s="24"/>
+      <c r="AY19" s="22"/>
+      <c r="AZ19" s="23"/>
+      <c r="BA19" s="23"/>
+      <c r="BB19" s="23"/>
+      <c r="BC19" s="23"/>
+      <c r="BD19" s="23"/>
+      <c r="BE19" s="24"/>
+    </row>
+    <row r="20" spans="1:57" x14ac:dyDescent="0.2">
+      <c r="A20" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="B20" s="16"/>
+      <c r="H20" s="18"/>
+      <c r="I20" s="16"/>
+      <c r="O20" s="18"/>
+      <c r="P20" s="16"/>
+      <c r="V20" s="18"/>
+      <c r="W20" s="16"/>
+      <c r="AC20" s="18"/>
+      <c r="AD20" s="16"/>
+      <c r="AJ20" s="18"/>
+      <c r="AK20" s="16"/>
+      <c r="AQ20" s="18"/>
+      <c r="AR20" s="22"/>
+      <c r="AS20" s="23"/>
+      <c r="AT20" s="23"/>
+      <c r="AU20" s="23"/>
+      <c r="AV20" s="23"/>
+      <c r="AW20" s="23"/>
+      <c r="AX20" s="24"/>
+      <c r="AY20" s="16"/>
+      <c r="BE20" s="18"/>
+    </row>
+    <row r="21" spans="1:57" x14ac:dyDescent="0.2">
+      <c r="A21" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="B21" s="16"/>
+      <c r="H21" s="18"/>
+      <c r="I21" s="16"/>
+      <c r="O21" s="18"/>
+      <c r="P21" s="16"/>
+      <c r="V21" s="18"/>
+      <c r="W21" s="16"/>
+      <c r="AC21" s="18"/>
+      <c r="AD21" s="16"/>
+      <c r="AJ21" s="18"/>
+      <c r="AK21" s="16"/>
+      <c r="AQ21" s="18"/>
+      <c r="AR21" s="16"/>
+      <c r="AX21" s="18"/>
+      <c r="AY21" s="16"/>
+      <c r="BE21" s="18"/>
+    </row>
+    <row r="22" spans="1:57" x14ac:dyDescent="0.2">
+      <c r="A22" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="B22" s="16"/>
+      <c r="H22" s="18"/>
+      <c r="I22" s="16"/>
+      <c r="O22" s="18"/>
+      <c r="P22" s="16"/>
+      <c r="V22" s="18"/>
+      <c r="W22" s="16"/>
+      <c r="AC22" s="18"/>
+      <c r="AD22" s="16"/>
+      <c r="AJ22" s="18"/>
+      <c r="AK22" s="16"/>
+      <c r="AQ22" s="18"/>
+      <c r="AR22" s="16"/>
+      <c r="AX22" s="18"/>
+      <c r="AY22" s="16"/>
+      <c r="BE22" s="18"/>
+    </row>
+    <row r="23" spans="1:57" x14ac:dyDescent="0.2">
+      <c r="A23" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="B23" s="16"/>
+      <c r="H23" s="18"/>
+      <c r="I23" s="16"/>
+      <c r="O23" s="18"/>
+      <c r="P23" s="16"/>
+      <c r="V23" s="18"/>
+      <c r="W23" s="16"/>
+      <c r="AC23" s="18"/>
+      <c r="AD23" s="16"/>
+      <c r="AJ23" s="18"/>
+      <c r="AK23" s="16"/>
+      <c r="AQ23" s="18"/>
+      <c r="AR23" s="16"/>
+      <c r="AX23" s="18"/>
+      <c r="AY23" s="16"/>
+      <c r="BE23" s="18"/>
+    </row>
+    <row r="24" spans="1:57" x14ac:dyDescent="0.2">
+      <c r="A24" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="B24" s="16"/>
+      <c r="H24" s="18"/>
+      <c r="I24" s="16"/>
+      <c r="O24" s="18"/>
+      <c r="P24" s="16"/>
+      <c r="V24" s="18"/>
+      <c r="W24" s="16"/>
+      <c r="AC24" s="18"/>
+      <c r="AD24" s="16"/>
+      <c r="AJ24" s="18"/>
+      <c r="AK24" s="16"/>
+      <c r="AQ24" s="18"/>
+      <c r="AR24" s="16"/>
+      <c r="AX24" s="18"/>
+      <c r="AY24" s="16"/>
+      <c r="BE24" s="18"/>
+    </row>
+    <row r="25" spans="1:57" x14ac:dyDescent="0.2">
+      <c r="A25" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="B25" s="16"/>
+      <c r="H25" s="18"/>
+      <c r="I25" s="16"/>
+      <c r="O25" s="18"/>
+      <c r="P25" s="16"/>
+      <c r="V25" s="18"/>
+      <c r="W25" s="16"/>
+      <c r="AC25" s="18"/>
+      <c r="AD25" s="16"/>
+      <c r="AJ25" s="18"/>
+      <c r="AK25" s="16"/>
+      <c r="AQ25" s="18"/>
+      <c r="AR25" s="16"/>
+      <c r="AX25" s="18"/>
+      <c r="AY25" s="16"/>
+      <c r="BE25" s="18"/>
+    </row>
+    <row r="26" spans="1:57" x14ac:dyDescent="0.2">
+      <c r="A26" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="B26" s="16"/>
+      <c r="H26" s="18"/>
+      <c r="I26" s="16"/>
+      <c r="O26" s="18"/>
+      <c r="P26" s="16"/>
+      <c r="V26" s="18"/>
+      <c r="W26" s="16"/>
+      <c r="AC26" s="18"/>
+      <c r="AD26" s="16"/>
+      <c r="AJ26" s="18"/>
+      <c r="AK26" s="16"/>
+      <c r="AQ26" s="18"/>
+      <c r="AR26" s="16"/>
+      <c r="AX26" s="18"/>
+      <c r="AY26" s="16"/>
+      <c r="BE26" s="18"/>
+    </row>
+    <row r="27" spans="1:57" x14ac:dyDescent="0.2">
+      <c r="A27" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="B27" s="16"/>
+      <c r="H27" s="18"/>
+      <c r="I27" s="16"/>
+      <c r="O27" s="18"/>
+      <c r="P27" s="16"/>
+      <c r="V27" s="18"/>
+      <c r="W27" s="16"/>
+      <c r="AC27" s="18"/>
+      <c r="AD27" s="16"/>
+      <c r="AJ27" s="18"/>
+      <c r="AK27" s="16"/>
+      <c r="AQ27" s="18"/>
+      <c r="AR27" s="16"/>
+      <c r="AX27" s="18"/>
+      <c r="AY27" s="16"/>
+      <c r="BE27" s="18"/>
+    </row>
+    <row r="28" spans="1:57" x14ac:dyDescent="0.2">
+      <c r="A28" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="B28" s="16"/>
+      <c r="H28" s="18"/>
+      <c r="I28" s="16"/>
+      <c r="O28" s="18"/>
+      <c r="P28" s="16"/>
+      <c r="V28" s="18"/>
+      <c r="W28" s="16"/>
+      <c r="AC28" s="18"/>
+      <c r="AD28" s="16"/>
+      <c r="AJ28" s="18"/>
+      <c r="AK28" s="16"/>
+      <c r="AQ28" s="18"/>
+      <c r="AR28" s="16"/>
+      <c r="AX28" s="18"/>
+      <c r="AY28" s="16"/>
+      <c r="BE28" s="18"/>
+    </row>
+    <row r="29" spans="1:57" x14ac:dyDescent="0.2">
+      <c r="A29" s="37" t="s">
+        <v>21</v>
+      </c>
+      <c r="B29" s="19"/>
+      <c r="C29" s="20"/>
+      <c r="D29" s="20"/>
+      <c r="E29" s="20"/>
+      <c r="F29" s="20"/>
+      <c r="G29" s="20"/>
+      <c r="H29" s="21"/>
+      <c r="I29" s="19"/>
+      <c r="J29" s="20"/>
+      <c r="K29" s="20"/>
+      <c r="L29" s="20"/>
+      <c r="M29" s="20"/>
+      <c r="N29" s="20"/>
+      <c r="O29" s="21"/>
+      <c r="P29" s="19"/>
+      <c r="Q29" s="20"/>
+      <c r="R29" s="20"/>
+      <c r="S29" s="20"/>
+      <c r="T29" s="20"/>
+      <c r="U29" s="20"/>
+      <c r="V29" s="21"/>
+      <c r="W29" s="19"/>
+      <c r="X29" s="20"/>
+      <c r="Y29" s="20"/>
+      <c r="Z29" s="20"/>
+      <c r="AA29" s="20"/>
+      <c r="AB29" s="20"/>
+      <c r="AC29" s="21"/>
+      <c r="AD29" s="19"/>
+      <c r="AE29" s="20"/>
+      <c r="AF29" s="20"/>
+      <c r="AG29" s="20"/>
+      <c r="AH29" s="20"/>
+      <c r="AI29" s="20"/>
+      <c r="AJ29" s="21"/>
+      <c r="AK29" s="19"/>
+      <c r="AL29" s="20"/>
+      <c r="AM29" s="20"/>
+      <c r="AN29" s="20"/>
+      <c r="AO29" s="20"/>
+      <c r="AP29" s="20"/>
+      <c r="AQ29" s="21"/>
+      <c r="AR29" s="19"/>
+      <c r="AS29" s="20"/>
+      <c r="AT29" s="20"/>
+      <c r="AU29" s="20"/>
+      <c r="AV29" s="20"/>
+      <c r="AW29" s="20"/>
+      <c r="AX29" s="21"/>
+      <c r="AY29" s="19"/>
+      <c r="AZ29" s="20"/>
+      <c r="BA29" s="20"/>
+      <c r="BB29" s="20"/>
+      <c r="BC29" s="20"/>
+      <c r="BD29" s="20"/>
+      <c r="BE29" s="21"/>
+    </row>
+    <row r="30" spans="1:57" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="37"/>
+    </row>
+    <row r="31" spans="1:57" x14ac:dyDescent="0.2">
+      <c r="A31" s="35" t="s">
+        <v>0</v>
+      </c>
+      <c r="B31" s="38" t="s">
+        <v>4</v>
+      </c>
+      <c r="C31" s="39"/>
+      <c r="D31" s="39"/>
+      <c r="E31" s="39"/>
+      <c r="F31" s="39"/>
+      <c r="G31" s="39"/>
+      <c r="H31" s="39"/>
+      <c r="I31" s="39"/>
+      <c r="J31" s="39"/>
+      <c r="K31" s="39"/>
+      <c r="L31" s="39"/>
+      <c r="M31" s="39"/>
+      <c r="N31" s="39"/>
+      <c r="O31" s="39"/>
+      <c r="P31" s="39"/>
+      <c r="Q31" s="39"/>
+      <c r="R31" s="39"/>
+      <c r="S31" s="39"/>
+      <c r="T31" s="39"/>
+      <c r="U31" s="39"/>
+      <c r="V31" s="40"/>
+      <c r="W31" s="30" t="s">
+        <v>5</v>
+      </c>
+      <c r="X31" s="28"/>
+      <c r="Y31" s="28"/>
+      <c r="Z31" s="28"/>
+      <c r="AA31" s="28"/>
+      <c r="AB31" s="28"/>
+      <c r="AC31" s="28"/>
+      <c r="AD31" s="28"/>
+      <c r="AE31" s="28"/>
+      <c r="AF31" s="28"/>
+      <c r="AG31" s="28"/>
+      <c r="AH31" s="28"/>
+      <c r="AI31" s="28"/>
+      <c r="AJ31" s="28"/>
+      <c r="AK31" s="28"/>
+      <c r="AL31" s="28"/>
+      <c r="AM31" s="28"/>
+      <c r="AN31" s="28"/>
+      <c r="AO31" s="28"/>
+      <c r="AP31" s="28"/>
+      <c r="AQ31" s="28"/>
+      <c r="AR31" s="28"/>
+      <c r="AS31" s="28"/>
+      <c r="AT31" s="28"/>
+      <c r="AU31" s="28"/>
+      <c r="AV31" s="28"/>
+      <c r="AW31" s="28"/>
+      <c r="AX31" s="28"/>
+      <c r="AY31" s="28"/>
+      <c r="AZ31" s="29"/>
+    </row>
+    <row r="32" spans="1:57" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="36" t="s">
+        <v>24</v>
+      </c>
+      <c r="B32" s="4">
         <v>11</v>
       </c>
-      <c r="AR15" s="5"/>
-      <c r="AS15" s="5"/>
-      <c r="AT15" s="5"/>
-      <c r="AU15" s="5"/>
-      <c r="AV15" s="5"/>
-      <c r="AW15" s="5"/>
-      <c r="AX15" s="5"/>
-    </row>
-    <row r="16" spans="1:115" x14ac:dyDescent="0.2">
-      <c r="A16" t="s">
+      <c r="C32" s="5">
+        <v>12</v>
+      </c>
+      <c r="D32" s="5">
+        <v>13</v>
+      </c>
+      <c r="E32" s="5">
         <v>14</v>
       </c>
-      <c r="AR16" s="5"/>
-      <c r="AS16" s="5"/>
-      <c r="AT16" s="5"/>
-      <c r="AU16" s="5"/>
-      <c r="AV16" s="5"/>
-      <c r="AW16" s="5"/>
-      <c r="AX16" s="5"/>
-      <c r="AY16" s="5"/>
-      <c r="AZ16" s="5"/>
-      <c r="BA16" s="5"/>
-      <c r="BB16" s="5"/>
-      <c r="BC16" s="5"/>
-      <c r="BD16" s="5"/>
-      <c r="BE16" s="5"/>
-      <c r="BF16" s="5"/>
-      <c r="BG16" s="5"/>
-      <c r="BH16" s="5"/>
-      <c r="BI16" s="5"/>
-      <c r="BJ16" s="5"/>
-      <c r="BK16" s="5"/>
-      <c r="BL16" s="5"/>
-    </row>
-    <row r="17" spans="1:115" x14ac:dyDescent="0.2">
-      <c r="A17" t="s">
+      <c r="F32" s="5">
         <v>15</v>
       </c>
-      <c r="AR17" s="5"/>
-      <c r="AS17" s="5"/>
-      <c r="AT17" s="5"/>
-      <c r="AU17" s="5"/>
-      <c r="AV17" s="5"/>
-      <c r="AW17" s="5"/>
-      <c r="AX17" s="5"/>
-      <c r="AY17" s="5"/>
-      <c r="AZ17" s="5"/>
-      <c r="BA17" s="5"/>
-      <c r="BB17" s="5"/>
-      <c r="BC17" s="5"/>
-      <c r="BD17" s="5"/>
-      <c r="BE17" s="5"/>
-      <c r="BF17" s="5"/>
-      <c r="BG17" s="5"/>
-      <c r="BH17" s="5"/>
-      <c r="BI17" s="5"/>
-      <c r="BJ17" s="5"/>
-      <c r="BK17" s="5"/>
-      <c r="BL17" s="5"/>
-    </row>
-    <row r="18" spans="1:115" x14ac:dyDescent="0.2">
-      <c r="A18" t="s">
+      <c r="G32" s="5">
         <v>16</v>
       </c>
-      <c r="AY18" s="5"/>
-      <c r="AZ18" s="5"/>
-      <c r="BA18" s="5"/>
-      <c r="BB18" s="5"/>
-      <c r="BC18" s="5"/>
-      <c r="BD18" s="5"/>
-      <c r="BE18" s="5"/>
-    </row>
-    <row r="19" spans="1:115" x14ac:dyDescent="0.2">
-      <c r="A19" t="s">
+      <c r="H32" s="6">
         <v>17</v>
       </c>
-      <c r="BM19" s="5"/>
-      <c r="BN19" s="5"/>
-      <c r="BO19" s="5"/>
-      <c r="BP19" s="5"/>
-      <c r="BQ19" s="5"/>
-      <c r="BR19" s="5"/>
-      <c r="BS19" s="5"/>
-    </row>
-    <row r="20" spans="1:115" x14ac:dyDescent="0.2">
-      <c r="A20" t="s">
+      <c r="I32" s="7">
         <v>18</v>
       </c>
-      <c r="BM20" s="5"/>
-      <c r="BN20" s="5"/>
-      <c r="BO20" s="5"/>
-      <c r="BP20" s="5"/>
-      <c r="BQ20" s="5"/>
-      <c r="BR20" s="5"/>
-      <c r="BS20" s="5"/>
-    </row>
-    <row r="21" spans="1:115" x14ac:dyDescent="0.2">
-      <c r="A21" t="s">
+      <c r="J32" s="2">
+        <v>19</v>
+      </c>
+      <c r="K32" s="2">
+        <v>20</v>
+      </c>
+      <c r="L32" s="12">
+        <v>21</v>
+      </c>
+      <c r="M32" s="2">
+        <v>22</v>
+      </c>
+      <c r="N32" s="2">
+        <v>23</v>
+      </c>
+      <c r="O32" s="3">
+        <v>24</v>
+      </c>
+      <c r="P32" s="4">
+        <v>25</v>
+      </c>
+      <c r="Q32" s="5">
+        <v>26</v>
+      </c>
+      <c r="R32" s="5">
+        <v>27</v>
+      </c>
+      <c r="S32" s="5">
+        <v>28</v>
+      </c>
+      <c r="T32" s="5">
+        <v>29</v>
+      </c>
+      <c r="U32" s="5">
+        <v>30</v>
+      </c>
+      <c r="V32" s="13">
+        <v>31</v>
+      </c>
+      <c r="W32" s="1">
+        <v>1</v>
+      </c>
+      <c r="X32" s="2">
+        <v>2</v>
+      </c>
+      <c r="Y32" s="2">
+        <v>3</v>
+      </c>
+      <c r="Z32" s="2">
+        <v>4</v>
+      </c>
+      <c r="AA32" s="2">
+        <v>5</v>
+      </c>
+      <c r="AB32" s="2">
+        <v>6</v>
+      </c>
+      <c r="AC32" s="3">
+        <v>7</v>
+      </c>
+      <c r="AD32" s="4">
+        <v>8</v>
+      </c>
+      <c r="AE32" s="5">
+        <v>9</v>
+      </c>
+      <c r="AF32" s="5">
+        <v>10</v>
+      </c>
+      <c r="AG32" s="5">
+        <v>11</v>
+      </c>
+      <c r="AH32" s="5">
+        <v>12</v>
+      </c>
+      <c r="AI32" s="5">
+        <v>13</v>
+      </c>
+      <c r="AJ32" s="6">
         <v>14</v>
       </c>
-      <c r="BT21" s="5"/>
-      <c r="BU21" s="5"/>
-      <c r="BV21" s="5"/>
-      <c r="BW21" s="5"/>
-      <c r="BX21" s="5"/>
-      <c r="BY21" s="5"/>
-      <c r="BZ21" s="5"/>
-      <c r="CA21" s="5"/>
-      <c r="CB21" s="5"/>
-      <c r="CC21" s="5"/>
-      <c r="CD21" s="5"/>
-      <c r="CE21" s="5"/>
-      <c r="CF21" s="5"/>
-      <c r="CG21" s="5"/>
-      <c r="CH21" s="5"/>
-      <c r="CI21" s="5"/>
-      <c r="CJ21" s="5"/>
-      <c r="CK21" s="5"/>
-      <c r="CL21" s="5"/>
-      <c r="CM21" s="5"/>
-      <c r="CN21" s="5"/>
-      <c r="CO21" s="5"/>
-      <c r="CP21" s="5"/>
-      <c r="CQ21" s="5"/>
-      <c r="CR21" s="5"/>
-      <c r="CS21" s="5"/>
-      <c r="CT21" s="5"/>
-      <c r="CU21" s="5"/>
-    </row>
-    <row r="22" spans="1:115" x14ac:dyDescent="0.2">
-      <c r="A22" t="s">
+      <c r="AK32" s="7">
         <v>15</v>
       </c>
-      <c r="BT22" s="5"/>
-      <c r="BU22" s="5"/>
-      <c r="BV22" s="5"/>
-      <c r="BW22" s="5"/>
-      <c r="BX22" s="5"/>
-      <c r="BY22" s="5"/>
-      <c r="BZ22" s="5"/>
-      <c r="CA22" s="5"/>
-      <c r="CB22" s="5"/>
-      <c r="CC22" s="5"/>
-      <c r="CD22" s="5"/>
-      <c r="CE22" s="5"/>
-      <c r="CF22" s="5"/>
-      <c r="CG22" s="5"/>
-      <c r="CH22" s="5"/>
-      <c r="CI22" s="5"/>
-      <c r="CJ22" s="5"/>
-      <c r="CK22" s="5"/>
-      <c r="CL22" s="5"/>
-      <c r="CM22" s="5"/>
-      <c r="CN22" s="5"/>
-      <c r="CO22" s="5"/>
-      <c r="CP22" s="5"/>
-      <c r="CQ22" s="5"/>
-      <c r="CR22" s="5"/>
-      <c r="CS22" s="5"/>
-      <c r="CT22" s="5"/>
-      <c r="CU22" s="5"/>
-    </row>
-    <row r="23" spans="1:115" x14ac:dyDescent="0.2">
-      <c r="A23" t="s">
+      <c r="AL32" s="2">
+        <v>16</v>
+      </c>
+      <c r="AM32" s="2">
+        <v>17</v>
+      </c>
+      <c r="AN32" s="2">
+        <v>18</v>
+      </c>
+      <c r="AO32" s="2">
         <v>19</v>
       </c>
-      <c r="CV23" s="5"/>
-      <c r="CW23" s="5"/>
-      <c r="CX23" s="5"/>
-      <c r="CY23" s="5"/>
-      <c r="CZ23" s="5"/>
-      <c r="DA23" s="5"/>
-      <c r="DB23" s="5"/>
-    </row>
-    <row r="24" spans="1:115" x14ac:dyDescent="0.2">
-      <c r="A24" t="s">
+      <c r="AP32" s="2">
         <v>20</v>
       </c>
-      <c r="CV24" s="5"/>
-      <c r="CW24" s="5"/>
-      <c r="CX24" s="5"/>
-      <c r="CY24" s="5"/>
-      <c r="CZ24" s="5"/>
-      <c r="DA24" s="5"/>
-      <c r="DB24" s="5"/>
-    </row>
-    <row r="25" spans="1:115" x14ac:dyDescent="0.2">
-      <c r="A25" t="s">
+      <c r="AQ32" s="3">
         <v>21</v>
       </c>
-      <c r="DC25" s="5"/>
-      <c r="DD25" s="5"/>
-      <c r="DE25" s="5"/>
-      <c r="DF25" s="5"/>
-      <c r="DG25" s="5"/>
-      <c r="DH25" s="5"/>
-      <c r="DI25" s="5"/>
-      <c r="DJ25" s="5"/>
-      <c r="DK25" s="5"/>
-    </row>
-    <row r="26" spans="1:115" x14ac:dyDescent="0.2">
-      <c r="A26" t="s">
+      <c r="AR32" s="4">
         <v>22</v>
       </c>
-      <c r="DC26" s="5"/>
-      <c r="DD26" s="5"/>
-      <c r="DE26" s="5"/>
-      <c r="DF26" s="5"/>
-      <c r="DG26" s="5"/>
-      <c r="DH26" s="5"/>
-      <c r="DI26" s="5"/>
-      <c r="DJ26" s="5"/>
-      <c r="DK26" s="5"/>
-    </row>
-    <row r="27" spans="1:115" x14ac:dyDescent="0.2">
-      <c r="A27" s="2" t="s">
+      <c r="AS32" s="5">
         <v>23</v>
       </c>
-      <c r="DC27" s="5"/>
-      <c r="DD27" s="5"/>
-      <c r="DE27" s="5"/>
-      <c r="DF27" s="5"/>
-      <c r="DG27" s="5"/>
-      <c r="DH27" s="5"/>
-      <c r="DI27" s="5"/>
-      <c r="DJ27" s="5"/>
-      <c r="DK27" s="5"/>
-    </row>
-    <row r="28" spans="1:115" x14ac:dyDescent="0.2">
-      <c r="A28" s="2"/>
-    </row>
-    <row r="29" spans="1:115" x14ac:dyDescent="0.2">
-      <c r="A29" s="2"/>
-    </row>
-    <row r="30" spans="1:115" x14ac:dyDescent="0.2">
-      <c r="A30" s="2"/>
-    </row>
-    <row r="31" spans="1:115" x14ac:dyDescent="0.2">
-      <c r="A31" s="2"/>
-    </row>
-    <row r="32" spans="1:115" x14ac:dyDescent="0.2">
-      <c r="A32" s="2"/>
-    </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A33" s="2"/>
-    </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A34" s="2"/>
-    </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A35" s="2"/>
-    </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A36" s="2"/>
-    </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A37" s="2"/>
-    </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A38" s="2"/>
+      <c r="AT32" s="5">
+        <v>24</v>
+      </c>
+      <c r="AU32" s="5">
+        <v>25</v>
+      </c>
+      <c r="AV32" s="5">
+        <v>26</v>
+      </c>
+      <c r="AW32" s="5">
+        <v>27</v>
+      </c>
+      <c r="AX32" s="6">
+        <v>28</v>
+      </c>
+      <c r="AY32" s="14">
+        <v>29</v>
+      </c>
+      <c r="AZ32" s="15">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="33" spans="1:52" x14ac:dyDescent="0.2">
+      <c r="B33" s="16"/>
+      <c r="H33" s="18"/>
+      <c r="I33" s="16"/>
+      <c r="O33" s="18"/>
+      <c r="P33" s="16"/>
+      <c r="V33" s="18"/>
+      <c r="W33" s="16"/>
+      <c r="AC33" s="18"/>
+      <c r="AD33" s="16"/>
+      <c r="AJ33" s="18"/>
+      <c r="AK33" s="16"/>
+      <c r="AQ33" s="18"/>
+      <c r="AR33" s="16"/>
+      <c r="AX33" s="18"/>
+      <c r="AY33" s="16"/>
+      <c r="AZ33" s="18"/>
+    </row>
+    <row r="34" spans="1:52" x14ac:dyDescent="0.2">
+      <c r="A34" s="17" t="s">
+        <v>1</v>
+      </c>
+      <c r="B34" s="16"/>
+      <c r="H34" s="18"/>
+      <c r="I34" s="16"/>
+      <c r="O34" s="18"/>
+      <c r="P34" s="16"/>
+      <c r="V34" s="18"/>
+      <c r="W34" s="16"/>
+      <c r="AC34" s="18"/>
+      <c r="AD34" s="16"/>
+      <c r="AJ34" s="18"/>
+      <c r="AK34" s="16"/>
+      <c r="AQ34" s="18"/>
+      <c r="AR34" s="16"/>
+      <c r="AX34" s="18"/>
+      <c r="AY34" s="16"/>
+      <c r="AZ34" s="18"/>
+    </row>
+    <row r="35" spans="1:52" x14ac:dyDescent="0.2">
+      <c r="A35" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="B35" s="16"/>
+      <c r="H35" s="18"/>
+      <c r="I35" s="16"/>
+      <c r="O35" s="18"/>
+      <c r="P35" s="16"/>
+      <c r="V35" s="18"/>
+      <c r="W35" s="16"/>
+      <c r="AC35" s="18"/>
+      <c r="AD35" s="16"/>
+      <c r="AJ35" s="18"/>
+      <c r="AK35" s="16"/>
+      <c r="AQ35" s="18"/>
+      <c r="AR35" s="16"/>
+      <c r="AX35" s="18"/>
+      <c r="AY35" s="16"/>
+      <c r="AZ35" s="18"/>
+    </row>
+    <row r="36" spans="1:52" x14ac:dyDescent="0.2">
+      <c r="A36" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="B36" s="16"/>
+      <c r="H36" s="18"/>
+      <c r="I36" s="16"/>
+      <c r="O36" s="18"/>
+      <c r="P36" s="16"/>
+      <c r="V36" s="18"/>
+      <c r="W36" s="16"/>
+      <c r="AC36" s="18"/>
+      <c r="AD36" s="16"/>
+      <c r="AJ36" s="18"/>
+      <c r="AK36" s="16"/>
+      <c r="AQ36" s="18"/>
+      <c r="AR36" s="16"/>
+      <c r="AX36" s="18"/>
+      <c r="AY36" s="16"/>
+      <c r="AZ36" s="18"/>
+    </row>
+    <row r="37" spans="1:52" x14ac:dyDescent="0.2">
+      <c r="A37" s="17" t="s">
+        <v>7</v>
+      </c>
+      <c r="B37" s="16"/>
+      <c r="H37" s="18"/>
+      <c r="I37" s="16"/>
+      <c r="O37" s="18"/>
+      <c r="P37" s="16"/>
+      <c r="V37" s="18"/>
+      <c r="W37" s="16"/>
+      <c r="AC37" s="18"/>
+      <c r="AD37" s="16"/>
+      <c r="AJ37" s="18"/>
+      <c r="AK37" s="16"/>
+      <c r="AQ37" s="18"/>
+      <c r="AR37" s="16"/>
+      <c r="AX37" s="18"/>
+      <c r="AY37" s="16"/>
+      <c r="AZ37" s="18"/>
+    </row>
+    <row r="38" spans="1:52" x14ac:dyDescent="0.2">
+      <c r="A38" s="17" t="s">
+        <v>8</v>
+      </c>
+      <c r="B38" s="16"/>
+      <c r="H38" s="18"/>
+      <c r="I38" s="16"/>
+      <c r="O38" s="18"/>
+      <c r="P38" s="16"/>
+      <c r="V38" s="18"/>
+      <c r="W38" s="16"/>
+      <c r="AC38" s="18"/>
+      <c r="AD38" s="16"/>
+      <c r="AJ38" s="18"/>
+      <c r="AK38" s="16"/>
+      <c r="AQ38" s="18"/>
+      <c r="AR38" s="16"/>
+      <c r="AX38" s="18"/>
+      <c r="AY38" s="16"/>
+      <c r="AZ38" s="18"/>
+    </row>
+    <row r="39" spans="1:52" x14ac:dyDescent="0.2">
+      <c r="A39" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="B39" s="16"/>
+      <c r="H39" s="18"/>
+      <c r="I39" s="16"/>
+      <c r="O39" s="18"/>
+      <c r="P39" s="16"/>
+      <c r="V39" s="18"/>
+      <c r="W39" s="16"/>
+      <c r="AC39" s="18"/>
+      <c r="AD39" s="16"/>
+      <c r="AJ39" s="18"/>
+      <c r="AK39" s="16"/>
+      <c r="AQ39" s="18"/>
+      <c r="AR39" s="16"/>
+      <c r="AX39" s="18"/>
+      <c r="AY39" s="16"/>
+      <c r="AZ39" s="18"/>
+    </row>
+    <row r="40" spans="1:52" x14ac:dyDescent="0.2">
+      <c r="A40" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="B40" s="16"/>
+      <c r="H40" s="18"/>
+      <c r="I40" s="16"/>
+      <c r="O40" s="18"/>
+      <c r="P40" s="16"/>
+      <c r="V40" s="18"/>
+      <c r="W40" s="16"/>
+      <c r="AC40" s="18"/>
+      <c r="AD40" s="16"/>
+      <c r="AJ40" s="18"/>
+      <c r="AK40" s="16"/>
+      <c r="AQ40" s="18"/>
+      <c r="AR40" s="16"/>
+      <c r="AX40" s="18"/>
+      <c r="AY40" s="16"/>
+      <c r="AZ40" s="18"/>
+    </row>
+    <row r="41" spans="1:52" x14ac:dyDescent="0.2">
+      <c r="A41" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="B41" s="16"/>
+      <c r="H41" s="18"/>
+      <c r="I41" s="16"/>
+      <c r="O41" s="18"/>
+      <c r="P41" s="16"/>
+      <c r="V41" s="18"/>
+      <c r="W41" s="16"/>
+      <c r="AC41" s="18"/>
+      <c r="AD41" s="16"/>
+      <c r="AJ41" s="18"/>
+      <c r="AK41" s="16"/>
+      <c r="AQ41" s="18"/>
+      <c r="AR41" s="16"/>
+      <c r="AX41" s="18"/>
+      <c r="AY41" s="16"/>
+      <c r="AZ41" s="18"/>
+    </row>
+    <row r="42" spans="1:52" x14ac:dyDescent="0.2">
+      <c r="A42" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="B42" s="16"/>
+      <c r="H42" s="18"/>
+      <c r="I42" s="16"/>
+      <c r="O42" s="18"/>
+      <c r="P42" s="16"/>
+      <c r="V42" s="18"/>
+      <c r="W42" s="16"/>
+      <c r="AC42" s="18"/>
+      <c r="AD42" s="16"/>
+      <c r="AJ42" s="18"/>
+      <c r="AK42" s="16"/>
+      <c r="AQ42" s="18"/>
+      <c r="AR42" s="16"/>
+      <c r="AX42" s="18"/>
+      <c r="AY42" s="16"/>
+      <c r="AZ42" s="18"/>
+    </row>
+    <row r="43" spans="1:52" x14ac:dyDescent="0.2">
+      <c r="A43" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="B43" s="16"/>
+      <c r="H43" s="18"/>
+      <c r="I43" s="16"/>
+      <c r="O43" s="18"/>
+      <c r="P43" s="16"/>
+      <c r="V43" s="18"/>
+      <c r="W43" s="16"/>
+      <c r="AC43" s="18"/>
+      <c r="AD43" s="16"/>
+      <c r="AJ43" s="18"/>
+      <c r="AK43" s="16"/>
+      <c r="AQ43" s="18"/>
+      <c r="AR43" s="16"/>
+      <c r="AX43" s="18"/>
+      <c r="AY43" s="16"/>
+      <c r="AZ43" s="18"/>
+    </row>
+    <row r="44" spans="1:52" x14ac:dyDescent="0.2">
+      <c r="A44" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="B44" s="22"/>
+      <c r="C44" s="23"/>
+      <c r="D44" s="23"/>
+      <c r="E44" s="23"/>
+      <c r="F44" s="23"/>
+      <c r="G44" s="23"/>
+      <c r="H44" s="24"/>
+      <c r="I44" s="16"/>
+      <c r="O44" s="18"/>
+      <c r="P44" s="16"/>
+      <c r="V44" s="18"/>
+      <c r="W44" s="16"/>
+      <c r="AC44" s="18"/>
+      <c r="AD44" s="16"/>
+      <c r="AJ44" s="18"/>
+      <c r="AK44" s="16"/>
+      <c r="AQ44" s="18"/>
+      <c r="AR44" s="16"/>
+      <c r="AX44" s="18"/>
+      <c r="AY44" s="16"/>
+      <c r="AZ44" s="18"/>
+    </row>
+    <row r="45" spans="1:52" x14ac:dyDescent="0.2">
+      <c r="A45" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="B45" s="22"/>
+      <c r="C45" s="23"/>
+      <c r="D45" s="23"/>
+      <c r="E45" s="23"/>
+      <c r="F45" s="23"/>
+      <c r="G45" s="23"/>
+      <c r="H45" s="24"/>
+      <c r="I45" s="16"/>
+      <c r="O45" s="18"/>
+      <c r="P45" s="16"/>
+      <c r="V45" s="18"/>
+      <c r="W45" s="16"/>
+      <c r="AC45" s="18"/>
+      <c r="AD45" s="16"/>
+      <c r="AJ45" s="18"/>
+      <c r="AK45" s="16"/>
+      <c r="AQ45" s="18"/>
+      <c r="AR45" s="16"/>
+      <c r="AX45" s="18"/>
+      <c r="AY45" s="16"/>
+      <c r="AZ45" s="18"/>
+    </row>
+    <row r="46" spans="1:52" x14ac:dyDescent="0.2">
+      <c r="A46" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="B46" s="16"/>
+      <c r="H46" s="18"/>
+      <c r="I46" s="22"/>
+      <c r="J46" s="23"/>
+      <c r="K46" s="23"/>
+      <c r="L46" s="23"/>
+      <c r="M46" s="23"/>
+      <c r="N46" s="23"/>
+      <c r="O46" s="24"/>
+      <c r="P46" s="22"/>
+      <c r="Q46" s="23"/>
+      <c r="R46" s="23"/>
+      <c r="S46" s="23"/>
+      <c r="T46" s="23"/>
+      <c r="U46" s="23"/>
+      <c r="V46" s="24"/>
+      <c r="W46" s="22"/>
+      <c r="X46" s="23"/>
+      <c r="Y46" s="23"/>
+      <c r="Z46" s="23"/>
+      <c r="AA46" s="23"/>
+      <c r="AB46" s="23"/>
+      <c r="AC46" s="24"/>
+      <c r="AD46" s="22"/>
+      <c r="AE46" s="23"/>
+      <c r="AF46" s="23"/>
+      <c r="AG46" s="23"/>
+      <c r="AH46" s="23"/>
+      <c r="AI46" s="23"/>
+      <c r="AJ46" s="24"/>
+      <c r="AK46" s="16"/>
+      <c r="AQ46" s="18"/>
+      <c r="AR46" s="16"/>
+      <c r="AX46" s="18"/>
+      <c r="AY46" s="16"/>
+      <c r="AZ46" s="18"/>
+    </row>
+    <row r="47" spans="1:52" x14ac:dyDescent="0.2">
+      <c r="A47" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="B47" s="16"/>
+      <c r="H47" s="18"/>
+      <c r="I47" s="22"/>
+      <c r="J47" s="23"/>
+      <c r="K47" s="23"/>
+      <c r="L47" s="23"/>
+      <c r="M47" s="23"/>
+      <c r="N47" s="23"/>
+      <c r="O47" s="24"/>
+      <c r="P47" s="22"/>
+      <c r="Q47" s="23"/>
+      <c r="R47" s="23"/>
+      <c r="S47" s="23"/>
+      <c r="T47" s="23"/>
+      <c r="U47" s="23"/>
+      <c r="V47" s="24"/>
+      <c r="W47" s="22"/>
+      <c r="X47" s="23"/>
+      <c r="Y47" s="23"/>
+      <c r="Z47" s="23"/>
+      <c r="AA47" s="23"/>
+      <c r="AB47" s="23"/>
+      <c r="AC47" s="24"/>
+      <c r="AD47" s="22"/>
+      <c r="AE47" s="23"/>
+      <c r="AF47" s="23"/>
+      <c r="AG47" s="23"/>
+      <c r="AH47" s="23"/>
+      <c r="AI47" s="23"/>
+      <c r="AJ47" s="24"/>
+      <c r="AK47" s="16"/>
+      <c r="AQ47" s="18"/>
+      <c r="AR47" s="16"/>
+      <c r="AX47" s="18"/>
+      <c r="AY47" s="16"/>
+      <c r="AZ47" s="18"/>
+    </row>
+    <row r="48" spans="1:52" x14ac:dyDescent="0.2">
+      <c r="A48" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="B48" s="16"/>
+      <c r="H48" s="18"/>
+      <c r="I48" s="16"/>
+      <c r="O48" s="18"/>
+      <c r="P48" s="16"/>
+      <c r="V48" s="18"/>
+      <c r="W48" s="16"/>
+      <c r="AC48" s="18"/>
+      <c r="AD48" s="16"/>
+      <c r="AJ48" s="18"/>
+      <c r="AK48" s="22"/>
+      <c r="AL48" s="23"/>
+      <c r="AM48" s="23"/>
+      <c r="AN48" s="23"/>
+      <c r="AO48" s="23"/>
+      <c r="AP48" s="23"/>
+      <c r="AQ48" s="24"/>
+      <c r="AR48" s="16"/>
+      <c r="AX48" s="18"/>
+      <c r="AY48" s="16"/>
+      <c r="AZ48" s="18"/>
+    </row>
+    <row r="49" spans="1:52" x14ac:dyDescent="0.2">
+      <c r="A49" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="B49" s="16"/>
+      <c r="H49" s="18"/>
+      <c r="I49" s="16"/>
+      <c r="O49" s="18"/>
+      <c r="P49" s="16"/>
+      <c r="V49" s="18"/>
+      <c r="W49" s="16"/>
+      <c r="AC49" s="18"/>
+      <c r="AD49" s="16"/>
+      <c r="AJ49" s="18"/>
+      <c r="AK49" s="22"/>
+      <c r="AL49" s="23"/>
+      <c r="AM49" s="23"/>
+      <c r="AN49" s="23"/>
+      <c r="AO49" s="23"/>
+      <c r="AP49" s="23"/>
+      <c r="AQ49" s="24"/>
+      <c r="AR49" s="16"/>
+      <c r="AX49" s="18"/>
+      <c r="AY49" s="16"/>
+      <c r="AZ49" s="18"/>
+    </row>
+    <row r="50" spans="1:52" x14ac:dyDescent="0.2">
+      <c r="A50" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="B50" s="16"/>
+      <c r="H50" s="18"/>
+      <c r="I50" s="16"/>
+      <c r="O50" s="18"/>
+      <c r="P50" s="16"/>
+      <c r="V50" s="18"/>
+      <c r="W50" s="16"/>
+      <c r="AC50" s="18"/>
+      <c r="AD50" s="16"/>
+      <c r="AJ50" s="18"/>
+      <c r="AK50" s="16"/>
+      <c r="AQ50" s="18"/>
+      <c r="AR50" s="22"/>
+      <c r="AS50" s="23"/>
+      <c r="AT50" s="23"/>
+      <c r="AU50" s="23"/>
+      <c r="AV50" s="23"/>
+      <c r="AW50" s="23"/>
+      <c r="AX50" s="24"/>
+      <c r="AY50" s="22"/>
+      <c r="AZ50" s="24"/>
+    </row>
+    <row r="51" spans="1:52" x14ac:dyDescent="0.2">
+      <c r="A51" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="B51" s="16"/>
+      <c r="H51" s="18"/>
+      <c r="I51" s="16"/>
+      <c r="O51" s="18"/>
+      <c r="P51" s="16"/>
+      <c r="V51" s="18"/>
+      <c r="W51" s="16"/>
+      <c r="AC51" s="18"/>
+      <c r="AD51" s="16"/>
+      <c r="AJ51" s="18"/>
+      <c r="AK51" s="16"/>
+      <c r="AQ51" s="18"/>
+      <c r="AR51" s="22"/>
+      <c r="AS51" s="23"/>
+      <c r="AT51" s="23"/>
+      <c r="AU51" s="23"/>
+      <c r="AV51" s="23"/>
+      <c r="AW51" s="23"/>
+      <c r="AX51" s="24"/>
+      <c r="AY51" s="22"/>
+      <c r="AZ51" s="24"/>
+    </row>
+    <row r="52" spans="1:52" x14ac:dyDescent="0.2">
+      <c r="A52" s="37" t="s">
+        <v>21</v>
+      </c>
+      <c r="B52" s="19"/>
+      <c r="C52" s="20"/>
+      <c r="D52" s="20"/>
+      <c r="E52" s="20"/>
+      <c r="F52" s="20"/>
+      <c r="G52" s="20"/>
+      <c r="H52" s="21"/>
+      <c r="I52" s="19"/>
+      <c r="J52" s="20"/>
+      <c r="K52" s="20"/>
+      <c r="L52" s="20"/>
+      <c r="M52" s="20"/>
+      <c r="N52" s="20"/>
+      <c r="O52" s="21"/>
+      <c r="P52" s="19"/>
+      <c r="Q52" s="20"/>
+      <c r="R52" s="20"/>
+      <c r="S52" s="20"/>
+      <c r="T52" s="20"/>
+      <c r="U52" s="20"/>
+      <c r="V52" s="21"/>
+      <c r="W52" s="19"/>
+      <c r="X52" s="20"/>
+      <c r="Y52" s="20"/>
+      <c r="Z52" s="20"/>
+      <c r="AA52" s="20"/>
+      <c r="AB52" s="20"/>
+      <c r="AC52" s="21"/>
+      <c r="AD52" s="19"/>
+      <c r="AE52" s="20"/>
+      <c r="AF52" s="20"/>
+      <c r="AG52" s="20"/>
+      <c r="AH52" s="20"/>
+      <c r="AI52" s="20"/>
+      <c r="AJ52" s="21"/>
+      <c r="AK52" s="19"/>
+      <c r="AL52" s="20"/>
+      <c r="AM52" s="20"/>
+      <c r="AN52" s="20"/>
+      <c r="AO52" s="20"/>
+      <c r="AP52" s="20"/>
+      <c r="AQ52" s="21"/>
+      <c r="AR52" s="25"/>
+      <c r="AS52" s="26"/>
+      <c r="AT52" s="26"/>
+      <c r="AU52" s="26"/>
+      <c r="AV52" s="26"/>
+      <c r="AW52" s="26"/>
+      <c r="AX52" s="27"/>
+      <c r="AY52" s="25"/>
+      <c r="AZ52" s="27"/>
     </row>
   </sheetData>
   <mergeCells count="5">
-    <mergeCell ref="CH5:DK5"/>
-    <mergeCell ref="A1:X1"/>
-    <mergeCell ref="B5:X5"/>
-    <mergeCell ref="Y5:BB5"/>
-    <mergeCell ref="BC5:CG5"/>
+    <mergeCell ref="B8:Q8"/>
+    <mergeCell ref="R8:AU8"/>
+    <mergeCell ref="W31:AZ31"/>
+    <mergeCell ref="B31:V31"/>
+    <mergeCell ref="AV8:BE8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Carta Gantt.xlsx
+++ b/Carta Gantt.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Carlos\Documents\GitHub\duoc_fullstack\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F046080F-D13B-499E-8BD3-3E35C6874D8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEA0EB90-0F03-445E-8E4C-7FD75055694C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6CCCA798-E65F-4DDC-AD8C-08062A140C3B}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="28">
   <si>
     <t>Semanas</t>
   </si>
@@ -122,6 +122,9 @@
   </si>
   <si>
     <t>FULLSTACK 3</t>
+  </si>
+  <si>
+    <t>Julio</t>
   </si>
 </sst>
 </file>
@@ -452,41 +455,45 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="13" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -496,19 +503,15 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -843,445 +846,204 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{477A3499-DDAC-41C4-A409-E01E2AE8668D}">
-  <dimension ref="A1:DF40"/>
+  <dimension ref="A1:DI40"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="21.88671875" style="17" bestFit="1" customWidth="1"/>
-    <col min="2" max="7" width="2.77734375" style="17" customWidth="1"/>
-    <col min="8" max="8" width="3.44140625" style="17" bestFit="1" customWidth="1"/>
-    <col min="9" max="14" width="2.77734375" style="17" customWidth="1"/>
-    <col min="15" max="15" width="3.21875" style="17" bestFit="1" customWidth="1"/>
-    <col min="16" max="42" width="2.77734375" style="17" customWidth="1"/>
-    <col min="43" max="43" width="3.21875" style="17" bestFit="1" customWidth="1"/>
-    <col min="44" max="56" width="2.77734375" style="17" customWidth="1"/>
-    <col min="57" max="57" width="3.44140625" style="17" bestFit="1" customWidth="1"/>
-    <col min="58" max="70" width="2.77734375" style="17" customWidth="1"/>
-    <col min="71" max="71" width="3.44140625" style="17" bestFit="1" customWidth="1"/>
-    <col min="72" max="105" width="2.77734375" style="17" customWidth="1"/>
-    <col min="106" max="107" width="3.21875" style="17" bestFit="1" customWidth="1"/>
-    <col min="108" max="108" width="2.77734375" style="17" customWidth="1"/>
-    <col min="109" max="110" width="11.5546875" style="17"/>
+    <col min="1" max="1" width="21.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="7" width="2.77734375" customWidth="1"/>
+    <col min="8" max="8" width="3.44140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="14" width="2.77734375" customWidth="1"/>
+    <col min="15" max="15" width="3.21875" bestFit="1" customWidth="1"/>
+    <col min="16" max="42" width="2.77734375" customWidth="1"/>
+    <col min="43" max="43" width="3.21875" bestFit="1" customWidth="1"/>
+    <col min="44" max="56" width="2.77734375" customWidth="1"/>
+    <col min="57" max="57" width="3.44140625" bestFit="1" customWidth="1"/>
+    <col min="58" max="70" width="2.77734375" customWidth="1"/>
+    <col min="71" max="71" width="3.44140625" bestFit="1" customWidth="1"/>
+    <col min="72" max="105" width="2.77734375" customWidth="1"/>
+    <col min="106" max="107" width="3.21875" bestFit="1" customWidth="1"/>
+    <col min="108" max="108" width="2.77734375" customWidth="1"/>
+    <col min="109" max="109" width="3.21875" bestFit="1" customWidth="1"/>
+    <col min="110" max="110" width="2.77734375" customWidth="1"/>
+    <col min="111" max="111" width="3.21875" bestFit="1" customWidth="1"/>
+    <col min="112" max="112" width="2.77734375" customWidth="1"/>
+    <col min="113" max="113" width="3.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:110" ht="20.25" x14ac:dyDescent="0.3">
-      <c r="A1" s="31" t="s">
+    <row r="1" spans="1:113" ht="20.25" x14ac:dyDescent="0.3">
+      <c r="A1" s="27" t="s">
         <v>25</v>
       </c>
-      <c r="B1" s="32"/>
-      <c r="C1" s="32"/>
-      <c r="D1" s="32"/>
-      <c r="E1" s="32"/>
-      <c r="F1" s="32"/>
-      <c r="G1" s="32"/>
-      <c r="H1" s="32"/>
-      <c r="I1" s="32"/>
-      <c r="J1" s="32"/>
-      <c r="K1" s="32"/>
-      <c r="L1" s="32"/>
-      <c r="M1" s="32"/>
-      <c r="N1" s="32"/>
-      <c r="O1" s="32"/>
-      <c r="P1" s="32"/>
-      <c r="Q1" s="32"/>
-    </row>
-    <row r="2" spans="1:110" ht="20.25" x14ac:dyDescent="0.3">
-      <c r="A2" s="31" t="s">
+    </row>
+    <row r="2" spans="1:113" ht="20.25" x14ac:dyDescent="0.3">
+      <c r="A2" s="27" t="s">
         <v>26</v>
       </c>
-      <c r="B2" s="32"/>
-      <c r="C2" s="32"/>
-      <c r="D2" s="32"/>
-      <c r="E2" s="32"/>
-      <c r="F2" s="32"/>
-      <c r="G2" s="32"/>
-      <c r="H2" s="32"/>
-      <c r="I2" s="32"/>
-      <c r="J2" s="32"/>
-      <c r="K2" s="32"/>
-      <c r="L2" s="32"/>
-      <c r="M2" s="32"/>
-      <c r="N2" s="32"/>
-      <c r="O2" s="32"/>
-      <c r="P2" s="32"/>
-      <c r="Q2" s="32"/>
-    </row>
-    <row r="3" spans="1:110" ht="20.25" x14ac:dyDescent="0.3">
-      <c r="A3" s="31">
+    </row>
+    <row r="3" spans="1:113" ht="20.25" x14ac:dyDescent="0.3">
+      <c r="A3" s="27">
         <v>2026</v>
       </c>
-      <c r="B3" s="32"/>
-      <c r="C3" s="32"/>
-      <c r="D3" s="32"/>
-      <c r="E3" s="32"/>
-      <c r="F3" s="32"/>
-      <c r="G3" s="32"/>
-      <c r="H3" s="32"/>
-      <c r="I3" s="32"/>
-      <c r="J3" s="32"/>
-      <c r="K3" s="32"/>
-      <c r="L3" s="32"/>
-      <c r="M3" s="32"/>
-      <c r="N3" s="32"/>
-      <c r="O3" s="32"/>
-      <c r="P3" s="32"/>
-      <c r="Q3" s="32"/>
-    </row>
-    <row r="4" spans="1:110" s="47" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A4" s="45"/>
-      <c r="B4" s="45"/>
-      <c r="C4" s="45"/>
-      <c r="D4" s="45"/>
-      <c r="E4" s="45"/>
-      <c r="F4" s="45"/>
-      <c r="G4" s="45"/>
-      <c r="H4" s="45"/>
-      <c r="I4" s="45"/>
-      <c r="J4" s="45"/>
-      <c r="K4" s="45"/>
-      <c r="L4" s="45"/>
-      <c r="M4" s="45"/>
-      <c r="N4" s="45"/>
-      <c r="O4" s="45"/>
-      <c r="P4" s="45"/>
-      <c r="Q4" s="45"/>
-      <c r="R4" s="46"/>
-      <c r="S4" s="46"/>
-      <c r="T4" s="46"/>
-      <c r="U4" s="46"/>
-      <c r="V4" s="46"/>
-      <c r="W4" s="46"/>
-      <c r="X4" s="46"/>
-      <c r="Y4" s="46"/>
-      <c r="Z4" s="46"/>
-      <c r="AA4" s="46"/>
-      <c r="AB4" s="46"/>
-      <c r="AC4" s="46"/>
-      <c r="AD4" s="46"/>
-      <c r="AE4" s="46"/>
-      <c r="AF4" s="46"/>
-      <c r="AG4" s="46"/>
-      <c r="AH4" s="46"/>
-      <c r="AI4" s="46"/>
-      <c r="AJ4" s="46"/>
-      <c r="AK4" s="46"/>
-      <c r="AL4" s="46"/>
-      <c r="AM4" s="46"/>
-      <c r="AN4" s="46"/>
-      <c r="AO4" s="46"/>
-      <c r="AP4" s="46"/>
-      <c r="AQ4" s="46"/>
-      <c r="AR4" s="46"/>
-      <c r="AS4" s="46"/>
-      <c r="AT4" s="46"/>
-      <c r="AU4" s="46"/>
-      <c r="AV4" s="46"/>
-      <c r="AW4" s="46"/>
-      <c r="AX4" s="46"/>
-      <c r="AY4" s="46"/>
-      <c r="AZ4" s="46"/>
-      <c r="BA4" s="46"/>
-      <c r="BB4" s="46"/>
-      <c r="BC4" s="46"/>
-      <c r="BD4" s="46"/>
-      <c r="BE4" s="46"/>
-      <c r="BF4" s="46"/>
-      <c r="BG4" s="46"/>
-      <c r="BH4" s="46"/>
-      <c r="BI4" s="46"/>
-      <c r="BJ4" s="46"/>
-      <c r="BK4" s="46"/>
-      <c r="BL4" s="46"/>
-      <c r="BM4" s="46"/>
-      <c r="BN4" s="46"/>
-      <c r="BO4" s="46"/>
-      <c r="BP4" s="46"/>
-      <c r="BQ4" s="46"/>
-      <c r="BR4" s="46"/>
-      <c r="BS4" s="46"/>
-      <c r="BT4" s="46"/>
-      <c r="BU4" s="46"/>
-      <c r="BV4" s="46"/>
-      <c r="BW4" s="46"/>
-      <c r="BX4" s="46"/>
-      <c r="BY4" s="46"/>
-      <c r="BZ4" s="46"/>
-      <c r="CA4" s="46"/>
-      <c r="CB4" s="46"/>
-      <c r="CC4" s="46"/>
-      <c r="CD4" s="46"/>
-      <c r="CE4" s="46"/>
-      <c r="CF4" s="46"/>
-      <c r="CG4" s="46"/>
-      <c r="CH4" s="46"/>
-      <c r="CI4" s="46"/>
-      <c r="CJ4" s="46"/>
-      <c r="CK4" s="46"/>
-      <c r="CL4" s="46"/>
-      <c r="CM4" s="46"/>
-      <c r="CN4" s="46"/>
-      <c r="CO4" s="46"/>
-      <c r="CP4" s="46"/>
-      <c r="CQ4" s="46"/>
-      <c r="CR4" s="46"/>
-      <c r="CS4" s="46"/>
-      <c r="CT4" s="46"/>
-      <c r="CU4" s="46"/>
-      <c r="CV4" s="46"/>
-      <c r="CW4" s="46"/>
-      <c r="CX4" s="46"/>
-      <c r="CY4" s="46"/>
-      <c r="CZ4" s="46"/>
-      <c r="DA4" s="46"/>
-      <c r="DB4" s="46"/>
-      <c r="DC4" s="46"/>
-      <c r="DD4" s="46"/>
-      <c r="DE4" s="46"/>
-      <c r="DF4" s="46"/>
-    </row>
-    <row r="5" spans="1:110" ht="18" x14ac:dyDescent="0.25">
-      <c r="A5" s="34" t="s">
+    </row>
+    <row r="4" spans="1:113" s="36" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A4" s="35"/>
+      <c r="B4" s="35"/>
+      <c r="C4" s="35"/>
+      <c r="D4" s="35"/>
+      <c r="E4" s="35"/>
+      <c r="F4" s="35"/>
+      <c r="G4" s="35"/>
+      <c r="H4" s="35"/>
+      <c r="I4" s="35"/>
+      <c r="J4" s="35"/>
+      <c r="K4" s="35"/>
+      <c r="L4" s="35"/>
+      <c r="M4" s="35"/>
+      <c r="N4" s="35"/>
+      <c r="O4" s="35"/>
+      <c r="P4" s="35"/>
+      <c r="Q4" s="35"/>
+    </row>
+    <row r="5" spans="1:113" ht="18" x14ac:dyDescent="0.25">
+      <c r="A5" s="29" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="6" spans="1:110" ht="18" x14ac:dyDescent="0.25">
-      <c r="A6" s="34" t="s">
+    <row r="6" spans="1:113" ht="18" x14ac:dyDescent="0.25">
+      <c r="A6" s="29" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="7" spans="1:110" s="47" customFormat="1" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="46"/>
-      <c r="B7" s="46"/>
-      <c r="C7" s="46"/>
-      <c r="D7" s="46"/>
-      <c r="E7" s="46"/>
-      <c r="F7" s="46"/>
-      <c r="G7" s="46"/>
-      <c r="H7" s="46"/>
-      <c r="I7" s="46"/>
-      <c r="J7" s="46"/>
-      <c r="K7" s="46"/>
-      <c r="L7" s="46"/>
-      <c r="M7" s="46"/>
-      <c r="N7" s="46"/>
-      <c r="O7" s="46"/>
-      <c r="P7" s="46"/>
-      <c r="Q7" s="46"/>
-      <c r="R7" s="46"/>
-      <c r="S7" s="46"/>
-      <c r="T7" s="46"/>
-      <c r="U7" s="46"/>
-      <c r="V7" s="46"/>
-      <c r="W7" s="46"/>
-      <c r="X7" s="46"/>
-      <c r="Y7" s="46"/>
-      <c r="Z7" s="46"/>
-      <c r="AA7" s="46"/>
-      <c r="AB7" s="46"/>
-      <c r="AC7" s="46"/>
-      <c r="AD7" s="46"/>
-      <c r="AE7" s="46"/>
-      <c r="AF7" s="46"/>
-      <c r="AG7" s="46"/>
-      <c r="AH7" s="46"/>
-      <c r="AI7" s="46"/>
-      <c r="AJ7" s="46"/>
-      <c r="AK7" s="46"/>
-      <c r="AL7" s="46"/>
-      <c r="AM7" s="46"/>
-      <c r="AN7" s="46"/>
-      <c r="AO7" s="46"/>
-      <c r="AP7" s="46"/>
-      <c r="AQ7" s="46"/>
-      <c r="AR7" s="46"/>
-      <c r="AS7" s="46"/>
-      <c r="AT7" s="46"/>
-      <c r="AU7" s="46"/>
-      <c r="AV7" s="46"/>
-      <c r="AW7" s="46"/>
-      <c r="AX7" s="46"/>
-      <c r="AY7" s="46"/>
-      <c r="AZ7" s="46"/>
-      <c r="BA7" s="46"/>
-      <c r="BB7" s="46"/>
-      <c r="BC7" s="46"/>
-      <c r="BD7" s="46"/>
-      <c r="BE7" s="46"/>
-      <c r="BF7" s="46"/>
-      <c r="BG7" s="46"/>
-      <c r="BH7" s="46"/>
-      <c r="BI7" s="46"/>
-      <c r="BJ7" s="46"/>
-      <c r="BK7" s="46"/>
-      <c r="BL7" s="46"/>
-      <c r="BM7" s="46"/>
-      <c r="BN7" s="46"/>
-      <c r="BO7" s="46"/>
-      <c r="BP7" s="46"/>
-      <c r="BQ7" s="46"/>
-      <c r="BR7" s="46"/>
-      <c r="BS7" s="46"/>
-      <c r="BT7" s="46"/>
-      <c r="BU7" s="46"/>
-      <c r="BV7" s="46"/>
-      <c r="BW7" s="46"/>
-      <c r="BX7" s="46"/>
-      <c r="BY7" s="46"/>
-      <c r="BZ7" s="46"/>
-      <c r="CA7" s="46"/>
-      <c r="CB7" s="46"/>
-      <c r="CC7" s="46"/>
-      <c r="CD7" s="46"/>
-      <c r="CE7" s="46"/>
-      <c r="CF7" s="46"/>
-      <c r="CG7" s="46"/>
-      <c r="CH7" s="46"/>
-      <c r="CI7" s="46"/>
-      <c r="CJ7" s="46"/>
-      <c r="CK7" s="46"/>
-      <c r="CL7" s="46"/>
-      <c r="CM7" s="46"/>
-      <c r="CN7" s="46"/>
-      <c r="CO7" s="46"/>
-      <c r="CP7" s="46"/>
-      <c r="CQ7" s="46"/>
-      <c r="CR7" s="46"/>
-      <c r="CS7" s="46"/>
-      <c r="CT7" s="46"/>
-      <c r="CU7" s="46"/>
-      <c r="CV7" s="46"/>
-      <c r="CW7" s="46"/>
-      <c r="CX7" s="46"/>
-      <c r="CY7" s="46"/>
-      <c r="CZ7" s="46"/>
-      <c r="DA7" s="46"/>
-      <c r="DB7" s="46"/>
-      <c r="DC7" s="46"/>
-      <c r="DD7" s="46"/>
-      <c r="DE7" s="46"/>
-      <c r="DF7" s="46"/>
-    </row>
-    <row r="8" spans="1:110" x14ac:dyDescent="0.2">
-      <c r="A8" s="35" t="s">
+    <row r="7" spans="1:113" s="36" customFormat="1" ht="13.5" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="8" spans="1:113" x14ac:dyDescent="0.2">
+      <c r="A8" s="30" t="s">
         <v>0</v>
       </c>
-      <c r="B8" s="30" t="s">
+      <c r="B8" s="37" t="s">
         <v>2</v>
       </c>
-      <c r="C8" s="28"/>
-      <c r="D8" s="28"/>
-      <c r="E8" s="28"/>
-      <c r="F8" s="28"/>
-      <c r="G8" s="28"/>
-      <c r="H8" s="28"/>
-      <c r="I8" s="28"/>
-      <c r="J8" s="28"/>
-      <c r="K8" s="28"/>
-      <c r="L8" s="28"/>
-      <c r="M8" s="28"/>
-      <c r="N8" s="28"/>
-      <c r="O8" s="28"/>
-      <c r="P8" s="28"/>
-      <c r="Q8" s="29"/>
-      <c r="R8" s="30" t="s">
+      <c r="C8" s="38"/>
+      <c r="D8" s="38"/>
+      <c r="E8" s="38"/>
+      <c r="F8" s="38"/>
+      <c r="G8" s="38"/>
+      <c r="H8" s="38"/>
+      <c r="I8" s="38"/>
+      <c r="J8" s="38"/>
+      <c r="K8" s="38"/>
+      <c r="L8" s="38"/>
+      <c r="M8" s="38"/>
+      <c r="N8" s="38"/>
+      <c r="O8" s="38"/>
+      <c r="P8" s="38"/>
+      <c r="Q8" s="39"/>
+      <c r="R8" s="37" t="s">
         <v>3</v>
       </c>
-      <c r="S8" s="28"/>
-      <c r="T8" s="28"/>
-      <c r="U8" s="28"/>
-      <c r="V8" s="28"/>
-      <c r="W8" s="28"/>
-      <c r="X8" s="28"/>
-      <c r="Y8" s="28"/>
-      <c r="Z8" s="28"/>
-      <c r="AA8" s="28"/>
-      <c r="AB8" s="28"/>
-      <c r="AC8" s="28"/>
-      <c r="AD8" s="28"/>
-      <c r="AE8" s="28"/>
-      <c r="AF8" s="28"/>
-      <c r="AG8" s="28"/>
-      <c r="AH8" s="28"/>
-      <c r="AI8" s="28"/>
-      <c r="AJ8" s="28"/>
-      <c r="AK8" s="28"/>
-      <c r="AL8" s="28"/>
-      <c r="AM8" s="28"/>
-      <c r="AN8" s="28"/>
-      <c r="AO8" s="28"/>
-      <c r="AP8" s="28"/>
-      <c r="AQ8" s="28"/>
-      <c r="AR8" s="28"/>
-      <c r="AS8" s="28"/>
-      <c r="AT8" s="28"/>
-      <c r="AU8" s="29"/>
-      <c r="AV8" s="30" t="s">
+      <c r="S8" s="38"/>
+      <c r="T8" s="38"/>
+      <c r="U8" s="38"/>
+      <c r="V8" s="38"/>
+      <c r="W8" s="38"/>
+      <c r="X8" s="38"/>
+      <c r="Y8" s="38"/>
+      <c r="Z8" s="38"/>
+      <c r="AA8" s="38"/>
+      <c r="AB8" s="38"/>
+      <c r="AC8" s="38"/>
+      <c r="AD8" s="38"/>
+      <c r="AE8" s="38"/>
+      <c r="AF8" s="38"/>
+      <c r="AG8" s="38"/>
+      <c r="AH8" s="38"/>
+      <c r="AI8" s="38"/>
+      <c r="AJ8" s="38"/>
+      <c r="AK8" s="38"/>
+      <c r="AL8" s="38"/>
+      <c r="AM8" s="38"/>
+      <c r="AN8" s="38"/>
+      <c r="AO8" s="38"/>
+      <c r="AP8" s="38"/>
+      <c r="AQ8" s="38"/>
+      <c r="AR8" s="38"/>
+      <c r="AS8" s="38"/>
+      <c r="AT8" s="38"/>
+      <c r="AU8" s="39"/>
+      <c r="AV8" s="37" t="s">
         <v>4</v>
       </c>
-      <c r="AW8" s="28"/>
-      <c r="AX8" s="28"/>
-      <c r="AY8" s="28"/>
-      <c r="AZ8" s="28"/>
-      <c r="BA8" s="28"/>
-      <c r="BB8" s="28"/>
-      <c r="BC8" s="28"/>
-      <c r="BD8" s="28"/>
-      <c r="BE8" s="28"/>
-      <c r="BF8" s="28"/>
-      <c r="BG8" s="28"/>
-      <c r="BH8" s="28"/>
-      <c r="BI8" s="28"/>
-      <c r="BJ8" s="28"/>
-      <c r="BK8" s="28"/>
-      <c r="BL8" s="28"/>
-      <c r="BM8" s="28"/>
-      <c r="BN8" s="28"/>
-      <c r="BO8" s="28"/>
-      <c r="BP8" s="28"/>
-      <c r="BQ8" s="28"/>
-      <c r="BR8" s="28"/>
-      <c r="BS8" s="28"/>
-      <c r="BT8" s="28"/>
-      <c r="BU8" s="28"/>
-      <c r="BV8" s="28"/>
-      <c r="BW8" s="28"/>
-      <c r="BX8" s="28"/>
-      <c r="BY8" s="28"/>
-      <c r="BZ8" s="29"/>
-      <c r="CA8" s="30" t="s">
+      <c r="AW8" s="38"/>
+      <c r="AX8" s="38"/>
+      <c r="AY8" s="38"/>
+      <c r="AZ8" s="38"/>
+      <c r="BA8" s="38"/>
+      <c r="BB8" s="38"/>
+      <c r="BC8" s="38"/>
+      <c r="BD8" s="38"/>
+      <c r="BE8" s="38"/>
+      <c r="BF8" s="38"/>
+      <c r="BG8" s="38"/>
+      <c r="BH8" s="38"/>
+      <c r="BI8" s="38"/>
+      <c r="BJ8" s="38"/>
+      <c r="BK8" s="38"/>
+      <c r="BL8" s="38"/>
+      <c r="BM8" s="38"/>
+      <c r="BN8" s="38"/>
+      <c r="BO8" s="38"/>
+      <c r="BP8" s="38"/>
+      <c r="BQ8" s="38"/>
+      <c r="BR8" s="38"/>
+      <c r="BS8" s="38"/>
+      <c r="BT8" s="38"/>
+      <c r="BU8" s="38"/>
+      <c r="BV8" s="38"/>
+      <c r="BW8" s="38"/>
+      <c r="BX8" s="38"/>
+      <c r="BY8" s="38"/>
+      <c r="BZ8" s="39"/>
+      <c r="CA8" s="37" t="s">
         <v>5</v>
       </c>
-      <c r="CB8" s="28"/>
-      <c r="CC8" s="28"/>
-      <c r="CD8" s="28"/>
-      <c r="CE8" s="28"/>
-      <c r="CF8" s="28"/>
-      <c r="CG8" s="28"/>
-      <c r="CH8" s="28"/>
-      <c r="CI8" s="28"/>
-      <c r="CJ8" s="28"/>
-      <c r="CK8" s="28"/>
-      <c r="CL8" s="28"/>
-      <c r="CM8" s="28"/>
-      <c r="CN8" s="28"/>
-      <c r="CO8" s="28"/>
-      <c r="CP8" s="28"/>
-      <c r="CQ8" s="28"/>
-      <c r="CR8" s="28"/>
-      <c r="CS8" s="28"/>
-      <c r="CT8" s="28"/>
-      <c r="CU8" s="28"/>
-      <c r="CV8" s="28"/>
-      <c r="CW8" s="28"/>
-      <c r="CX8" s="28"/>
-      <c r="CY8" s="28"/>
-      <c r="CZ8" s="28"/>
-      <c r="DA8" s="28"/>
-      <c r="DB8" s="28"/>
-      <c r="DC8" s="28"/>
-      <c r="DD8" s="29"/>
-    </row>
-    <row r="9" spans="1:110" ht="15" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="36" t="s">
+      <c r="CB8" s="38"/>
+      <c r="CC8" s="38"/>
+      <c r="CD8" s="38"/>
+      <c r="CE8" s="38"/>
+      <c r="CF8" s="38"/>
+      <c r="CG8" s="38"/>
+      <c r="CH8" s="38"/>
+      <c r="CI8" s="38"/>
+      <c r="CJ8" s="38"/>
+      <c r="CK8" s="38"/>
+      <c r="CL8" s="38"/>
+      <c r="CM8" s="38"/>
+      <c r="CN8" s="38"/>
+      <c r="CO8" s="38"/>
+      <c r="CP8" s="38"/>
+      <c r="CQ8" s="38"/>
+      <c r="CR8" s="38"/>
+      <c r="CS8" s="38"/>
+      <c r="CT8" s="38"/>
+      <c r="CU8" s="38"/>
+      <c r="CV8" s="38"/>
+      <c r="CW8" s="38"/>
+      <c r="CX8" s="38"/>
+      <c r="CY8" s="38"/>
+      <c r="CZ8" s="38"/>
+      <c r="DA8" s="38"/>
+      <c r="DB8" s="38"/>
+      <c r="DC8" s="38"/>
+      <c r="DD8" s="39"/>
+      <c r="DE8" s="43" t="s">
+        <v>27</v>
+      </c>
+      <c r="DF8" s="41"/>
+      <c r="DG8" s="41"/>
+      <c r="DH8" s="41"/>
+      <c r="DI8" s="42"/>
+    </row>
+    <row r="9" spans="1:113" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="31" t="s">
         <v>24</v>
       </c>
       <c r="B9" s="9">
@@ -1596,7 +1358,7 @@
       <c r="DA9" s="5">
         <v>27</v>
       </c>
-      <c r="DB9" s="6">
+      <c r="DB9" s="10">
         <v>28</v>
       </c>
       <c r="DC9" s="14">
@@ -1605,998 +1367,1114 @@
       <c r="DD9" s="15">
         <v>30</v>
       </c>
-    </row>
-    <row r="10" spans="1:110" x14ac:dyDescent="0.2">
+      <c r="DE9" s="1">
+        <v>1</v>
+      </c>
+      <c r="DF9" s="2">
+        <v>2</v>
+      </c>
+      <c r="DG9" s="2">
+        <v>3</v>
+      </c>
+      <c r="DH9" s="2">
+        <v>4</v>
+      </c>
+      <c r="DI9" s="47">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:113" x14ac:dyDescent="0.2">
       <c r="B10" s="16"/>
-      <c r="H10" s="18"/>
+      <c r="H10" s="17"/>
       <c r="I10" s="16"/>
-      <c r="O10" s="18"/>
+      <c r="O10" s="17"/>
       <c r="P10" s="16"/>
-      <c r="V10" s="18"/>
+      <c r="V10" s="17"/>
       <c r="W10" s="16"/>
-      <c r="AC10" s="18"/>
+      <c r="AC10" s="17"/>
       <c r="AD10" s="16"/>
-      <c r="AJ10" s="18"/>
+      <c r="AJ10" s="17"/>
       <c r="AK10" s="16"/>
-      <c r="AQ10" s="18"/>
+      <c r="AQ10" s="17"/>
       <c r="AR10" s="16"/>
-      <c r="AX10" s="18"/>
+      <c r="AX10" s="17"/>
       <c r="AY10" s="16"/>
-      <c r="BE10" s="18"/>
+      <c r="BE10" s="17"/>
       <c r="BF10" s="16"/>
-      <c r="BL10" s="18"/>
+      <c r="BL10" s="17"/>
       <c r="BM10" s="16"/>
-      <c r="BS10" s="18"/>
+      <c r="BS10" s="17"/>
       <c r="BT10" s="16"/>
-      <c r="BZ10" s="18"/>
+      <c r="BZ10" s="17"/>
       <c r="CA10" s="16"/>
-      <c r="CG10" s="18"/>
+      <c r="CG10" s="17"/>
       <c r="CH10" s="16"/>
-      <c r="CN10" s="18"/>
+      <c r="CN10" s="17"/>
       <c r="CO10" s="16"/>
-      <c r="CU10" s="18"/>
+      <c r="CU10" s="17"/>
       <c r="CV10" s="16"/>
-      <c r="DB10" s="18"/>
+      <c r="DB10" s="45"/>
       <c r="DC10" s="16"/>
-      <c r="DD10" s="18"/>
-    </row>
-    <row r="11" spans="1:110" ht="15" x14ac:dyDescent="0.2">
-      <c r="A11" s="43" t="s">
+      <c r="DD10" s="45"/>
+      <c r="DE10" s="45"/>
+      <c r="DF10" s="45"/>
+      <c r="DG10" s="45"/>
+      <c r="DH10" s="45"/>
+      <c r="DI10" s="17"/>
+    </row>
+    <row r="11" spans="1:113" ht="15" x14ac:dyDescent="0.2">
+      <c r="A11" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="B11" s="22"/>
-      <c r="C11" s="23"/>
-      <c r="D11" s="23"/>
-      <c r="E11" s="23"/>
-      <c r="F11" s="23"/>
-      <c r="G11" s="23"/>
-      <c r="H11" s="24"/>
+      <c r="B11" s="21"/>
+      <c r="C11" s="22"/>
+      <c r="D11" s="22"/>
+      <c r="E11" s="22"/>
+      <c r="F11" s="22"/>
+      <c r="G11" s="22"/>
+      <c r="H11" s="23"/>
       <c r="I11" s="16"/>
-      <c r="O11" s="18"/>
+      <c r="O11" s="17"/>
       <c r="P11" s="16"/>
-      <c r="V11" s="18"/>
+      <c r="V11" s="17"/>
       <c r="W11" s="16"/>
-      <c r="AC11" s="18"/>
+      <c r="AC11" s="17"/>
       <c r="AD11" s="16"/>
-      <c r="AJ11" s="18"/>
+      <c r="AJ11" s="17"/>
       <c r="AK11" s="16"/>
-      <c r="AQ11" s="18"/>
+      <c r="AQ11" s="17"/>
       <c r="AR11" s="16"/>
-      <c r="AX11" s="18"/>
+      <c r="AX11" s="17"/>
       <c r="AY11" s="16"/>
-      <c r="BE11" s="18"/>
+      <c r="BE11" s="17"/>
       <c r="BF11" s="16"/>
-      <c r="BL11" s="18"/>
+      <c r="BL11" s="17"/>
       <c r="BM11" s="16"/>
-      <c r="BS11" s="18"/>
+      <c r="BS11" s="17"/>
       <c r="BT11" s="16"/>
-      <c r="BZ11" s="18"/>
+      <c r="BZ11" s="17"/>
       <c r="CA11" s="16"/>
-      <c r="CG11" s="18"/>
+      <c r="CG11" s="17"/>
       <c r="CH11" s="16"/>
-      <c r="CN11" s="18"/>
+      <c r="CN11" s="17"/>
       <c r="CO11" s="16"/>
-      <c r="CU11" s="18"/>
+      <c r="CU11" s="17"/>
       <c r="CV11" s="16"/>
-      <c r="DB11" s="18"/>
+      <c r="DB11" s="45"/>
       <c r="DC11" s="16"/>
-      <c r="DD11" s="18"/>
-    </row>
-    <row r="12" spans="1:110" ht="15" x14ac:dyDescent="0.2">
-      <c r="A12" s="43" t="s">
+      <c r="DD11" s="45"/>
+      <c r="DE11" s="45"/>
+      <c r="DF11" s="45"/>
+      <c r="DG11" s="45"/>
+      <c r="DH11" s="45"/>
+      <c r="DI11" s="17"/>
+    </row>
+    <row r="12" spans="1:113" ht="15" x14ac:dyDescent="0.2">
+      <c r="A12" s="33" t="s">
         <v>6</v>
       </c>
       <c r="B12" s="16"/>
-      <c r="H12" s="18"/>
-      <c r="I12" s="22"/>
-      <c r="J12" s="23"/>
-      <c r="K12" s="23"/>
-      <c r="L12" s="23"/>
-      <c r="M12" s="23"/>
-      <c r="N12" s="23"/>
-      <c r="O12" s="24"/>
+      <c r="H12" s="17"/>
+      <c r="I12" s="21"/>
+      <c r="J12" s="22"/>
+      <c r="K12" s="22"/>
+      <c r="L12" s="22"/>
+      <c r="M12" s="22"/>
+      <c r="N12" s="22"/>
+      <c r="O12" s="23"/>
       <c r="P12" s="16"/>
-      <c r="V12" s="18"/>
+      <c r="V12" s="17"/>
       <c r="W12" s="16"/>
-      <c r="AC12" s="18"/>
+      <c r="AC12" s="17"/>
       <c r="AD12" s="16"/>
-      <c r="AJ12" s="18"/>
+      <c r="AJ12" s="17"/>
       <c r="AK12" s="16"/>
-      <c r="AQ12" s="18"/>
+      <c r="AQ12" s="17"/>
       <c r="AR12" s="16"/>
-      <c r="AX12" s="18"/>
+      <c r="AX12" s="17"/>
       <c r="AY12" s="16"/>
-      <c r="BE12" s="18"/>
+      <c r="BE12" s="17"/>
       <c r="BF12" s="16"/>
-      <c r="BL12" s="18"/>
+      <c r="BL12" s="17"/>
       <c r="BM12" s="16"/>
-      <c r="BS12" s="18"/>
+      <c r="BS12" s="17"/>
       <c r="BT12" s="16"/>
-      <c r="BZ12" s="18"/>
+      <c r="BZ12" s="17"/>
       <c r="CA12" s="16"/>
-      <c r="CG12" s="18"/>
+      <c r="CG12" s="17"/>
       <c r="CH12" s="16"/>
-      <c r="CN12" s="18"/>
+      <c r="CN12" s="17"/>
       <c r="CO12" s="16"/>
-      <c r="CU12" s="18"/>
+      <c r="CU12" s="17"/>
       <c r="CV12" s="16"/>
-      <c r="DB12" s="18"/>
+      <c r="DB12" s="45"/>
       <c r="DC12" s="16"/>
-      <c r="DD12" s="18"/>
-    </row>
-    <row r="13" spans="1:110" ht="15" x14ac:dyDescent="0.2">
-      <c r="A13" s="43" t="s">
+      <c r="DD12" s="45"/>
+      <c r="DE12" s="45"/>
+      <c r="DF12" s="45"/>
+      <c r="DG12" s="45"/>
+      <c r="DH12" s="45"/>
+      <c r="DI12" s="17"/>
+    </row>
+    <row r="13" spans="1:113" ht="15" x14ac:dyDescent="0.2">
+      <c r="A13" s="33" t="s">
         <v>11</v>
       </c>
       <c r="B13" s="16"/>
-      <c r="H13" s="18"/>
+      <c r="H13" s="17"/>
       <c r="I13" s="16"/>
-      <c r="O13" s="18"/>
-      <c r="P13" s="22"/>
-      <c r="Q13" s="23"/>
-      <c r="R13" s="23"/>
-      <c r="S13" s="23"/>
-      <c r="T13" s="23"/>
-      <c r="U13" s="23"/>
-      <c r="V13" s="24"/>
+      <c r="O13" s="17"/>
+      <c r="P13" s="21"/>
+      <c r="Q13" s="22"/>
+      <c r="R13" s="22"/>
+      <c r="S13" s="22"/>
+      <c r="T13" s="22"/>
+      <c r="U13" s="22"/>
+      <c r="V13" s="23"/>
       <c r="W13" s="16"/>
-      <c r="AC13" s="18"/>
+      <c r="AC13" s="17"/>
       <c r="AD13" s="16"/>
-      <c r="AJ13" s="18"/>
+      <c r="AJ13" s="17"/>
       <c r="AK13" s="16"/>
-      <c r="AQ13" s="18"/>
+      <c r="AQ13" s="17"/>
       <c r="AR13" s="16"/>
-      <c r="AX13" s="18"/>
+      <c r="AX13" s="17"/>
       <c r="AY13" s="16"/>
-      <c r="BE13" s="18"/>
+      <c r="BE13" s="17"/>
       <c r="BF13" s="16"/>
-      <c r="BL13" s="18"/>
+      <c r="BL13" s="17"/>
       <c r="BM13" s="16"/>
-      <c r="BS13" s="18"/>
+      <c r="BS13" s="17"/>
       <c r="BT13" s="16"/>
-      <c r="BZ13" s="18"/>
+      <c r="BZ13" s="17"/>
       <c r="CA13" s="16"/>
-      <c r="CG13" s="18"/>
+      <c r="CG13" s="17"/>
       <c r="CH13" s="16"/>
-      <c r="CN13" s="18"/>
+      <c r="CN13" s="17"/>
       <c r="CO13" s="16"/>
-      <c r="CU13" s="18"/>
+      <c r="CU13" s="17"/>
       <c r="CV13" s="16"/>
-      <c r="DB13" s="18"/>
+      <c r="DB13" s="45"/>
       <c r="DC13" s="16"/>
-      <c r="DD13" s="18"/>
-    </row>
-    <row r="14" spans="1:110" ht="15" x14ac:dyDescent="0.2">
-      <c r="A14" s="43" t="s">
+      <c r="DD13" s="45"/>
+      <c r="DE13" s="45"/>
+      <c r="DF13" s="45"/>
+      <c r="DG13" s="45"/>
+      <c r="DH13" s="45"/>
+      <c r="DI13" s="17"/>
+    </row>
+    <row r="14" spans="1:113" ht="15" x14ac:dyDescent="0.2">
+      <c r="A14" s="33" t="s">
         <v>7</v>
       </c>
       <c r="B14" s="16"/>
-      <c r="H14" s="18"/>
+      <c r="H14" s="17"/>
       <c r="I14" s="16"/>
-      <c r="O14" s="18"/>
-      <c r="P14" s="22"/>
-      <c r="Q14" s="23"/>
-      <c r="R14" s="23"/>
-      <c r="S14" s="23"/>
-      <c r="T14" s="23"/>
-      <c r="U14" s="23"/>
-      <c r="V14" s="24"/>
+      <c r="O14" s="17"/>
+      <c r="P14" s="21"/>
+      <c r="Q14" s="22"/>
+      <c r="R14" s="22"/>
+      <c r="S14" s="22"/>
+      <c r="T14" s="22"/>
+      <c r="U14" s="22"/>
+      <c r="V14" s="23"/>
       <c r="W14" s="16"/>
-      <c r="AC14" s="18"/>
+      <c r="AC14" s="17"/>
       <c r="AD14" s="16"/>
-      <c r="AJ14" s="18"/>
+      <c r="AJ14" s="17"/>
       <c r="AK14" s="16"/>
-      <c r="AQ14" s="18"/>
+      <c r="AQ14" s="17"/>
       <c r="AR14" s="16"/>
-      <c r="AX14" s="18"/>
+      <c r="AX14" s="17"/>
       <c r="AY14" s="16"/>
-      <c r="BE14" s="18"/>
+      <c r="BE14" s="17"/>
       <c r="BF14" s="16"/>
-      <c r="BL14" s="18"/>
+      <c r="BL14" s="17"/>
       <c r="BM14" s="16"/>
-      <c r="BS14" s="18"/>
+      <c r="BS14" s="17"/>
       <c r="BT14" s="16"/>
-      <c r="BZ14" s="18"/>
+      <c r="BZ14" s="17"/>
       <c r="CA14" s="16"/>
-      <c r="CG14" s="18"/>
+      <c r="CG14" s="17"/>
       <c r="CH14" s="16"/>
-      <c r="CN14" s="18"/>
+      <c r="CN14" s="17"/>
       <c r="CO14" s="16"/>
-      <c r="CU14" s="18"/>
+      <c r="CU14" s="17"/>
       <c r="CV14" s="16"/>
-      <c r="DB14" s="18"/>
+      <c r="DB14" s="45"/>
       <c r="DC14" s="16"/>
-      <c r="DD14" s="18"/>
-    </row>
-    <row r="15" spans="1:110" ht="15" x14ac:dyDescent="0.2">
-      <c r="A15" s="43" t="s">
+      <c r="DD14" s="45"/>
+      <c r="DE14" s="45"/>
+      <c r="DF14" s="45"/>
+      <c r="DG14" s="45"/>
+      <c r="DH14" s="45"/>
+      <c r="DI14" s="17"/>
+    </row>
+    <row r="15" spans="1:113" ht="15" x14ac:dyDescent="0.2">
+      <c r="A15" s="33" t="s">
         <v>8</v>
       </c>
       <c r="B15" s="16"/>
-      <c r="H15" s="18"/>
+      <c r="H15" s="17"/>
       <c r="I15" s="16"/>
-      <c r="O15" s="18"/>
+      <c r="O15" s="17"/>
       <c r="P15" s="16"/>
-      <c r="V15" s="18"/>
-      <c r="W15" s="22"/>
-      <c r="X15" s="23"/>
-      <c r="Y15" s="23"/>
-      <c r="Z15" s="23"/>
-      <c r="AA15" s="23"/>
-      <c r="AB15" s="23"/>
-      <c r="AC15" s="24"/>
+      <c r="V15" s="17"/>
+      <c r="W15" s="21"/>
+      <c r="X15" s="22"/>
+      <c r="Y15" s="22"/>
+      <c r="Z15" s="22"/>
+      <c r="AA15" s="22"/>
+      <c r="AB15" s="22"/>
+      <c r="AC15" s="23"/>
       <c r="AD15" s="16"/>
-      <c r="AJ15" s="18"/>
+      <c r="AJ15" s="17"/>
       <c r="AK15" s="16"/>
-      <c r="AQ15" s="18"/>
+      <c r="AQ15" s="17"/>
       <c r="AR15" s="16"/>
-      <c r="AX15" s="18"/>
+      <c r="AX15" s="17"/>
       <c r="AY15" s="16"/>
-      <c r="BE15" s="18"/>
+      <c r="BE15" s="17"/>
       <c r="BF15" s="16"/>
-      <c r="BL15" s="18"/>
+      <c r="BL15" s="17"/>
       <c r="BM15" s="16"/>
-      <c r="BS15" s="18"/>
+      <c r="BS15" s="17"/>
       <c r="BT15" s="16"/>
-      <c r="BZ15" s="18"/>
+      <c r="BZ15" s="17"/>
       <c r="CA15" s="16"/>
-      <c r="CG15" s="18"/>
+      <c r="CG15" s="17"/>
       <c r="CH15" s="16"/>
-      <c r="CN15" s="18"/>
+      <c r="CN15" s="17"/>
       <c r="CO15" s="16"/>
-      <c r="CU15" s="18"/>
+      <c r="CU15" s="17"/>
       <c r="CV15" s="16"/>
-      <c r="DB15" s="18"/>
+      <c r="DB15" s="45"/>
       <c r="DC15" s="16"/>
-      <c r="DD15" s="18"/>
-    </row>
-    <row r="16" spans="1:110" ht="15" x14ac:dyDescent="0.2">
-      <c r="A16" s="43" t="s">
+      <c r="DD15" s="45"/>
+      <c r="DE15" s="45"/>
+      <c r="DF15" s="45"/>
+      <c r="DG15" s="45"/>
+      <c r="DH15" s="45"/>
+      <c r="DI15" s="17"/>
+    </row>
+    <row r="16" spans="1:113" ht="15" x14ac:dyDescent="0.2">
+      <c r="A16" s="33" t="s">
         <v>10</v>
       </c>
       <c r="B16" s="16"/>
-      <c r="H16" s="18"/>
+      <c r="H16" s="17"/>
       <c r="I16" s="16"/>
-      <c r="O16" s="18"/>
+      <c r="O16" s="17"/>
       <c r="P16" s="16"/>
-      <c r="V16" s="18"/>
+      <c r="V16" s="17"/>
       <c r="W16" s="16"/>
-      <c r="AC16" s="18"/>
-      <c r="AD16" s="22"/>
-      <c r="AE16" s="23"/>
-      <c r="AF16" s="23"/>
-      <c r="AG16" s="23"/>
-      <c r="AH16" s="23"/>
-      <c r="AI16" s="23"/>
-      <c r="AJ16" s="24"/>
+      <c r="AC16" s="17"/>
+      <c r="AD16" s="21"/>
+      <c r="AE16" s="22"/>
+      <c r="AF16" s="22"/>
+      <c r="AG16" s="22"/>
+      <c r="AH16" s="22"/>
+      <c r="AI16" s="22"/>
+      <c r="AJ16" s="23"/>
       <c r="AK16" s="16"/>
-      <c r="AQ16" s="18"/>
+      <c r="AQ16" s="17"/>
       <c r="AR16" s="16"/>
-      <c r="AX16" s="18"/>
+      <c r="AX16" s="17"/>
       <c r="AY16" s="16"/>
-      <c r="BE16" s="18"/>
+      <c r="BE16" s="17"/>
       <c r="BF16" s="16"/>
-      <c r="BL16" s="18"/>
+      <c r="BL16" s="17"/>
       <c r="BM16" s="16"/>
-      <c r="BS16" s="18"/>
+      <c r="BS16" s="17"/>
       <c r="BT16" s="16"/>
-      <c r="BZ16" s="18"/>
+      <c r="BZ16" s="17"/>
       <c r="CA16" s="16"/>
-      <c r="CG16" s="18"/>
+      <c r="CG16" s="17"/>
       <c r="CH16" s="16"/>
-      <c r="CN16" s="18"/>
+      <c r="CN16" s="17"/>
       <c r="CO16" s="16"/>
-      <c r="CU16" s="18"/>
+      <c r="CU16" s="17"/>
       <c r="CV16" s="16"/>
-      <c r="DB16" s="18"/>
+      <c r="DB16" s="45"/>
       <c r="DC16" s="16"/>
-      <c r="DD16" s="18"/>
-    </row>
-    <row r="17" spans="1:108" ht="15" x14ac:dyDescent="0.2">
-      <c r="A17" s="43" t="s">
+      <c r="DD16" s="45"/>
+      <c r="DE16" s="45"/>
+      <c r="DF16" s="45"/>
+      <c r="DG16" s="45"/>
+      <c r="DH16" s="45"/>
+      <c r="DI16" s="17"/>
+    </row>
+    <row r="17" spans="1:113" ht="15" x14ac:dyDescent="0.2">
+      <c r="A17" s="33" t="s">
         <v>9</v>
       </c>
       <c r="B17" s="16"/>
-      <c r="H17" s="18"/>
+      <c r="H17" s="17"/>
       <c r="I17" s="16"/>
-      <c r="O17" s="18"/>
+      <c r="O17" s="17"/>
       <c r="P17" s="16"/>
-      <c r="V17" s="18"/>
+      <c r="V17" s="17"/>
       <c r="W17" s="16"/>
-      <c r="AC17" s="18"/>
+      <c r="AC17" s="17"/>
       <c r="AD17" s="16"/>
-      <c r="AJ17" s="18"/>
-      <c r="AK17" s="22"/>
-      <c r="AL17" s="23"/>
-      <c r="AM17" s="23"/>
-      <c r="AN17" s="23"/>
-      <c r="AO17" s="23"/>
-      <c r="AP17" s="23"/>
-      <c r="AQ17" s="24"/>
+      <c r="AJ17" s="17"/>
+      <c r="AK17" s="21"/>
+      <c r="AL17" s="22"/>
+      <c r="AM17" s="22"/>
+      <c r="AN17" s="22"/>
+      <c r="AO17" s="22"/>
+      <c r="AP17" s="22"/>
+      <c r="AQ17" s="23"/>
       <c r="AR17" s="16"/>
-      <c r="AX17" s="18"/>
+      <c r="AX17" s="17"/>
       <c r="AY17" s="16"/>
-      <c r="BE17" s="18"/>
+      <c r="BE17" s="17"/>
       <c r="BF17" s="16"/>
-      <c r="BL17" s="18"/>
+      <c r="BL17" s="17"/>
       <c r="BM17" s="16"/>
-      <c r="BS17" s="18"/>
+      <c r="BS17" s="17"/>
       <c r="BT17" s="16"/>
-      <c r="BZ17" s="18"/>
+      <c r="BZ17" s="17"/>
       <c r="CA17" s="16"/>
-      <c r="CG17" s="18"/>
+      <c r="CG17" s="17"/>
       <c r="CH17" s="16"/>
-      <c r="CN17" s="18"/>
+      <c r="CN17" s="17"/>
       <c r="CO17" s="16"/>
-      <c r="CU17" s="18"/>
+      <c r="CU17" s="17"/>
       <c r="CV17" s="16"/>
-      <c r="DB17" s="18"/>
+      <c r="DB17" s="45"/>
       <c r="DC17" s="16"/>
-      <c r="DD17" s="18"/>
-    </row>
-    <row r="18" spans="1:108" ht="15" x14ac:dyDescent="0.2">
-      <c r="A18" s="43" t="s">
+      <c r="DD17" s="45"/>
+      <c r="DE17" s="45"/>
+      <c r="DF17" s="45"/>
+      <c r="DG17" s="45"/>
+      <c r="DH17" s="45"/>
+      <c r="DI17" s="17"/>
+    </row>
+    <row r="18" spans="1:113" ht="15" x14ac:dyDescent="0.2">
+      <c r="A18" s="33" t="s">
         <v>12</v>
       </c>
       <c r="B18" s="16"/>
-      <c r="H18" s="18"/>
+      <c r="H18" s="17"/>
       <c r="I18" s="16"/>
-      <c r="O18" s="18"/>
+      <c r="O18" s="17"/>
       <c r="P18" s="16"/>
-      <c r="V18" s="18"/>
+      <c r="V18" s="17"/>
       <c r="W18" s="16"/>
-      <c r="AC18" s="18"/>
+      <c r="AC18" s="17"/>
       <c r="AD18" s="16"/>
-      <c r="AJ18" s="18"/>
-      <c r="AK18" s="22"/>
-      <c r="AL18" s="23"/>
-      <c r="AM18" s="23"/>
-      <c r="AN18" s="23"/>
-      <c r="AO18" s="23"/>
-      <c r="AP18" s="23"/>
-      <c r="AQ18" s="24"/>
-      <c r="AR18" s="22"/>
-      <c r="AS18" s="23"/>
-      <c r="AT18" s="23"/>
-      <c r="AU18" s="23"/>
-      <c r="AV18" s="23"/>
-      <c r="AW18" s="23"/>
-      <c r="AX18" s="24"/>
-      <c r="AY18" s="22"/>
-      <c r="AZ18" s="23"/>
-      <c r="BA18" s="23"/>
-      <c r="BB18" s="23"/>
-      <c r="BC18" s="23"/>
-      <c r="BD18" s="23"/>
-      <c r="BE18" s="24"/>
+      <c r="AJ18" s="17"/>
+      <c r="AK18" s="21"/>
+      <c r="AL18" s="22"/>
+      <c r="AM18" s="22"/>
+      <c r="AN18" s="22"/>
+      <c r="AO18" s="22"/>
+      <c r="AP18" s="22"/>
+      <c r="AQ18" s="23"/>
+      <c r="AR18" s="21"/>
+      <c r="AS18" s="22"/>
+      <c r="AT18" s="22"/>
+      <c r="AU18" s="22"/>
+      <c r="AV18" s="22"/>
+      <c r="AW18" s="22"/>
+      <c r="AX18" s="23"/>
+      <c r="AY18" s="21"/>
+      <c r="AZ18" s="22"/>
+      <c r="BA18" s="22"/>
+      <c r="BB18" s="22"/>
+      <c r="BC18" s="22"/>
+      <c r="BD18" s="22"/>
+      <c r="BE18" s="23"/>
       <c r="BF18" s="16"/>
-      <c r="BL18" s="18"/>
+      <c r="BL18" s="17"/>
       <c r="BM18" s="16"/>
-      <c r="BS18" s="18"/>
+      <c r="BS18" s="17"/>
       <c r="BT18" s="16"/>
-      <c r="BZ18" s="18"/>
+      <c r="BZ18" s="17"/>
       <c r="CA18" s="16"/>
-      <c r="CG18" s="18"/>
+      <c r="CG18" s="17"/>
       <c r="CH18" s="16"/>
-      <c r="CN18" s="18"/>
+      <c r="CN18" s="17"/>
       <c r="CO18" s="16"/>
-      <c r="CU18" s="18"/>
+      <c r="CU18" s="17"/>
       <c r="CV18" s="16"/>
-      <c r="DB18" s="18"/>
+      <c r="DB18" s="45"/>
       <c r="DC18" s="16"/>
-      <c r="DD18" s="18"/>
-    </row>
-    <row r="19" spans="1:108" ht="15" x14ac:dyDescent="0.2">
-      <c r="A19" s="43" t="s">
+      <c r="DD18" s="45"/>
+      <c r="DE18" s="45"/>
+      <c r="DF18" s="45"/>
+      <c r="DG18" s="45"/>
+      <c r="DH18" s="45"/>
+      <c r="DI18" s="17"/>
+    </row>
+    <row r="19" spans="1:113" ht="15" x14ac:dyDescent="0.2">
+      <c r="A19" s="33" t="s">
         <v>13</v>
       </c>
       <c r="B19" s="16"/>
-      <c r="H19" s="18"/>
+      <c r="H19" s="17"/>
       <c r="I19" s="16"/>
-      <c r="O19" s="18"/>
+      <c r="O19" s="17"/>
       <c r="P19" s="16"/>
-      <c r="V19" s="18"/>
+      <c r="V19" s="17"/>
       <c r="W19" s="16"/>
-      <c r="AC19" s="18"/>
+      <c r="AC19" s="17"/>
       <c r="AD19" s="16"/>
-      <c r="AJ19" s="18"/>
-      <c r="AK19" s="22"/>
-      <c r="AL19" s="23"/>
-      <c r="AM19" s="23"/>
-      <c r="AN19" s="23"/>
-      <c r="AO19" s="23"/>
-      <c r="AP19" s="23"/>
-      <c r="AQ19" s="24"/>
-      <c r="AR19" s="22"/>
-      <c r="AS19" s="23"/>
-      <c r="AT19" s="23"/>
-      <c r="AU19" s="23"/>
-      <c r="AV19" s="23"/>
-      <c r="AW19" s="23"/>
-      <c r="AX19" s="24"/>
-      <c r="AY19" s="22"/>
-      <c r="AZ19" s="23"/>
-      <c r="BA19" s="23"/>
-      <c r="BB19" s="23"/>
-      <c r="BC19" s="23"/>
-      <c r="BD19" s="23"/>
-      <c r="BE19" s="24"/>
+      <c r="AJ19" s="17"/>
+      <c r="AK19" s="21"/>
+      <c r="AL19" s="22"/>
+      <c r="AM19" s="22"/>
+      <c r="AN19" s="22"/>
+      <c r="AO19" s="22"/>
+      <c r="AP19" s="22"/>
+      <c r="AQ19" s="23"/>
+      <c r="AR19" s="21"/>
+      <c r="AS19" s="22"/>
+      <c r="AT19" s="22"/>
+      <c r="AU19" s="22"/>
+      <c r="AV19" s="22"/>
+      <c r="AW19" s="22"/>
+      <c r="AX19" s="23"/>
+      <c r="AY19" s="21"/>
+      <c r="AZ19" s="22"/>
+      <c r="BA19" s="22"/>
+      <c r="BB19" s="22"/>
+      <c r="BC19" s="22"/>
+      <c r="BD19" s="22"/>
+      <c r="BE19" s="23"/>
       <c r="BF19" s="16"/>
-      <c r="BL19" s="18"/>
+      <c r="BL19" s="17"/>
       <c r="BM19" s="16"/>
-      <c r="BS19" s="18"/>
+      <c r="BS19" s="17"/>
       <c r="BT19" s="16"/>
-      <c r="BZ19" s="18"/>
+      <c r="BZ19" s="17"/>
       <c r="CA19" s="16"/>
-      <c r="CG19" s="18"/>
+      <c r="CG19" s="17"/>
       <c r="CH19" s="16"/>
-      <c r="CN19" s="18"/>
+      <c r="CN19" s="17"/>
       <c r="CO19" s="16"/>
-      <c r="CU19" s="18"/>
+      <c r="CU19" s="17"/>
       <c r="CV19" s="16"/>
-      <c r="DB19" s="18"/>
+      <c r="DB19" s="45"/>
       <c r="DC19" s="16"/>
-      <c r="DD19" s="18"/>
-    </row>
-    <row r="20" spans="1:108" ht="15" x14ac:dyDescent="0.2">
-      <c r="A20" s="43" t="s">
+      <c r="DD19" s="45"/>
+      <c r="DE19" s="45"/>
+      <c r="DF19" s="45"/>
+      <c r="DG19" s="45"/>
+      <c r="DH19" s="45"/>
+      <c r="DI19" s="17"/>
+    </row>
+    <row r="20" spans="1:113" ht="15" x14ac:dyDescent="0.2">
+      <c r="A20" s="33" t="s">
         <v>14</v>
       </c>
       <c r="B20" s="16"/>
-      <c r="H20" s="18"/>
+      <c r="H20" s="17"/>
       <c r="I20" s="16"/>
-      <c r="O20" s="18"/>
+      <c r="O20" s="17"/>
       <c r="P20" s="16"/>
-      <c r="V20" s="18"/>
+      <c r="V20" s="17"/>
       <c r="W20" s="16"/>
-      <c r="AC20" s="18"/>
+      <c r="AC20" s="17"/>
       <c r="AD20" s="16"/>
-      <c r="AJ20" s="18"/>
+      <c r="AJ20" s="17"/>
       <c r="AK20" s="16"/>
-      <c r="AQ20" s="18"/>
-      <c r="AR20" s="22"/>
-      <c r="AS20" s="23"/>
-      <c r="AT20" s="23"/>
-      <c r="AU20" s="23"/>
-      <c r="AV20" s="23"/>
-      <c r="AW20" s="23"/>
-      <c r="AX20" s="24"/>
+      <c r="AQ20" s="17"/>
+      <c r="AR20" s="21"/>
+      <c r="AS20" s="22"/>
+      <c r="AT20" s="22"/>
+      <c r="AU20" s="22"/>
+      <c r="AV20" s="22"/>
+      <c r="AW20" s="22"/>
+      <c r="AX20" s="23"/>
       <c r="AY20" s="16"/>
-      <c r="BE20" s="18"/>
+      <c r="BE20" s="17"/>
       <c r="BF20" s="16"/>
-      <c r="BL20" s="18"/>
+      <c r="BL20" s="17"/>
       <c r="BM20" s="16"/>
-      <c r="BS20" s="18"/>
+      <c r="BS20" s="17"/>
       <c r="BT20" s="16"/>
-      <c r="BZ20" s="18"/>
+      <c r="BZ20" s="17"/>
       <c r="CA20" s="16"/>
-      <c r="CG20" s="18"/>
+      <c r="CG20" s="17"/>
       <c r="CH20" s="16"/>
-      <c r="CN20" s="18"/>
+      <c r="CN20" s="17"/>
       <c r="CO20" s="16"/>
-      <c r="CU20" s="18"/>
+      <c r="CU20" s="17"/>
       <c r="CV20" s="16"/>
-      <c r="DB20" s="18"/>
+      <c r="DB20" s="45"/>
       <c r="DC20" s="16"/>
-      <c r="DD20" s="18"/>
-    </row>
-    <row r="21" spans="1:108" ht="15" x14ac:dyDescent="0.2">
-      <c r="A21" s="43" t="s">
+      <c r="DD20" s="45"/>
+      <c r="DE20" s="45"/>
+      <c r="DF20" s="45"/>
+      <c r="DG20" s="45"/>
+      <c r="DH20" s="45"/>
+      <c r="DI20" s="17"/>
+    </row>
+    <row r="21" spans="1:113" ht="15" x14ac:dyDescent="0.2">
+      <c r="A21" s="33" t="s">
         <v>15</v>
       </c>
       <c r="B21" s="16"/>
-      <c r="H21" s="18"/>
+      <c r="H21" s="17"/>
       <c r="I21" s="16"/>
-      <c r="O21" s="18"/>
+      <c r="O21" s="17"/>
       <c r="P21" s="16"/>
-      <c r="V21" s="18"/>
+      <c r="V21" s="17"/>
       <c r="W21" s="16"/>
-      <c r="AC21" s="18"/>
+      <c r="AC21" s="17"/>
       <c r="AD21" s="16"/>
-      <c r="AJ21" s="18"/>
+      <c r="AJ21" s="17"/>
       <c r="AK21" s="16"/>
-      <c r="AQ21" s="18"/>
+      <c r="AQ21" s="17"/>
       <c r="AR21" s="16"/>
-      <c r="AX21" s="18"/>
+      <c r="AX21" s="17"/>
       <c r="AY21" s="16"/>
-      <c r="BE21" s="18"/>
-      <c r="BF21" s="22"/>
-      <c r="BG21" s="23"/>
-      <c r="BH21" s="23"/>
-      <c r="BI21" s="23"/>
-      <c r="BJ21" s="23"/>
-      <c r="BK21" s="23"/>
-      <c r="BL21" s="24"/>
+      <c r="BE21" s="17"/>
+      <c r="BF21" s="21"/>
+      <c r="BG21" s="22"/>
+      <c r="BH21" s="22"/>
+      <c r="BI21" s="22"/>
+      <c r="BJ21" s="22"/>
+      <c r="BK21" s="22"/>
+      <c r="BL21" s="23"/>
       <c r="BM21" s="16"/>
-      <c r="BS21" s="18"/>
+      <c r="BS21" s="17"/>
       <c r="BT21" s="16"/>
-      <c r="BZ21" s="18"/>
+      <c r="BZ21" s="17"/>
       <c r="CA21" s="16"/>
-      <c r="CG21" s="18"/>
+      <c r="CG21" s="17"/>
       <c r="CH21" s="16"/>
-      <c r="CN21" s="18"/>
+      <c r="CN21" s="17"/>
       <c r="CO21" s="16"/>
-      <c r="CU21" s="18"/>
+      <c r="CU21" s="17"/>
       <c r="CV21" s="16"/>
-      <c r="DB21" s="18"/>
+      <c r="DB21" s="45"/>
       <c r="DC21" s="16"/>
-      <c r="DD21" s="18"/>
-    </row>
-    <row r="22" spans="1:108" ht="15" x14ac:dyDescent="0.2">
-      <c r="A22" s="43" t="s">
+      <c r="DD21" s="45"/>
+      <c r="DE21" s="45"/>
+      <c r="DF21" s="45"/>
+      <c r="DG21" s="45"/>
+      <c r="DH21" s="45"/>
+      <c r="DI21" s="17"/>
+    </row>
+    <row r="22" spans="1:113" ht="15" x14ac:dyDescent="0.2">
+      <c r="A22" s="33" t="s">
         <v>16</v>
       </c>
       <c r="B22" s="16"/>
-      <c r="H22" s="18"/>
+      <c r="H22" s="17"/>
       <c r="I22" s="16"/>
-      <c r="O22" s="18"/>
+      <c r="O22" s="17"/>
       <c r="P22" s="16"/>
-      <c r="V22" s="18"/>
+      <c r="V22" s="17"/>
       <c r="W22" s="16"/>
-      <c r="AC22" s="18"/>
+      <c r="AC22" s="17"/>
       <c r="AD22" s="16"/>
-      <c r="AJ22" s="18"/>
+      <c r="AJ22" s="17"/>
       <c r="AK22" s="16"/>
-      <c r="AQ22" s="18"/>
+      <c r="AQ22" s="17"/>
       <c r="AR22" s="16"/>
-      <c r="AX22" s="18"/>
+      <c r="AX22" s="17"/>
       <c r="AY22" s="16"/>
-      <c r="BE22" s="18"/>
-      <c r="BF22" s="22"/>
-      <c r="BG22" s="23"/>
-      <c r="BH22" s="23"/>
-      <c r="BI22" s="23"/>
-      <c r="BJ22" s="23"/>
-      <c r="BK22" s="23"/>
-      <c r="BL22" s="24"/>
+      <c r="BE22" s="17"/>
+      <c r="BF22" s="21"/>
+      <c r="BG22" s="22"/>
+      <c r="BH22" s="22"/>
+      <c r="BI22" s="22"/>
+      <c r="BJ22" s="22"/>
+      <c r="BK22" s="22"/>
+      <c r="BL22" s="23"/>
       <c r="BM22" s="16"/>
-      <c r="BS22" s="18"/>
+      <c r="BS22" s="17"/>
       <c r="BT22" s="16"/>
-      <c r="BZ22" s="18"/>
+      <c r="BZ22" s="17"/>
       <c r="CA22" s="16"/>
-      <c r="CG22" s="18"/>
+      <c r="CG22" s="17"/>
       <c r="CH22" s="16"/>
-      <c r="CN22" s="18"/>
+      <c r="CN22" s="17"/>
       <c r="CO22" s="16"/>
-      <c r="CU22" s="18"/>
+      <c r="CU22" s="17"/>
       <c r="CV22" s="16"/>
-      <c r="DB22" s="18"/>
+      <c r="DB22" s="45"/>
       <c r="DC22" s="16"/>
-      <c r="DD22" s="18"/>
-    </row>
-    <row r="23" spans="1:108" ht="15" x14ac:dyDescent="0.2">
-      <c r="A23" s="43" t="s">
+      <c r="DD22" s="45"/>
+      <c r="DE22" s="45"/>
+      <c r="DF22" s="45"/>
+      <c r="DG22" s="45"/>
+      <c r="DH22" s="45"/>
+      <c r="DI22" s="17"/>
+    </row>
+    <row r="23" spans="1:113" ht="15" x14ac:dyDescent="0.2">
+      <c r="A23" s="33" t="s">
         <v>12</v>
       </c>
       <c r="B23" s="16"/>
-      <c r="H23" s="18"/>
+      <c r="H23" s="17"/>
       <c r="I23" s="16"/>
-      <c r="O23" s="18"/>
+      <c r="O23" s="17"/>
       <c r="P23" s="16"/>
-      <c r="V23" s="18"/>
+      <c r="V23" s="17"/>
       <c r="W23" s="16"/>
-      <c r="AC23" s="18"/>
+      <c r="AC23" s="17"/>
       <c r="AD23" s="16"/>
-      <c r="AJ23" s="18"/>
+      <c r="AJ23" s="17"/>
       <c r="AK23" s="16"/>
-      <c r="AQ23" s="18"/>
+      <c r="AQ23" s="17"/>
       <c r="AR23" s="16"/>
-      <c r="AX23" s="18"/>
+      <c r="AX23" s="17"/>
       <c r="AY23" s="16"/>
-      <c r="BE23" s="18"/>
+      <c r="BE23" s="17"/>
       <c r="BF23" s="16"/>
-      <c r="BL23" s="18"/>
-      <c r="BM23" s="22"/>
-      <c r="BN23" s="23"/>
-      <c r="BO23" s="23"/>
-      <c r="BP23" s="23"/>
-      <c r="BQ23" s="23"/>
-      <c r="BR23" s="23"/>
-      <c r="BS23" s="24"/>
-      <c r="BT23" s="22"/>
-      <c r="BU23" s="23"/>
-      <c r="BV23" s="23"/>
-      <c r="BW23" s="23"/>
-      <c r="BX23" s="23"/>
-      <c r="BY23" s="23"/>
-      <c r="BZ23" s="24"/>
-      <c r="CA23" s="22"/>
-      <c r="CB23" s="23"/>
-      <c r="CC23" s="23"/>
-      <c r="CD23" s="23"/>
-      <c r="CE23" s="23"/>
-      <c r="CF23" s="23"/>
-      <c r="CG23" s="24"/>
-      <c r="CH23" s="22"/>
-      <c r="CI23" s="23"/>
-      <c r="CJ23" s="23"/>
-      <c r="CK23" s="23"/>
-      <c r="CL23" s="23"/>
-      <c r="CM23" s="23"/>
-      <c r="CN23" s="24"/>
-      <c r="CO23" s="16"/>
-      <c r="CU23" s="18"/>
+      <c r="BL23" s="17"/>
+      <c r="BM23" s="21"/>
+      <c r="BN23" s="22"/>
+      <c r="BO23" s="22"/>
+      <c r="BP23" s="22"/>
+      <c r="BQ23" s="22"/>
+      <c r="BR23" s="22"/>
+      <c r="BS23" s="23"/>
+      <c r="BT23" s="21"/>
+      <c r="BU23" s="22"/>
+      <c r="BV23" s="22"/>
+      <c r="BW23" s="22"/>
+      <c r="BX23" s="22"/>
+      <c r="BY23" s="22"/>
+      <c r="BZ23" s="23"/>
+      <c r="CA23" s="21"/>
+      <c r="CB23" s="22"/>
+      <c r="CC23" s="22"/>
+      <c r="CD23" s="22"/>
+      <c r="CE23" s="22"/>
+      <c r="CF23" s="22"/>
+      <c r="CG23" s="23"/>
+      <c r="CH23" s="21"/>
+      <c r="CI23" s="22"/>
+      <c r="CJ23" s="22"/>
+      <c r="CK23" s="22"/>
+      <c r="CL23" s="22"/>
+      <c r="CM23" s="22"/>
+      <c r="CN23" s="23"/>
+      <c r="CO23" s="23"/>
+      <c r="CP23" s="23"/>
+      <c r="CQ23" s="23"/>
+      <c r="CR23" s="23"/>
+      <c r="CS23" s="23"/>
+      <c r="CT23" s="23"/>
+      <c r="CU23" s="23"/>
       <c r="CV23" s="16"/>
-      <c r="DB23" s="18"/>
+      <c r="DB23" s="45"/>
       <c r="DC23" s="16"/>
-      <c r="DD23" s="18"/>
-    </row>
-    <row r="24" spans="1:108" ht="15" x14ac:dyDescent="0.2">
-      <c r="A24" s="43" t="s">
+      <c r="DD23" s="45"/>
+      <c r="DE23" s="45"/>
+      <c r="DF23" s="45"/>
+      <c r="DG23" s="45"/>
+      <c r="DH23" s="45"/>
+      <c r="DI23" s="17"/>
+    </row>
+    <row r="24" spans="1:113" ht="15" x14ac:dyDescent="0.2">
+      <c r="A24" s="33" t="s">
         <v>13</v>
       </c>
       <c r="B24" s="16"/>
-      <c r="H24" s="18"/>
+      <c r="H24" s="17"/>
       <c r="I24" s="16"/>
-      <c r="O24" s="18"/>
+      <c r="O24" s="17"/>
       <c r="P24" s="16"/>
-      <c r="V24" s="18"/>
+      <c r="V24" s="17"/>
       <c r="W24" s="16"/>
-      <c r="AC24" s="18"/>
+      <c r="AC24" s="17"/>
       <c r="AD24" s="16"/>
-      <c r="AJ24" s="18"/>
+      <c r="AJ24" s="17"/>
       <c r="AK24" s="16"/>
-      <c r="AQ24" s="18"/>
+      <c r="AQ24" s="17"/>
       <c r="AR24" s="16"/>
-      <c r="AX24" s="18"/>
+      <c r="AX24" s="17"/>
       <c r="AY24" s="16"/>
-      <c r="BE24" s="18"/>
+      <c r="BE24" s="17"/>
       <c r="BF24" s="16"/>
-      <c r="BL24" s="18"/>
-      <c r="BM24" s="22"/>
-      <c r="BN24" s="23"/>
-      <c r="BO24" s="23"/>
-      <c r="BP24" s="23"/>
-      <c r="BQ24" s="23"/>
-      <c r="BR24" s="23"/>
-      <c r="BS24" s="24"/>
-      <c r="BT24" s="22"/>
-      <c r="BU24" s="23"/>
-      <c r="BV24" s="23"/>
-      <c r="BW24" s="23"/>
-      <c r="BX24" s="23"/>
-      <c r="BY24" s="23"/>
-      <c r="BZ24" s="24"/>
-      <c r="CA24" s="22"/>
-      <c r="CB24" s="23"/>
-      <c r="CC24" s="23"/>
-      <c r="CD24" s="23"/>
-      <c r="CE24" s="23"/>
-      <c r="CF24" s="23"/>
-      <c r="CG24" s="24"/>
-      <c r="CH24" s="22"/>
-      <c r="CI24" s="23"/>
-      <c r="CJ24" s="23"/>
-      <c r="CK24" s="23"/>
-      <c r="CL24" s="23"/>
-      <c r="CM24" s="23"/>
-      <c r="CN24" s="24"/>
-      <c r="CO24" s="16"/>
-      <c r="CU24" s="18"/>
+      <c r="BL24" s="17"/>
+      <c r="BM24" s="21"/>
+      <c r="BN24" s="22"/>
+      <c r="BO24" s="22"/>
+      <c r="BP24" s="22"/>
+      <c r="BQ24" s="22"/>
+      <c r="BR24" s="22"/>
+      <c r="BS24" s="23"/>
+      <c r="BT24" s="21"/>
+      <c r="BU24" s="22"/>
+      <c r="BV24" s="22"/>
+      <c r="BW24" s="22"/>
+      <c r="BX24" s="22"/>
+      <c r="BY24" s="22"/>
+      <c r="BZ24" s="23"/>
+      <c r="CA24" s="21"/>
+      <c r="CB24" s="22"/>
+      <c r="CC24" s="22"/>
+      <c r="CD24" s="22"/>
+      <c r="CE24" s="22"/>
+      <c r="CF24" s="22"/>
+      <c r="CG24" s="23"/>
+      <c r="CH24" s="21"/>
+      <c r="CI24" s="22"/>
+      <c r="CJ24" s="22"/>
+      <c r="CK24" s="22"/>
+      <c r="CL24" s="22"/>
+      <c r="CM24" s="22"/>
+      <c r="CN24" s="23"/>
+      <c r="CO24" s="23"/>
+      <c r="CP24" s="23"/>
+      <c r="CQ24" s="23"/>
+      <c r="CR24" s="23"/>
+      <c r="CS24" s="23"/>
+      <c r="CT24" s="23"/>
+      <c r="CU24" s="23"/>
       <c r="CV24" s="16"/>
-      <c r="DB24" s="18"/>
+      <c r="DB24" s="45"/>
       <c r="DC24" s="16"/>
-      <c r="DD24" s="18"/>
-    </row>
-    <row r="25" spans="1:108" ht="15" x14ac:dyDescent="0.2">
-      <c r="A25" s="43" t="s">
+      <c r="DD24" s="45"/>
+      <c r="DE24" s="45"/>
+      <c r="DF24" s="45"/>
+      <c r="DG24" s="45"/>
+      <c r="DH24" s="45"/>
+      <c r="DI24" s="17"/>
+    </row>
+    <row r="25" spans="1:113" ht="15" x14ac:dyDescent="0.2">
+      <c r="A25" s="33" t="s">
         <v>17</v>
       </c>
       <c r="B25" s="16"/>
-      <c r="H25" s="18"/>
+      <c r="H25" s="17"/>
       <c r="I25" s="16"/>
-      <c r="O25" s="18"/>
+      <c r="O25" s="17"/>
       <c r="P25" s="16"/>
-      <c r="V25" s="18"/>
+      <c r="V25" s="17"/>
       <c r="W25" s="16"/>
-      <c r="AC25" s="18"/>
+      <c r="AC25" s="17"/>
       <c r="AD25" s="16"/>
-      <c r="AJ25" s="18"/>
+      <c r="AJ25" s="17"/>
       <c r="AK25" s="16"/>
-      <c r="AQ25" s="18"/>
+      <c r="AQ25" s="17"/>
       <c r="AR25" s="16"/>
-      <c r="AX25" s="18"/>
+      <c r="AX25" s="17"/>
       <c r="AY25" s="16"/>
-      <c r="BE25" s="18"/>
+      <c r="BE25" s="17"/>
       <c r="BF25" s="16"/>
-      <c r="BL25" s="18"/>
+      <c r="BL25" s="17"/>
       <c r="BM25" s="16"/>
-      <c r="BS25" s="18"/>
+      <c r="BS25" s="17"/>
       <c r="BT25" s="16"/>
-      <c r="BZ25" s="18"/>
+      <c r="BZ25" s="17"/>
       <c r="CA25" s="16"/>
-      <c r="CG25" s="18"/>
+      <c r="CG25" s="17"/>
       <c r="CH25" s="16"/>
-      <c r="CN25" s="18"/>
-      <c r="CO25" s="22"/>
-      <c r="CP25" s="23"/>
-      <c r="CQ25" s="23"/>
-      <c r="CR25" s="23"/>
-      <c r="CS25" s="23"/>
-      <c r="CT25" s="23"/>
-      <c r="CU25" s="24"/>
-      <c r="CV25" s="16"/>
-      <c r="DB25" s="18"/>
+      <c r="CN25" s="17"/>
+      <c r="CO25" s="16"/>
+      <c r="CU25" s="17"/>
+      <c r="CV25" s="21"/>
+      <c r="CW25" s="22"/>
+      <c r="CX25" s="22"/>
+      <c r="CY25" s="22"/>
+      <c r="CZ25" s="22"/>
+      <c r="DA25" s="22"/>
+      <c r="DB25" s="46"/>
       <c r="DC25" s="16"/>
-      <c r="DD25" s="18"/>
-    </row>
-    <row r="26" spans="1:108" ht="15" x14ac:dyDescent="0.2">
-      <c r="A26" s="43" t="s">
+      <c r="DD25" s="45"/>
+      <c r="DE25" s="45"/>
+      <c r="DF25" s="45"/>
+      <c r="DG25" s="45"/>
+      <c r="DH25" s="45"/>
+      <c r="DI25" s="17"/>
+    </row>
+    <row r="26" spans="1:113" ht="15" x14ac:dyDescent="0.2">
+      <c r="A26" s="33" t="s">
         <v>18</v>
       </c>
       <c r="B26" s="16"/>
-      <c r="H26" s="18"/>
+      <c r="H26" s="17"/>
       <c r="I26" s="16"/>
-      <c r="O26" s="18"/>
+      <c r="O26" s="17"/>
       <c r="P26" s="16"/>
-      <c r="V26" s="18"/>
+      <c r="V26" s="17"/>
       <c r="W26" s="16"/>
-      <c r="AC26" s="18"/>
+      <c r="AC26" s="17"/>
       <c r="AD26" s="16"/>
-      <c r="AJ26" s="18"/>
+      <c r="AJ26" s="17"/>
       <c r="AK26" s="16"/>
-      <c r="AQ26" s="18"/>
+      <c r="AQ26" s="17"/>
       <c r="AR26" s="16"/>
-      <c r="AX26" s="18"/>
+      <c r="AX26" s="17"/>
       <c r="AY26" s="16"/>
-      <c r="BE26" s="18"/>
+      <c r="BE26" s="17"/>
       <c r="BF26" s="16"/>
-      <c r="BL26" s="18"/>
+      <c r="BL26" s="17"/>
       <c r="BM26" s="16"/>
-      <c r="BS26" s="18"/>
+      <c r="BS26" s="17"/>
       <c r="BT26" s="16"/>
-      <c r="BZ26" s="18"/>
+      <c r="BZ26" s="17"/>
       <c r="CA26" s="16"/>
-      <c r="CG26" s="18"/>
+      <c r="CG26" s="17"/>
       <c r="CH26" s="16"/>
-      <c r="CN26" s="18"/>
-      <c r="CO26" s="22"/>
-      <c r="CP26" s="23"/>
-      <c r="CQ26" s="23"/>
-      <c r="CR26" s="23"/>
-      <c r="CS26" s="23"/>
-      <c r="CT26" s="23"/>
-      <c r="CU26" s="24"/>
-      <c r="CV26" s="16"/>
-      <c r="DB26" s="18"/>
+      <c r="CN26" s="17"/>
+      <c r="CO26" s="16"/>
+      <c r="CU26" s="17"/>
+      <c r="CV26" s="21"/>
+      <c r="CW26" s="22"/>
+      <c r="CX26" s="22"/>
+      <c r="CY26" s="22"/>
+      <c r="CZ26" s="22"/>
+      <c r="DA26" s="22"/>
+      <c r="DB26" s="46"/>
       <c r="DC26" s="16"/>
-      <c r="DD26" s="18"/>
-    </row>
-    <row r="27" spans="1:108" ht="15" x14ac:dyDescent="0.2">
-      <c r="A27" s="43" t="s">
+      <c r="DD26" s="45"/>
+      <c r="DE26" s="45"/>
+      <c r="DF26" s="45"/>
+      <c r="DG26" s="45"/>
+      <c r="DH26" s="45"/>
+      <c r="DI26" s="17"/>
+    </row>
+    <row r="27" spans="1:113" ht="15" x14ac:dyDescent="0.2">
+      <c r="A27" s="33" t="s">
         <v>19</v>
       </c>
       <c r="B27" s="16"/>
-      <c r="H27" s="18"/>
+      <c r="H27" s="17"/>
       <c r="I27" s="16"/>
-      <c r="O27" s="18"/>
+      <c r="O27" s="17"/>
       <c r="P27" s="16"/>
-      <c r="V27" s="18"/>
+      <c r="V27" s="17"/>
       <c r="W27" s="16"/>
-      <c r="AC27" s="18"/>
+      <c r="AC27" s="17"/>
       <c r="AD27" s="16"/>
-      <c r="AJ27" s="18"/>
+      <c r="AJ27" s="17"/>
       <c r="AK27" s="16"/>
-      <c r="AQ27" s="18"/>
+      <c r="AQ27" s="17"/>
       <c r="AR27" s="16"/>
-      <c r="AX27" s="18"/>
+      <c r="AX27" s="17"/>
       <c r="AY27" s="16"/>
-      <c r="BE27" s="18"/>
+      <c r="BE27" s="17"/>
       <c r="BF27" s="16"/>
-      <c r="BL27" s="18"/>
+      <c r="BL27" s="17"/>
       <c r="BM27" s="16"/>
-      <c r="BS27" s="18"/>
+      <c r="BS27" s="17"/>
       <c r="BT27" s="16"/>
-      <c r="BZ27" s="18"/>
+      <c r="BZ27" s="17"/>
       <c r="CA27" s="16"/>
-      <c r="CG27" s="18"/>
+      <c r="CG27" s="17"/>
       <c r="CH27" s="16"/>
-      <c r="CN27" s="18"/>
+      <c r="CN27" s="17"/>
       <c r="CO27" s="16"/>
-      <c r="CU27" s="18"/>
-      <c r="CV27" s="22"/>
-      <c r="CW27" s="23"/>
-      <c r="CX27" s="23"/>
-      <c r="CY27" s="23"/>
-      <c r="CZ27" s="23"/>
-      <c r="DA27" s="23"/>
-      <c r="DB27" s="24"/>
-      <c r="DC27" s="22"/>
-      <c r="DD27" s="24"/>
-    </row>
-    <row r="28" spans="1:108" ht="15" x14ac:dyDescent="0.2">
-      <c r="A28" s="43" t="s">
+      <c r="CU27" s="17"/>
+      <c r="CV27" s="16"/>
+      <c r="DB27" s="17"/>
+      <c r="DC27" s="21"/>
+      <c r="DD27" s="46"/>
+      <c r="DE27" s="46"/>
+      <c r="DF27" s="46"/>
+      <c r="DG27" s="46"/>
+      <c r="DH27" s="46"/>
+      <c r="DI27" s="23"/>
+    </row>
+    <row r="28" spans="1:113" ht="15" x14ac:dyDescent="0.2">
+      <c r="A28" s="33" t="s">
         <v>20</v>
       </c>
       <c r="B28" s="16"/>
-      <c r="H28" s="18"/>
+      <c r="H28" s="17"/>
       <c r="I28" s="16"/>
-      <c r="O28" s="18"/>
+      <c r="O28" s="17"/>
       <c r="P28" s="16"/>
-      <c r="V28" s="18"/>
+      <c r="V28" s="17"/>
       <c r="W28" s="16"/>
-      <c r="AC28" s="18"/>
+      <c r="AC28" s="17"/>
       <c r="AD28" s="16"/>
-      <c r="AJ28" s="18"/>
+      <c r="AJ28" s="17"/>
       <c r="AK28" s="16"/>
-      <c r="AQ28" s="18"/>
+      <c r="AQ28" s="17"/>
       <c r="AR28" s="16"/>
-      <c r="AX28" s="18"/>
+      <c r="AX28" s="17"/>
       <c r="AY28" s="16"/>
-      <c r="BE28" s="18"/>
+      <c r="BE28" s="17"/>
       <c r="BF28" s="16"/>
-      <c r="BL28" s="18"/>
+      <c r="BL28" s="17"/>
       <c r="BM28" s="16"/>
-      <c r="BS28" s="18"/>
+      <c r="BS28" s="17"/>
       <c r="BT28" s="16"/>
-      <c r="BZ28" s="18"/>
+      <c r="BZ28" s="17"/>
       <c r="CA28" s="16"/>
-      <c r="CG28" s="18"/>
+      <c r="CG28" s="17"/>
       <c r="CH28" s="16"/>
-      <c r="CN28" s="18"/>
+      <c r="CN28" s="17"/>
       <c r="CO28" s="16"/>
-      <c r="CU28" s="18"/>
-      <c r="CV28" s="22"/>
-      <c r="CW28" s="23"/>
-      <c r="CX28" s="23"/>
-      <c r="CY28" s="23"/>
-      <c r="CZ28" s="23"/>
-      <c r="DA28" s="23"/>
-      <c r="DB28" s="24"/>
-      <c r="DC28" s="22"/>
-      <c r="DD28" s="24"/>
-    </row>
-    <row r="29" spans="1:108" ht="15" x14ac:dyDescent="0.2">
-      <c r="A29" s="44" t="s">
+      <c r="CU28" s="17"/>
+      <c r="CV28" s="16"/>
+      <c r="DB28" s="17"/>
+      <c r="DC28" s="21"/>
+      <c r="DD28" s="46"/>
+      <c r="DE28" s="46"/>
+      <c r="DF28" s="46"/>
+      <c r="DG28" s="46"/>
+      <c r="DH28" s="46"/>
+      <c r="DI28" s="23"/>
+    </row>
+    <row r="29" spans="1:113" ht="15" x14ac:dyDescent="0.2">
+      <c r="A29" s="34" t="s">
         <v>21</v>
       </c>
-      <c r="B29" s="19"/>
-      <c r="C29" s="20"/>
-      <c r="D29" s="20"/>
-      <c r="E29" s="20"/>
-      <c r="F29" s="20"/>
-      <c r="G29" s="20"/>
-      <c r="H29" s="21"/>
-      <c r="I29" s="19"/>
-      <c r="J29" s="20"/>
-      <c r="K29" s="20"/>
-      <c r="L29" s="20"/>
-      <c r="M29" s="20"/>
-      <c r="N29" s="20"/>
-      <c r="O29" s="21"/>
-      <c r="P29" s="19"/>
-      <c r="Q29" s="20"/>
-      <c r="R29" s="20"/>
-      <c r="S29" s="20"/>
-      <c r="T29" s="20"/>
-      <c r="U29" s="20"/>
-      <c r="V29" s="21"/>
-      <c r="W29" s="19"/>
-      <c r="X29" s="20"/>
-      <c r="Y29" s="20"/>
-      <c r="Z29" s="20"/>
-      <c r="AA29" s="20"/>
-      <c r="AB29" s="20"/>
-      <c r="AC29" s="21"/>
-      <c r="AD29" s="19"/>
-      <c r="AE29" s="20"/>
-      <c r="AF29" s="20"/>
-      <c r="AG29" s="20"/>
-      <c r="AH29" s="20"/>
-      <c r="AI29" s="20"/>
-      <c r="AJ29" s="21"/>
-      <c r="AK29" s="19"/>
-      <c r="AL29" s="20"/>
-      <c r="AM29" s="20"/>
-      <c r="AN29" s="20"/>
-      <c r="AO29" s="20"/>
-      <c r="AP29" s="20"/>
-      <c r="AQ29" s="21"/>
-      <c r="AR29" s="19"/>
-      <c r="AS29" s="20"/>
-      <c r="AT29" s="20"/>
-      <c r="AU29" s="20"/>
-      <c r="AV29" s="20"/>
-      <c r="AW29" s="20"/>
-      <c r="AX29" s="21"/>
-      <c r="AY29" s="19"/>
-      <c r="AZ29" s="20"/>
-      <c r="BA29" s="20"/>
-      <c r="BB29" s="20"/>
-      <c r="BC29" s="20"/>
-      <c r="BD29" s="20"/>
-      <c r="BE29" s="21"/>
-      <c r="BF29" s="19"/>
-      <c r="BG29" s="20"/>
-      <c r="BH29" s="20"/>
-      <c r="BI29" s="20"/>
-      <c r="BJ29" s="20"/>
-      <c r="BK29" s="20"/>
-      <c r="BL29" s="21"/>
-      <c r="BM29" s="19"/>
-      <c r="BN29" s="20"/>
-      <c r="BO29" s="20"/>
-      <c r="BP29" s="20"/>
-      <c r="BQ29" s="20"/>
-      <c r="BR29" s="20"/>
-      <c r="BS29" s="21"/>
-      <c r="BT29" s="19"/>
-      <c r="BU29" s="20"/>
-      <c r="BV29" s="20"/>
-      <c r="BW29" s="20"/>
-      <c r="BX29" s="20"/>
-      <c r="BY29" s="20"/>
-      <c r="BZ29" s="21"/>
-      <c r="CA29" s="19"/>
-      <c r="CB29" s="20"/>
-      <c r="CC29" s="20"/>
-      <c r="CD29" s="20"/>
-      <c r="CE29" s="20"/>
-      <c r="CF29" s="20"/>
-      <c r="CG29" s="21"/>
-      <c r="CH29" s="19"/>
-      <c r="CI29" s="20"/>
-      <c r="CJ29" s="20"/>
-      <c r="CK29" s="20"/>
-      <c r="CL29" s="20"/>
-      <c r="CM29" s="20"/>
-      <c r="CN29" s="21"/>
-      <c r="CO29" s="19"/>
-      <c r="CP29" s="20"/>
-      <c r="CQ29" s="20"/>
-      <c r="CR29" s="20"/>
-      <c r="CS29" s="20"/>
-      <c r="CT29" s="20"/>
-      <c r="CU29" s="21"/>
-      <c r="CV29" s="25"/>
-      <c r="CW29" s="26"/>
-      <c r="CX29" s="26"/>
-      <c r="CY29" s="26"/>
-      <c r="CZ29" s="26"/>
-      <c r="DA29" s="26"/>
-      <c r="DB29" s="27"/>
-      <c r="DC29" s="25"/>
-      <c r="DD29" s="27"/>
-    </row>
-    <row r="30" spans="1:108" x14ac:dyDescent="0.2">
-      <c r="A30" s="37"/>
-    </row>
-    <row r="31" spans="1:108" x14ac:dyDescent="0.2">
-      <c r="A31" s="37"/>
-    </row>
-    <row r="32" spans="1:108" x14ac:dyDescent="0.2">
-      <c r="A32" s="37"/>
+      <c r="B29" s="18"/>
+      <c r="C29" s="19"/>
+      <c r="D29" s="19"/>
+      <c r="E29" s="19"/>
+      <c r="F29" s="19"/>
+      <c r="G29" s="19"/>
+      <c r="H29" s="20"/>
+      <c r="I29" s="18"/>
+      <c r="J29" s="19"/>
+      <c r="K29" s="19"/>
+      <c r="L29" s="19"/>
+      <c r="M29" s="19"/>
+      <c r="N29" s="19"/>
+      <c r="O29" s="20"/>
+      <c r="P29" s="18"/>
+      <c r="Q29" s="19"/>
+      <c r="R29" s="19"/>
+      <c r="S29" s="19"/>
+      <c r="T29" s="19"/>
+      <c r="U29" s="19"/>
+      <c r="V29" s="20"/>
+      <c r="W29" s="18"/>
+      <c r="X29" s="19"/>
+      <c r="Y29" s="19"/>
+      <c r="Z29" s="19"/>
+      <c r="AA29" s="19"/>
+      <c r="AB29" s="19"/>
+      <c r="AC29" s="20"/>
+      <c r="AD29" s="18"/>
+      <c r="AE29" s="19"/>
+      <c r="AF29" s="19"/>
+      <c r="AG29" s="19"/>
+      <c r="AH29" s="19"/>
+      <c r="AI29" s="19"/>
+      <c r="AJ29" s="20"/>
+      <c r="AK29" s="18"/>
+      <c r="AL29" s="19"/>
+      <c r="AM29" s="19"/>
+      <c r="AN29" s="19"/>
+      <c r="AO29" s="19"/>
+      <c r="AP29" s="19"/>
+      <c r="AQ29" s="20"/>
+      <c r="AR29" s="18"/>
+      <c r="AS29" s="19"/>
+      <c r="AT29" s="19"/>
+      <c r="AU29" s="19"/>
+      <c r="AV29" s="19"/>
+      <c r="AW29" s="19"/>
+      <c r="AX29" s="20"/>
+      <c r="AY29" s="18"/>
+      <c r="AZ29" s="19"/>
+      <c r="BA29" s="19"/>
+      <c r="BB29" s="19"/>
+      <c r="BC29" s="19"/>
+      <c r="BD29" s="19"/>
+      <c r="BE29" s="20"/>
+      <c r="BF29" s="18"/>
+      <c r="BG29" s="19"/>
+      <c r="BH29" s="19"/>
+      <c r="BI29" s="19"/>
+      <c r="BJ29" s="19"/>
+      <c r="BK29" s="19"/>
+      <c r="BL29" s="20"/>
+      <c r="BM29" s="18"/>
+      <c r="BN29" s="19"/>
+      <c r="BO29" s="19"/>
+      <c r="BP29" s="19"/>
+      <c r="BQ29" s="19"/>
+      <c r="BR29" s="19"/>
+      <c r="BS29" s="20"/>
+      <c r="BT29" s="18"/>
+      <c r="BU29" s="19"/>
+      <c r="BV29" s="19"/>
+      <c r="BW29" s="19"/>
+      <c r="BX29" s="19"/>
+      <c r="BY29" s="19"/>
+      <c r="BZ29" s="20"/>
+      <c r="CA29" s="18"/>
+      <c r="CB29" s="19"/>
+      <c r="CC29" s="19"/>
+      <c r="CD29" s="19"/>
+      <c r="CE29" s="19"/>
+      <c r="CF29" s="19"/>
+      <c r="CG29" s="20"/>
+      <c r="CH29" s="18"/>
+      <c r="CI29" s="19"/>
+      <c r="CJ29" s="19"/>
+      <c r="CK29" s="19"/>
+      <c r="CL29" s="19"/>
+      <c r="CM29" s="19"/>
+      <c r="CN29" s="20"/>
+      <c r="CO29" s="18"/>
+      <c r="CP29" s="19"/>
+      <c r="CQ29" s="19"/>
+      <c r="CR29" s="19"/>
+      <c r="CS29" s="19"/>
+      <c r="CT29" s="19"/>
+      <c r="CU29" s="20"/>
+      <c r="CV29" s="18"/>
+      <c r="CW29" s="19"/>
+      <c r="CX29" s="19"/>
+      <c r="CY29" s="19"/>
+      <c r="CZ29" s="19"/>
+      <c r="DA29" s="19"/>
+      <c r="DB29" s="20"/>
+      <c r="DC29" s="24"/>
+      <c r="DD29" s="25"/>
+      <c r="DE29" s="25"/>
+      <c r="DF29" s="25"/>
+      <c r="DG29" s="25"/>
+      <c r="DH29" s="25"/>
+      <c r="DI29" s="26"/>
+    </row>
+    <row r="30" spans="1:113" x14ac:dyDescent="0.2">
+      <c r="A30" s="32"/>
+    </row>
+    <row r="31" spans="1:113" x14ac:dyDescent="0.2">
+      <c r="A31" s="32"/>
+    </row>
+    <row r="32" spans="1:113" x14ac:dyDescent="0.2">
+      <c r="A32" s="32"/>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A33" s="37"/>
+      <c r="A33" s="32"/>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A34" s="37"/>
+      <c r="A34" s="32"/>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A35" s="37"/>
+      <c r="A35" s="32"/>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A36" s="37"/>
+      <c r="A36" s="32"/>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A37" s="37"/>
+      <c r="A37" s="32"/>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A38" s="37"/>
+      <c r="A38" s="32"/>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A39" s="37"/>
+      <c r="A39" s="32"/>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A40" s="37"/>
+      <c r="A40" s="32"/>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="5">
     <mergeCell ref="CA8:DD8"/>
     <mergeCell ref="B8:Q8"/>
     <mergeCell ref="R8:AU8"/>
     <mergeCell ref="AV8:BZ8"/>
+    <mergeCell ref="DE8:DI8"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2605,235 +2483,186 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A2DD1884-97C5-4E94-84EE-735838CDBC98}">
-  <dimension ref="A1:DF40"/>
+  <dimension ref="A1:DD40"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="20.88671875" style="17" bestFit="1" customWidth="1"/>
-    <col min="2" max="14" width="2.77734375" style="17" customWidth="1"/>
-    <col min="15" max="15" width="3.21875" style="17" bestFit="1" customWidth="1"/>
-    <col min="16" max="42" width="2.77734375" style="17" customWidth="1"/>
-    <col min="43" max="43" width="3.21875" style="17" bestFit="1" customWidth="1"/>
-    <col min="44" max="105" width="2.77734375" style="17" customWidth="1"/>
-    <col min="106" max="107" width="3.21875" style="17" bestFit="1" customWidth="1"/>
-    <col min="108" max="108" width="2.77734375" style="17" customWidth="1"/>
-    <col min="109" max="110" width="11.5546875" style="17"/>
+    <col min="1" max="1" width="20.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="14" width="2.77734375" customWidth="1"/>
+    <col min="15" max="15" width="3.21875" bestFit="1" customWidth="1"/>
+    <col min="16" max="42" width="2.77734375" customWidth="1"/>
+    <col min="43" max="43" width="3.21875" bestFit="1" customWidth="1"/>
+    <col min="44" max="105" width="2.77734375" customWidth="1"/>
+    <col min="106" max="107" width="3.21875" bestFit="1" customWidth="1"/>
+    <col min="108" max="108" width="2.77734375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:108" ht="20.25" x14ac:dyDescent="0.3">
-      <c r="A1" s="31" t="s">
+      <c r="A1" s="27" t="s">
         <v>25</v>
       </c>
-      <c r="B1" s="32"/>
-      <c r="C1" s="32"/>
-      <c r="D1" s="32"/>
-      <c r="E1" s="32"/>
-      <c r="F1" s="32"/>
-      <c r="G1" s="32"/>
-      <c r="H1" s="32"/>
-      <c r="I1" s="32"/>
-      <c r="J1" s="32"/>
-      <c r="K1" s="32"/>
-      <c r="L1" s="32"/>
-      <c r="M1" s="32"/>
-      <c r="N1" s="32"/>
-      <c r="O1" s="32"/>
-      <c r="P1" s="32"/>
-      <c r="Q1" s="32"/>
     </row>
     <row r="2" spans="1:108" ht="20.25" x14ac:dyDescent="0.3">
-      <c r="A2" s="31" t="s">
+      <c r="A2" s="27" t="s">
         <v>26</v>
       </c>
-      <c r="B2" s="32"/>
-      <c r="C2" s="32"/>
-      <c r="D2" s="32"/>
-      <c r="E2" s="32"/>
-      <c r="F2" s="32"/>
-      <c r="G2" s="32"/>
-      <c r="H2" s="32"/>
-      <c r="I2" s="32"/>
-      <c r="J2" s="32"/>
-      <c r="K2" s="32"/>
-      <c r="L2" s="32"/>
-      <c r="M2" s="32"/>
-      <c r="N2" s="32"/>
-      <c r="O2" s="32"/>
-      <c r="P2" s="32"/>
-      <c r="Q2" s="32"/>
     </row>
     <row r="3" spans="1:108" ht="20.25" x14ac:dyDescent="0.3">
-      <c r="A3" s="31">
+      <c r="A3" s="27">
         <v>2026</v>
       </c>
-      <c r="B3" s="32"/>
-      <c r="C3" s="32"/>
-      <c r="D3" s="32"/>
-      <c r="E3" s="32"/>
-      <c r="F3" s="32"/>
-      <c r="G3" s="32"/>
-      <c r="H3" s="32"/>
-      <c r="I3" s="32"/>
-      <c r="J3" s="32"/>
-      <c r="K3" s="32"/>
-      <c r="L3" s="32"/>
-      <c r="M3" s="32"/>
-      <c r="N3" s="32"/>
-      <c r="O3" s="32"/>
-      <c r="P3" s="32"/>
-      <c r="Q3" s="32"/>
     </row>
     <row r="4" spans="1:108" x14ac:dyDescent="0.2">
-      <c r="A4" s="33"/>
-      <c r="B4" s="33"/>
-      <c r="C4" s="33"/>
-      <c r="D4" s="33"/>
-      <c r="E4" s="33"/>
-      <c r="F4" s="33"/>
-      <c r="G4" s="33"/>
-      <c r="H4" s="33"/>
-      <c r="I4" s="33"/>
-      <c r="J4" s="33"/>
-      <c r="K4" s="33"/>
-      <c r="L4" s="33"/>
-      <c r="M4" s="33"/>
-      <c r="N4" s="33"/>
-      <c r="O4" s="33"/>
-      <c r="P4" s="33"/>
-      <c r="Q4" s="33"/>
+      <c r="A4" s="28"/>
+      <c r="B4" s="28"/>
+      <c r="C4" s="28"/>
+      <c r="D4" s="28"/>
+      <c r="E4" s="28"/>
+      <c r="F4" s="28"/>
+      <c r="G4" s="28"/>
+      <c r="H4" s="28"/>
+      <c r="I4" s="28"/>
+      <c r="J4" s="28"/>
+      <c r="K4" s="28"/>
+      <c r="L4" s="28"/>
+      <c r="M4" s="28"/>
+      <c r="N4" s="28"/>
+      <c r="O4" s="28"/>
+      <c r="P4" s="28"/>
+      <c r="Q4" s="28"/>
     </row>
     <row r="5" spans="1:108" ht="18" x14ac:dyDescent="0.25">
-      <c r="A5" s="34" t="s">
+      <c r="A5" s="29" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="6" spans="1:108" ht="18" x14ac:dyDescent="0.25">
-      <c r="A6" s="34" t="s">
+      <c r="A6" s="29" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="7" spans="1:108" ht="15" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="8" spans="1:108" x14ac:dyDescent="0.2">
-      <c r="A8" s="35" t="s">
+      <c r="A8" s="30" t="s">
         <v>0</v>
       </c>
-      <c r="B8" s="30" t="s">
+      <c r="B8" s="37" t="s">
         <v>2</v>
       </c>
-      <c r="C8" s="28"/>
-      <c r="D8" s="28"/>
-      <c r="E8" s="28"/>
-      <c r="F8" s="28"/>
-      <c r="G8" s="28"/>
-      <c r="H8" s="28"/>
-      <c r="I8" s="28"/>
-      <c r="J8" s="28"/>
-      <c r="K8" s="28"/>
-      <c r="L8" s="28"/>
-      <c r="M8" s="28"/>
-      <c r="N8" s="28"/>
-      <c r="O8" s="28"/>
-      <c r="P8" s="28"/>
-      <c r="Q8" s="29"/>
-      <c r="R8" s="30" t="s">
+      <c r="C8" s="38"/>
+      <c r="D8" s="38"/>
+      <c r="E8" s="38"/>
+      <c r="F8" s="38"/>
+      <c r="G8" s="38"/>
+      <c r="H8" s="38"/>
+      <c r="I8" s="38"/>
+      <c r="J8" s="38"/>
+      <c r="K8" s="38"/>
+      <c r="L8" s="38"/>
+      <c r="M8" s="38"/>
+      <c r="N8" s="38"/>
+      <c r="O8" s="38"/>
+      <c r="P8" s="38"/>
+      <c r="Q8" s="39"/>
+      <c r="R8" s="37" t="s">
         <v>3</v>
       </c>
-      <c r="S8" s="28"/>
-      <c r="T8" s="28"/>
-      <c r="U8" s="28"/>
-      <c r="V8" s="28"/>
-      <c r="W8" s="28"/>
-      <c r="X8" s="28"/>
-      <c r="Y8" s="28"/>
-      <c r="Z8" s="28"/>
-      <c r="AA8" s="28"/>
-      <c r="AB8" s="28"/>
-      <c r="AC8" s="28"/>
-      <c r="AD8" s="28"/>
-      <c r="AE8" s="28"/>
-      <c r="AF8" s="28"/>
-      <c r="AG8" s="28"/>
-      <c r="AH8" s="28"/>
-      <c r="AI8" s="28"/>
-      <c r="AJ8" s="28"/>
-      <c r="AK8" s="28"/>
-      <c r="AL8" s="28"/>
-      <c r="AM8" s="28"/>
-      <c r="AN8" s="28"/>
-      <c r="AO8" s="28"/>
-      <c r="AP8" s="28"/>
-      <c r="AQ8" s="28"/>
-      <c r="AR8" s="28"/>
-      <c r="AS8" s="28"/>
-      <c r="AT8" s="28"/>
-      <c r="AU8" s="29"/>
-      <c r="AV8" s="30" t="s">
+      <c r="S8" s="38"/>
+      <c r="T8" s="38"/>
+      <c r="U8" s="38"/>
+      <c r="V8" s="38"/>
+      <c r="W8" s="38"/>
+      <c r="X8" s="38"/>
+      <c r="Y8" s="38"/>
+      <c r="Z8" s="38"/>
+      <c r="AA8" s="38"/>
+      <c r="AB8" s="38"/>
+      <c r="AC8" s="38"/>
+      <c r="AD8" s="38"/>
+      <c r="AE8" s="38"/>
+      <c r="AF8" s="38"/>
+      <c r="AG8" s="38"/>
+      <c r="AH8" s="38"/>
+      <c r="AI8" s="38"/>
+      <c r="AJ8" s="38"/>
+      <c r="AK8" s="38"/>
+      <c r="AL8" s="38"/>
+      <c r="AM8" s="38"/>
+      <c r="AN8" s="38"/>
+      <c r="AO8" s="38"/>
+      <c r="AP8" s="38"/>
+      <c r="AQ8" s="38"/>
+      <c r="AR8" s="38"/>
+      <c r="AS8" s="38"/>
+      <c r="AT8" s="38"/>
+      <c r="AU8" s="39"/>
+      <c r="AV8" s="37" t="s">
         <v>4</v>
       </c>
-      <c r="AW8" s="28"/>
-      <c r="AX8" s="28"/>
-      <c r="AY8" s="28"/>
-      <c r="AZ8" s="28"/>
-      <c r="BA8" s="28"/>
-      <c r="BB8" s="28"/>
-      <c r="BC8" s="28"/>
-      <c r="BD8" s="28"/>
-      <c r="BE8" s="28"/>
-      <c r="BF8" s="28"/>
-      <c r="BG8" s="28"/>
-      <c r="BH8" s="28"/>
-      <c r="BI8" s="28"/>
-      <c r="BJ8" s="28"/>
-      <c r="BK8" s="28"/>
-      <c r="BL8" s="28"/>
-      <c r="BM8" s="28"/>
-      <c r="BN8" s="28"/>
-      <c r="BO8" s="28"/>
-      <c r="BP8" s="28"/>
-      <c r="BQ8" s="28"/>
-      <c r="BR8" s="28"/>
-      <c r="BS8" s="28"/>
-      <c r="BT8" s="28"/>
-      <c r="BU8" s="28"/>
-      <c r="BV8" s="28"/>
-      <c r="BW8" s="28"/>
-      <c r="BX8" s="28"/>
-      <c r="BY8" s="28"/>
-      <c r="BZ8" s="29"/>
-      <c r="CA8" s="30" t="s">
+      <c r="AW8" s="38"/>
+      <c r="AX8" s="38"/>
+      <c r="AY8" s="38"/>
+      <c r="AZ8" s="38"/>
+      <c r="BA8" s="38"/>
+      <c r="BB8" s="38"/>
+      <c r="BC8" s="38"/>
+      <c r="BD8" s="38"/>
+      <c r="BE8" s="38"/>
+      <c r="BF8" s="38"/>
+      <c r="BG8" s="38"/>
+      <c r="BH8" s="38"/>
+      <c r="BI8" s="38"/>
+      <c r="BJ8" s="38"/>
+      <c r="BK8" s="38"/>
+      <c r="BL8" s="38"/>
+      <c r="BM8" s="38"/>
+      <c r="BN8" s="38"/>
+      <c r="BO8" s="38"/>
+      <c r="BP8" s="38"/>
+      <c r="BQ8" s="38"/>
+      <c r="BR8" s="38"/>
+      <c r="BS8" s="38"/>
+      <c r="BT8" s="38"/>
+      <c r="BU8" s="38"/>
+      <c r="BV8" s="38"/>
+      <c r="BW8" s="38"/>
+      <c r="BX8" s="38"/>
+      <c r="BY8" s="38"/>
+      <c r="BZ8" s="39"/>
+      <c r="CA8" s="37" t="s">
         <v>5</v>
       </c>
-      <c r="CB8" s="28"/>
-      <c r="CC8" s="28"/>
-      <c r="CD8" s="28"/>
-      <c r="CE8" s="28"/>
-      <c r="CF8" s="28"/>
-      <c r="CG8" s="28"/>
-      <c r="CH8" s="28"/>
-      <c r="CI8" s="28"/>
-      <c r="CJ8" s="28"/>
-      <c r="CK8" s="28"/>
-      <c r="CL8" s="28"/>
-      <c r="CM8" s="28"/>
-      <c r="CN8" s="28"/>
-      <c r="CO8" s="28"/>
-      <c r="CP8" s="28"/>
-      <c r="CQ8" s="28"/>
-      <c r="CR8" s="28"/>
-      <c r="CS8" s="28"/>
-      <c r="CT8" s="28"/>
-      <c r="CU8" s="28"/>
-      <c r="CV8" s="28"/>
-      <c r="CW8" s="28"/>
-      <c r="CX8" s="28"/>
-      <c r="CY8" s="28"/>
-      <c r="CZ8" s="28"/>
-      <c r="DA8" s="28"/>
-      <c r="DB8" s="28"/>
-      <c r="DC8" s="28"/>
-      <c r="DD8" s="29"/>
+      <c r="CB8" s="38"/>
+      <c r="CC8" s="38"/>
+      <c r="CD8" s="38"/>
+      <c r="CE8" s="38"/>
+      <c r="CF8" s="38"/>
+      <c r="CG8" s="38"/>
+      <c r="CH8" s="38"/>
+      <c r="CI8" s="38"/>
+      <c r="CJ8" s="38"/>
+      <c r="CK8" s="38"/>
+      <c r="CL8" s="38"/>
+      <c r="CM8" s="38"/>
+      <c r="CN8" s="38"/>
+      <c r="CO8" s="38"/>
+      <c r="CP8" s="38"/>
+      <c r="CQ8" s="38"/>
+      <c r="CR8" s="38"/>
+      <c r="CS8" s="38"/>
+      <c r="CT8" s="38"/>
+      <c r="CU8" s="38"/>
+      <c r="CV8" s="38"/>
+      <c r="CW8" s="38"/>
+      <c r="CX8" s="38"/>
+      <c r="CY8" s="38"/>
+      <c r="CZ8" s="38"/>
+      <c r="DA8" s="38"/>
+      <c r="DB8" s="38"/>
+      <c r="DC8" s="38"/>
+      <c r="DD8" s="39"/>
     </row>
     <row r="9" spans="1:108" ht="15" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="36" t="s">
+      <c r="A9" s="31" t="s">
         <v>24</v>
       </c>
       <c r="B9" s="9">
@@ -3160,988 +2989,988 @@
     </row>
     <row r="10" spans="1:108" x14ac:dyDescent="0.2">
       <c r="B10" s="16"/>
-      <c r="H10" s="18"/>
+      <c r="H10" s="17"/>
       <c r="I10" s="16"/>
-      <c r="O10" s="18"/>
+      <c r="O10" s="17"/>
       <c r="P10" s="16"/>
-      <c r="V10" s="18"/>
+      <c r="V10" s="17"/>
       <c r="W10" s="16"/>
-      <c r="AC10" s="18"/>
+      <c r="AC10" s="17"/>
       <c r="AD10" s="16"/>
-      <c r="AJ10" s="18"/>
+      <c r="AJ10" s="17"/>
       <c r="AK10" s="16"/>
-      <c r="AQ10" s="18"/>
+      <c r="AQ10" s="17"/>
       <c r="AR10" s="16"/>
-      <c r="AX10" s="18"/>
+      <c r="AX10" s="17"/>
       <c r="AY10" s="16"/>
-      <c r="BE10" s="18"/>
+      <c r="BE10" s="17"/>
       <c r="BF10" s="16"/>
-      <c r="BL10" s="18"/>
+      <c r="BL10" s="17"/>
       <c r="BM10" s="16"/>
-      <c r="BS10" s="18"/>
+      <c r="BS10" s="17"/>
       <c r="BT10" s="16"/>
-      <c r="BZ10" s="18"/>
+      <c r="BZ10" s="17"/>
       <c r="CA10" s="16"/>
-      <c r="CG10" s="18"/>
+      <c r="CG10" s="17"/>
       <c r="CH10" s="16"/>
-      <c r="CN10" s="18"/>
+      <c r="CN10" s="17"/>
       <c r="CO10" s="16"/>
-      <c r="CU10" s="18"/>
+      <c r="CU10" s="17"/>
       <c r="CV10" s="16"/>
-      <c r="DB10" s="18"/>
+      <c r="DB10" s="17"/>
       <c r="DC10" s="16"/>
-      <c r="DD10" s="18"/>
+      <c r="DD10" s="17"/>
     </row>
     <row r="11" spans="1:108" x14ac:dyDescent="0.2">
-      <c r="A11" s="17" t="s">
+      <c r="A11" t="s">
         <v>1</v>
       </c>
-      <c r="B11" s="22"/>
-      <c r="C11" s="23"/>
-      <c r="D11" s="23"/>
-      <c r="E11" s="23"/>
-      <c r="F11" s="23"/>
-      <c r="G11" s="23"/>
-      <c r="H11" s="24"/>
+      <c r="B11" s="21"/>
+      <c r="C11" s="22"/>
+      <c r="D11" s="22"/>
+      <c r="E11" s="22"/>
+      <c r="F11" s="22"/>
+      <c r="G11" s="22"/>
+      <c r="H11" s="23"/>
       <c r="I11" s="16"/>
-      <c r="O11" s="18"/>
+      <c r="O11" s="17"/>
       <c r="P11" s="16"/>
-      <c r="V11" s="18"/>
+      <c r="V11" s="17"/>
       <c r="W11" s="16"/>
-      <c r="AC11" s="18"/>
+      <c r="AC11" s="17"/>
       <c r="AD11" s="16"/>
-      <c r="AJ11" s="18"/>
+      <c r="AJ11" s="17"/>
       <c r="AK11" s="16"/>
-      <c r="AQ11" s="18"/>
+      <c r="AQ11" s="17"/>
       <c r="AR11" s="16"/>
-      <c r="AX11" s="18"/>
+      <c r="AX11" s="17"/>
       <c r="AY11" s="16"/>
-      <c r="BE11" s="18"/>
+      <c r="BE11" s="17"/>
       <c r="BF11" s="16"/>
-      <c r="BL11" s="18"/>
+      <c r="BL11" s="17"/>
       <c r="BM11" s="16"/>
-      <c r="BS11" s="18"/>
+      <c r="BS11" s="17"/>
       <c r="BT11" s="16"/>
-      <c r="BZ11" s="18"/>
+      <c r="BZ11" s="17"/>
       <c r="CA11" s="16"/>
-      <c r="CG11" s="18"/>
+      <c r="CG11" s="17"/>
       <c r="CH11" s="16"/>
-      <c r="CN11" s="18"/>
+      <c r="CN11" s="17"/>
       <c r="CO11" s="16"/>
-      <c r="CU11" s="18"/>
+      <c r="CU11" s="17"/>
       <c r="CV11" s="16"/>
-      <c r="DB11" s="18"/>
+      <c r="DB11" s="17"/>
       <c r="DC11" s="16"/>
-      <c r="DD11" s="18"/>
+      <c r="DD11" s="17"/>
     </row>
     <row r="12" spans="1:108" x14ac:dyDescent="0.2">
-      <c r="A12" s="17" t="s">
+      <c r="A12" t="s">
         <v>6</v>
       </c>
       <c r="B12" s="16"/>
-      <c r="H12" s="18"/>
-      <c r="I12" s="22"/>
-      <c r="J12" s="23"/>
-      <c r="K12" s="23"/>
-      <c r="L12" s="23"/>
-      <c r="M12" s="23"/>
-      <c r="N12" s="23"/>
-      <c r="O12" s="24"/>
+      <c r="H12" s="17"/>
+      <c r="I12" s="21"/>
+      <c r="J12" s="22"/>
+      <c r="K12" s="22"/>
+      <c r="L12" s="22"/>
+      <c r="M12" s="22"/>
+      <c r="N12" s="22"/>
+      <c r="O12" s="23"/>
       <c r="P12" s="16"/>
-      <c r="V12" s="18"/>
+      <c r="V12" s="17"/>
       <c r="W12" s="16"/>
-      <c r="AC12" s="18"/>
+      <c r="AC12" s="17"/>
       <c r="AD12" s="16"/>
-      <c r="AJ12" s="18"/>
+      <c r="AJ12" s="17"/>
       <c r="AK12" s="16"/>
-      <c r="AQ12" s="18"/>
+      <c r="AQ12" s="17"/>
       <c r="AR12" s="16"/>
-      <c r="AX12" s="18"/>
+      <c r="AX12" s="17"/>
       <c r="AY12" s="16"/>
-      <c r="BE12" s="18"/>
+      <c r="BE12" s="17"/>
       <c r="BF12" s="16"/>
-      <c r="BL12" s="18"/>
+      <c r="BL12" s="17"/>
       <c r="BM12" s="16"/>
-      <c r="BS12" s="18"/>
+      <c r="BS12" s="17"/>
       <c r="BT12" s="16"/>
-      <c r="BZ12" s="18"/>
+      <c r="BZ12" s="17"/>
       <c r="CA12" s="16"/>
-      <c r="CG12" s="18"/>
+      <c r="CG12" s="17"/>
       <c r="CH12" s="16"/>
-      <c r="CN12" s="18"/>
+      <c r="CN12" s="17"/>
       <c r="CO12" s="16"/>
-      <c r="CU12" s="18"/>
+      <c r="CU12" s="17"/>
       <c r="CV12" s="16"/>
-      <c r="DB12" s="18"/>
+      <c r="DB12" s="17"/>
       <c r="DC12" s="16"/>
-      <c r="DD12" s="18"/>
+      <c r="DD12" s="17"/>
     </row>
     <row r="13" spans="1:108" x14ac:dyDescent="0.2">
-      <c r="A13" s="17" t="s">
+      <c r="A13" t="s">
         <v>11</v>
       </c>
       <c r="B13" s="16"/>
-      <c r="H13" s="18"/>
+      <c r="H13" s="17"/>
       <c r="I13" s="16"/>
-      <c r="O13" s="18"/>
-      <c r="P13" s="22"/>
-      <c r="Q13" s="23"/>
-      <c r="R13" s="23"/>
-      <c r="S13" s="23"/>
-      <c r="T13" s="23"/>
-      <c r="U13" s="23"/>
-      <c r="V13" s="24"/>
+      <c r="O13" s="17"/>
+      <c r="P13" s="21"/>
+      <c r="Q13" s="22"/>
+      <c r="R13" s="22"/>
+      <c r="S13" s="22"/>
+      <c r="T13" s="22"/>
+      <c r="U13" s="22"/>
+      <c r="V13" s="23"/>
       <c r="W13" s="16"/>
-      <c r="AC13" s="18"/>
+      <c r="AC13" s="17"/>
       <c r="AD13" s="16"/>
-      <c r="AJ13" s="18"/>
+      <c r="AJ13" s="17"/>
       <c r="AK13" s="16"/>
-      <c r="AQ13" s="18"/>
+      <c r="AQ13" s="17"/>
       <c r="AR13" s="16"/>
-      <c r="AX13" s="18"/>
+      <c r="AX13" s="17"/>
       <c r="AY13" s="16"/>
-      <c r="BE13" s="18"/>
+      <c r="BE13" s="17"/>
       <c r="BF13" s="16"/>
-      <c r="BL13" s="18"/>
+      <c r="BL13" s="17"/>
       <c r="BM13" s="16"/>
-      <c r="BS13" s="18"/>
+      <c r="BS13" s="17"/>
       <c r="BT13" s="16"/>
-      <c r="BZ13" s="18"/>
+      <c r="BZ13" s="17"/>
       <c r="CA13" s="16"/>
-      <c r="CG13" s="18"/>
+      <c r="CG13" s="17"/>
       <c r="CH13" s="16"/>
-      <c r="CN13" s="18"/>
+      <c r="CN13" s="17"/>
       <c r="CO13" s="16"/>
-      <c r="CU13" s="18"/>
+      <c r="CU13" s="17"/>
       <c r="CV13" s="16"/>
-      <c r="DB13" s="18"/>
+      <c r="DB13" s="17"/>
       <c r="DC13" s="16"/>
-      <c r="DD13" s="18"/>
+      <c r="DD13" s="17"/>
     </row>
     <row r="14" spans="1:108" x14ac:dyDescent="0.2">
-      <c r="A14" s="17" t="s">
+      <c r="A14" t="s">
         <v>7</v>
       </c>
       <c r="B14" s="16"/>
-      <c r="H14" s="18"/>
+      <c r="H14" s="17"/>
       <c r="I14" s="16"/>
-      <c r="O14" s="18"/>
-      <c r="P14" s="22"/>
-      <c r="Q14" s="23"/>
-      <c r="R14" s="23"/>
-      <c r="S14" s="23"/>
-      <c r="T14" s="23"/>
-      <c r="U14" s="23"/>
-      <c r="V14" s="24"/>
+      <c r="O14" s="17"/>
+      <c r="P14" s="21"/>
+      <c r="Q14" s="22"/>
+      <c r="R14" s="22"/>
+      <c r="S14" s="22"/>
+      <c r="T14" s="22"/>
+      <c r="U14" s="22"/>
+      <c r="V14" s="23"/>
       <c r="W14" s="16"/>
-      <c r="AC14" s="18"/>
+      <c r="AC14" s="17"/>
       <c r="AD14" s="16"/>
-      <c r="AJ14" s="18"/>
+      <c r="AJ14" s="17"/>
       <c r="AK14" s="16"/>
-      <c r="AQ14" s="18"/>
+      <c r="AQ14" s="17"/>
       <c r="AR14" s="16"/>
-      <c r="AX14" s="18"/>
+      <c r="AX14" s="17"/>
       <c r="AY14" s="16"/>
-      <c r="BE14" s="18"/>
+      <c r="BE14" s="17"/>
       <c r="BF14" s="16"/>
-      <c r="BL14" s="18"/>
+      <c r="BL14" s="17"/>
       <c r="BM14" s="16"/>
-      <c r="BS14" s="18"/>
+      <c r="BS14" s="17"/>
       <c r="BT14" s="16"/>
-      <c r="BZ14" s="18"/>
+      <c r="BZ14" s="17"/>
       <c r="CA14" s="16"/>
-      <c r="CG14" s="18"/>
+      <c r="CG14" s="17"/>
       <c r="CH14" s="16"/>
-      <c r="CN14" s="18"/>
+      <c r="CN14" s="17"/>
       <c r="CO14" s="16"/>
-      <c r="CU14" s="18"/>
+      <c r="CU14" s="17"/>
       <c r="CV14" s="16"/>
-      <c r="DB14" s="18"/>
+      <c r="DB14" s="17"/>
       <c r="DC14" s="16"/>
-      <c r="DD14" s="18"/>
+      <c r="DD14" s="17"/>
     </row>
     <row r="15" spans="1:108" x14ac:dyDescent="0.2">
-      <c r="A15" s="17" t="s">
+      <c r="A15" t="s">
         <v>8</v>
       </c>
       <c r="B15" s="16"/>
-      <c r="H15" s="18"/>
+      <c r="H15" s="17"/>
       <c r="I15" s="16"/>
-      <c r="O15" s="18"/>
+      <c r="O15" s="17"/>
       <c r="P15" s="16"/>
-      <c r="V15" s="18"/>
-      <c r="W15" s="22"/>
-      <c r="X15" s="23"/>
-      <c r="Y15" s="23"/>
-      <c r="Z15" s="23"/>
-      <c r="AA15" s="23"/>
-      <c r="AB15" s="23"/>
-      <c r="AC15" s="24"/>
+      <c r="V15" s="17"/>
+      <c r="W15" s="21"/>
+      <c r="X15" s="22"/>
+      <c r="Y15" s="22"/>
+      <c r="Z15" s="22"/>
+      <c r="AA15" s="22"/>
+      <c r="AB15" s="22"/>
+      <c r="AC15" s="23"/>
       <c r="AD15" s="16"/>
-      <c r="AJ15" s="18"/>
+      <c r="AJ15" s="17"/>
       <c r="AK15" s="16"/>
-      <c r="AQ15" s="18"/>
+      <c r="AQ15" s="17"/>
       <c r="AR15" s="16"/>
-      <c r="AX15" s="18"/>
+      <c r="AX15" s="17"/>
       <c r="AY15" s="16"/>
-      <c r="BE15" s="18"/>
+      <c r="BE15" s="17"/>
       <c r="BF15" s="16"/>
-      <c r="BL15" s="18"/>
+      <c r="BL15" s="17"/>
       <c r="BM15" s="16"/>
-      <c r="BS15" s="18"/>
+      <c r="BS15" s="17"/>
       <c r="BT15" s="16"/>
-      <c r="BZ15" s="18"/>
+      <c r="BZ15" s="17"/>
       <c r="CA15" s="16"/>
-      <c r="CG15" s="18"/>
+      <c r="CG15" s="17"/>
       <c r="CH15" s="16"/>
-      <c r="CN15" s="18"/>
+      <c r="CN15" s="17"/>
       <c r="CO15" s="16"/>
-      <c r="CU15" s="18"/>
+      <c r="CU15" s="17"/>
       <c r="CV15" s="16"/>
-      <c r="DB15" s="18"/>
+      <c r="DB15" s="17"/>
       <c r="DC15" s="16"/>
-      <c r="DD15" s="18"/>
+      <c r="DD15" s="17"/>
     </row>
     <row r="16" spans="1:108" x14ac:dyDescent="0.2">
-      <c r="A16" s="17" t="s">
+      <c r="A16" t="s">
         <v>10</v>
       </c>
       <c r="B16" s="16"/>
-      <c r="H16" s="18"/>
+      <c r="H16" s="17"/>
       <c r="I16" s="16"/>
-      <c r="O16" s="18"/>
+      <c r="O16" s="17"/>
       <c r="P16" s="16"/>
-      <c r="V16" s="18"/>
+      <c r="V16" s="17"/>
       <c r="W16" s="16"/>
-      <c r="AC16" s="18"/>
-      <c r="AD16" s="22"/>
-      <c r="AE16" s="23"/>
-      <c r="AF16" s="23"/>
-      <c r="AG16" s="23"/>
-      <c r="AH16" s="23"/>
-      <c r="AI16" s="23"/>
-      <c r="AJ16" s="24"/>
+      <c r="AC16" s="17"/>
+      <c r="AD16" s="21"/>
+      <c r="AE16" s="22"/>
+      <c r="AF16" s="22"/>
+      <c r="AG16" s="22"/>
+      <c r="AH16" s="22"/>
+      <c r="AI16" s="22"/>
+      <c r="AJ16" s="23"/>
       <c r="AK16" s="16"/>
-      <c r="AQ16" s="18"/>
+      <c r="AQ16" s="17"/>
       <c r="AR16" s="16"/>
-      <c r="AX16" s="18"/>
+      <c r="AX16" s="17"/>
       <c r="AY16" s="16"/>
-      <c r="BE16" s="18"/>
+      <c r="BE16" s="17"/>
       <c r="BF16" s="16"/>
-      <c r="BL16" s="18"/>
+      <c r="BL16" s="17"/>
       <c r="BM16" s="16"/>
-      <c r="BS16" s="18"/>
+      <c r="BS16" s="17"/>
       <c r="BT16" s="16"/>
-      <c r="BZ16" s="18"/>
+      <c r="BZ16" s="17"/>
       <c r="CA16" s="16"/>
-      <c r="CG16" s="18"/>
+      <c r="CG16" s="17"/>
       <c r="CH16" s="16"/>
-      <c r="CN16" s="18"/>
+      <c r="CN16" s="17"/>
       <c r="CO16" s="16"/>
-      <c r="CU16" s="18"/>
+      <c r="CU16" s="17"/>
       <c r="CV16" s="16"/>
-      <c r="DB16" s="18"/>
+      <c r="DB16" s="17"/>
       <c r="DC16" s="16"/>
-      <c r="DD16" s="18"/>
+      <c r="DD16" s="17"/>
     </row>
     <row r="17" spans="1:108" x14ac:dyDescent="0.2">
-      <c r="A17" s="17" t="s">
+      <c r="A17" t="s">
         <v>9</v>
       </c>
       <c r="B17" s="16"/>
-      <c r="H17" s="18"/>
+      <c r="H17" s="17"/>
       <c r="I17" s="16"/>
-      <c r="O17" s="18"/>
+      <c r="O17" s="17"/>
       <c r="P17" s="16"/>
-      <c r="V17" s="18"/>
+      <c r="V17" s="17"/>
       <c r="W17" s="16"/>
-      <c r="AC17" s="18"/>
+      <c r="AC17" s="17"/>
       <c r="AD17" s="16"/>
-      <c r="AJ17" s="18"/>
-      <c r="AK17" s="22"/>
-      <c r="AL17" s="23"/>
-      <c r="AM17" s="23"/>
-      <c r="AN17" s="23"/>
-      <c r="AO17" s="23"/>
-      <c r="AP17" s="23"/>
-      <c r="AQ17" s="24"/>
+      <c r="AJ17" s="17"/>
+      <c r="AK17" s="21"/>
+      <c r="AL17" s="22"/>
+      <c r="AM17" s="22"/>
+      <c r="AN17" s="22"/>
+      <c r="AO17" s="22"/>
+      <c r="AP17" s="22"/>
+      <c r="AQ17" s="23"/>
       <c r="AR17" s="16"/>
-      <c r="AX17" s="18"/>
+      <c r="AX17" s="17"/>
       <c r="AY17" s="16"/>
-      <c r="BE17" s="18"/>
+      <c r="BE17" s="17"/>
       <c r="BF17" s="16"/>
-      <c r="BL17" s="18"/>
+      <c r="BL17" s="17"/>
       <c r="BM17" s="16"/>
-      <c r="BS17" s="18"/>
+      <c r="BS17" s="17"/>
       <c r="BT17" s="16"/>
-      <c r="BZ17" s="18"/>
+      <c r="BZ17" s="17"/>
       <c r="CA17" s="16"/>
-      <c r="CG17" s="18"/>
+      <c r="CG17" s="17"/>
       <c r="CH17" s="16"/>
-      <c r="CN17" s="18"/>
+      <c r="CN17" s="17"/>
       <c r="CO17" s="16"/>
-      <c r="CU17" s="18"/>
+      <c r="CU17" s="17"/>
       <c r="CV17" s="16"/>
-      <c r="DB17" s="18"/>
+      <c r="DB17" s="17"/>
       <c r="DC17" s="16"/>
-      <c r="DD17" s="18"/>
+      <c r="DD17" s="17"/>
     </row>
     <row r="18" spans="1:108" x14ac:dyDescent="0.2">
-      <c r="A18" s="17" t="s">
+      <c r="A18" t="s">
         <v>12</v>
       </c>
       <c r="B18" s="16"/>
-      <c r="H18" s="18"/>
+      <c r="H18" s="17"/>
       <c r="I18" s="16"/>
-      <c r="O18" s="18"/>
+      <c r="O18" s="17"/>
       <c r="P18" s="16"/>
-      <c r="V18" s="18"/>
+      <c r="V18" s="17"/>
       <c r="W18" s="16"/>
-      <c r="AC18" s="18"/>
+      <c r="AC18" s="17"/>
       <c r="AD18" s="16"/>
-      <c r="AJ18" s="18"/>
-      <c r="AK18" s="22"/>
-      <c r="AL18" s="23"/>
-      <c r="AM18" s="23"/>
-      <c r="AN18" s="23"/>
-      <c r="AO18" s="23"/>
-      <c r="AP18" s="23"/>
-      <c r="AQ18" s="24"/>
-      <c r="AR18" s="22"/>
-      <c r="AS18" s="23"/>
-      <c r="AT18" s="23"/>
-      <c r="AU18" s="23"/>
-      <c r="AV18" s="23"/>
-      <c r="AW18" s="23"/>
-      <c r="AX18" s="24"/>
-      <c r="AY18" s="22"/>
-      <c r="AZ18" s="23"/>
-      <c r="BA18" s="23"/>
-      <c r="BB18" s="23"/>
-      <c r="BC18" s="23"/>
-      <c r="BD18" s="23"/>
-      <c r="BE18" s="24"/>
+      <c r="AJ18" s="17"/>
+      <c r="AK18" s="21"/>
+      <c r="AL18" s="22"/>
+      <c r="AM18" s="22"/>
+      <c r="AN18" s="22"/>
+      <c r="AO18" s="22"/>
+      <c r="AP18" s="22"/>
+      <c r="AQ18" s="23"/>
+      <c r="AR18" s="21"/>
+      <c r="AS18" s="22"/>
+      <c r="AT18" s="22"/>
+      <c r="AU18" s="22"/>
+      <c r="AV18" s="22"/>
+      <c r="AW18" s="22"/>
+      <c r="AX18" s="23"/>
+      <c r="AY18" s="21"/>
+      <c r="AZ18" s="22"/>
+      <c r="BA18" s="22"/>
+      <c r="BB18" s="22"/>
+      <c r="BC18" s="22"/>
+      <c r="BD18" s="22"/>
+      <c r="BE18" s="23"/>
       <c r="BF18" s="16"/>
-      <c r="BL18" s="18"/>
+      <c r="BL18" s="17"/>
       <c r="BM18" s="16"/>
-      <c r="BS18" s="18"/>
+      <c r="BS18" s="17"/>
       <c r="BT18" s="16"/>
-      <c r="BZ18" s="18"/>
+      <c r="BZ18" s="17"/>
       <c r="CA18" s="16"/>
-      <c r="CG18" s="18"/>
+      <c r="CG18" s="17"/>
       <c r="CH18" s="16"/>
-      <c r="CN18" s="18"/>
+      <c r="CN18" s="17"/>
       <c r="CO18" s="16"/>
-      <c r="CU18" s="18"/>
+      <c r="CU18" s="17"/>
       <c r="CV18" s="16"/>
-      <c r="DB18" s="18"/>
+      <c r="DB18" s="17"/>
       <c r="DC18" s="16"/>
-      <c r="DD18" s="18"/>
+      <c r="DD18" s="17"/>
     </row>
     <row r="19" spans="1:108" x14ac:dyDescent="0.2">
-      <c r="A19" s="17" t="s">
+      <c r="A19" t="s">
         <v>13</v>
       </c>
       <c r="B19" s="16"/>
-      <c r="H19" s="18"/>
+      <c r="H19" s="17"/>
       <c r="I19" s="16"/>
-      <c r="O19" s="18"/>
+      <c r="O19" s="17"/>
       <c r="P19" s="16"/>
-      <c r="V19" s="18"/>
+      <c r="V19" s="17"/>
       <c r="W19" s="16"/>
-      <c r="AC19" s="18"/>
+      <c r="AC19" s="17"/>
       <c r="AD19" s="16"/>
-      <c r="AJ19" s="18"/>
-      <c r="AK19" s="22"/>
-      <c r="AL19" s="23"/>
-      <c r="AM19" s="23"/>
-      <c r="AN19" s="23"/>
-      <c r="AO19" s="23"/>
-      <c r="AP19" s="23"/>
-      <c r="AQ19" s="24"/>
-      <c r="AR19" s="22"/>
-      <c r="AS19" s="23"/>
-      <c r="AT19" s="23"/>
-      <c r="AU19" s="23"/>
-      <c r="AV19" s="23"/>
-      <c r="AW19" s="23"/>
-      <c r="AX19" s="24"/>
-      <c r="AY19" s="22"/>
-      <c r="AZ19" s="23"/>
-      <c r="BA19" s="23"/>
-      <c r="BB19" s="23"/>
-      <c r="BC19" s="23"/>
-      <c r="BD19" s="23"/>
-      <c r="BE19" s="24"/>
+      <c r="AJ19" s="17"/>
+      <c r="AK19" s="21"/>
+      <c r="AL19" s="22"/>
+      <c r="AM19" s="22"/>
+      <c r="AN19" s="22"/>
+      <c r="AO19" s="22"/>
+      <c r="AP19" s="22"/>
+      <c r="AQ19" s="23"/>
+      <c r="AR19" s="21"/>
+      <c r="AS19" s="22"/>
+      <c r="AT19" s="22"/>
+      <c r="AU19" s="22"/>
+      <c r="AV19" s="22"/>
+      <c r="AW19" s="22"/>
+      <c r="AX19" s="23"/>
+      <c r="AY19" s="21"/>
+      <c r="AZ19" s="22"/>
+      <c r="BA19" s="22"/>
+      <c r="BB19" s="22"/>
+      <c r="BC19" s="22"/>
+      <c r="BD19" s="22"/>
+      <c r="BE19" s="23"/>
       <c r="BF19" s="16"/>
-      <c r="BL19" s="18"/>
+      <c r="BL19" s="17"/>
       <c r="BM19" s="16"/>
-      <c r="BS19" s="18"/>
+      <c r="BS19" s="17"/>
       <c r="BT19" s="16"/>
-      <c r="BZ19" s="18"/>
+      <c r="BZ19" s="17"/>
       <c r="CA19" s="16"/>
-      <c r="CG19" s="18"/>
+      <c r="CG19" s="17"/>
       <c r="CH19" s="16"/>
-      <c r="CN19" s="18"/>
+      <c r="CN19" s="17"/>
       <c r="CO19" s="16"/>
-      <c r="CU19" s="18"/>
+      <c r="CU19" s="17"/>
       <c r="CV19" s="16"/>
-      <c r="DB19" s="18"/>
+      <c r="DB19" s="17"/>
       <c r="DC19" s="16"/>
-      <c r="DD19" s="18"/>
+      <c r="DD19" s="17"/>
     </row>
     <row r="20" spans="1:108" x14ac:dyDescent="0.2">
-      <c r="A20" s="17" t="s">
+      <c r="A20" t="s">
         <v>14</v>
       </c>
       <c r="B20" s="16"/>
-      <c r="H20" s="18"/>
+      <c r="H20" s="17"/>
       <c r="I20" s="16"/>
-      <c r="O20" s="18"/>
+      <c r="O20" s="17"/>
       <c r="P20" s="16"/>
-      <c r="V20" s="18"/>
+      <c r="V20" s="17"/>
       <c r="W20" s="16"/>
-      <c r="AC20" s="18"/>
+      <c r="AC20" s="17"/>
       <c r="AD20" s="16"/>
-      <c r="AJ20" s="18"/>
+      <c r="AJ20" s="17"/>
       <c r="AK20" s="16"/>
-      <c r="AQ20" s="18"/>
-      <c r="AR20" s="22"/>
-      <c r="AS20" s="23"/>
-      <c r="AT20" s="23"/>
-      <c r="AU20" s="23"/>
-      <c r="AV20" s="23"/>
-      <c r="AW20" s="23"/>
-      <c r="AX20" s="24"/>
+      <c r="AQ20" s="17"/>
+      <c r="AR20" s="21"/>
+      <c r="AS20" s="22"/>
+      <c r="AT20" s="22"/>
+      <c r="AU20" s="22"/>
+      <c r="AV20" s="22"/>
+      <c r="AW20" s="22"/>
+      <c r="AX20" s="23"/>
       <c r="AY20" s="16"/>
-      <c r="BE20" s="18"/>
+      <c r="BE20" s="17"/>
       <c r="BF20" s="16"/>
-      <c r="BL20" s="18"/>
+      <c r="BL20" s="17"/>
       <c r="BM20" s="16"/>
-      <c r="BS20" s="18"/>
+      <c r="BS20" s="17"/>
       <c r="BT20" s="16"/>
-      <c r="BZ20" s="18"/>
+      <c r="BZ20" s="17"/>
       <c r="CA20" s="16"/>
-      <c r="CG20" s="18"/>
+      <c r="CG20" s="17"/>
       <c r="CH20" s="16"/>
-      <c r="CN20" s="18"/>
+      <c r="CN20" s="17"/>
       <c r="CO20" s="16"/>
-      <c r="CU20" s="18"/>
+      <c r="CU20" s="17"/>
       <c r="CV20" s="16"/>
-      <c r="DB20" s="18"/>
+      <c r="DB20" s="17"/>
       <c r="DC20" s="16"/>
-      <c r="DD20" s="18"/>
+      <c r="DD20" s="17"/>
     </row>
     <row r="21" spans="1:108" x14ac:dyDescent="0.2">
-      <c r="A21" s="17" t="s">
+      <c r="A21" t="s">
         <v>15</v>
       </c>
       <c r="B21" s="16"/>
-      <c r="H21" s="18"/>
+      <c r="H21" s="17"/>
       <c r="I21" s="16"/>
-      <c r="O21" s="18"/>
+      <c r="O21" s="17"/>
       <c r="P21" s="16"/>
-      <c r="V21" s="18"/>
+      <c r="V21" s="17"/>
       <c r="W21" s="16"/>
-      <c r="AC21" s="18"/>
+      <c r="AC21" s="17"/>
       <c r="AD21" s="16"/>
-      <c r="AJ21" s="18"/>
+      <c r="AJ21" s="17"/>
       <c r="AK21" s="16"/>
-      <c r="AQ21" s="18"/>
+      <c r="AQ21" s="17"/>
       <c r="AR21" s="16"/>
-      <c r="AX21" s="18"/>
+      <c r="AX21" s="17"/>
       <c r="AY21" s="16"/>
-      <c r="BE21" s="18"/>
-      <c r="BF21" s="22"/>
-      <c r="BG21" s="23"/>
-      <c r="BH21" s="23"/>
-      <c r="BI21" s="23"/>
-      <c r="BJ21" s="23"/>
-      <c r="BK21" s="23"/>
-      <c r="BL21" s="24"/>
+      <c r="BE21" s="17"/>
+      <c r="BF21" s="21"/>
+      <c r="BG21" s="22"/>
+      <c r="BH21" s="22"/>
+      <c r="BI21" s="22"/>
+      <c r="BJ21" s="22"/>
+      <c r="BK21" s="22"/>
+      <c r="BL21" s="23"/>
       <c r="BM21" s="16"/>
-      <c r="BS21" s="18"/>
+      <c r="BS21" s="17"/>
       <c r="BT21" s="16"/>
-      <c r="BZ21" s="18"/>
+      <c r="BZ21" s="17"/>
       <c r="CA21" s="16"/>
-      <c r="CG21" s="18"/>
+      <c r="CG21" s="17"/>
       <c r="CH21" s="16"/>
-      <c r="CN21" s="18"/>
+      <c r="CN21" s="17"/>
       <c r="CO21" s="16"/>
-      <c r="CU21" s="18"/>
+      <c r="CU21" s="17"/>
       <c r="CV21" s="16"/>
-      <c r="DB21" s="18"/>
+      <c r="DB21" s="17"/>
       <c r="DC21" s="16"/>
-      <c r="DD21" s="18"/>
+      <c r="DD21" s="17"/>
     </row>
     <row r="22" spans="1:108" x14ac:dyDescent="0.2">
-      <c r="A22" s="17" t="s">
+      <c r="A22" t="s">
         <v>16</v>
       </c>
       <c r="B22" s="16"/>
-      <c r="H22" s="18"/>
+      <c r="H22" s="17"/>
       <c r="I22" s="16"/>
-      <c r="O22" s="18"/>
+      <c r="O22" s="17"/>
       <c r="P22" s="16"/>
-      <c r="V22" s="18"/>
+      <c r="V22" s="17"/>
       <c r="W22" s="16"/>
-      <c r="AC22" s="18"/>
+      <c r="AC22" s="17"/>
       <c r="AD22" s="16"/>
-      <c r="AJ22" s="18"/>
+      <c r="AJ22" s="17"/>
       <c r="AK22" s="16"/>
-      <c r="AQ22" s="18"/>
+      <c r="AQ22" s="17"/>
       <c r="AR22" s="16"/>
-      <c r="AX22" s="18"/>
+      <c r="AX22" s="17"/>
       <c r="AY22" s="16"/>
-      <c r="BE22" s="18"/>
-      <c r="BF22" s="22"/>
-      <c r="BG22" s="23"/>
-      <c r="BH22" s="23"/>
-      <c r="BI22" s="23"/>
-      <c r="BJ22" s="23"/>
-      <c r="BK22" s="23"/>
-      <c r="BL22" s="24"/>
+      <c r="BE22" s="17"/>
+      <c r="BF22" s="21"/>
+      <c r="BG22" s="22"/>
+      <c r="BH22" s="22"/>
+      <c r="BI22" s="22"/>
+      <c r="BJ22" s="22"/>
+      <c r="BK22" s="22"/>
+      <c r="BL22" s="23"/>
       <c r="BM22" s="16"/>
-      <c r="BS22" s="18"/>
+      <c r="BS22" s="17"/>
       <c r="BT22" s="16"/>
-      <c r="BZ22" s="18"/>
+      <c r="BZ22" s="17"/>
       <c r="CA22" s="16"/>
-      <c r="CG22" s="18"/>
+      <c r="CG22" s="17"/>
       <c r="CH22" s="16"/>
-      <c r="CN22" s="18"/>
+      <c r="CN22" s="17"/>
       <c r="CO22" s="16"/>
-      <c r="CU22" s="18"/>
+      <c r="CU22" s="17"/>
       <c r="CV22" s="16"/>
-      <c r="DB22" s="18"/>
+      <c r="DB22" s="17"/>
       <c r="DC22" s="16"/>
-      <c r="DD22" s="18"/>
+      <c r="DD22" s="17"/>
     </row>
     <row r="23" spans="1:108" x14ac:dyDescent="0.2">
-      <c r="A23" s="17" t="s">
+      <c r="A23" t="s">
         <v>12</v>
       </c>
       <c r="B23" s="16"/>
-      <c r="H23" s="18"/>
+      <c r="H23" s="17"/>
       <c r="I23" s="16"/>
-      <c r="O23" s="18"/>
+      <c r="O23" s="17"/>
       <c r="P23" s="16"/>
-      <c r="V23" s="18"/>
+      <c r="V23" s="17"/>
       <c r="W23" s="16"/>
-      <c r="AC23" s="18"/>
+      <c r="AC23" s="17"/>
       <c r="AD23" s="16"/>
-      <c r="AJ23" s="18"/>
+      <c r="AJ23" s="17"/>
       <c r="AK23" s="16"/>
-      <c r="AQ23" s="18"/>
+      <c r="AQ23" s="17"/>
       <c r="AR23" s="16"/>
-      <c r="AX23" s="18"/>
+      <c r="AX23" s="17"/>
       <c r="AY23" s="16"/>
-      <c r="BE23" s="18"/>
+      <c r="BE23" s="17"/>
       <c r="BF23" s="16"/>
-      <c r="BL23" s="18"/>
-      <c r="BM23" s="22"/>
-      <c r="BN23" s="23"/>
-      <c r="BO23" s="23"/>
-      <c r="BP23" s="23"/>
-      <c r="BQ23" s="23"/>
-      <c r="BR23" s="23"/>
-      <c r="BS23" s="24"/>
-      <c r="BT23" s="22"/>
-      <c r="BU23" s="23"/>
-      <c r="BV23" s="23"/>
-      <c r="BW23" s="23"/>
-      <c r="BX23" s="23"/>
-      <c r="BY23" s="23"/>
-      <c r="BZ23" s="24"/>
-      <c r="CA23" s="22"/>
-      <c r="CB23" s="23"/>
-      <c r="CC23" s="23"/>
-      <c r="CD23" s="23"/>
-      <c r="CE23" s="23"/>
-      <c r="CF23" s="23"/>
-      <c r="CG23" s="24"/>
-      <c r="CH23" s="22"/>
-      <c r="CI23" s="23"/>
-      <c r="CJ23" s="23"/>
-      <c r="CK23" s="23"/>
-      <c r="CL23" s="23"/>
-      <c r="CM23" s="23"/>
-      <c r="CN23" s="24"/>
+      <c r="BL23" s="17"/>
+      <c r="BM23" s="21"/>
+      <c r="BN23" s="22"/>
+      <c r="BO23" s="22"/>
+      <c r="BP23" s="22"/>
+      <c r="BQ23" s="22"/>
+      <c r="BR23" s="22"/>
+      <c r="BS23" s="23"/>
+      <c r="BT23" s="21"/>
+      <c r="BU23" s="22"/>
+      <c r="BV23" s="22"/>
+      <c r="BW23" s="22"/>
+      <c r="BX23" s="22"/>
+      <c r="BY23" s="22"/>
+      <c r="BZ23" s="23"/>
+      <c r="CA23" s="21"/>
+      <c r="CB23" s="22"/>
+      <c r="CC23" s="22"/>
+      <c r="CD23" s="22"/>
+      <c r="CE23" s="22"/>
+      <c r="CF23" s="22"/>
+      <c r="CG23" s="23"/>
+      <c r="CH23" s="21"/>
+      <c r="CI23" s="22"/>
+      <c r="CJ23" s="22"/>
+      <c r="CK23" s="22"/>
+      <c r="CL23" s="22"/>
+      <c r="CM23" s="22"/>
+      <c r="CN23" s="23"/>
       <c r="CO23" s="16"/>
-      <c r="CU23" s="18"/>
+      <c r="CU23" s="17"/>
       <c r="CV23" s="16"/>
-      <c r="DB23" s="18"/>
+      <c r="DB23" s="17"/>
       <c r="DC23" s="16"/>
-      <c r="DD23" s="18"/>
+      <c r="DD23" s="17"/>
     </row>
     <row r="24" spans="1:108" x14ac:dyDescent="0.2">
-      <c r="A24" s="17" t="s">
+      <c r="A24" t="s">
         <v>13</v>
       </c>
       <c r="B24" s="16"/>
-      <c r="H24" s="18"/>
+      <c r="H24" s="17"/>
       <c r="I24" s="16"/>
-      <c r="O24" s="18"/>
+      <c r="O24" s="17"/>
       <c r="P24" s="16"/>
-      <c r="V24" s="18"/>
+      <c r="V24" s="17"/>
       <c r="W24" s="16"/>
-      <c r="AC24" s="18"/>
+      <c r="AC24" s="17"/>
       <c r="AD24" s="16"/>
-      <c r="AJ24" s="18"/>
+      <c r="AJ24" s="17"/>
       <c r="AK24" s="16"/>
-      <c r="AQ24" s="18"/>
+      <c r="AQ24" s="17"/>
       <c r="AR24" s="16"/>
-      <c r="AX24" s="18"/>
+      <c r="AX24" s="17"/>
       <c r="AY24" s="16"/>
-      <c r="BE24" s="18"/>
+      <c r="BE24" s="17"/>
       <c r="BF24" s="16"/>
-      <c r="BL24" s="18"/>
-      <c r="BM24" s="22"/>
-      <c r="BN24" s="23"/>
-      <c r="BO24" s="23"/>
-      <c r="BP24" s="23"/>
-      <c r="BQ24" s="23"/>
-      <c r="BR24" s="23"/>
-      <c r="BS24" s="24"/>
-      <c r="BT24" s="22"/>
-      <c r="BU24" s="23"/>
-      <c r="BV24" s="23"/>
-      <c r="BW24" s="23"/>
-      <c r="BX24" s="23"/>
-      <c r="BY24" s="23"/>
-      <c r="BZ24" s="24"/>
-      <c r="CA24" s="22"/>
-      <c r="CB24" s="23"/>
-      <c r="CC24" s="23"/>
-      <c r="CD24" s="23"/>
-      <c r="CE24" s="23"/>
-      <c r="CF24" s="23"/>
-      <c r="CG24" s="24"/>
-      <c r="CH24" s="22"/>
-      <c r="CI24" s="23"/>
-      <c r="CJ24" s="23"/>
-      <c r="CK24" s="23"/>
-      <c r="CL24" s="23"/>
-      <c r="CM24" s="23"/>
-      <c r="CN24" s="24"/>
+      <c r="BL24" s="17"/>
+      <c r="BM24" s="21"/>
+      <c r="BN24" s="22"/>
+      <c r="BO24" s="22"/>
+      <c r="BP24" s="22"/>
+      <c r="BQ24" s="22"/>
+      <c r="BR24" s="22"/>
+      <c r="BS24" s="23"/>
+      <c r="BT24" s="21"/>
+      <c r="BU24" s="22"/>
+      <c r="BV24" s="22"/>
+      <c r="BW24" s="22"/>
+      <c r="BX24" s="22"/>
+      <c r="BY24" s="22"/>
+      <c r="BZ24" s="23"/>
+      <c r="CA24" s="21"/>
+      <c r="CB24" s="22"/>
+      <c r="CC24" s="22"/>
+      <c r="CD24" s="22"/>
+      <c r="CE24" s="22"/>
+      <c r="CF24" s="22"/>
+      <c r="CG24" s="23"/>
+      <c r="CH24" s="21"/>
+      <c r="CI24" s="22"/>
+      <c r="CJ24" s="22"/>
+      <c r="CK24" s="22"/>
+      <c r="CL24" s="22"/>
+      <c r="CM24" s="22"/>
+      <c r="CN24" s="23"/>
       <c r="CO24" s="16"/>
-      <c r="CU24" s="18"/>
+      <c r="CU24" s="17"/>
       <c r="CV24" s="16"/>
-      <c r="DB24" s="18"/>
+      <c r="DB24" s="17"/>
       <c r="DC24" s="16"/>
-      <c r="DD24" s="18"/>
+      <c r="DD24" s="17"/>
     </row>
     <row r="25" spans="1:108" x14ac:dyDescent="0.2">
-      <c r="A25" s="17" t="s">
+      <c r="A25" t="s">
         <v>17</v>
       </c>
       <c r="B25" s="16"/>
-      <c r="H25" s="18"/>
+      <c r="H25" s="17"/>
       <c r="I25" s="16"/>
-      <c r="O25" s="18"/>
+      <c r="O25" s="17"/>
       <c r="P25" s="16"/>
-      <c r="V25" s="18"/>
+      <c r="V25" s="17"/>
       <c r="W25" s="16"/>
-      <c r="AC25" s="18"/>
+      <c r="AC25" s="17"/>
       <c r="AD25" s="16"/>
-      <c r="AJ25" s="18"/>
+      <c r="AJ25" s="17"/>
       <c r="AK25" s="16"/>
-      <c r="AQ25" s="18"/>
+      <c r="AQ25" s="17"/>
       <c r="AR25" s="16"/>
-      <c r="AX25" s="18"/>
+      <c r="AX25" s="17"/>
       <c r="AY25" s="16"/>
-      <c r="BE25" s="18"/>
+      <c r="BE25" s="17"/>
       <c r="BF25" s="16"/>
-      <c r="BL25" s="18"/>
+      <c r="BL25" s="17"/>
       <c r="BM25" s="16"/>
-      <c r="BS25" s="18"/>
+      <c r="BS25" s="17"/>
       <c r="BT25" s="16"/>
-      <c r="BZ25" s="18"/>
+      <c r="BZ25" s="17"/>
       <c r="CA25" s="16"/>
-      <c r="CG25" s="18"/>
+      <c r="CG25" s="17"/>
       <c r="CH25" s="16"/>
-      <c r="CN25" s="18"/>
-      <c r="CO25" s="22"/>
-      <c r="CP25" s="23"/>
-      <c r="CQ25" s="23"/>
-      <c r="CR25" s="23"/>
-      <c r="CS25" s="23"/>
-      <c r="CT25" s="23"/>
-      <c r="CU25" s="24"/>
+      <c r="CN25" s="17"/>
+      <c r="CO25" s="21"/>
+      <c r="CP25" s="22"/>
+      <c r="CQ25" s="22"/>
+      <c r="CR25" s="22"/>
+      <c r="CS25" s="22"/>
+      <c r="CT25" s="22"/>
+      <c r="CU25" s="23"/>
       <c r="CV25" s="16"/>
-      <c r="DB25" s="18"/>
+      <c r="DB25" s="17"/>
       <c r="DC25" s="16"/>
-      <c r="DD25" s="18"/>
+      <c r="DD25" s="17"/>
     </row>
     <row r="26" spans="1:108" x14ac:dyDescent="0.2">
-      <c r="A26" s="17" t="s">
+      <c r="A26" t="s">
         <v>18</v>
       </c>
       <c r="B26" s="16"/>
-      <c r="H26" s="18"/>
+      <c r="H26" s="17"/>
       <c r="I26" s="16"/>
-      <c r="O26" s="18"/>
+      <c r="O26" s="17"/>
       <c r="P26" s="16"/>
-      <c r="V26" s="18"/>
+      <c r="V26" s="17"/>
       <c r="W26" s="16"/>
-      <c r="AC26" s="18"/>
+      <c r="AC26" s="17"/>
       <c r="AD26" s="16"/>
-      <c r="AJ26" s="18"/>
+      <c r="AJ26" s="17"/>
       <c r="AK26" s="16"/>
-      <c r="AQ26" s="18"/>
+      <c r="AQ26" s="17"/>
       <c r="AR26" s="16"/>
-      <c r="AX26" s="18"/>
+      <c r="AX26" s="17"/>
       <c r="AY26" s="16"/>
-      <c r="BE26" s="18"/>
+      <c r="BE26" s="17"/>
       <c r="BF26" s="16"/>
-      <c r="BL26" s="18"/>
+      <c r="BL26" s="17"/>
       <c r="BM26" s="16"/>
-      <c r="BS26" s="18"/>
+      <c r="BS26" s="17"/>
       <c r="BT26" s="16"/>
-      <c r="BZ26" s="18"/>
+      <c r="BZ26" s="17"/>
       <c r="CA26" s="16"/>
-      <c r="CG26" s="18"/>
+      <c r="CG26" s="17"/>
       <c r="CH26" s="16"/>
-      <c r="CN26" s="18"/>
-      <c r="CO26" s="22"/>
-      <c r="CP26" s="23"/>
-      <c r="CQ26" s="23"/>
-      <c r="CR26" s="23"/>
-      <c r="CS26" s="23"/>
-      <c r="CT26" s="23"/>
-      <c r="CU26" s="24"/>
+      <c r="CN26" s="17"/>
+      <c r="CO26" s="21"/>
+      <c r="CP26" s="22"/>
+      <c r="CQ26" s="22"/>
+      <c r="CR26" s="22"/>
+      <c r="CS26" s="22"/>
+      <c r="CT26" s="22"/>
+      <c r="CU26" s="23"/>
       <c r="CV26" s="16"/>
-      <c r="DB26" s="18"/>
+      <c r="DB26" s="17"/>
       <c r="DC26" s="16"/>
-      <c r="DD26" s="18"/>
+      <c r="DD26" s="17"/>
     </row>
     <row r="27" spans="1:108" x14ac:dyDescent="0.2">
-      <c r="A27" s="17" t="s">
+      <c r="A27" t="s">
         <v>19</v>
       </c>
       <c r="B27" s="16"/>
-      <c r="H27" s="18"/>
+      <c r="H27" s="17"/>
       <c r="I27" s="16"/>
-      <c r="O27" s="18"/>
+      <c r="O27" s="17"/>
       <c r="P27" s="16"/>
-      <c r="V27" s="18"/>
+      <c r="V27" s="17"/>
       <c r="W27" s="16"/>
-      <c r="AC27" s="18"/>
+      <c r="AC27" s="17"/>
       <c r="AD27" s="16"/>
-      <c r="AJ27" s="18"/>
+      <c r="AJ27" s="17"/>
       <c r="AK27" s="16"/>
-      <c r="AQ27" s="18"/>
+      <c r="AQ27" s="17"/>
       <c r="AR27" s="16"/>
-      <c r="AX27" s="18"/>
+      <c r="AX27" s="17"/>
       <c r="AY27" s="16"/>
-      <c r="BE27" s="18"/>
+      <c r="BE27" s="17"/>
       <c r="BF27" s="16"/>
-      <c r="BL27" s="18"/>
+      <c r="BL27" s="17"/>
       <c r="BM27" s="16"/>
-      <c r="BS27" s="18"/>
+      <c r="BS27" s="17"/>
       <c r="BT27" s="16"/>
-      <c r="BZ27" s="18"/>
+      <c r="BZ27" s="17"/>
       <c r="CA27" s="16"/>
-      <c r="CG27" s="18"/>
+      <c r="CG27" s="17"/>
       <c r="CH27" s="16"/>
-      <c r="CN27" s="18"/>
+      <c r="CN27" s="17"/>
       <c r="CO27" s="16"/>
-      <c r="CU27" s="18"/>
-      <c r="CV27" s="22"/>
-      <c r="CW27" s="23"/>
-      <c r="CX27" s="23"/>
-      <c r="CY27" s="23"/>
-      <c r="CZ27" s="23"/>
-      <c r="DA27" s="23"/>
-      <c r="DB27" s="24"/>
-      <c r="DC27" s="22"/>
-      <c r="DD27" s="24"/>
+      <c r="CU27" s="17"/>
+      <c r="CV27" s="21"/>
+      <c r="CW27" s="22"/>
+      <c r="CX27" s="22"/>
+      <c r="CY27" s="22"/>
+      <c r="CZ27" s="22"/>
+      <c r="DA27" s="22"/>
+      <c r="DB27" s="23"/>
+      <c r="DC27" s="21"/>
+      <c r="DD27" s="23"/>
     </row>
     <row r="28" spans="1:108" x14ac:dyDescent="0.2">
-      <c r="A28" s="17" t="s">
+      <c r="A28" t="s">
         <v>20</v>
       </c>
       <c r="B28" s="16"/>
-      <c r="H28" s="18"/>
+      <c r="H28" s="17"/>
       <c r="I28" s="16"/>
-      <c r="O28" s="18"/>
+      <c r="O28" s="17"/>
       <c r="P28" s="16"/>
-      <c r="V28" s="18"/>
+      <c r="V28" s="17"/>
       <c r="W28" s="16"/>
-      <c r="AC28" s="18"/>
+      <c r="AC28" s="17"/>
       <c r="AD28" s="16"/>
-      <c r="AJ28" s="18"/>
+      <c r="AJ28" s="17"/>
       <c r="AK28" s="16"/>
-      <c r="AQ28" s="18"/>
+      <c r="AQ28" s="17"/>
       <c r="AR28" s="16"/>
-      <c r="AX28" s="18"/>
+      <c r="AX28" s="17"/>
       <c r="AY28" s="16"/>
-      <c r="BE28" s="18"/>
+      <c r="BE28" s="17"/>
       <c r="BF28" s="16"/>
-      <c r="BL28" s="18"/>
+      <c r="BL28" s="17"/>
       <c r="BM28" s="16"/>
-      <c r="BS28" s="18"/>
+      <c r="BS28" s="17"/>
       <c r="BT28" s="16"/>
-      <c r="BZ28" s="18"/>
+      <c r="BZ28" s="17"/>
       <c r="CA28" s="16"/>
-      <c r="CG28" s="18"/>
+      <c r="CG28" s="17"/>
       <c r="CH28" s="16"/>
-      <c r="CN28" s="18"/>
+      <c r="CN28" s="17"/>
       <c r="CO28" s="16"/>
-      <c r="CU28" s="18"/>
-      <c r="CV28" s="22"/>
-      <c r="CW28" s="23"/>
-      <c r="CX28" s="23"/>
-      <c r="CY28" s="23"/>
-      <c r="CZ28" s="23"/>
-      <c r="DA28" s="23"/>
-      <c r="DB28" s="24"/>
-      <c r="DC28" s="22"/>
-      <c r="DD28" s="24"/>
+      <c r="CU28" s="17"/>
+      <c r="CV28" s="21"/>
+      <c r="CW28" s="22"/>
+      <c r="CX28" s="22"/>
+      <c r="CY28" s="22"/>
+      <c r="CZ28" s="22"/>
+      <c r="DA28" s="22"/>
+      <c r="DB28" s="23"/>
+      <c r="DC28" s="21"/>
+      <c r="DD28" s="23"/>
     </row>
     <row r="29" spans="1:108" x14ac:dyDescent="0.2">
-      <c r="A29" s="37" t="s">
+      <c r="A29" s="32" t="s">
         <v>21</v>
       </c>
-      <c r="B29" s="19"/>
-      <c r="C29" s="20"/>
-      <c r="D29" s="20"/>
-      <c r="E29" s="20"/>
-      <c r="F29" s="20"/>
-      <c r="G29" s="20"/>
-      <c r="H29" s="21"/>
-      <c r="I29" s="19"/>
-      <c r="J29" s="20"/>
-      <c r="K29" s="20"/>
-      <c r="L29" s="20"/>
-      <c r="M29" s="20"/>
-      <c r="N29" s="20"/>
-      <c r="O29" s="21"/>
-      <c r="P29" s="19"/>
-      <c r="Q29" s="20"/>
-      <c r="R29" s="20"/>
-      <c r="S29" s="20"/>
-      <c r="T29" s="20"/>
-      <c r="U29" s="20"/>
-      <c r="V29" s="21"/>
-      <c r="W29" s="19"/>
-      <c r="X29" s="20"/>
-      <c r="Y29" s="20"/>
-      <c r="Z29" s="20"/>
-      <c r="AA29" s="20"/>
-      <c r="AB29" s="20"/>
-      <c r="AC29" s="21"/>
-      <c r="AD29" s="19"/>
-      <c r="AE29" s="20"/>
-      <c r="AF29" s="20"/>
-      <c r="AG29" s="20"/>
-      <c r="AH29" s="20"/>
-      <c r="AI29" s="20"/>
-      <c r="AJ29" s="21"/>
-      <c r="AK29" s="19"/>
-      <c r="AL29" s="20"/>
-      <c r="AM29" s="20"/>
-      <c r="AN29" s="20"/>
-      <c r="AO29" s="20"/>
-      <c r="AP29" s="20"/>
-      <c r="AQ29" s="21"/>
-      <c r="AR29" s="19"/>
-      <c r="AS29" s="20"/>
-      <c r="AT29" s="20"/>
-      <c r="AU29" s="20"/>
-      <c r="AV29" s="20"/>
-      <c r="AW29" s="20"/>
-      <c r="AX29" s="21"/>
-      <c r="AY29" s="19"/>
-      <c r="AZ29" s="20"/>
-      <c r="BA29" s="20"/>
-      <c r="BB29" s="20"/>
-      <c r="BC29" s="20"/>
-      <c r="BD29" s="20"/>
-      <c r="BE29" s="21"/>
-      <c r="BF29" s="19"/>
-      <c r="BG29" s="20"/>
-      <c r="BH29" s="20"/>
-      <c r="BI29" s="20"/>
-      <c r="BJ29" s="20"/>
-      <c r="BK29" s="20"/>
-      <c r="BL29" s="21"/>
-      <c r="BM29" s="19"/>
-      <c r="BN29" s="20"/>
-      <c r="BO29" s="20"/>
-      <c r="BP29" s="20"/>
-      <c r="BQ29" s="20"/>
-      <c r="BR29" s="20"/>
-      <c r="BS29" s="21"/>
-      <c r="BT29" s="19"/>
-      <c r="BU29" s="20"/>
-      <c r="BV29" s="20"/>
-      <c r="BW29" s="20"/>
-      <c r="BX29" s="20"/>
-      <c r="BY29" s="20"/>
-      <c r="BZ29" s="21"/>
-      <c r="CA29" s="19"/>
-      <c r="CB29" s="20"/>
-      <c r="CC29" s="20"/>
-      <c r="CD29" s="20"/>
-      <c r="CE29" s="20"/>
-      <c r="CF29" s="20"/>
-      <c r="CG29" s="21"/>
-      <c r="CH29" s="19"/>
-      <c r="CI29" s="20"/>
-      <c r="CJ29" s="20"/>
-      <c r="CK29" s="20"/>
-      <c r="CL29" s="20"/>
-      <c r="CM29" s="20"/>
-      <c r="CN29" s="21"/>
-      <c r="CO29" s="19"/>
-      <c r="CP29" s="20"/>
-      <c r="CQ29" s="20"/>
-      <c r="CR29" s="20"/>
-      <c r="CS29" s="20"/>
-      <c r="CT29" s="20"/>
-      <c r="CU29" s="21"/>
-      <c r="CV29" s="25"/>
-      <c r="CW29" s="26"/>
-      <c r="CX29" s="26"/>
-      <c r="CY29" s="26"/>
-      <c r="CZ29" s="26"/>
-      <c r="DA29" s="26"/>
-      <c r="DB29" s="27"/>
-      <c r="DC29" s="25"/>
-      <c r="DD29" s="27"/>
+      <c r="B29" s="18"/>
+      <c r="C29" s="19"/>
+      <c r="D29" s="19"/>
+      <c r="E29" s="19"/>
+      <c r="F29" s="19"/>
+      <c r="G29" s="19"/>
+      <c r="H29" s="20"/>
+      <c r="I29" s="18"/>
+      <c r="J29" s="19"/>
+      <c r="K29" s="19"/>
+      <c r="L29" s="19"/>
+      <c r="M29" s="19"/>
+      <c r="N29" s="19"/>
+      <c r="O29" s="20"/>
+      <c r="P29" s="18"/>
+      <c r="Q29" s="19"/>
+      <c r="R29" s="19"/>
+      <c r="S29" s="19"/>
+      <c r="T29" s="19"/>
+      <c r="U29" s="19"/>
+      <c r="V29" s="20"/>
+      <c r="W29" s="18"/>
+      <c r="X29" s="19"/>
+      <c r="Y29" s="19"/>
+      <c r="Z29" s="19"/>
+      <c r="AA29" s="19"/>
+      <c r="AB29" s="19"/>
+      <c r="AC29" s="20"/>
+      <c r="AD29" s="18"/>
+      <c r="AE29" s="19"/>
+      <c r="AF29" s="19"/>
+      <c r="AG29" s="19"/>
+      <c r="AH29" s="19"/>
+      <c r="AI29" s="19"/>
+      <c r="AJ29" s="20"/>
+      <c r="AK29" s="18"/>
+      <c r="AL29" s="19"/>
+      <c r="AM29" s="19"/>
+      <c r="AN29" s="19"/>
+      <c r="AO29" s="19"/>
+      <c r="AP29" s="19"/>
+      <c r="AQ29" s="20"/>
+      <c r="AR29" s="18"/>
+      <c r="AS29" s="19"/>
+      <c r="AT29" s="19"/>
+      <c r="AU29" s="19"/>
+      <c r="AV29" s="19"/>
+      <c r="AW29" s="19"/>
+      <c r="AX29" s="20"/>
+      <c r="AY29" s="18"/>
+      <c r="AZ29" s="19"/>
+      <c r="BA29" s="19"/>
+      <c r="BB29" s="19"/>
+      <c r="BC29" s="19"/>
+      <c r="BD29" s="19"/>
+      <c r="BE29" s="20"/>
+      <c r="BF29" s="18"/>
+      <c r="BG29" s="19"/>
+      <c r="BH29" s="19"/>
+      <c r="BI29" s="19"/>
+      <c r="BJ29" s="19"/>
+      <c r="BK29" s="19"/>
+      <c r="BL29" s="20"/>
+      <c r="BM29" s="18"/>
+      <c r="BN29" s="19"/>
+      <c r="BO29" s="19"/>
+      <c r="BP29" s="19"/>
+      <c r="BQ29" s="19"/>
+      <c r="BR29" s="19"/>
+      <c r="BS29" s="20"/>
+      <c r="BT29" s="18"/>
+      <c r="BU29" s="19"/>
+      <c r="BV29" s="19"/>
+      <c r="BW29" s="19"/>
+      <c r="BX29" s="19"/>
+      <c r="BY29" s="19"/>
+      <c r="BZ29" s="20"/>
+      <c r="CA29" s="18"/>
+      <c r="CB29" s="19"/>
+      <c r="CC29" s="19"/>
+      <c r="CD29" s="19"/>
+      <c r="CE29" s="19"/>
+      <c r="CF29" s="19"/>
+      <c r="CG29" s="20"/>
+      <c r="CH29" s="18"/>
+      <c r="CI29" s="19"/>
+      <c r="CJ29" s="19"/>
+      <c r="CK29" s="19"/>
+      <c r="CL29" s="19"/>
+      <c r="CM29" s="19"/>
+      <c r="CN29" s="20"/>
+      <c r="CO29" s="18"/>
+      <c r="CP29" s="19"/>
+      <c r="CQ29" s="19"/>
+      <c r="CR29" s="19"/>
+      <c r="CS29" s="19"/>
+      <c r="CT29" s="19"/>
+      <c r="CU29" s="20"/>
+      <c r="CV29" s="24"/>
+      <c r="CW29" s="25"/>
+      <c r="CX29" s="25"/>
+      <c r="CY29" s="25"/>
+      <c r="CZ29" s="25"/>
+      <c r="DA29" s="25"/>
+      <c r="DB29" s="26"/>
+      <c r="DC29" s="24"/>
+      <c r="DD29" s="26"/>
     </row>
     <row r="30" spans="1:108" x14ac:dyDescent="0.2">
-      <c r="A30" s="37"/>
+      <c r="A30" s="32"/>
     </row>
     <row r="31" spans="1:108" x14ac:dyDescent="0.2">
-      <c r="A31" s="37"/>
+      <c r="A31" s="32"/>
     </row>
     <row r="32" spans="1:108" x14ac:dyDescent="0.2">
-      <c r="A32" s="37"/>
+      <c r="A32" s="32"/>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A33" s="37"/>
+      <c r="A33" s="32"/>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A34" s="37"/>
+      <c r="A34" s="32"/>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A35" s="37"/>
+      <c r="A35" s="32"/>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A36" s="37"/>
+      <c r="A36" s="32"/>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A37" s="37"/>
+      <c r="A37" s="32"/>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A38" s="37"/>
+      <c r="A38" s="32"/>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A39" s="37"/>
+      <c r="A39" s="32"/>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A40" s="37"/>
+      <c r="A40" s="32"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -4156,182 +3985,133 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D7CCD592-E217-46A0-898D-B6277524B4F3}">
-  <dimension ref="A1:BF52"/>
+  <dimension ref="A1:BE52"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="20.88671875" style="17" bestFit="1" customWidth="1"/>
-    <col min="2" max="14" width="2.77734375" style="17" customWidth="1"/>
-    <col min="15" max="15" width="3.21875" style="17" bestFit="1" customWidth="1"/>
-    <col min="16" max="42" width="2.77734375" style="17" customWidth="1"/>
-    <col min="43" max="43" width="3.21875" style="17" bestFit="1" customWidth="1"/>
-    <col min="44" max="49" width="2.77734375" style="17" customWidth="1"/>
-    <col min="50" max="51" width="3.21875" style="17" bestFit="1" customWidth="1"/>
-    <col min="52" max="57" width="2.77734375" style="17" customWidth="1"/>
-    <col min="58" max="58" width="11.5546875" style="17"/>
+    <col min="1" max="1" width="20.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="14" width="2.77734375" customWidth="1"/>
+    <col min="15" max="15" width="3.21875" bestFit="1" customWidth="1"/>
+    <col min="16" max="42" width="2.77734375" customWidth="1"/>
+    <col min="43" max="43" width="3.21875" bestFit="1" customWidth="1"/>
+    <col min="44" max="49" width="2.77734375" customWidth="1"/>
+    <col min="50" max="51" width="3.21875" bestFit="1" customWidth="1"/>
+    <col min="52" max="57" width="2.77734375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:57" ht="20.25" x14ac:dyDescent="0.3">
-      <c r="A1" s="31" t="s">
+      <c r="A1" s="27" t="s">
         <v>25</v>
       </c>
-      <c r="B1" s="32"/>
-      <c r="C1" s="32"/>
-      <c r="D1" s="32"/>
-      <c r="E1" s="32"/>
-      <c r="F1" s="32"/>
-      <c r="G1" s="32"/>
-      <c r="H1" s="32"/>
-      <c r="I1" s="32"/>
-      <c r="J1" s="32"/>
-      <c r="K1" s="32"/>
-      <c r="L1" s="32"/>
-      <c r="M1" s="32"/>
-      <c r="N1" s="32"/>
-      <c r="O1" s="32"/>
-      <c r="P1" s="32"/>
-      <c r="Q1" s="32"/>
     </row>
     <row r="2" spans="1:57" ht="20.25" x14ac:dyDescent="0.3">
-      <c r="A2" s="31" t="s">
+      <c r="A2" s="27" t="s">
         <v>26</v>
       </c>
-      <c r="B2" s="32"/>
-      <c r="C2" s="32"/>
-      <c r="D2" s="32"/>
-      <c r="E2" s="32"/>
-      <c r="F2" s="32"/>
-      <c r="G2" s="32"/>
-      <c r="H2" s="32"/>
-      <c r="I2" s="32"/>
-      <c r="J2" s="32"/>
-      <c r="K2" s="32"/>
-      <c r="L2" s="32"/>
-      <c r="M2" s="32"/>
-      <c r="N2" s="32"/>
-      <c r="O2" s="32"/>
-      <c r="P2" s="32"/>
-      <c r="Q2" s="32"/>
     </row>
     <row r="3" spans="1:57" ht="20.25" x14ac:dyDescent="0.3">
-      <c r="A3" s="31">
+      <c r="A3" s="27">
         <v>2026</v>
       </c>
-      <c r="B3" s="32"/>
-      <c r="C3" s="32"/>
-      <c r="D3" s="32"/>
-      <c r="E3" s="32"/>
-      <c r="F3" s="32"/>
-      <c r="G3" s="32"/>
-      <c r="H3" s="32"/>
-      <c r="I3" s="32"/>
-      <c r="J3" s="32"/>
-      <c r="K3" s="32"/>
-      <c r="L3" s="32"/>
-      <c r="M3" s="32"/>
-      <c r="N3" s="32"/>
-      <c r="O3" s="32"/>
-      <c r="P3" s="32"/>
-      <c r="Q3" s="32"/>
     </row>
     <row r="4" spans="1:57" x14ac:dyDescent="0.2">
-      <c r="A4" s="33"/>
-      <c r="B4" s="33"/>
-      <c r="C4" s="33"/>
-      <c r="D4" s="33"/>
-      <c r="E4" s="33"/>
-      <c r="F4" s="33"/>
-      <c r="G4" s="33"/>
-      <c r="H4" s="33"/>
-      <c r="I4" s="33"/>
-      <c r="J4" s="33"/>
-      <c r="K4" s="33"/>
-      <c r="L4" s="33"/>
-      <c r="M4" s="33"/>
-      <c r="N4" s="33"/>
-      <c r="O4" s="33"/>
-      <c r="P4" s="33"/>
-      <c r="Q4" s="33"/>
+      <c r="A4" s="28"/>
+      <c r="B4" s="28"/>
+      <c r="C4" s="28"/>
+      <c r="D4" s="28"/>
+      <c r="E4" s="28"/>
+      <c r="F4" s="28"/>
+      <c r="G4" s="28"/>
+      <c r="H4" s="28"/>
+      <c r="I4" s="28"/>
+      <c r="J4" s="28"/>
+      <c r="K4" s="28"/>
+      <c r="L4" s="28"/>
+      <c r="M4" s="28"/>
+      <c r="N4" s="28"/>
+      <c r="O4" s="28"/>
+      <c r="P4" s="28"/>
+      <c r="Q4" s="28"/>
     </row>
     <row r="5" spans="1:57" ht="18" x14ac:dyDescent="0.25">
-      <c r="A5" s="34" t="s">
+      <c r="A5" s="29" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="6" spans="1:57" ht="18" x14ac:dyDescent="0.25">
-      <c r="A6" s="34" t="s">
+      <c r="A6" s="29" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="7" spans="1:57" ht="15" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="8" spans="1:57" x14ac:dyDescent="0.2">
-      <c r="A8" s="35" t="s">
+      <c r="A8" s="30" t="s">
         <v>0</v>
       </c>
-      <c r="B8" s="30" t="s">
+      <c r="B8" s="37" t="s">
         <v>2</v>
       </c>
-      <c r="C8" s="28"/>
-      <c r="D8" s="28"/>
-      <c r="E8" s="28"/>
-      <c r="F8" s="28"/>
-      <c r="G8" s="28"/>
-      <c r="H8" s="28"/>
-      <c r="I8" s="28"/>
-      <c r="J8" s="28"/>
-      <c r="K8" s="28"/>
-      <c r="L8" s="28"/>
-      <c r="M8" s="28"/>
-      <c r="N8" s="28"/>
-      <c r="O8" s="28"/>
-      <c r="P8" s="28"/>
-      <c r="Q8" s="29"/>
-      <c r="R8" s="30" t="s">
+      <c r="C8" s="38"/>
+      <c r="D8" s="38"/>
+      <c r="E8" s="38"/>
+      <c r="F8" s="38"/>
+      <c r="G8" s="38"/>
+      <c r="H8" s="38"/>
+      <c r="I8" s="38"/>
+      <c r="J8" s="38"/>
+      <c r="K8" s="38"/>
+      <c r="L8" s="38"/>
+      <c r="M8" s="38"/>
+      <c r="N8" s="38"/>
+      <c r="O8" s="38"/>
+      <c r="P8" s="38"/>
+      <c r="Q8" s="39"/>
+      <c r="R8" s="37" t="s">
         <v>3</v>
       </c>
-      <c r="S8" s="28"/>
-      <c r="T8" s="28"/>
-      <c r="U8" s="28"/>
-      <c r="V8" s="28"/>
-      <c r="W8" s="28"/>
-      <c r="X8" s="28"/>
-      <c r="Y8" s="28"/>
-      <c r="Z8" s="28"/>
-      <c r="AA8" s="28"/>
-      <c r="AB8" s="28"/>
-      <c r="AC8" s="28"/>
-      <c r="AD8" s="28"/>
-      <c r="AE8" s="28"/>
-      <c r="AF8" s="28"/>
-      <c r="AG8" s="28"/>
-      <c r="AH8" s="28"/>
-      <c r="AI8" s="28"/>
-      <c r="AJ8" s="28"/>
-      <c r="AK8" s="28"/>
-      <c r="AL8" s="28"/>
-      <c r="AM8" s="28"/>
-      <c r="AN8" s="28"/>
-      <c r="AO8" s="28"/>
-      <c r="AP8" s="28"/>
-      <c r="AQ8" s="28"/>
-      <c r="AR8" s="28"/>
-      <c r="AS8" s="28"/>
-      <c r="AT8" s="28"/>
-      <c r="AU8" s="29"/>
-      <c r="AV8" s="42" t="s">
+      <c r="S8" s="38"/>
+      <c r="T8" s="38"/>
+      <c r="U8" s="38"/>
+      <c r="V8" s="38"/>
+      <c r="W8" s="38"/>
+      <c r="X8" s="38"/>
+      <c r="Y8" s="38"/>
+      <c r="Z8" s="38"/>
+      <c r="AA8" s="38"/>
+      <c r="AB8" s="38"/>
+      <c r="AC8" s="38"/>
+      <c r="AD8" s="38"/>
+      <c r="AE8" s="38"/>
+      <c r="AF8" s="38"/>
+      <c r="AG8" s="38"/>
+      <c r="AH8" s="38"/>
+      <c r="AI8" s="38"/>
+      <c r="AJ8" s="38"/>
+      <c r="AK8" s="38"/>
+      <c r="AL8" s="38"/>
+      <c r="AM8" s="38"/>
+      <c r="AN8" s="38"/>
+      <c r="AO8" s="38"/>
+      <c r="AP8" s="38"/>
+      <c r="AQ8" s="38"/>
+      <c r="AR8" s="38"/>
+      <c r="AS8" s="38"/>
+      <c r="AT8" s="38"/>
+      <c r="AU8" s="39"/>
+      <c r="AV8" s="43" t="s">
         <v>4</v>
       </c>
-      <c r="AW8" s="39"/>
-      <c r="AX8" s="39"/>
-      <c r="AY8" s="39"/>
-      <c r="AZ8" s="39"/>
-      <c r="BA8" s="39"/>
-      <c r="BB8" s="39"/>
-      <c r="BC8" s="39"/>
-      <c r="BD8" s="39"/>
-      <c r="BE8" s="41"/>
+      <c r="AW8" s="41"/>
+      <c r="AX8" s="41"/>
+      <c r="AY8" s="41"/>
+      <c r="AZ8" s="41"/>
+      <c r="BA8" s="41"/>
+      <c r="BB8" s="41"/>
+      <c r="BC8" s="41"/>
+      <c r="BD8" s="41"/>
+      <c r="BE8" s="44"/>
     </row>
     <row r="9" spans="1:57" ht="15" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="36" t="s">
+      <c r="A9" s="31" t="s">
         <v>24</v>
       </c>
       <c r="B9" s="9">
@@ -4505,596 +4285,596 @@
     </row>
     <row r="10" spans="1:57" x14ac:dyDescent="0.2">
       <c r="B10" s="16"/>
-      <c r="H10" s="18"/>
+      <c r="H10" s="17"/>
       <c r="I10" s="16"/>
-      <c r="O10" s="18"/>
+      <c r="O10" s="17"/>
       <c r="P10" s="16"/>
-      <c r="V10" s="18"/>
+      <c r="V10" s="17"/>
       <c r="W10" s="16"/>
-      <c r="AC10" s="18"/>
+      <c r="AC10" s="17"/>
       <c r="AD10" s="16"/>
-      <c r="AJ10" s="18"/>
+      <c r="AJ10" s="17"/>
       <c r="AK10" s="16"/>
-      <c r="AQ10" s="18"/>
+      <c r="AQ10" s="17"/>
       <c r="AR10" s="16"/>
-      <c r="AX10" s="18"/>
+      <c r="AX10" s="17"/>
       <c r="AY10" s="16"/>
-      <c r="BE10" s="18"/>
+      <c r="BE10" s="17"/>
     </row>
     <row r="11" spans="1:57" x14ac:dyDescent="0.2">
-      <c r="A11" s="17" t="s">
+      <c r="A11" t="s">
         <v>1</v>
       </c>
-      <c r="B11" s="22"/>
-      <c r="C11" s="23"/>
-      <c r="D11" s="23"/>
-      <c r="E11" s="23"/>
-      <c r="F11" s="23"/>
-      <c r="G11" s="23"/>
-      <c r="H11" s="24"/>
+      <c r="B11" s="21"/>
+      <c r="C11" s="22"/>
+      <c r="D11" s="22"/>
+      <c r="E11" s="22"/>
+      <c r="F11" s="22"/>
+      <c r="G11" s="22"/>
+      <c r="H11" s="23"/>
       <c r="I11" s="16"/>
-      <c r="O11" s="18"/>
+      <c r="O11" s="17"/>
       <c r="P11" s="16"/>
-      <c r="V11" s="18"/>
+      <c r="V11" s="17"/>
       <c r="W11" s="16"/>
-      <c r="AC11" s="18"/>
+      <c r="AC11" s="17"/>
       <c r="AD11" s="16"/>
-      <c r="AJ11" s="18"/>
+      <c r="AJ11" s="17"/>
       <c r="AK11" s="16"/>
-      <c r="AQ11" s="18"/>
+      <c r="AQ11" s="17"/>
       <c r="AR11" s="16"/>
-      <c r="AX11" s="18"/>
+      <c r="AX11" s="17"/>
       <c r="AY11" s="16"/>
-      <c r="BE11" s="18"/>
+      <c r="BE11" s="17"/>
     </row>
     <row r="12" spans="1:57" x14ac:dyDescent="0.2">
-      <c r="A12" s="17" t="s">
+      <c r="A12" t="s">
         <v>6</v>
       </c>
       <c r="B12" s="16"/>
-      <c r="H12" s="18"/>
-      <c r="I12" s="22"/>
-      <c r="J12" s="23"/>
-      <c r="K12" s="23"/>
-      <c r="L12" s="23"/>
-      <c r="M12" s="23"/>
-      <c r="N12" s="23"/>
-      <c r="O12" s="24"/>
+      <c r="H12" s="17"/>
+      <c r="I12" s="21"/>
+      <c r="J12" s="22"/>
+      <c r="K12" s="22"/>
+      <c r="L12" s="22"/>
+      <c r="M12" s="22"/>
+      <c r="N12" s="22"/>
+      <c r="O12" s="23"/>
       <c r="P12" s="16"/>
-      <c r="V12" s="18"/>
+      <c r="V12" s="17"/>
       <c r="W12" s="16"/>
-      <c r="AC12" s="18"/>
+      <c r="AC12" s="17"/>
       <c r="AD12" s="16"/>
-      <c r="AJ12" s="18"/>
+      <c r="AJ12" s="17"/>
       <c r="AK12" s="16"/>
-      <c r="AQ12" s="18"/>
+      <c r="AQ12" s="17"/>
       <c r="AR12" s="16"/>
-      <c r="AX12" s="18"/>
+      <c r="AX12" s="17"/>
       <c r="AY12" s="16"/>
-      <c r="BE12" s="18"/>
+      <c r="BE12" s="17"/>
     </row>
     <row r="13" spans="1:57" x14ac:dyDescent="0.2">
-      <c r="A13" s="17" t="s">
+      <c r="A13" t="s">
         <v>11</v>
       </c>
       <c r="B13" s="16"/>
-      <c r="H13" s="18"/>
+      <c r="H13" s="17"/>
       <c r="I13" s="16"/>
-      <c r="O13" s="18"/>
-      <c r="P13" s="22"/>
-      <c r="Q13" s="23"/>
-      <c r="R13" s="23"/>
-      <c r="S13" s="23"/>
-      <c r="T13" s="23"/>
-      <c r="U13" s="23"/>
-      <c r="V13" s="24"/>
+      <c r="O13" s="17"/>
+      <c r="P13" s="21"/>
+      <c r="Q13" s="22"/>
+      <c r="R13" s="22"/>
+      <c r="S13" s="22"/>
+      <c r="T13" s="22"/>
+      <c r="U13" s="22"/>
+      <c r="V13" s="23"/>
       <c r="W13" s="16"/>
-      <c r="AC13" s="18"/>
+      <c r="AC13" s="17"/>
       <c r="AD13" s="16"/>
-      <c r="AJ13" s="18"/>
+      <c r="AJ13" s="17"/>
       <c r="AK13" s="16"/>
-      <c r="AQ13" s="18"/>
+      <c r="AQ13" s="17"/>
       <c r="AR13" s="16"/>
-      <c r="AX13" s="18"/>
+      <c r="AX13" s="17"/>
       <c r="AY13" s="16"/>
-      <c r="BE13" s="18"/>
+      <c r="BE13" s="17"/>
     </row>
     <row r="14" spans="1:57" x14ac:dyDescent="0.2">
-      <c r="A14" s="17" t="s">
+      <c r="A14" t="s">
         <v>7</v>
       </c>
       <c r="B14" s="16"/>
-      <c r="H14" s="18"/>
+      <c r="H14" s="17"/>
       <c r="I14" s="16"/>
-      <c r="O14" s="18"/>
-      <c r="P14" s="22"/>
-      <c r="Q14" s="23"/>
-      <c r="R14" s="23"/>
-      <c r="S14" s="23"/>
-      <c r="T14" s="23"/>
-      <c r="U14" s="23"/>
-      <c r="V14" s="24"/>
+      <c r="O14" s="17"/>
+      <c r="P14" s="21"/>
+      <c r="Q14" s="22"/>
+      <c r="R14" s="22"/>
+      <c r="S14" s="22"/>
+      <c r="T14" s="22"/>
+      <c r="U14" s="22"/>
+      <c r="V14" s="23"/>
       <c r="W14" s="16"/>
-      <c r="AC14" s="18"/>
+      <c r="AC14" s="17"/>
       <c r="AD14" s="16"/>
-      <c r="AJ14" s="18"/>
+      <c r="AJ14" s="17"/>
       <c r="AK14" s="16"/>
-      <c r="AQ14" s="18"/>
+      <c r="AQ14" s="17"/>
       <c r="AR14" s="16"/>
-      <c r="AX14" s="18"/>
+      <c r="AX14" s="17"/>
       <c r="AY14" s="16"/>
-      <c r="BE14" s="18"/>
+      <c r="BE14" s="17"/>
     </row>
     <row r="15" spans="1:57" x14ac:dyDescent="0.2">
-      <c r="A15" s="17" t="s">
+      <c r="A15" t="s">
         <v>8</v>
       </c>
       <c r="B15" s="16"/>
-      <c r="H15" s="18"/>
+      <c r="H15" s="17"/>
       <c r="I15" s="16"/>
-      <c r="O15" s="18"/>
+      <c r="O15" s="17"/>
       <c r="P15" s="16"/>
-      <c r="V15" s="18"/>
-      <c r="W15" s="22"/>
-      <c r="X15" s="23"/>
-      <c r="Y15" s="23"/>
-      <c r="Z15" s="23"/>
-      <c r="AA15" s="23"/>
-      <c r="AB15" s="23"/>
-      <c r="AC15" s="24"/>
+      <c r="V15" s="17"/>
+      <c r="W15" s="21"/>
+      <c r="X15" s="22"/>
+      <c r="Y15" s="22"/>
+      <c r="Z15" s="22"/>
+      <c r="AA15" s="22"/>
+      <c r="AB15" s="22"/>
+      <c r="AC15" s="23"/>
       <c r="AD15" s="16"/>
-      <c r="AJ15" s="18"/>
+      <c r="AJ15" s="17"/>
       <c r="AK15" s="16"/>
-      <c r="AQ15" s="18"/>
+      <c r="AQ15" s="17"/>
       <c r="AR15" s="16"/>
-      <c r="AX15" s="18"/>
+      <c r="AX15" s="17"/>
       <c r="AY15" s="16"/>
-      <c r="BE15" s="18"/>
+      <c r="BE15" s="17"/>
     </row>
     <row r="16" spans="1:57" x14ac:dyDescent="0.2">
-      <c r="A16" s="17" t="s">
+      <c r="A16" t="s">
         <v>10</v>
       </c>
       <c r="B16" s="16"/>
-      <c r="H16" s="18"/>
+      <c r="H16" s="17"/>
       <c r="I16" s="16"/>
-      <c r="O16" s="18"/>
+      <c r="O16" s="17"/>
       <c r="P16" s="16"/>
-      <c r="V16" s="18"/>
+      <c r="V16" s="17"/>
       <c r="W16" s="16"/>
-      <c r="AC16" s="18"/>
-      <c r="AD16" s="22"/>
-      <c r="AE16" s="23"/>
-      <c r="AF16" s="23"/>
-      <c r="AG16" s="23"/>
-      <c r="AH16" s="23"/>
-      <c r="AI16" s="23"/>
-      <c r="AJ16" s="24"/>
+      <c r="AC16" s="17"/>
+      <c r="AD16" s="21"/>
+      <c r="AE16" s="22"/>
+      <c r="AF16" s="22"/>
+      <c r="AG16" s="22"/>
+      <c r="AH16" s="22"/>
+      <c r="AI16" s="22"/>
+      <c r="AJ16" s="23"/>
       <c r="AK16" s="16"/>
-      <c r="AQ16" s="18"/>
+      <c r="AQ16" s="17"/>
       <c r="AR16" s="16"/>
-      <c r="AX16" s="18"/>
+      <c r="AX16" s="17"/>
       <c r="AY16" s="16"/>
-      <c r="BE16" s="18"/>
+      <c r="BE16" s="17"/>
     </row>
     <row r="17" spans="1:57" x14ac:dyDescent="0.2">
-      <c r="A17" s="17" t="s">
+      <c r="A17" t="s">
         <v>9</v>
       </c>
       <c r="B17" s="16"/>
-      <c r="H17" s="18"/>
+      <c r="H17" s="17"/>
       <c r="I17" s="16"/>
-      <c r="O17" s="18"/>
+      <c r="O17" s="17"/>
       <c r="P17" s="16"/>
-      <c r="V17" s="18"/>
+      <c r="V17" s="17"/>
       <c r="W17" s="16"/>
-      <c r="AC17" s="18"/>
+      <c r="AC17" s="17"/>
       <c r="AD17" s="16"/>
-      <c r="AJ17" s="18"/>
-      <c r="AK17" s="22"/>
-      <c r="AL17" s="23"/>
-      <c r="AM17" s="23"/>
-      <c r="AN17" s="23"/>
-      <c r="AO17" s="23"/>
-      <c r="AP17" s="23"/>
-      <c r="AQ17" s="24"/>
+      <c r="AJ17" s="17"/>
+      <c r="AK17" s="21"/>
+      <c r="AL17" s="22"/>
+      <c r="AM17" s="22"/>
+      <c r="AN17" s="22"/>
+      <c r="AO17" s="22"/>
+      <c r="AP17" s="22"/>
+      <c r="AQ17" s="23"/>
       <c r="AR17" s="16"/>
-      <c r="AX17" s="18"/>
+      <c r="AX17" s="17"/>
       <c r="AY17" s="16"/>
-      <c r="BE17" s="18"/>
+      <c r="BE17" s="17"/>
     </row>
     <row r="18" spans="1:57" x14ac:dyDescent="0.2">
-      <c r="A18" s="17" t="s">
+      <c r="A18" t="s">
         <v>12</v>
       </c>
       <c r="B18" s="16"/>
-      <c r="H18" s="18"/>
+      <c r="H18" s="17"/>
       <c r="I18" s="16"/>
-      <c r="O18" s="18"/>
+      <c r="O18" s="17"/>
       <c r="P18" s="16"/>
-      <c r="V18" s="18"/>
+      <c r="V18" s="17"/>
       <c r="W18" s="16"/>
-      <c r="AC18" s="18"/>
+      <c r="AC18" s="17"/>
       <c r="AD18" s="16"/>
-      <c r="AJ18" s="18"/>
-      <c r="AK18" s="22"/>
-      <c r="AL18" s="23"/>
-      <c r="AM18" s="23"/>
-      <c r="AN18" s="23"/>
-      <c r="AO18" s="23"/>
-      <c r="AP18" s="23"/>
-      <c r="AQ18" s="24"/>
-      <c r="AR18" s="22"/>
-      <c r="AS18" s="23"/>
-      <c r="AT18" s="23"/>
-      <c r="AU18" s="23"/>
-      <c r="AV18" s="23"/>
-      <c r="AW18" s="23"/>
-      <c r="AX18" s="24"/>
-      <c r="AY18" s="22"/>
-      <c r="AZ18" s="23"/>
-      <c r="BA18" s="23"/>
-      <c r="BB18" s="23"/>
-      <c r="BC18" s="23"/>
-      <c r="BD18" s="23"/>
-      <c r="BE18" s="24"/>
+      <c r="AJ18" s="17"/>
+      <c r="AK18" s="21"/>
+      <c r="AL18" s="22"/>
+      <c r="AM18" s="22"/>
+      <c r="AN18" s="22"/>
+      <c r="AO18" s="22"/>
+      <c r="AP18" s="22"/>
+      <c r="AQ18" s="23"/>
+      <c r="AR18" s="21"/>
+      <c r="AS18" s="22"/>
+      <c r="AT18" s="22"/>
+      <c r="AU18" s="22"/>
+      <c r="AV18" s="22"/>
+      <c r="AW18" s="22"/>
+      <c r="AX18" s="23"/>
+      <c r="AY18" s="21"/>
+      <c r="AZ18" s="22"/>
+      <c r="BA18" s="22"/>
+      <c r="BB18" s="22"/>
+      <c r="BC18" s="22"/>
+      <c r="BD18" s="22"/>
+      <c r="BE18" s="23"/>
     </row>
     <row r="19" spans="1:57" x14ac:dyDescent="0.2">
-      <c r="A19" s="17" t="s">
+      <c r="A19" t="s">
         <v>13</v>
       </c>
       <c r="B19" s="16"/>
-      <c r="H19" s="18"/>
+      <c r="H19" s="17"/>
       <c r="I19" s="16"/>
-      <c r="O19" s="18"/>
+      <c r="O19" s="17"/>
       <c r="P19" s="16"/>
-      <c r="V19" s="18"/>
+      <c r="V19" s="17"/>
       <c r="W19" s="16"/>
-      <c r="AC19" s="18"/>
+      <c r="AC19" s="17"/>
       <c r="AD19" s="16"/>
-      <c r="AJ19" s="18"/>
-      <c r="AK19" s="22"/>
-      <c r="AL19" s="23"/>
-      <c r="AM19" s="23"/>
-      <c r="AN19" s="23"/>
-      <c r="AO19" s="23"/>
-      <c r="AP19" s="23"/>
-      <c r="AQ19" s="24"/>
-      <c r="AR19" s="22"/>
-      <c r="AS19" s="23"/>
-      <c r="AT19" s="23"/>
-      <c r="AU19" s="23"/>
-      <c r="AV19" s="23"/>
-      <c r="AW19" s="23"/>
-      <c r="AX19" s="24"/>
-      <c r="AY19" s="22"/>
-      <c r="AZ19" s="23"/>
-      <c r="BA19" s="23"/>
-      <c r="BB19" s="23"/>
-      <c r="BC19" s="23"/>
-      <c r="BD19" s="23"/>
-      <c r="BE19" s="24"/>
+      <c r="AJ19" s="17"/>
+      <c r="AK19" s="21"/>
+      <c r="AL19" s="22"/>
+      <c r="AM19" s="22"/>
+      <c r="AN19" s="22"/>
+      <c r="AO19" s="22"/>
+      <c r="AP19" s="22"/>
+      <c r="AQ19" s="23"/>
+      <c r="AR19" s="21"/>
+      <c r="AS19" s="22"/>
+      <c r="AT19" s="22"/>
+      <c r="AU19" s="22"/>
+      <c r="AV19" s="22"/>
+      <c r="AW19" s="22"/>
+      <c r="AX19" s="23"/>
+      <c r="AY19" s="21"/>
+      <c r="AZ19" s="22"/>
+      <c r="BA19" s="22"/>
+      <c r="BB19" s="22"/>
+      <c r="BC19" s="22"/>
+      <c r="BD19" s="22"/>
+      <c r="BE19" s="23"/>
     </row>
     <row r="20" spans="1:57" x14ac:dyDescent="0.2">
-      <c r="A20" s="17" t="s">
+      <c r="A20" t="s">
         <v>14</v>
       </c>
       <c r="B20" s="16"/>
-      <c r="H20" s="18"/>
+      <c r="H20" s="17"/>
       <c r="I20" s="16"/>
-      <c r="O20" s="18"/>
+      <c r="O20" s="17"/>
       <c r="P20" s="16"/>
-      <c r="V20" s="18"/>
+      <c r="V20" s="17"/>
       <c r="W20" s="16"/>
-      <c r="AC20" s="18"/>
+      <c r="AC20" s="17"/>
       <c r="AD20" s="16"/>
-      <c r="AJ20" s="18"/>
+      <c r="AJ20" s="17"/>
       <c r="AK20" s="16"/>
-      <c r="AQ20" s="18"/>
-      <c r="AR20" s="22"/>
-      <c r="AS20" s="23"/>
-      <c r="AT20" s="23"/>
-      <c r="AU20" s="23"/>
-      <c r="AV20" s="23"/>
-      <c r="AW20" s="23"/>
-      <c r="AX20" s="24"/>
+      <c r="AQ20" s="17"/>
+      <c r="AR20" s="21"/>
+      <c r="AS20" s="22"/>
+      <c r="AT20" s="22"/>
+      <c r="AU20" s="22"/>
+      <c r="AV20" s="22"/>
+      <c r="AW20" s="22"/>
+      <c r="AX20" s="23"/>
       <c r="AY20" s="16"/>
-      <c r="BE20" s="18"/>
+      <c r="BE20" s="17"/>
     </row>
     <row r="21" spans="1:57" x14ac:dyDescent="0.2">
-      <c r="A21" s="17" t="s">
+      <c r="A21" t="s">
         <v>15</v>
       </c>
       <c r="B21" s="16"/>
-      <c r="H21" s="18"/>
+      <c r="H21" s="17"/>
       <c r="I21" s="16"/>
-      <c r="O21" s="18"/>
+      <c r="O21" s="17"/>
       <c r="P21" s="16"/>
-      <c r="V21" s="18"/>
+      <c r="V21" s="17"/>
       <c r="W21" s="16"/>
-      <c r="AC21" s="18"/>
+      <c r="AC21" s="17"/>
       <c r="AD21" s="16"/>
-      <c r="AJ21" s="18"/>
+      <c r="AJ21" s="17"/>
       <c r="AK21" s="16"/>
-      <c r="AQ21" s="18"/>
+      <c r="AQ21" s="17"/>
       <c r="AR21" s="16"/>
-      <c r="AX21" s="18"/>
+      <c r="AX21" s="17"/>
       <c r="AY21" s="16"/>
-      <c r="BE21" s="18"/>
+      <c r="BE21" s="17"/>
     </row>
     <row r="22" spans="1:57" x14ac:dyDescent="0.2">
-      <c r="A22" s="17" t="s">
+      <c r="A22" t="s">
         <v>16</v>
       </c>
       <c r="B22" s="16"/>
-      <c r="H22" s="18"/>
+      <c r="H22" s="17"/>
       <c r="I22" s="16"/>
-      <c r="O22" s="18"/>
+      <c r="O22" s="17"/>
       <c r="P22" s="16"/>
-      <c r="V22" s="18"/>
+      <c r="V22" s="17"/>
       <c r="W22" s="16"/>
-      <c r="AC22" s="18"/>
+      <c r="AC22" s="17"/>
       <c r="AD22" s="16"/>
-      <c r="AJ22" s="18"/>
+      <c r="AJ22" s="17"/>
       <c r="AK22" s="16"/>
-      <c r="AQ22" s="18"/>
+      <c r="AQ22" s="17"/>
       <c r="AR22" s="16"/>
-      <c r="AX22" s="18"/>
+      <c r="AX22" s="17"/>
       <c r="AY22" s="16"/>
-      <c r="BE22" s="18"/>
+      <c r="BE22" s="17"/>
     </row>
     <row r="23" spans="1:57" x14ac:dyDescent="0.2">
-      <c r="A23" s="17" t="s">
+      <c r="A23" t="s">
         <v>12</v>
       </c>
       <c r="B23" s="16"/>
-      <c r="H23" s="18"/>
+      <c r="H23" s="17"/>
       <c r="I23" s="16"/>
-      <c r="O23" s="18"/>
+      <c r="O23" s="17"/>
       <c r="P23" s="16"/>
-      <c r="V23" s="18"/>
+      <c r="V23" s="17"/>
       <c r="W23" s="16"/>
-      <c r="AC23" s="18"/>
+      <c r="AC23" s="17"/>
       <c r="AD23" s="16"/>
-      <c r="AJ23" s="18"/>
+      <c r="AJ23" s="17"/>
       <c r="AK23" s="16"/>
-      <c r="AQ23" s="18"/>
+      <c r="AQ23" s="17"/>
       <c r="AR23" s="16"/>
-      <c r="AX23" s="18"/>
+      <c r="AX23" s="17"/>
       <c r="AY23" s="16"/>
-      <c r="BE23" s="18"/>
+      <c r="BE23" s="17"/>
     </row>
     <row r="24" spans="1:57" x14ac:dyDescent="0.2">
-      <c r="A24" s="17" t="s">
+      <c r="A24" t="s">
         <v>13</v>
       </c>
       <c r="B24" s="16"/>
-      <c r="H24" s="18"/>
+      <c r="H24" s="17"/>
       <c r="I24" s="16"/>
-      <c r="O24" s="18"/>
+      <c r="O24" s="17"/>
       <c r="P24" s="16"/>
-      <c r="V24" s="18"/>
+      <c r="V24" s="17"/>
       <c r="W24" s="16"/>
-      <c r="AC24" s="18"/>
+      <c r="AC24" s="17"/>
       <c r="AD24" s="16"/>
-      <c r="AJ24" s="18"/>
+      <c r="AJ24" s="17"/>
       <c r="AK24" s="16"/>
-      <c r="AQ24" s="18"/>
+      <c r="AQ24" s="17"/>
       <c r="AR24" s="16"/>
-      <c r="AX24" s="18"/>
+      <c r="AX24" s="17"/>
       <c r="AY24" s="16"/>
-      <c r="BE24" s="18"/>
+      <c r="BE24" s="17"/>
     </row>
     <row r="25" spans="1:57" x14ac:dyDescent="0.2">
-      <c r="A25" s="17" t="s">
+      <c r="A25" t="s">
         <v>17</v>
       </c>
       <c r="B25" s="16"/>
-      <c r="H25" s="18"/>
+      <c r="H25" s="17"/>
       <c r="I25" s="16"/>
-      <c r="O25" s="18"/>
+      <c r="O25" s="17"/>
       <c r="P25" s="16"/>
-      <c r="V25" s="18"/>
+      <c r="V25" s="17"/>
       <c r="W25" s="16"/>
-      <c r="AC25" s="18"/>
+      <c r="AC25" s="17"/>
       <c r="AD25" s="16"/>
-      <c r="AJ25" s="18"/>
+      <c r="AJ25" s="17"/>
       <c r="AK25" s="16"/>
-      <c r="AQ25" s="18"/>
+      <c r="AQ25" s="17"/>
       <c r="AR25" s="16"/>
-      <c r="AX25" s="18"/>
+      <c r="AX25" s="17"/>
       <c r="AY25" s="16"/>
-      <c r="BE25" s="18"/>
+      <c r="BE25" s="17"/>
     </row>
     <row r="26" spans="1:57" x14ac:dyDescent="0.2">
-      <c r="A26" s="17" t="s">
+      <c r="A26" t="s">
         <v>18</v>
       </c>
       <c r="B26" s="16"/>
-      <c r="H26" s="18"/>
+      <c r="H26" s="17"/>
       <c r="I26" s="16"/>
-      <c r="O26" s="18"/>
+      <c r="O26" s="17"/>
       <c r="P26" s="16"/>
-      <c r="V26" s="18"/>
+      <c r="V26" s="17"/>
       <c r="W26" s="16"/>
-      <c r="AC26" s="18"/>
+      <c r="AC26" s="17"/>
       <c r="AD26" s="16"/>
-      <c r="AJ26" s="18"/>
+      <c r="AJ26" s="17"/>
       <c r="AK26" s="16"/>
-      <c r="AQ26" s="18"/>
+      <c r="AQ26" s="17"/>
       <c r="AR26" s="16"/>
-      <c r="AX26" s="18"/>
+      <c r="AX26" s="17"/>
       <c r="AY26" s="16"/>
-      <c r="BE26" s="18"/>
+      <c r="BE26" s="17"/>
     </row>
     <row r="27" spans="1:57" x14ac:dyDescent="0.2">
-      <c r="A27" s="17" t="s">
+      <c r="A27" t="s">
         <v>19</v>
       </c>
       <c r="B27" s="16"/>
-      <c r="H27" s="18"/>
+      <c r="H27" s="17"/>
       <c r="I27" s="16"/>
-      <c r="O27" s="18"/>
+      <c r="O27" s="17"/>
       <c r="P27" s="16"/>
-      <c r="V27" s="18"/>
+      <c r="V27" s="17"/>
       <c r="W27" s="16"/>
-      <c r="AC27" s="18"/>
+      <c r="AC27" s="17"/>
       <c r="AD27" s="16"/>
-      <c r="AJ27" s="18"/>
+      <c r="AJ27" s="17"/>
       <c r="AK27" s="16"/>
-      <c r="AQ27" s="18"/>
+      <c r="AQ27" s="17"/>
       <c r="AR27" s="16"/>
-      <c r="AX27" s="18"/>
+      <c r="AX27" s="17"/>
       <c r="AY27" s="16"/>
-      <c r="BE27" s="18"/>
+      <c r="BE27" s="17"/>
     </row>
     <row r="28" spans="1:57" x14ac:dyDescent="0.2">
-      <c r="A28" s="17" t="s">
+      <c r="A28" t="s">
         <v>20</v>
       </c>
       <c r="B28" s="16"/>
-      <c r="H28" s="18"/>
+      <c r="H28" s="17"/>
       <c r="I28" s="16"/>
-      <c r="O28" s="18"/>
+      <c r="O28" s="17"/>
       <c r="P28" s="16"/>
-      <c r="V28" s="18"/>
+      <c r="V28" s="17"/>
       <c r="W28" s="16"/>
-      <c r="AC28" s="18"/>
+      <c r="AC28" s="17"/>
       <c r="AD28" s="16"/>
-      <c r="AJ28" s="18"/>
+      <c r="AJ28" s="17"/>
       <c r="AK28" s="16"/>
-      <c r="AQ28" s="18"/>
+      <c r="AQ28" s="17"/>
       <c r="AR28" s="16"/>
-      <c r="AX28" s="18"/>
+      <c r="AX28" s="17"/>
       <c r="AY28" s="16"/>
-      <c r="BE28" s="18"/>
+      <c r="BE28" s="17"/>
     </row>
     <row r="29" spans="1:57" x14ac:dyDescent="0.2">
-      <c r="A29" s="37" t="s">
+      <c r="A29" s="32" t="s">
         <v>21</v>
       </c>
-      <c r="B29" s="19"/>
-      <c r="C29" s="20"/>
-      <c r="D29" s="20"/>
-      <c r="E29" s="20"/>
-      <c r="F29" s="20"/>
-      <c r="G29" s="20"/>
-      <c r="H29" s="21"/>
-      <c r="I29" s="19"/>
-      <c r="J29" s="20"/>
-      <c r="K29" s="20"/>
-      <c r="L29" s="20"/>
-      <c r="M29" s="20"/>
-      <c r="N29" s="20"/>
-      <c r="O29" s="21"/>
-      <c r="P29" s="19"/>
-      <c r="Q29" s="20"/>
-      <c r="R29" s="20"/>
-      <c r="S29" s="20"/>
-      <c r="T29" s="20"/>
-      <c r="U29" s="20"/>
-      <c r="V29" s="21"/>
-      <c r="W29" s="19"/>
-      <c r="X29" s="20"/>
-      <c r="Y29" s="20"/>
-      <c r="Z29" s="20"/>
-      <c r="AA29" s="20"/>
-      <c r="AB29" s="20"/>
-      <c r="AC29" s="21"/>
-      <c r="AD29" s="19"/>
-      <c r="AE29" s="20"/>
-      <c r="AF29" s="20"/>
-      <c r="AG29" s="20"/>
-      <c r="AH29" s="20"/>
-      <c r="AI29" s="20"/>
-      <c r="AJ29" s="21"/>
-      <c r="AK29" s="19"/>
-      <c r="AL29" s="20"/>
-      <c r="AM29" s="20"/>
-      <c r="AN29" s="20"/>
-      <c r="AO29" s="20"/>
-      <c r="AP29" s="20"/>
-      <c r="AQ29" s="21"/>
-      <c r="AR29" s="19"/>
-      <c r="AS29" s="20"/>
-      <c r="AT29" s="20"/>
-      <c r="AU29" s="20"/>
-      <c r="AV29" s="20"/>
-      <c r="AW29" s="20"/>
-      <c r="AX29" s="21"/>
-      <c r="AY29" s="19"/>
-      <c r="AZ29" s="20"/>
-      <c r="BA29" s="20"/>
-      <c r="BB29" s="20"/>
-      <c r="BC29" s="20"/>
-      <c r="BD29" s="20"/>
-      <c r="BE29" s="21"/>
+      <c r="B29" s="18"/>
+      <c r="C29" s="19"/>
+      <c r="D29" s="19"/>
+      <c r="E29" s="19"/>
+      <c r="F29" s="19"/>
+      <c r="G29" s="19"/>
+      <c r="H29" s="20"/>
+      <c r="I29" s="18"/>
+      <c r="J29" s="19"/>
+      <c r="K29" s="19"/>
+      <c r="L29" s="19"/>
+      <c r="M29" s="19"/>
+      <c r="N29" s="19"/>
+      <c r="O29" s="20"/>
+      <c r="P29" s="18"/>
+      <c r="Q29" s="19"/>
+      <c r="R29" s="19"/>
+      <c r="S29" s="19"/>
+      <c r="T29" s="19"/>
+      <c r="U29" s="19"/>
+      <c r="V29" s="20"/>
+      <c r="W29" s="18"/>
+      <c r="X29" s="19"/>
+      <c r="Y29" s="19"/>
+      <c r="Z29" s="19"/>
+      <c r="AA29" s="19"/>
+      <c r="AB29" s="19"/>
+      <c r="AC29" s="20"/>
+      <c r="AD29" s="18"/>
+      <c r="AE29" s="19"/>
+      <c r="AF29" s="19"/>
+      <c r="AG29" s="19"/>
+      <c r="AH29" s="19"/>
+      <c r="AI29" s="19"/>
+      <c r="AJ29" s="20"/>
+      <c r="AK29" s="18"/>
+      <c r="AL29" s="19"/>
+      <c r="AM29" s="19"/>
+      <c r="AN29" s="19"/>
+      <c r="AO29" s="19"/>
+      <c r="AP29" s="19"/>
+      <c r="AQ29" s="20"/>
+      <c r="AR29" s="18"/>
+      <c r="AS29" s="19"/>
+      <c r="AT29" s="19"/>
+      <c r="AU29" s="19"/>
+      <c r="AV29" s="19"/>
+      <c r="AW29" s="19"/>
+      <c r="AX29" s="20"/>
+      <c r="AY29" s="18"/>
+      <c r="AZ29" s="19"/>
+      <c r="BA29" s="19"/>
+      <c r="BB29" s="19"/>
+      <c r="BC29" s="19"/>
+      <c r="BD29" s="19"/>
+      <c r="BE29" s="20"/>
     </row>
     <row r="30" spans="1:57" ht="15" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="37"/>
+      <c r="A30" s="32"/>
     </row>
     <row r="31" spans="1:57" x14ac:dyDescent="0.2">
-      <c r="A31" s="35" t="s">
+      <c r="A31" s="30" t="s">
         <v>0</v>
       </c>
-      <c r="B31" s="38" t="s">
+      <c r="B31" s="40" t="s">
         <v>4</v>
       </c>
-      <c r="C31" s="39"/>
-      <c r="D31" s="39"/>
-      <c r="E31" s="39"/>
-      <c r="F31" s="39"/>
-      <c r="G31" s="39"/>
-      <c r="H31" s="39"/>
-      <c r="I31" s="39"/>
-      <c r="J31" s="39"/>
-      <c r="K31" s="39"/>
-      <c r="L31" s="39"/>
-      <c r="M31" s="39"/>
-      <c r="N31" s="39"/>
-      <c r="O31" s="39"/>
-      <c r="P31" s="39"/>
-      <c r="Q31" s="39"/>
-      <c r="R31" s="39"/>
-      <c r="S31" s="39"/>
-      <c r="T31" s="39"/>
-      <c r="U31" s="39"/>
-      <c r="V31" s="40"/>
-      <c r="W31" s="30" t="s">
+      <c r="C31" s="41"/>
+      <c r="D31" s="41"/>
+      <c r="E31" s="41"/>
+      <c r="F31" s="41"/>
+      <c r="G31" s="41"/>
+      <c r="H31" s="41"/>
+      <c r="I31" s="41"/>
+      <c r="J31" s="41"/>
+      <c r="K31" s="41"/>
+      <c r="L31" s="41"/>
+      <c r="M31" s="41"/>
+      <c r="N31" s="41"/>
+      <c r="O31" s="41"/>
+      <c r="P31" s="41"/>
+      <c r="Q31" s="41"/>
+      <c r="R31" s="41"/>
+      <c r="S31" s="41"/>
+      <c r="T31" s="41"/>
+      <c r="U31" s="41"/>
+      <c r="V31" s="42"/>
+      <c r="W31" s="37" t="s">
         <v>5</v>
       </c>
-      <c r="X31" s="28"/>
-      <c r="Y31" s="28"/>
-      <c r="Z31" s="28"/>
-      <c r="AA31" s="28"/>
-      <c r="AB31" s="28"/>
-      <c r="AC31" s="28"/>
-      <c r="AD31" s="28"/>
-      <c r="AE31" s="28"/>
-      <c r="AF31" s="28"/>
-      <c r="AG31" s="28"/>
-      <c r="AH31" s="28"/>
-      <c r="AI31" s="28"/>
-      <c r="AJ31" s="28"/>
-      <c r="AK31" s="28"/>
-      <c r="AL31" s="28"/>
-      <c r="AM31" s="28"/>
-      <c r="AN31" s="28"/>
-      <c r="AO31" s="28"/>
-      <c r="AP31" s="28"/>
-      <c r="AQ31" s="28"/>
-      <c r="AR31" s="28"/>
-      <c r="AS31" s="28"/>
-      <c r="AT31" s="28"/>
-      <c r="AU31" s="28"/>
-      <c r="AV31" s="28"/>
-      <c r="AW31" s="28"/>
-      <c r="AX31" s="28"/>
-      <c r="AY31" s="28"/>
-      <c r="AZ31" s="29"/>
+      <c r="X31" s="38"/>
+      <c r="Y31" s="38"/>
+      <c r="Z31" s="38"/>
+      <c r="AA31" s="38"/>
+      <c r="AB31" s="38"/>
+      <c r="AC31" s="38"/>
+      <c r="AD31" s="38"/>
+      <c r="AE31" s="38"/>
+      <c r="AF31" s="38"/>
+      <c r="AG31" s="38"/>
+      <c r="AH31" s="38"/>
+      <c r="AI31" s="38"/>
+      <c r="AJ31" s="38"/>
+      <c r="AK31" s="38"/>
+      <c r="AL31" s="38"/>
+      <c r="AM31" s="38"/>
+      <c r="AN31" s="38"/>
+      <c r="AO31" s="38"/>
+      <c r="AP31" s="38"/>
+      <c r="AQ31" s="38"/>
+      <c r="AR31" s="38"/>
+      <c r="AS31" s="38"/>
+      <c r="AT31" s="38"/>
+      <c r="AU31" s="38"/>
+      <c r="AV31" s="38"/>
+      <c r="AW31" s="38"/>
+      <c r="AX31" s="38"/>
+      <c r="AY31" s="38"/>
+      <c r="AZ31" s="39"/>
     </row>
     <row r="32" spans="1:57" ht="15" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="36" t="s">
+      <c r="A32" s="31" t="s">
         <v>24</v>
       </c>
       <c r="B32" s="4">
@@ -5253,525 +5033,525 @@
     </row>
     <row r="33" spans="1:52" x14ac:dyDescent="0.2">
       <c r="B33" s="16"/>
-      <c r="H33" s="18"/>
+      <c r="H33" s="17"/>
       <c r="I33" s="16"/>
-      <c r="O33" s="18"/>
+      <c r="O33" s="17"/>
       <c r="P33" s="16"/>
-      <c r="V33" s="18"/>
+      <c r="V33" s="17"/>
       <c r="W33" s="16"/>
-      <c r="AC33" s="18"/>
+      <c r="AC33" s="17"/>
       <c r="AD33" s="16"/>
-      <c r="AJ33" s="18"/>
+      <c r="AJ33" s="17"/>
       <c r="AK33" s="16"/>
-      <c r="AQ33" s="18"/>
+      <c r="AQ33" s="17"/>
       <c r="AR33" s="16"/>
-      <c r="AX33" s="18"/>
+      <c r="AX33" s="17"/>
       <c r="AY33" s="16"/>
-      <c r="AZ33" s="18"/>
+      <c r="AZ33" s="17"/>
     </row>
     <row r="34" spans="1:52" x14ac:dyDescent="0.2">
-      <c r="A34" s="17" t="s">
+      <c r="A34" t="s">
         <v>1</v>
       </c>
       <c r="B34" s="16"/>
-      <c r="H34" s="18"/>
+      <c r="H34" s="17"/>
       <c r="I34" s="16"/>
-      <c r="O34" s="18"/>
+      <c r="O34" s="17"/>
       <c r="P34" s="16"/>
-      <c r="V34" s="18"/>
+      <c r="V34" s="17"/>
       <c r="W34" s="16"/>
-      <c r="AC34" s="18"/>
+      <c r="AC34" s="17"/>
       <c r="AD34" s="16"/>
-      <c r="AJ34" s="18"/>
+      <c r="AJ34" s="17"/>
       <c r="AK34" s="16"/>
-      <c r="AQ34" s="18"/>
+      <c r="AQ34" s="17"/>
       <c r="AR34" s="16"/>
-      <c r="AX34" s="18"/>
+      <c r="AX34" s="17"/>
       <c r="AY34" s="16"/>
-      <c r="AZ34" s="18"/>
+      <c r="AZ34" s="17"/>
     </row>
     <row r="35" spans="1:52" x14ac:dyDescent="0.2">
-      <c r="A35" s="17" t="s">
+      <c r="A35" t="s">
         <v>6</v>
       </c>
       <c r="B35" s="16"/>
-      <c r="H35" s="18"/>
+      <c r="H35" s="17"/>
       <c r="I35" s="16"/>
-      <c r="O35" s="18"/>
+      <c r="O35" s="17"/>
       <c r="P35" s="16"/>
-      <c r="V35" s="18"/>
+      <c r="V35" s="17"/>
       <c r="W35" s="16"/>
-      <c r="AC35" s="18"/>
+      <c r="AC35" s="17"/>
       <c r="AD35" s="16"/>
-      <c r="AJ35" s="18"/>
+      <c r="AJ35" s="17"/>
       <c r="AK35" s="16"/>
-      <c r="AQ35" s="18"/>
+      <c r="AQ35" s="17"/>
       <c r="AR35" s="16"/>
-      <c r="AX35" s="18"/>
+      <c r="AX35" s="17"/>
       <c r="AY35" s="16"/>
-      <c r="AZ35" s="18"/>
+      <c r="AZ35" s="17"/>
     </row>
     <row r="36" spans="1:52" x14ac:dyDescent="0.2">
-      <c r="A36" s="17" t="s">
+      <c r="A36" t="s">
         <v>11</v>
       </c>
       <c r="B36" s="16"/>
-      <c r="H36" s="18"/>
+      <c r="H36" s="17"/>
       <c r="I36" s="16"/>
-      <c r="O36" s="18"/>
+      <c r="O36" s="17"/>
       <c r="P36" s="16"/>
-      <c r="V36" s="18"/>
+      <c r="V36" s="17"/>
       <c r="W36" s="16"/>
-      <c r="AC36" s="18"/>
+      <c r="AC36" s="17"/>
       <c r="AD36" s="16"/>
-      <c r="AJ36" s="18"/>
+      <c r="AJ36" s="17"/>
       <c r="AK36" s="16"/>
-      <c r="AQ36" s="18"/>
+      <c r="AQ36" s="17"/>
       <c r="AR36" s="16"/>
-      <c r="AX36" s="18"/>
+      <c r="AX36" s="17"/>
       <c r="AY36" s="16"/>
-      <c r="AZ36" s="18"/>
+      <c r="AZ36" s="17"/>
     </row>
     <row r="37" spans="1:52" x14ac:dyDescent="0.2">
-      <c r="A37" s="17" t="s">
+      <c r="A37" t="s">
         <v>7</v>
       </c>
       <c r="B37" s="16"/>
-      <c r="H37" s="18"/>
+      <c r="H37" s="17"/>
       <c r="I37" s="16"/>
-      <c r="O37" s="18"/>
+      <c r="O37" s="17"/>
       <c r="P37" s="16"/>
-      <c r="V37" s="18"/>
+      <c r="V37" s="17"/>
       <c r="W37" s="16"/>
-      <c r="AC37" s="18"/>
+      <c r="AC37" s="17"/>
       <c r="AD37" s="16"/>
-      <c r="AJ37" s="18"/>
+      <c r="AJ37" s="17"/>
       <c r="AK37" s="16"/>
-      <c r="AQ37" s="18"/>
+      <c r="AQ37" s="17"/>
       <c r="AR37" s="16"/>
-      <c r="AX37" s="18"/>
+      <c r="AX37" s="17"/>
       <c r="AY37" s="16"/>
-      <c r="AZ37" s="18"/>
+      <c r="AZ37" s="17"/>
     </row>
     <row r="38" spans="1:52" x14ac:dyDescent="0.2">
-      <c r="A38" s="17" t="s">
+      <c r="A38" t="s">
         <v>8</v>
       </c>
       <c r="B38" s="16"/>
-      <c r="H38" s="18"/>
+      <c r="H38" s="17"/>
       <c r="I38" s="16"/>
-      <c r="O38" s="18"/>
+      <c r="O38" s="17"/>
       <c r="P38" s="16"/>
-      <c r="V38" s="18"/>
+      <c r="V38" s="17"/>
       <c r="W38" s="16"/>
-      <c r="AC38" s="18"/>
+      <c r="AC38" s="17"/>
       <c r="AD38" s="16"/>
-      <c r="AJ38" s="18"/>
+      <c r="AJ38" s="17"/>
       <c r="AK38" s="16"/>
-      <c r="AQ38" s="18"/>
+      <c r="AQ38" s="17"/>
       <c r="AR38" s="16"/>
-      <c r="AX38" s="18"/>
+      <c r="AX38" s="17"/>
       <c r="AY38" s="16"/>
-      <c r="AZ38" s="18"/>
+      <c r="AZ38" s="17"/>
     </row>
     <row r="39" spans="1:52" x14ac:dyDescent="0.2">
-      <c r="A39" s="17" t="s">
+      <c r="A39" t="s">
         <v>10</v>
       </c>
       <c r="B39" s="16"/>
-      <c r="H39" s="18"/>
+      <c r="H39" s="17"/>
       <c r="I39" s="16"/>
-      <c r="O39" s="18"/>
+      <c r="O39" s="17"/>
       <c r="P39" s="16"/>
-      <c r="V39" s="18"/>
+      <c r="V39" s="17"/>
       <c r="W39" s="16"/>
-      <c r="AC39" s="18"/>
+      <c r="AC39" s="17"/>
       <c r="AD39" s="16"/>
-      <c r="AJ39" s="18"/>
+      <c r="AJ39" s="17"/>
       <c r="AK39" s="16"/>
-      <c r="AQ39" s="18"/>
+      <c r="AQ39" s="17"/>
       <c r="AR39" s="16"/>
-      <c r="AX39" s="18"/>
+      <c r="AX39" s="17"/>
       <c r="AY39" s="16"/>
-      <c r="AZ39" s="18"/>
+      <c r="AZ39" s="17"/>
     </row>
     <row r="40" spans="1:52" x14ac:dyDescent="0.2">
-      <c r="A40" s="17" t="s">
+      <c r="A40" t="s">
         <v>9</v>
       </c>
       <c r="B40" s="16"/>
-      <c r="H40" s="18"/>
+      <c r="H40" s="17"/>
       <c r="I40" s="16"/>
-      <c r="O40" s="18"/>
+      <c r="O40" s="17"/>
       <c r="P40" s="16"/>
-      <c r="V40" s="18"/>
+      <c r="V40" s="17"/>
       <c r="W40" s="16"/>
-      <c r="AC40" s="18"/>
+      <c r="AC40" s="17"/>
       <c r="AD40" s="16"/>
-      <c r="AJ40" s="18"/>
+      <c r="AJ40" s="17"/>
       <c r="AK40" s="16"/>
-      <c r="AQ40" s="18"/>
+      <c r="AQ40" s="17"/>
       <c r="AR40" s="16"/>
-      <c r="AX40" s="18"/>
+      <c r="AX40" s="17"/>
       <c r="AY40" s="16"/>
-      <c r="AZ40" s="18"/>
+      <c r="AZ40" s="17"/>
     </row>
     <row r="41" spans="1:52" x14ac:dyDescent="0.2">
-      <c r="A41" s="17" t="s">
+      <c r="A41" t="s">
         <v>12</v>
       </c>
       <c r="B41" s="16"/>
-      <c r="H41" s="18"/>
+      <c r="H41" s="17"/>
       <c r="I41" s="16"/>
-      <c r="O41" s="18"/>
+      <c r="O41" s="17"/>
       <c r="P41" s="16"/>
-      <c r="V41" s="18"/>
+      <c r="V41" s="17"/>
       <c r="W41" s="16"/>
-      <c r="AC41" s="18"/>
+      <c r="AC41" s="17"/>
       <c r="AD41" s="16"/>
-      <c r="AJ41" s="18"/>
+      <c r="AJ41" s="17"/>
       <c r="AK41" s="16"/>
-      <c r="AQ41" s="18"/>
+      <c r="AQ41" s="17"/>
       <c r="AR41" s="16"/>
-      <c r="AX41" s="18"/>
+      <c r="AX41" s="17"/>
       <c r="AY41" s="16"/>
-      <c r="AZ41" s="18"/>
+      <c r="AZ41" s="17"/>
     </row>
     <row r="42" spans="1:52" x14ac:dyDescent="0.2">
-      <c r="A42" s="17" t="s">
+      <c r="A42" t="s">
         <v>13</v>
       </c>
       <c r="B42" s="16"/>
-      <c r="H42" s="18"/>
+      <c r="H42" s="17"/>
       <c r="I42" s="16"/>
-      <c r="O42" s="18"/>
+      <c r="O42" s="17"/>
       <c r="P42" s="16"/>
-      <c r="V42" s="18"/>
+      <c r="V42" s="17"/>
       <c r="W42" s="16"/>
-      <c r="AC42" s="18"/>
+      <c r="AC42" s="17"/>
       <c r="AD42" s="16"/>
-      <c r="AJ42" s="18"/>
+      <c r="AJ42" s="17"/>
       <c r="AK42" s="16"/>
-      <c r="AQ42" s="18"/>
+      <c r="AQ42" s="17"/>
       <c r="AR42" s="16"/>
-      <c r="AX42" s="18"/>
+      <c r="AX42" s="17"/>
       <c r="AY42" s="16"/>
-      <c r="AZ42" s="18"/>
+      <c r="AZ42" s="17"/>
     </row>
     <row r="43" spans="1:52" x14ac:dyDescent="0.2">
-      <c r="A43" s="17" t="s">
+      <c r="A43" t="s">
         <v>14</v>
       </c>
       <c r="B43" s="16"/>
-      <c r="H43" s="18"/>
+      <c r="H43" s="17"/>
       <c r="I43" s="16"/>
-      <c r="O43" s="18"/>
+      <c r="O43" s="17"/>
       <c r="P43" s="16"/>
-      <c r="V43" s="18"/>
+      <c r="V43" s="17"/>
       <c r="W43" s="16"/>
-      <c r="AC43" s="18"/>
+      <c r="AC43" s="17"/>
       <c r="AD43" s="16"/>
-      <c r="AJ43" s="18"/>
+      <c r="AJ43" s="17"/>
       <c r="AK43" s="16"/>
-      <c r="AQ43" s="18"/>
+      <c r="AQ43" s="17"/>
       <c r="AR43" s="16"/>
-      <c r="AX43" s="18"/>
+      <c r="AX43" s="17"/>
       <c r="AY43" s="16"/>
-      <c r="AZ43" s="18"/>
+      <c r="AZ43" s="17"/>
     </row>
     <row r="44" spans="1:52" x14ac:dyDescent="0.2">
-      <c r="A44" s="17" t="s">
+      <c r="A44" t="s">
         <v>15</v>
       </c>
-      <c r="B44" s="22"/>
-      <c r="C44" s="23"/>
-      <c r="D44" s="23"/>
-      <c r="E44" s="23"/>
-      <c r="F44" s="23"/>
-      <c r="G44" s="23"/>
-      <c r="H44" s="24"/>
+      <c r="B44" s="21"/>
+      <c r="C44" s="22"/>
+      <c r="D44" s="22"/>
+      <c r="E44" s="22"/>
+      <c r="F44" s="22"/>
+      <c r="G44" s="22"/>
+      <c r="H44" s="23"/>
       <c r="I44" s="16"/>
-      <c r="O44" s="18"/>
+      <c r="O44" s="17"/>
       <c r="P44" s="16"/>
-      <c r="V44" s="18"/>
+      <c r="V44" s="17"/>
       <c r="W44" s="16"/>
-      <c r="AC44" s="18"/>
+      <c r="AC44" s="17"/>
       <c r="AD44" s="16"/>
-      <c r="AJ44" s="18"/>
+      <c r="AJ44" s="17"/>
       <c r="AK44" s="16"/>
-      <c r="AQ44" s="18"/>
+      <c r="AQ44" s="17"/>
       <c r="AR44" s="16"/>
-      <c r="AX44" s="18"/>
+      <c r="AX44" s="17"/>
       <c r="AY44" s="16"/>
-      <c r="AZ44" s="18"/>
+      <c r="AZ44" s="17"/>
     </row>
     <row r="45" spans="1:52" x14ac:dyDescent="0.2">
-      <c r="A45" s="17" t="s">
+      <c r="A45" t="s">
         <v>16</v>
       </c>
-      <c r="B45" s="22"/>
-      <c r="C45" s="23"/>
-      <c r="D45" s="23"/>
-      <c r="E45" s="23"/>
-      <c r="F45" s="23"/>
-      <c r="G45" s="23"/>
-      <c r="H45" s="24"/>
+      <c r="B45" s="21"/>
+      <c r="C45" s="22"/>
+      <c r="D45" s="22"/>
+      <c r="E45" s="22"/>
+      <c r="F45" s="22"/>
+      <c r="G45" s="22"/>
+      <c r="H45" s="23"/>
       <c r="I45" s="16"/>
-      <c r="O45" s="18"/>
+      <c r="O45" s="17"/>
       <c r="P45" s="16"/>
-      <c r="V45" s="18"/>
+      <c r="V45" s="17"/>
       <c r="W45" s="16"/>
-      <c r="AC45" s="18"/>
+      <c r="AC45" s="17"/>
       <c r="AD45" s="16"/>
-      <c r="AJ45" s="18"/>
+      <c r="AJ45" s="17"/>
       <c r="AK45" s="16"/>
-      <c r="AQ45" s="18"/>
+      <c r="AQ45" s="17"/>
       <c r="AR45" s="16"/>
-      <c r="AX45" s="18"/>
+      <c r="AX45" s="17"/>
       <c r="AY45" s="16"/>
-      <c r="AZ45" s="18"/>
+      <c r="AZ45" s="17"/>
     </row>
     <row r="46" spans="1:52" x14ac:dyDescent="0.2">
-      <c r="A46" s="17" t="s">
+      <c r="A46" t="s">
         <v>12</v>
       </c>
       <c r="B46" s="16"/>
-      <c r="H46" s="18"/>
-      <c r="I46" s="22"/>
-      <c r="J46" s="23"/>
-      <c r="K46" s="23"/>
-      <c r="L46" s="23"/>
-      <c r="M46" s="23"/>
-      <c r="N46" s="23"/>
-      <c r="O46" s="24"/>
-      <c r="P46" s="22"/>
-      <c r="Q46" s="23"/>
-      <c r="R46" s="23"/>
-      <c r="S46" s="23"/>
-      <c r="T46" s="23"/>
-      <c r="U46" s="23"/>
-      <c r="V46" s="24"/>
-      <c r="W46" s="22"/>
-      <c r="X46" s="23"/>
-      <c r="Y46" s="23"/>
-      <c r="Z46" s="23"/>
-      <c r="AA46" s="23"/>
-      <c r="AB46" s="23"/>
-      <c r="AC46" s="24"/>
-      <c r="AD46" s="22"/>
-      <c r="AE46" s="23"/>
-      <c r="AF46" s="23"/>
-      <c r="AG46" s="23"/>
-      <c r="AH46" s="23"/>
-      <c r="AI46" s="23"/>
-      <c r="AJ46" s="24"/>
+      <c r="H46" s="17"/>
+      <c r="I46" s="21"/>
+      <c r="J46" s="22"/>
+      <c r="K46" s="22"/>
+      <c r="L46" s="22"/>
+      <c r="M46" s="22"/>
+      <c r="N46" s="22"/>
+      <c r="O46" s="23"/>
+      <c r="P46" s="21"/>
+      <c r="Q46" s="22"/>
+      <c r="R46" s="22"/>
+      <c r="S46" s="22"/>
+      <c r="T46" s="22"/>
+      <c r="U46" s="22"/>
+      <c r="V46" s="23"/>
+      <c r="W46" s="21"/>
+      <c r="X46" s="22"/>
+      <c r="Y46" s="22"/>
+      <c r="Z46" s="22"/>
+      <c r="AA46" s="22"/>
+      <c r="AB46" s="22"/>
+      <c r="AC46" s="23"/>
+      <c r="AD46" s="21"/>
+      <c r="AE46" s="22"/>
+      <c r="AF46" s="22"/>
+      <c r="AG46" s="22"/>
+      <c r="AH46" s="22"/>
+      <c r="AI46" s="22"/>
+      <c r="AJ46" s="23"/>
       <c r="AK46" s="16"/>
-      <c r="AQ46" s="18"/>
+      <c r="AQ46" s="17"/>
       <c r="AR46" s="16"/>
-      <c r="AX46" s="18"/>
+      <c r="AX46" s="17"/>
       <c r="AY46" s="16"/>
-      <c r="AZ46" s="18"/>
+      <c r="AZ46" s="17"/>
     </row>
     <row r="47" spans="1:52" x14ac:dyDescent="0.2">
-      <c r="A47" s="17" t="s">
+      <c r="A47" t="s">
         <v>13</v>
       </c>
       <c r="B47" s="16"/>
-      <c r="H47" s="18"/>
-      <c r="I47" s="22"/>
-      <c r="J47" s="23"/>
-      <c r="K47" s="23"/>
-      <c r="L47" s="23"/>
-      <c r="M47" s="23"/>
-      <c r="N47" s="23"/>
-      <c r="O47" s="24"/>
-      <c r="P47" s="22"/>
-      <c r="Q47" s="23"/>
-      <c r="R47" s="23"/>
-      <c r="S47" s="23"/>
-      <c r="T47" s="23"/>
-      <c r="U47" s="23"/>
-      <c r="V47" s="24"/>
-      <c r="W47" s="22"/>
-      <c r="X47" s="23"/>
-      <c r="Y47" s="23"/>
-      <c r="Z47" s="23"/>
-      <c r="AA47" s="23"/>
-      <c r="AB47" s="23"/>
-      <c r="AC47" s="24"/>
-      <c r="AD47" s="22"/>
-      <c r="AE47" s="23"/>
-      <c r="AF47" s="23"/>
-      <c r="AG47" s="23"/>
-      <c r="AH47" s="23"/>
-      <c r="AI47" s="23"/>
-      <c r="AJ47" s="24"/>
+      <c r="H47" s="17"/>
+      <c r="I47" s="21"/>
+      <c r="J47" s="22"/>
+      <c r="K47" s="22"/>
+      <c r="L47" s="22"/>
+      <c r="M47" s="22"/>
+      <c r="N47" s="22"/>
+      <c r="O47" s="23"/>
+      <c r="P47" s="21"/>
+      <c r="Q47" s="22"/>
+      <c r="R47" s="22"/>
+      <c r="S47" s="22"/>
+      <c r="T47" s="22"/>
+      <c r="U47" s="22"/>
+      <c r="V47" s="23"/>
+      <c r="W47" s="21"/>
+      <c r="X47" s="22"/>
+      <c r="Y47" s="22"/>
+      <c r="Z47" s="22"/>
+      <c r="AA47" s="22"/>
+      <c r="AB47" s="22"/>
+      <c r="AC47" s="23"/>
+      <c r="AD47" s="21"/>
+      <c r="AE47" s="22"/>
+      <c r="AF47" s="22"/>
+      <c r="AG47" s="22"/>
+      <c r="AH47" s="22"/>
+      <c r="AI47" s="22"/>
+      <c r="AJ47" s="23"/>
       <c r="AK47" s="16"/>
-      <c r="AQ47" s="18"/>
+      <c r="AQ47" s="17"/>
       <c r="AR47" s="16"/>
-      <c r="AX47" s="18"/>
+      <c r="AX47" s="17"/>
       <c r="AY47" s="16"/>
-      <c r="AZ47" s="18"/>
+      <c r="AZ47" s="17"/>
     </row>
     <row r="48" spans="1:52" x14ac:dyDescent="0.2">
-      <c r="A48" s="17" t="s">
+      <c r="A48" t="s">
         <v>17</v>
       </c>
       <c r="B48" s="16"/>
-      <c r="H48" s="18"/>
+      <c r="H48" s="17"/>
       <c r="I48" s="16"/>
-      <c r="O48" s="18"/>
+      <c r="O48" s="17"/>
       <c r="P48" s="16"/>
-      <c r="V48" s="18"/>
+      <c r="V48" s="17"/>
       <c r="W48" s="16"/>
-      <c r="AC48" s="18"/>
+      <c r="AC48" s="17"/>
       <c r="AD48" s="16"/>
-      <c r="AJ48" s="18"/>
-      <c r="AK48" s="22"/>
-      <c r="AL48" s="23"/>
-      <c r="AM48" s="23"/>
-      <c r="AN48" s="23"/>
-      <c r="AO48" s="23"/>
-      <c r="AP48" s="23"/>
-      <c r="AQ48" s="24"/>
+      <c r="AJ48" s="17"/>
+      <c r="AK48" s="21"/>
+      <c r="AL48" s="22"/>
+      <c r="AM48" s="22"/>
+      <c r="AN48" s="22"/>
+      <c r="AO48" s="22"/>
+      <c r="AP48" s="22"/>
+      <c r="AQ48" s="23"/>
       <c r="AR48" s="16"/>
-      <c r="AX48" s="18"/>
+      <c r="AX48" s="17"/>
       <c r="AY48" s="16"/>
-      <c r="AZ48" s="18"/>
+      <c r="AZ48" s="17"/>
     </row>
     <row r="49" spans="1:52" x14ac:dyDescent="0.2">
-      <c r="A49" s="17" t="s">
+      <c r="A49" t="s">
         <v>18</v>
       </c>
       <c r="B49" s="16"/>
-      <c r="H49" s="18"/>
+      <c r="H49" s="17"/>
       <c r="I49" s="16"/>
-      <c r="O49" s="18"/>
+      <c r="O49" s="17"/>
       <c r="P49" s="16"/>
-      <c r="V49" s="18"/>
+      <c r="V49" s="17"/>
       <c r="W49" s="16"/>
-      <c r="AC49" s="18"/>
+      <c r="AC49" s="17"/>
       <c r="AD49" s="16"/>
-      <c r="AJ49" s="18"/>
-      <c r="AK49" s="22"/>
-      <c r="AL49" s="23"/>
-      <c r="AM49" s="23"/>
-      <c r="AN49" s="23"/>
-      <c r="AO49" s="23"/>
-      <c r="AP49" s="23"/>
-      <c r="AQ49" s="24"/>
+      <c r="AJ49" s="17"/>
+      <c r="AK49" s="21"/>
+      <c r="AL49" s="22"/>
+      <c r="AM49" s="22"/>
+      <c r="AN49" s="22"/>
+      <c r="AO49" s="22"/>
+      <c r="AP49" s="22"/>
+      <c r="AQ49" s="23"/>
       <c r="AR49" s="16"/>
-      <c r="AX49" s="18"/>
+      <c r="AX49" s="17"/>
       <c r="AY49" s="16"/>
-      <c r="AZ49" s="18"/>
+      <c r="AZ49" s="17"/>
     </row>
     <row r="50" spans="1:52" x14ac:dyDescent="0.2">
-      <c r="A50" s="17" t="s">
+      <c r="A50" t="s">
         <v>19</v>
       </c>
       <c r="B50" s="16"/>
-      <c r="H50" s="18"/>
+      <c r="H50" s="17"/>
       <c r="I50" s="16"/>
-      <c r="O50" s="18"/>
+      <c r="O50" s="17"/>
       <c r="P50" s="16"/>
-      <c r="V50" s="18"/>
+      <c r="V50" s="17"/>
       <c r="W50" s="16"/>
-      <c r="AC50" s="18"/>
+      <c r="AC50" s="17"/>
       <c r="AD50" s="16"/>
-      <c r="AJ50" s="18"/>
+      <c r="AJ50" s="17"/>
       <c r="AK50" s="16"/>
-      <c r="AQ50" s="18"/>
-      <c r="AR50" s="22"/>
-      <c r="AS50" s="23"/>
-      <c r="AT50" s="23"/>
-      <c r="AU50" s="23"/>
-      <c r="AV50" s="23"/>
-      <c r="AW50" s="23"/>
-      <c r="AX50" s="24"/>
-      <c r="AY50" s="22"/>
-      <c r="AZ50" s="24"/>
+      <c r="AQ50" s="17"/>
+      <c r="AR50" s="21"/>
+      <c r="AS50" s="22"/>
+      <c r="AT50" s="22"/>
+      <c r="AU50" s="22"/>
+      <c r="AV50" s="22"/>
+      <c r="AW50" s="22"/>
+      <c r="AX50" s="23"/>
+      <c r="AY50" s="21"/>
+      <c r="AZ50" s="23"/>
     </row>
     <row r="51" spans="1:52" x14ac:dyDescent="0.2">
-      <c r="A51" s="17" t="s">
+      <c r="A51" t="s">
         <v>20</v>
       </c>
       <c r="B51" s="16"/>
-      <c r="H51" s="18"/>
+      <c r="H51" s="17"/>
       <c r="I51" s="16"/>
-      <c r="O51" s="18"/>
+      <c r="O51" s="17"/>
       <c r="P51" s="16"/>
-      <c r="V51" s="18"/>
+      <c r="V51" s="17"/>
       <c r="W51" s="16"/>
-      <c r="AC51" s="18"/>
+      <c r="AC51" s="17"/>
       <c r="AD51" s="16"/>
-      <c r="AJ51" s="18"/>
+      <c r="AJ51" s="17"/>
       <c r="AK51" s="16"/>
-      <c r="AQ51" s="18"/>
-      <c r="AR51" s="22"/>
-      <c r="AS51" s="23"/>
-      <c r="AT51" s="23"/>
-      <c r="AU51" s="23"/>
-      <c r="AV51" s="23"/>
-      <c r="AW51" s="23"/>
-      <c r="AX51" s="24"/>
-      <c r="AY51" s="22"/>
-      <c r="AZ51" s="24"/>
+      <c r="AQ51" s="17"/>
+      <c r="AR51" s="21"/>
+      <c r="AS51" s="22"/>
+      <c r="AT51" s="22"/>
+      <c r="AU51" s="22"/>
+      <c r="AV51" s="22"/>
+      <c r="AW51" s="22"/>
+      <c r="AX51" s="23"/>
+      <c r="AY51" s="21"/>
+      <c r="AZ51" s="23"/>
     </row>
     <row r="52" spans="1:52" x14ac:dyDescent="0.2">
-      <c r="A52" s="37" t="s">
+      <c r="A52" s="32" t="s">
         <v>21</v>
       </c>
-      <c r="B52" s="19"/>
-      <c r="C52" s="20"/>
-      <c r="D52" s="20"/>
-      <c r="E52" s="20"/>
-      <c r="F52" s="20"/>
-      <c r="G52" s="20"/>
-      <c r="H52" s="21"/>
-      <c r="I52" s="19"/>
-      <c r="J52" s="20"/>
-      <c r="K52" s="20"/>
-      <c r="L52" s="20"/>
-      <c r="M52" s="20"/>
-      <c r="N52" s="20"/>
-      <c r="O52" s="21"/>
-      <c r="P52" s="19"/>
-      <c r="Q52" s="20"/>
-      <c r="R52" s="20"/>
-      <c r="S52" s="20"/>
-      <c r="T52" s="20"/>
-      <c r="U52" s="20"/>
-      <c r="V52" s="21"/>
-      <c r="W52" s="19"/>
-      <c r="X52" s="20"/>
-      <c r="Y52" s="20"/>
-      <c r="Z52" s="20"/>
-      <c r="AA52" s="20"/>
-      <c r="AB52" s="20"/>
-      <c r="AC52" s="21"/>
-      <c r="AD52" s="19"/>
-      <c r="AE52" s="20"/>
-      <c r="AF52" s="20"/>
-      <c r="AG52" s="20"/>
-      <c r="AH52" s="20"/>
-      <c r="AI52" s="20"/>
-      <c r="AJ52" s="21"/>
-      <c r="AK52" s="19"/>
-      <c r="AL52" s="20"/>
-      <c r="AM52" s="20"/>
-      <c r="AN52" s="20"/>
-      <c r="AO52" s="20"/>
-      <c r="AP52" s="20"/>
-      <c r="AQ52" s="21"/>
-      <c r="AR52" s="25"/>
-      <c r="AS52" s="26"/>
-      <c r="AT52" s="26"/>
-      <c r="AU52" s="26"/>
-      <c r="AV52" s="26"/>
-      <c r="AW52" s="26"/>
-      <c r="AX52" s="27"/>
-      <c r="AY52" s="25"/>
-      <c r="AZ52" s="27"/>
+      <c r="B52" s="18"/>
+      <c r="C52" s="19"/>
+      <c r="D52" s="19"/>
+      <c r="E52" s="19"/>
+      <c r="F52" s="19"/>
+      <c r="G52" s="19"/>
+      <c r="H52" s="20"/>
+      <c r="I52" s="18"/>
+      <c r="J52" s="19"/>
+      <c r="K52" s="19"/>
+      <c r="L52" s="19"/>
+      <c r="M52" s="19"/>
+      <c r="N52" s="19"/>
+      <c r="O52" s="20"/>
+      <c r="P52" s="18"/>
+      <c r="Q52" s="19"/>
+      <c r="R52" s="19"/>
+      <c r="S52" s="19"/>
+      <c r="T52" s="19"/>
+      <c r="U52" s="19"/>
+      <c r="V52" s="20"/>
+      <c r="W52" s="18"/>
+      <c r="X52" s="19"/>
+      <c r="Y52" s="19"/>
+      <c r="Z52" s="19"/>
+      <c r="AA52" s="19"/>
+      <c r="AB52" s="19"/>
+      <c r="AC52" s="20"/>
+      <c r="AD52" s="18"/>
+      <c r="AE52" s="19"/>
+      <c r="AF52" s="19"/>
+      <c r="AG52" s="19"/>
+      <c r="AH52" s="19"/>
+      <c r="AI52" s="19"/>
+      <c r="AJ52" s="20"/>
+      <c r="AK52" s="18"/>
+      <c r="AL52" s="19"/>
+      <c r="AM52" s="19"/>
+      <c r="AN52" s="19"/>
+      <c r="AO52" s="19"/>
+      <c r="AP52" s="19"/>
+      <c r="AQ52" s="20"/>
+      <c r="AR52" s="24"/>
+      <c r="AS52" s="25"/>
+      <c r="AT52" s="25"/>
+      <c r="AU52" s="25"/>
+      <c r="AV52" s="25"/>
+      <c r="AW52" s="25"/>
+      <c r="AX52" s="26"/>
+      <c r="AY52" s="24"/>
+      <c r="AZ52" s="26"/>
     </row>
   </sheetData>
   <mergeCells count="5">
